--- a/Food Log Main.xlsx
+++ b/Food Log Main.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91998\VS\Food Log Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F971226E-83E9-4B84-AFD1-0EF047B35E5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F1EEBD-A345-4042-BEEC-EF52AA19AD77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main Format 12 oct" sheetId="1" r:id="rId1"/>
@@ -21,8 +21,8 @@
     <sheet name="Daily 23 to 11oct" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Main Format 12 oct'!$A$1:$J$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Weight Tracker 23sep'!$A$1:$I$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Main Format 12 oct'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Weight Tracker 23sep'!$A$1:$H$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Workouts 19oct'!$A$1:$H$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1503" uniqueCount="793">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="845">
   <si>
     <t>date</t>
   </si>
@@ -211,9 +211,6 @@
     <t>Meal 2 (rice + chicken masala)</t>
   </si>
   <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
     <t>22:00</t>
   </si>
   <si>
@@ -425,9 +422,6 @@
   </si>
   <si>
     <t>source</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
   </si>
   <si>
     <t>Starting value (same as 23rd per note)</t>
@@ -2437,6 +2431,168 @@
   </si>
   <si>
     <t>1000131703.jpg</t>
+  </si>
+  <si>
+    <t>FD20241211-0830-c3d4</t>
+  </si>
+  <si>
+    <t>FD20241211-1100-e5f6</t>
+  </si>
+  <si>
+    <t>FD20241211-1130-g7h8</t>
+  </si>
+  <si>
+    <t>FD20241211-1230-i9j0</t>
+  </si>
+  <si>
+    <t>FD20241211-1900-k1l2</t>
+  </si>
+  <si>
+    <t>FD20241211-1900-m3n4</t>
+  </si>
+  <si>
+    <t>FD20241211-1930-o5p6</t>
+  </si>
+  <si>
+    <t>FD20241211-2000-q7r8</t>
+  </si>
+  <si>
+    <t>FD20241212-0800-s9t0</t>
+  </si>
+  <si>
+    <t>FD20241212-0830-u1v2</t>
+  </si>
+  <si>
+    <t>FD20241212-1230-w3x4</t>
+  </si>
+  <si>
+    <t>FD20241212-1300-y5z6</t>
+  </si>
+  <si>
+    <t>FD20241212-1400-a7b8</t>
+  </si>
+  <si>
+    <t>FD20241212-1600-c9d0</t>
+  </si>
+  <si>
+    <t>FD20241212-1830-e1f2</t>
+  </si>
+  <si>
+    <t>Coffee with milk</t>
+  </si>
+  <si>
+    <t>FD20241212-1900-g3h4</t>
+  </si>
+  <si>
+    <t>Half sourdough chicken sandwich</t>
+  </si>
+  <si>
+    <t>FD20241212-2100-i5j6</t>
+  </si>
+  <si>
+    <t>FD20241212-2130-k7l8</t>
+  </si>
+  <si>
+    <t>FD20241213-0700-m9n0</t>
+  </si>
+  <si>
+    <t>FD20241213-0730-o1p2</t>
+  </si>
+  <si>
+    <t>FD20241213-0800-q3r4</t>
+  </si>
+  <si>
+    <t>FD20241213-1230-s5t6</t>
+  </si>
+  <si>
+    <t>FD20241213-1300-u7v8</t>
+  </si>
+  <si>
+    <t>FD20241213-1500-w9x0</t>
+  </si>
+  <si>
+    <t>FD20241213-2200-y1z2</t>
+  </si>
+  <si>
+    <t>3 slices of prawns pizza</t>
+  </si>
+  <si>
+    <t>FD20241213-2230-a3b4</t>
+  </si>
+  <si>
+    <t>100g grilled chicken</t>
+  </si>
+  <si>
+    <t>FD20241213-2300-c5d6</t>
+  </si>
+  <si>
+    <t>FD20241214-0800-e7f8</t>
+  </si>
+  <si>
+    <t>FD20241214-0900-g9h0</t>
+  </si>
+  <si>
+    <t>FD20241214-0930-i1j2</t>
+  </si>
+  <si>
+    <t>FD20241214-1000-k3l4</t>
+  </si>
+  <si>
+    <t>FD20241214-1230-m5n6</t>
+  </si>
+  <si>
+    <t>FD20241214-1300-o7p8</t>
+  </si>
+  <si>
+    <t>FD20241214-1400-q9r0</t>
+  </si>
+  <si>
+    <t>FD20241214-1430-s1t2</t>
+  </si>
+  <si>
+    <t>FD20241214-1900-u3v4</t>
+  </si>
+  <si>
+    <t>FD20241214-1930-w5x6</t>
+  </si>
+  <si>
+    <t>FD20241214-2000-y7z8</t>
+  </si>
+  <si>
+    <t>FD20241214-2000-a9b0</t>
+  </si>
+  <si>
+    <t>Roti with 60g chicken</t>
+  </si>
+  <si>
+    <t>FD20241215-0800-c1d2</t>
+  </si>
+  <si>
+    <t>FD20241215-1300-e3f4</t>
+  </si>
+  <si>
+    <t>FD20241215-1330-g5h6</t>
+  </si>
+  <si>
+    <t>FD20241215-1730-i7j8</t>
+  </si>
+  <si>
+    <t>FD20241215-1830-k9l0</t>
+  </si>
+  <si>
+    <t>FD20241215-1900-m1n2</t>
+  </si>
+  <si>
+    <t>FD20241215-1930-o3p4</t>
+  </si>
+  <si>
+    <t>Provided text data</t>
+  </si>
+  <si>
+    <t>WK20241210-p750</t>
+  </si>
+  <si>
+    <t>WK20241212-p750</t>
   </si>
 </sst>
 </file>
@@ -2881,7 +3037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K500"/>
+  <dimension ref="A1:K546"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -3588,10 +3744,10 @@
         <v>45945</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>27</v>
@@ -3624,10 +3780,10 @@
         <v>28</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="E23" s="2">
         <v>128</v>
@@ -3654,10 +3810,10 @@
         <v>45945</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>32</v>
@@ -3690,10 +3846,10 @@
         <v>28</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="E25" s="2">
         <v>290</v>
@@ -3723,7 +3879,7 @@
         <v>33</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>52</v>
@@ -3753,10 +3909,10 @@
         <v>45945</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>57</v>
@@ -3786,10 +3942,10 @@
         <v>45945</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>55</v>
@@ -3822,7 +3978,7 @@
         <v>13</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>27</v>
@@ -3852,10 +4008,10 @@
         <v>45946</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>15</v>
@@ -3885,10 +4041,10 @@
         <v>45946</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>15</v>
@@ -3918,10 +4074,10 @@
         <v>45946</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>32</v>
@@ -3954,7 +4110,7 @@
         <v>33</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>52</v>
@@ -3984,10 +4140,10 @@
         <v>45946</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>57</v>
@@ -4017,10 +4173,10 @@
         <v>45946</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>57</v>
@@ -4050,10 +4206,10 @@
         <v>45947</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>32</v>
@@ -4083,10 +4239,10 @@
         <v>45947</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>52</v>
@@ -4116,13 +4272,13 @@
         <v>45947</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="E38" s="2">
         <v>1340</v>
@@ -4152,10 +4308,10 @@
         <v>33</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E39" s="2">
         <v>155</v>
@@ -4182,10 +4338,10 @@
         <v>45948</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>32</v>
@@ -4215,13 +4371,13 @@
         <v>45948</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E41" s="2">
         <v>670</v>
@@ -4251,10 +4407,10 @@
         <v>19</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E42" s="2">
         <v>204</v>
@@ -4284,7 +4440,7 @@
         <v>30</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>32</v>
@@ -4317,10 +4473,10 @@
         <v>39</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E44" s="2">
         <v>155</v>
@@ -4347,13 +4503,13 @@
         <v>45949</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E45" s="2">
         <v>175</v>
@@ -4380,13 +4536,13 @@
         <v>45949</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E46" s="2">
         <v>155</v>
@@ -4416,10 +4572,10 @@
         <v>53</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E47" s="2">
         <v>670</v>
@@ -4449,7 +4605,7 @@
         <v>28</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>32</v>
@@ -4479,13 +4635,13 @@
         <v>45949</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E49" s="2">
         <v>230</v>
@@ -4512,13 +4668,13 @@
         <v>45949</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E50" s="2">
         <v>130</v>
@@ -4545,13 +4701,13 @@
         <v>45949</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E51" s="2">
         <v>147</v>
@@ -4578,13 +4734,13 @@
         <v>45950</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E52" s="2">
         <v>155</v>
@@ -4611,10 +4767,10 @@
         <v>45950</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>32</v>
@@ -4644,13 +4800,13 @@
         <v>45950</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E54" s="2">
         <v>450</v>
@@ -4677,13 +4833,13 @@
         <v>45950</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E55" s="2">
         <v>450</v>
@@ -4713,10 +4869,10 @@
         <v>13</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E56" s="2">
         <v>573</v>
@@ -4743,13 +4899,13 @@
         <v>45950</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E57" s="2">
         <v>308</v>
@@ -4779,10 +4935,10 @@
         <v>33</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E58" s="2">
         <v>155</v>
@@ -4809,10 +4965,10 @@
         <v>45951</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>32</v>
@@ -4842,13 +4998,13 @@
         <v>45951</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E60" s="2">
         <v>670</v>
@@ -4878,10 +5034,10 @@
         <v>53</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E61" s="2">
         <v>128</v>
@@ -4911,10 +5067,10 @@
         <v>19</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E62" s="2">
         <v>155</v>
@@ -4944,10 +5100,10 @@
         <v>42</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E63" s="2">
         <v>180</v>
@@ -4977,10 +5133,10 @@
         <v>16</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E64" s="2">
         <v>77</v>
@@ -5007,13 +5163,13 @@
         <v>45951</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E65" s="2">
         <v>308</v>
@@ -5040,13 +5196,13 @@
         <v>45951</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E66" s="2">
         <v>670</v>
@@ -5076,10 +5232,10 @@
         <v>33</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E67" s="2">
         <v>175</v>
@@ -5106,13 +5262,13 @@
         <v>45952</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E68" s="2">
         <v>180</v>
@@ -5139,10 +5295,10 @@
         <v>45952</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>32</v>
@@ -5172,13 +5328,13 @@
         <v>45952</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E70" s="2">
         <v>670</v>
@@ -5208,7 +5364,7 @@
         <v>19</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>27</v>
@@ -5241,7 +5397,7 @@
         <v>39</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>32</v>
@@ -5274,10 +5430,10 @@
         <v>39</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E73" s="2">
         <v>155</v>
@@ -5304,13 +5460,13 @@
         <v>45953</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E74" s="2">
         <v>155</v>
@@ -5340,10 +5496,10 @@
         <v>24</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E75" s="2">
         <v>155</v>
@@ -5370,10 +5526,10 @@
         <v>45953</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>32</v>
@@ -5403,13 +5559,13 @@
         <v>45953</v>
       </c>
       <c r="B77" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>243</v>
-      </c>
       <c r="D77" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E77" s="2">
         <v>670</v>
@@ -5436,13 +5592,13 @@
         <v>45953</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E78" s="2">
         <v>256</v>
@@ -5469,13 +5625,13 @@
         <v>45953</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E79" s="2">
         <v>102</v>
@@ -5502,13 +5658,13 @@
         <v>45953</v>
       </c>
       <c r="B80" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D80" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>249</v>
       </c>
       <c r="E80" s="2">
         <v>545</v>
@@ -5535,13 +5691,13 @@
         <v>45954</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E81" s="2">
         <v>155</v>
@@ -5571,7 +5727,7 @@
         <v>49</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>32</v>
@@ -5604,7 +5760,7 @@
         <v>36</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>55</v>
@@ -5637,10 +5793,10 @@
         <v>36</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E84" s="2">
         <v>175</v>
@@ -5667,13 +5823,13 @@
         <v>45954</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E85" s="2">
         <v>77</v>
@@ -5703,10 +5859,10 @@
         <v>13</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E86" s="2">
         <v>670</v>
@@ -5736,10 +5892,10 @@
         <v>39</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E87" s="2">
         <v>128</v>
@@ -5766,13 +5922,13 @@
         <v>45955</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E88" s="2">
         <v>155</v>
@@ -5799,13 +5955,13 @@
         <v>45955</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E89" s="2">
         <v>128</v>
@@ -5832,13 +5988,13 @@
         <v>45955</v>
       </c>
       <c r="B90" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C90" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="C90" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="D90" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E90" s="2">
         <v>204</v>
@@ -5868,7 +6024,7 @@
         <v>53</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>32</v>
@@ -5901,10 +6057,10 @@
         <v>36</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E92" s="2">
         <v>68</v>
@@ -5931,13 +6087,13 @@
         <v>45955</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E93" s="2">
         <v>300</v>
@@ -5964,13 +6120,13 @@
         <v>45955</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E94" s="2">
         <v>670</v>
@@ -5997,13 +6153,13 @@
         <v>45955</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E95" s="2">
         <v>175</v>
@@ -6030,13 +6186,13 @@
         <v>45955</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E96" s="2">
         <v>128</v>
@@ -6063,13 +6219,13 @@
         <v>45956</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E97" s="2">
         <v>155</v>
@@ -6096,13 +6252,13 @@
         <v>45956</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E98" s="2">
         <v>68</v>
@@ -6132,10 +6288,10 @@
         <v>53</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E99" s="2">
         <v>760</v>
@@ -6165,10 +6321,10 @@
         <v>36</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E100" s="2">
         <v>175</v>
@@ -6198,7 +6354,7 @@
         <v>42</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>27</v>
@@ -6228,13 +6384,13 @@
         <v>45956</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E102" s="2">
         <v>77</v>
@@ -6264,10 +6420,10 @@
         <v>28</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E103" s="2">
         <v>620</v>
@@ -6294,13 +6450,13 @@
         <v>45956</v>
       </c>
       <c r="B104" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D104" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>292</v>
       </c>
       <c r="E104" s="2">
         <v>105</v>
@@ -6327,10 +6483,10 @@
         <v>45956</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>32</v>
@@ -6363,10 +6519,10 @@
         <v>33</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E106" s="2">
         <v>155</v>
@@ -6393,13 +6549,13 @@
         <v>45957</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E107" s="2">
         <v>68</v>
@@ -6426,10 +6582,10 @@
         <v>45957</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>32</v>
@@ -6459,13 +6615,13 @@
         <v>45957</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E109" s="2">
         <v>670</v>
@@ -6495,10 +6651,10 @@
         <v>49</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E110" s="2">
         <v>128</v>
@@ -6528,10 +6684,10 @@
         <v>42</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E111" s="2">
         <v>128</v>
@@ -6558,13 +6714,13 @@
         <v>45957</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E112" s="2">
         <v>155</v>
@@ -6594,10 +6750,10 @@
         <v>16</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E113" s="2">
         <v>238</v>
@@ -6627,10 +6783,10 @@
         <v>30</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E114" s="2">
         <v>795</v>
@@ -6660,10 +6816,10 @@
         <v>33</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E115" s="2">
         <v>155</v>
@@ -6693,10 +6849,10 @@
         <v>10</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E116" s="2">
         <v>68</v>
@@ -6723,10 +6879,10 @@
         <v>45958</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>32</v>
@@ -6759,10 +6915,10 @@
         <v>53</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E118" s="2">
         <v>670</v>
@@ -6792,10 +6948,10 @@
         <v>19</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E119" s="2">
         <v>128</v>
@@ -6822,13 +6978,13 @@
         <v>45958</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E120" s="2">
         <v>77</v>
@@ -6858,10 +7014,10 @@
         <v>33</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E121" s="2">
         <v>155</v>
@@ -6888,10 +7044,10 @@
         <v>45959</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>32</v>
@@ -6921,13 +7077,13 @@
         <v>45959</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E123" s="2">
         <v>670</v>
@@ -6954,13 +7110,13 @@
         <v>45959</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E124" s="2">
         <v>175</v>
@@ -6987,13 +7143,13 @@
         <v>45959</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E125" s="2">
         <v>128</v>
@@ -7023,10 +7179,10 @@
         <v>39</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E126" s="2">
         <v>100</v>
@@ -7053,13 +7209,13 @@
         <v>45960</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E127" s="2">
         <v>155</v>
@@ -7086,13 +7242,13 @@
         <v>45960</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E128" s="2">
         <v>180</v>
@@ -7122,7 +7278,7 @@
         <v>24</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>32</v>
@@ -7152,13 +7308,13 @@
         <v>45960</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E130" s="2">
         <v>128</v>
@@ -7188,10 +7344,10 @@
         <v>42</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E131" s="2">
         <v>60</v>
@@ -7221,10 +7377,10 @@
         <v>13</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E132" s="2">
         <v>850</v>
@@ -7251,13 +7407,13 @@
         <v>45961</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E133" s="2">
         <v>155</v>
@@ -7284,13 +7440,13 @@
         <v>45961</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E134" s="2">
         <v>77</v>
@@ -7320,7 +7476,7 @@
         <v>53</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>55</v>
@@ -7353,10 +7509,10 @@
         <v>36</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E136" s="2">
         <v>155</v>
@@ -7383,13 +7539,13 @@
         <v>45961</v>
       </c>
       <c r="B137" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D137" s="2" t="s">
         <v>332</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>334</v>
       </c>
       <c r="E137" s="2">
         <v>90</v>
@@ -7416,13 +7572,13 @@
         <v>45961</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E138" s="2">
         <v>200</v>
@@ -7449,13 +7605,13 @@
         <v>45961</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E139" s="2">
         <v>650</v>
@@ -7482,13 +7638,13 @@
         <v>45961</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E140" s="2">
         <v>60</v>
@@ -7515,13 +7671,13 @@
         <v>45961</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E141" s="2">
         <v>360</v>
@@ -7551,10 +7707,10 @@
         <v>10</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E142" s="2">
         <v>175</v>
@@ -7581,13 +7737,13 @@
         <v>45962</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E143" s="2">
         <v>204</v>
@@ -7614,10 +7770,10 @@
         <v>45962</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>32</v>
@@ -7647,13 +7803,13 @@
         <v>45962</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E145" s="2">
         <v>670</v>
@@ -7683,10 +7839,10 @@
         <v>30</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E146" s="2">
         <v>480</v>
@@ -7716,10 +7872,10 @@
         <v>13</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E147" s="2">
         <v>180</v>
@@ -7749,10 +7905,10 @@
         <v>33</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E148" s="2">
         <v>155</v>
@@ -7779,10 +7935,10 @@
         <v>45963</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>32</v>
@@ -7812,10 +7968,10 @@
         <v>45963</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>55</v>
@@ -7848,10 +8004,10 @@
         <v>53</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E151" s="2">
         <v>155</v>
@@ -7881,10 +8037,10 @@
         <v>13</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E152" s="2">
         <v>670</v>
@@ -7911,13 +8067,13 @@
         <v>45963</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E153" s="2">
         <v>128</v>
@@ -7947,10 +8103,10 @@
         <v>33</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E154" s="2">
         <v>155</v>
@@ -7977,10 +8133,10 @@
         <v>45964</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>32</v>
@@ -8010,10 +8166,10 @@
         <v>45964</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>55</v>
@@ -8046,10 +8202,10 @@
         <v>19</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E157" s="2">
         <v>155</v>
@@ -8076,13 +8232,13 @@
         <v>45964</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E158" s="2">
         <v>77</v>
@@ -8112,10 +8268,10 @@
         <v>39</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E159" s="2">
         <v>128</v>
@@ -8145,10 +8301,10 @@
         <v>28</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E160" s="2">
         <v>670</v>
@@ -8178,10 +8334,10 @@
         <v>33</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E161" s="2">
         <v>155</v>
@@ -8208,13 +8364,13 @@
         <v>45965</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E162" s="2">
         <v>158</v>
@@ -8241,10 +8397,10 @@
         <v>45965</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>32</v>
@@ -8274,13 +8430,13 @@
         <v>45965</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E164" s="2">
         <v>380</v>
@@ -8310,10 +8466,10 @@
         <v>53</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E165" s="2">
         <v>169</v>
@@ -8343,7 +8499,7 @@
         <v>19</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>27</v>
@@ -8376,10 +8532,10 @@
         <v>13</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E167" s="2">
         <v>670</v>
@@ -8409,10 +8565,10 @@
         <v>39</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E168" s="2">
         <v>256</v>
@@ -8439,13 +8595,13 @@
         <v>45965</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E169" s="2">
         <v>473</v>
@@ -8472,13 +8628,13 @@
         <v>45965</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E170" s="2">
         <v>128</v>
@@ -8505,13 +8661,13 @@
         <v>45965</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E171" s="2">
         <v>85</v>
@@ -8538,13 +8694,13 @@
         <v>45965</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E172" s="2">
         <v>68</v>
@@ -8574,10 +8730,10 @@
         <v>33</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E173" s="2">
         <v>155</v>
@@ -8607,10 +8763,10 @@
         <v>33</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E174" s="2">
         <v>68</v>
@@ -8637,13 +8793,13 @@
         <v>45966</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E175" s="2">
         <v>89</v>
@@ -8670,13 +8826,13 @@
         <v>45966</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E176" s="2">
         <v>128</v>
@@ -8703,10 +8859,10 @@
         <v>45966</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>32</v>
@@ -8736,13 +8892,13 @@
         <v>45966</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E178" s="2">
         <v>670</v>
@@ -8772,10 +8928,10 @@
         <v>16</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E179" s="2">
         <v>77</v>
@@ -8805,10 +8961,10 @@
         <v>13</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E180" s="2">
         <v>380</v>
@@ -8838,10 +8994,10 @@
         <v>13</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E181" s="2">
         <v>68</v>
@@ -8868,13 +9024,13 @@
         <v>45966</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E182" s="2">
         <v>128</v>
@@ -8904,10 +9060,10 @@
         <v>33</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E183" s="2">
         <v>155</v>
@@ -8937,7 +9093,7 @@
         <v>10</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>27</v>
@@ -8970,7 +9126,7 @@
         <v>24</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>32</v>
@@ -9000,13 +9156,13 @@
         <v>45967</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E186" s="2">
         <v>670</v>
@@ -9036,10 +9192,10 @@
         <v>53</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E187" s="2">
         <v>155</v>
@@ -9069,10 +9225,10 @@
         <v>16</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E188" s="2">
         <v>77</v>
@@ -9102,10 +9258,10 @@
         <v>28</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E189" s="2">
         <v>380</v>
@@ -9135,10 +9291,10 @@
         <v>28</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E190" s="2">
         <v>128</v>
@@ -9168,10 +9324,10 @@
         <v>33</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E191" s="2">
         <v>65</v>
@@ -9201,10 +9357,10 @@
         <v>10</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E192" s="2">
         <v>77</v>
@@ -9231,13 +9387,13 @@
         <v>45968</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E193" s="2">
         <v>525</v>
@@ -9264,13 +9420,13 @@
         <v>45968</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E194" s="2">
         <v>85</v>
@@ -9300,10 +9456,10 @@
         <v>53</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E195" s="2">
         <v>150</v>
@@ -9330,10 +9486,10 @@
         <v>45968</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>32</v>
@@ -9366,10 +9522,10 @@
         <v>16</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E197" s="2">
         <v>77</v>
@@ -9396,13 +9552,13 @@
         <v>45968</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E198" s="2">
         <v>520</v>
@@ -9432,10 +9588,10 @@
         <v>30</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E199" s="2">
         <v>90</v>
@@ -9462,13 +9618,13 @@
         <v>45969</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E200" s="2">
         <v>125</v>
@@ -9498,10 +9654,10 @@
         <v>10</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E201" s="2">
         <v>90</v>
@@ -9528,10 +9684,10 @@
         <v>45969</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>32</v>
@@ -9561,13 +9717,13 @@
         <v>45969</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E203" s="2">
         <v>660</v>
@@ -9594,13 +9750,13 @@
         <v>45969</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E204" s="2">
         <v>89</v>
@@ -9630,10 +9786,10 @@
         <v>19</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E205" s="2">
         <v>270</v>
@@ -9660,13 +9816,13 @@
         <v>45969</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E206" s="2">
         <v>105</v>
@@ -9693,13 +9849,13 @@
         <v>45969</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E207" s="2">
         <v>670</v>
@@ -9726,13 +9882,13 @@
         <v>45969</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E208" s="2">
         <v>128</v>
@@ -9762,10 +9918,10 @@
         <v>28</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E209" s="2">
         <v>256</v>
@@ -9795,10 +9951,10 @@
         <v>10</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E210" s="2">
         <v>155</v>
@@ -9825,13 +9981,13 @@
         <v>45970</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E211" s="2">
         <v>204</v>
@@ -9858,10 +10014,10 @@
         <v>45970</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>32</v>
@@ -9891,10 +10047,10 @@
         <v>45970</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>55</v>
@@ -9927,10 +10083,10 @@
         <v>49</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E214" s="2">
         <v>175</v>
@@ -9957,13 +10113,13 @@
         <v>45970</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E215" s="2">
         <v>77</v>
@@ -9990,13 +10146,13 @@
         <v>45970</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E216" s="2">
         <v>150</v>
@@ -10023,13 +10179,13 @@
         <v>45970</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E217" s="2">
         <v>670</v>
@@ -10056,13 +10212,13 @@
         <v>45970</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E218" s="2">
         <v>270</v>
@@ -10089,13 +10245,13 @@
         <v>45970</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E219" s="2">
         <v>89</v>
@@ -10122,13 +10278,13 @@
         <v>45970</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E220" s="2">
         <v>128</v>
@@ -10158,10 +10314,10 @@
         <v>33</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E221" s="2">
         <v>155</v>
@@ -10191,10 +10347,10 @@
         <v>10</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E222" s="2">
         <v>77</v>
@@ -10221,10 +10377,10 @@
         <v>45971</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>32</v>
@@ -10254,13 +10410,13 @@
         <v>45971</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E224" s="2">
         <v>670</v>
@@ -10290,10 +10446,10 @@
         <v>49</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E225" s="2">
         <v>128</v>
@@ -10323,10 +10479,10 @@
         <v>49</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E226" s="2">
         <v>150</v>
@@ -10353,13 +10509,13 @@
         <v>45971</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E227" s="2">
         <v>155</v>
@@ -10386,10 +10542,10 @@
         <v>45971</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>32</v>
@@ -10419,13 +10575,13 @@
         <v>45971</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E229" s="2">
         <v>36</v>
@@ -10452,13 +10608,13 @@
         <v>45971</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E230" s="2">
         <v>128</v>
@@ -10488,10 +10644,10 @@
         <v>13</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E231" s="2">
         <v>85</v>
@@ -10518,13 +10674,13 @@
         <v>45972</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E232" s="2">
         <v>155</v>
@@ -10551,13 +10707,13 @@
         <v>45972</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E233" s="2">
         <v>77</v>
@@ -10587,7 +10743,7 @@
         <v>42</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>32</v>
@@ -10617,13 +10773,13 @@
         <v>45972</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E235" s="2">
         <v>155</v>
@@ -10653,10 +10809,10 @@
         <v>16</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E236" s="2">
         <v>670</v>
@@ -10683,13 +10839,13 @@
         <v>45972</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E237" s="2">
         <v>270</v>
@@ -10716,13 +10872,13 @@
         <v>45972</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E238" s="2">
         <v>128</v>
@@ -10749,13 +10905,13 @@
         <v>45972</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E239" s="2">
         <v>143</v>
@@ -10785,10 +10941,10 @@
         <v>33</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E240" s="2">
         <v>155</v>
@@ -10818,10 +10974,10 @@
         <v>10</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E241" s="2">
         <v>77</v>
@@ -10848,10 +11004,10 @@
         <v>45973</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D242" s="2" t="s">
         <v>32</v>
@@ -10881,10 +11037,10 @@
         <v>45973</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>55</v>
@@ -10917,10 +11073,10 @@
         <v>49</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E244" s="2">
         <v>155</v>
@@ -10950,10 +11106,10 @@
         <v>16</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E245" s="2">
         <v>77</v>
@@ -10983,10 +11139,10 @@
         <v>13</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E246" s="2">
         <v>585</v>
@@ -11016,10 +11172,10 @@
         <v>39</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E247" s="2">
         <v>128</v>
@@ -11049,10 +11205,10 @@
         <v>33</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E248" s="2">
         <v>155</v>
@@ -11079,13 +11235,13 @@
         <v>45974</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E249" s="2">
         <v>90</v>
@@ -11115,10 +11271,10 @@
         <v>10</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E250" s="2">
         <v>128</v>
@@ -11148,7 +11304,7 @@
         <v>53</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D251" s="2" t="s">
         <v>32</v>
@@ -11181,10 +11337,10 @@
         <v>53</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E252" s="2">
         <v>120</v>
@@ -11214,7 +11370,7 @@
         <v>19</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>55</v>
@@ -11244,13 +11400,13 @@
         <v>45974</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E254" s="2">
         <v>77</v>
@@ -11280,10 +11436,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C255" s="14" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D255" s="14" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E255" s="10">
         <v>155</v>
@@ -11313,10 +11469,10 @@
         <v>0.375</v>
       </c>
       <c r="C256" s="14" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D256" s="14" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E256" s="10">
         <v>77</v>
@@ -11346,7 +11502,7 @@
         <v>0.5</v>
       </c>
       <c r="C257" s="14" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D257" s="14" t="s">
         <v>32</v>
@@ -11379,7 +11535,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C258" s="14" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D258" s="14" t="s">
         <v>55</v>
@@ -11412,10 +11568,10 @@
         <v>0.5625</v>
       </c>
       <c r="C259" s="14" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D259" s="14" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E259" s="10">
         <v>175</v>
@@ -11445,10 +11601,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="C260" s="14" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D260" s="14" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E260" s="10">
         <v>77</v>
@@ -11478,10 +11634,10 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="C261" s="14" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D261" s="14" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E261" s="10">
         <v>120</v>
@@ -11511,10 +11667,10 @@
         <v>0.875</v>
       </c>
       <c r="C262" s="14" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D262" s="14" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E262" s="10">
         <v>670</v>
@@ -11544,10 +11700,10 @@
         <v>0.89583333333333337</v>
       </c>
       <c r="C263" s="14" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D263" s="14" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E263" s="10">
         <v>85</v>
@@ -11577,10 +11733,10 @@
         <v>10</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E264" s="2">
         <v>155</v>
@@ -11607,13 +11763,13 @@
         <v>45976</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E265" s="2">
         <v>77</v>
@@ -11640,13 +11796,13 @@
         <v>45976</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E266" s="2">
         <v>128</v>
@@ -11673,10 +11829,10 @@
         <v>45976</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>32</v>
@@ -11706,10 +11862,10 @@
         <v>45976</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D268" s="2" t="s">
         <v>55</v>
@@ -11742,10 +11898,10 @@
         <v>49</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E269" s="2">
         <v>155</v>
@@ -11775,10 +11931,10 @@
         <v>42</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E270" s="2">
         <v>45</v>
@@ -11805,13 +11961,13 @@
         <v>45976</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E271" s="2">
         <v>670</v>
@@ -11838,13 +11994,13 @@
         <v>45976</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E272" s="2">
         <v>85</v>
@@ -11871,13 +12027,13 @@
         <v>45976</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="E273" s="2">
         <v>308</v>
@@ -11904,13 +12060,13 @@
         <v>45976</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E274" s="2">
         <v>128</v>
@@ -11940,10 +12096,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E275" s="2">
         <v>155</v>
@@ -11973,10 +12129,10 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E276" s="2">
         <v>360</v>
@@ -12006,7 +12162,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>32</v>
@@ -12039,10 +12195,10 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E278" s="2">
         <v>175</v>
@@ -12072,10 +12228,10 @@
         <v>0.875</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E279" s="2">
         <v>380</v>
@@ -12105,10 +12261,10 @@
         <v>0.89583333333333337</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E280" s="2">
         <v>143</v>
@@ -12138,10 +12294,10 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E281" s="2">
         <v>290</v>
@@ -12171,10 +12327,10 @@
         <v>0.9375</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E282" s="2">
         <v>128</v>
@@ -12204,10 +12360,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E283" s="2">
         <v>155</v>
@@ -12237,10 +12393,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E284" s="2">
         <v>77</v>
@@ -12270,7 +12426,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>32</v>
@@ -12303,10 +12459,10 @@
         <v>0.6875</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E286" s="2">
         <v>143</v>
@@ -12336,10 +12492,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E287" s="2">
         <v>960</v>
@@ -12369,10 +12525,10 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E288" s="2">
         <v>128</v>
@@ -12402,10 +12558,10 @@
         <v>0.875</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E289" s="2">
         <v>175</v>
@@ -12435,10 +12591,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E290" s="2">
         <v>155</v>
@@ -12468,10 +12624,10 @@
         <v>0.4375</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E291" s="2">
         <v>77</v>
@@ -12501,7 +12657,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>32</v>
@@ -12534,10 +12690,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E293" s="2">
         <v>380</v>
@@ -12567,10 +12723,10 @@
         <v>0.5625</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E294" s="2">
         <v>128</v>
@@ -12600,10 +12756,10 @@
         <v>0.625</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E295" s="2">
         <v>155</v>
@@ -12633,10 +12789,10 @@
         <v>0.6875</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E296" s="2">
         <v>77</v>
@@ -12666,10 +12822,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E297" s="2">
         <v>670</v>
@@ -12699,10 +12855,10 @@
         <v>0.8125</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E298" s="2">
         <v>147</v>
@@ -12732,10 +12888,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E299" s="2">
         <v>155</v>
@@ -12765,10 +12921,10 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E300" s="2">
         <v>77</v>
@@ -12798,10 +12954,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E301" s="2">
         <v>128</v>
@@ -12831,10 +12987,10 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E302" s="2">
         <v>126</v>
@@ -12864,7 +13020,7 @@
         <v>0.5</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D303" s="2" t="s">
         <v>32</v>
@@ -12897,10 +13053,10 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E304" s="2">
         <v>380</v>
@@ -12930,10 +13086,10 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E305" s="2">
         <v>155</v>
@@ -12963,10 +13119,10 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E306" s="2">
         <v>158</v>
@@ -12996,10 +13152,10 @@
         <v>0.8125</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E307" s="2">
         <v>670</v>
@@ -13029,10 +13185,10 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="E308" s="2">
         <v>147</v>
@@ -13062,10 +13218,10 @@
         <v>0.875</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E309" s="2">
         <v>128</v>
@@ -13095,10 +13251,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E310" s="2">
         <v>155</v>
@@ -13128,10 +13284,10 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E311" s="2">
         <v>77</v>
@@ -13161,10 +13317,10 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E312" s="2">
         <v>126</v>
@@ -13194,7 +13350,7 @@
         <v>0.5</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="D313" s="2" t="s">
         <v>32</v>
@@ -13227,10 +13383,10 @@
         <v>0.5625</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E314" s="2">
         <v>380</v>
@@ -13260,10 +13416,10 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E315" s="2">
         <v>175</v>
@@ -13293,10 +13449,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E316" s="2">
         <v>670</v>
@@ -13326,10 +13482,10 @@
         <v>0.8125</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E317" s="2">
         <v>158</v>
@@ -13359,10 +13515,10 @@
         <v>0.3125</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E318" s="2">
         <v>71</v>
@@ -13392,10 +13548,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E319" s="2">
         <v>155</v>
@@ -13425,10 +13581,10 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E320" s="2">
         <v>77</v>
@@ -13458,10 +13614,10 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E321" s="2">
         <v>128</v>
@@ -13491,7 +13647,7 @@
         <v>0.5</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="D322" s="2" t="s">
         <v>32</v>
@@ -13524,10 +13680,10 @@
         <v>0.5625</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E323" s="2">
         <v>380</v>
@@ -13557,10 +13713,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E324" s="2">
         <v>158</v>
@@ -13590,10 +13746,10 @@
         <v>0.875</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E325" s="2">
         <v>670</v>
@@ -13623,10 +13779,10 @@
         <v>0.89583333333333337</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E326" s="2">
         <v>71</v>
@@ -13656,10 +13812,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E327" s="2">
         <v>155</v>
@@ -13689,10 +13845,10 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E328" s="2">
         <v>128</v>
@@ -13722,10 +13878,10 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E329" s="2">
         <v>86</v>
@@ -13755,7 +13911,7 @@
         <v>0.5</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D330" s="2" t="s">
         <v>32</v>
@@ -13788,10 +13944,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E331" s="2">
         <v>380</v>
@@ -13821,10 +13977,10 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E332" s="2">
         <v>175</v>
@@ -13854,10 +14010,10 @@
         <v>0.625</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E333" s="2">
         <v>158</v>
@@ -13887,10 +14043,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E334" s="2">
         <v>77</v>
@@ -13920,10 +14076,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E335" s="2">
         <v>670</v>
@@ -13953,10 +14109,10 @@
         <v>0.4375</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E336" s="2">
         <v>155</v>
@@ -13986,10 +14142,10 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E337" s="2">
         <v>128</v>
@@ -14019,10 +14175,10 @@
         <v>0.5</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E338" s="2">
         <v>360</v>
@@ -14052,7 +14208,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D339" s="2" t="s">
         <v>32</v>
@@ -14085,10 +14241,10 @@
         <v>0.75</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E340" s="2">
         <v>380</v>
@@ -14118,10 +14274,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E341" s="2">
         <v>155</v>
@@ -14151,7 +14307,7 @@
         <v>0.8125</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="D342" s="2" t="s">
         <v>32</v>
@@ -14184,10 +14340,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E343" s="2">
         <v>86</v>
@@ -14217,10 +14373,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E344" s="2">
         <v>155</v>
@@ -14250,10 +14406,10 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E345" s="2">
         <v>128</v>
@@ -14283,7 +14439,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="D346" s="2" t="s">
         <v>32</v>
@@ -14316,10 +14472,10 @@
         <v>0.625</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E347" s="2">
         <v>380</v>
@@ -14349,10 +14505,10 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E348" s="2">
         <v>155</v>
@@ -14382,10 +14538,10 @@
         <v>0.6875</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E349" s="2">
         <v>114</v>
@@ -14415,10 +14571,10 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E350" s="2">
         <v>670</v>
@@ -14448,10 +14604,10 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E351" s="2">
         <v>155</v>
@@ -14481,10 +14637,10 @@
         <v>0.375</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E352" s="2">
         <v>103</v>
@@ -14514,10 +14670,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E353" s="2">
         <v>77</v>
@@ -14547,7 +14703,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D354" s="2" t="s">
         <v>32</v>
@@ -14580,10 +14736,10 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E355" s="2">
         <v>155</v>
@@ -14613,10 +14769,10 @@
         <v>0.75</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E356" s="2">
         <v>77</v>
@@ -14646,10 +14802,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E357" s="2">
         <v>670</v>
@@ -14679,10 +14835,10 @@
         <v>0.8125</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E358" s="2">
         <v>104</v>
@@ -14712,10 +14868,10 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E359" s="2">
         <v>128</v>
@@ -14745,10 +14901,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E360" s="2">
         <v>155</v>
@@ -14778,10 +14934,10 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E361" s="2">
         <v>77</v>
@@ -14811,7 +14967,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="D362" s="2" t="s">
         <v>32</v>
@@ -14844,10 +15000,10 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E363" s="2">
         <v>128</v>
@@ -14877,10 +15033,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E364" s="2">
         <v>380</v>
@@ -14910,10 +15066,10 @@
         <v>0.6875</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E365" s="2">
         <v>155</v>
@@ -14943,10 +15099,10 @@
         <v>0.8125</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E366" s="2">
         <v>670</v>
@@ -14976,10 +15132,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E367" s="2">
         <v>104</v>
@@ -15009,10 +15165,10 @@
         <v>0.84375</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E368" s="2">
         <v>110</v>
@@ -15042,10 +15198,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E369" s="2">
         <v>155</v>
@@ -15075,10 +15231,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E370" s="2">
         <v>128</v>
@@ -15108,10 +15264,10 @@
         <v>0.375</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E371" s="2">
         <v>114</v>
@@ -15141,7 +15297,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D372" s="2" t="s">
         <v>32</v>
@@ -15174,10 +15330,10 @@
         <v>0.6875</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E373" s="2">
         <v>155</v>
@@ -15207,10 +15363,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D374" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E374" s="2">
         <v>670</v>
@@ -15240,10 +15396,10 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E375" s="2">
         <v>158</v>
@@ -15273,10 +15429,10 @@
         <v>0.86458333333333337</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E376" s="2">
         <v>128</v>
@@ -15306,10 +15462,10 @@
         <v>0.86458333333333337</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E377" s="2">
         <v>104</v>
@@ -15339,10 +15495,10 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D378" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E378" s="2">
         <v>114</v>
@@ -15372,10 +15528,10 @@
         <v>0.3125</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E379" s="2">
         <v>158</v>
@@ -15405,10 +15561,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="D380" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E380" s="2">
         <v>175</v>
@@ -15438,10 +15594,10 @@
         <v>0.4375</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E381" s="2">
         <v>77</v>
@@ -15471,7 +15627,7 @@
         <v>0.5</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="D382" s="2" t="s">
         <v>32</v>
@@ -15504,10 +15660,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E383" s="2">
         <v>380</v>
@@ -15537,10 +15693,10 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D384" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E384" s="2">
         <v>175</v>
@@ -15570,10 +15726,10 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D385" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E385" s="2">
         <v>670</v>
@@ -15603,10 +15759,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E386" s="2">
         <v>128</v>
@@ -15636,10 +15792,10 @@
         <v>0.3125</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E387" s="2">
         <v>175</v>
@@ -15669,10 +15825,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E388" s="2">
         <v>128</v>
@@ -15702,10 +15858,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E389" s="2">
         <v>158</v>
@@ -15735,10 +15891,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="E390" s="2">
         <v>270</v>
@@ -15768,10 +15924,10 @@
         <v>0.4375</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E391" s="2">
         <v>77</v>
@@ -15801,7 +15957,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D392" s="2" t="s">
         <v>32</v>
@@ -15834,10 +15990,10 @@
         <v>0.625</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E393" s="2">
         <v>114</v>
@@ -15867,10 +16023,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E394" s="2">
         <v>380</v>
@@ -15900,10 +16056,10 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E395" s="2">
         <v>670</v>
@@ -15933,10 +16089,10 @@
         <v>0.75</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="E396" s="2">
         <v>74</v>
@@ -15966,10 +16122,10 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E397" s="2">
         <v>120</v>
@@ -15999,10 +16155,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D398" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E398" s="2">
         <v>350</v>
@@ -16032,10 +16188,10 @@
         <v>0.875</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D399" s="2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="E399" s="2">
         <v>97</v>
@@ -16065,10 +16221,10 @@
         <v>0.375</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="D400" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E400" s="2">
         <v>77</v>
@@ -16098,10 +16254,10 @@
         <v>0.5</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E401" s="2">
         <v>360</v>
@@ -16131,10 +16287,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E402" s="2">
         <v>175</v>
@@ -16164,10 +16320,10 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D403" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E403" s="2">
         <v>670</v>
@@ -16197,10 +16353,10 @@
         <v>0.75</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="D404" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E404" s="2">
         <v>175</v>
@@ -16230,10 +16386,10 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D405" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="E405" s="2">
         <v>74</v>
@@ -16263,10 +16419,10 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D406" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="E406" s="2">
         <v>270</v>
@@ -16296,10 +16452,10 @@
         <v>0.25</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D407" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E407" s="2">
         <v>104</v>
@@ -16329,10 +16485,10 @@
         <v>0.27083333333333331</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D408" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E408" s="2">
         <v>188</v>
@@ -16362,10 +16518,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D409" s="2" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E409" s="2">
         <v>449</v>
@@ -16393,10 +16549,10 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="D410" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="E410" s="2">
         <v>60</v>
@@ -16426,10 +16582,10 @@
         <v>0.75</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="D411" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="E411" s="2">
         <v>200</v>
@@ -16459,10 +16615,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D412" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="E412" s="2">
         <v>644</v>
@@ -16492,10 +16648,10 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="D413" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E413" s="2">
         <v>100</v>
@@ -16525,10 +16681,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D414" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E414" s="2">
         <v>520</v>
@@ -16558,10 +16714,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="D415" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E415" s="2">
         <v>77</v>
@@ -16591,10 +16747,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="D416" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E416" s="2">
         <v>77</v>
@@ -16624,10 +16780,10 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="D417" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="E417" s="2">
         <v>450</v>
@@ -16657,10 +16813,10 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="D418" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E418" s="2">
         <v>77</v>
@@ -16690,10 +16846,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="D419" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="E419" s="2">
         <v>400</v>
@@ -16723,10 +16879,10 @@
         <v>0.8125</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="D420" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E420" s="2">
         <v>77</v>
@@ -16756,10 +16912,10 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="D421" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E421" s="2">
         <v>150</v>
@@ -16789,10 +16945,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="D422" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E422" s="2">
         <v>380</v>
@@ -16822,10 +16978,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D423" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E423" s="2">
         <v>77</v>
@@ -16855,10 +17011,10 @@
         <v>0.4375</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D424" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="E424" s="2">
         <v>40</v>
@@ -16888,10 +17044,10 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D425" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E425" s="2">
         <v>25</v>
@@ -16921,10 +17077,10 @@
         <v>0.625</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="D426" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E426" s="2">
         <v>150</v>
@@ -16954,10 +17110,10 @@
         <v>0.625</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="D427" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="E427" s="2">
         <v>40</v>
@@ -16987,10 +17143,10 @@
         <v>0.6875</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="D428" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="E428" s="2">
         <v>496</v>
@@ -17020,10 +17176,10 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E429" s="2">
         <v>77</v>
@@ -17053,10 +17209,10 @@
         <v>0.8125</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="D430" s="2" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="E430" s="2">
         <v>450</v>
@@ -17086,10 +17242,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E431" s="2">
         <v>380</v>
@@ -17119,10 +17275,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E432" s="2">
         <v>77</v>
@@ -17152,10 +17308,10 @@
         <v>0.4375</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="E433" s="2">
         <v>493</v>
@@ -17183,10 +17339,10 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="E434" s="2">
         <v>476</v>
@@ -17216,10 +17372,10 @@
         <v>0.8125</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E435" s="2">
         <v>77</v>
@@ -17249,10 +17405,10 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="E436" s="2">
         <v>125</v>
@@ -17282,10 +17438,10 @@
         <v>0.3125</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E437" s="2">
         <v>77</v>
@@ -17315,10 +17471,10 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E438" s="2">
         <v>89</v>
@@ -17348,10 +17504,10 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="E439" s="2">
         <v>125</v>
@@ -17381,10 +17537,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E440" s="2">
         <v>670</v>
@@ -17414,10 +17570,10 @@
         <v>0.5625</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E441" s="2">
         <v>175</v>
@@ -17447,7 +17603,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="D442" s="2" t="s">
         <v>32</v>
@@ -17480,10 +17636,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E443" s="2">
         <v>77</v>
@@ -17513,10 +17669,10 @@
         <v>0.6875</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E444" s="2">
         <v>158</v>
@@ -17546,10 +17702,10 @@
         <v>0.8125</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D445" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E445" s="2">
         <v>670</v>
@@ -17579,10 +17735,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E446" s="2">
         <v>128</v>
@@ -17612,10 +17768,10 @@
         <v>0.875</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E447" s="2">
         <v>158</v>
@@ -17645,10 +17801,10 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E448" s="2">
         <v>128</v>
@@ -17678,10 +17834,10 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E449" s="2">
         <v>175</v>
@@ -17710,10 +17866,10 @@
         <v>0.4375</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E450" s="2">
         <v>77</v>
@@ -17742,7 +17898,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="D451" s="2" t="s">
         <v>32</v>
@@ -17774,10 +17930,10 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E452" s="2">
         <v>380</v>
@@ -17806,10 +17962,10 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E453" s="2">
         <v>175</v>
@@ -17838,10 +17994,10 @@
         <v>0.625</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E454" s="2">
         <v>158</v>
@@ -17870,10 +18026,10 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E455" s="2">
         <v>77</v>
@@ -17902,10 +18058,10 @@
         <v>0.6875</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E456" s="2">
         <v>256</v>
@@ -17934,10 +18090,10 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E457" s="2">
         <v>380</v>
@@ -17966,10 +18122,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="E458" s="2">
         <v>85</v>
@@ -17998,10 +18154,10 @@
         <v>0.875</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E459" s="2">
         <v>157.5</v>
@@ -18030,10 +18186,10 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="E460" s="2">
         <v>270</v>
@@ -18062,10 +18218,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="D461" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E461" s="2">
         <v>77</v>
@@ -18094,10 +18250,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D462" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E462" s="2">
         <v>155</v>
@@ -18126,10 +18282,10 @@
         <v>0.375</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E463" s="2">
         <v>128</v>
@@ -18158,7 +18314,7 @@
         <v>0.5</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D464" s="2" t="s">
         <v>32</v>
@@ -18190,10 +18346,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="C465" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="D465" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E465" s="2">
         <v>104</v>
@@ -18222,10 +18378,10 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="D466" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E466" s="2">
         <v>380</v>
@@ -18254,10 +18410,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="D467" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E467" s="2">
         <v>155</v>
@@ -18286,10 +18442,10 @@
         <v>0.6875</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="D468" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E468" s="2">
         <v>104</v>
@@ -18318,10 +18474,10 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="C469" s="2" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D469" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E469" s="2">
         <v>77</v>
@@ -18350,10 +18506,10 @@
         <v>0.75</v>
       </c>
       <c r="C470" s="2" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D470" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E470" s="2">
         <v>128</v>
@@ -18382,10 +18538,10 @@
         <v>0.8125</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="D471" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E471" s="2">
         <v>670</v>
@@ -18414,10 +18570,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="C472" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="D472" s="2" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="E472" s="2">
         <v>85</v>
@@ -18446,10 +18602,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="D473" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E473" s="2">
         <v>77</v>
@@ -18478,10 +18634,10 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="C474" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D474" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E474" s="2">
         <v>155</v>
@@ -18510,10 +18666,10 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D475" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E475" s="2">
         <v>128</v>
@@ -18542,7 +18698,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="C476" s="2" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="D476" s="2" t="s">
         <v>32</v>
@@ -18574,10 +18730,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D477" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E477" s="2">
         <v>77</v>
@@ -18606,7 +18762,7 @@
         <v>0.875</v>
       </c>
       <c r="C478" s="2" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="D478" s="2" t="s">
         <v>32</v>
@@ -18638,10 +18794,10 @@
         <v>0.89583333333333337</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="D479" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E479" s="2">
         <v>670</v>
@@ -18670,10 +18826,10 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D480" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E480" s="2">
         <v>128</v>
@@ -18702,10 +18858,10 @@
         <v>0.9375</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="D481" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E481" s="2">
         <v>128</v>
@@ -18734,10 +18890,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="D482" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E482" s="2">
         <v>77</v>
@@ -18766,7 +18922,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D483" s="2" t="s">
         <v>32</v>
@@ -18798,10 +18954,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C484" s="2" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="D484" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E484" s="2">
         <v>380</v>
@@ -18830,10 +18986,10 @@
         <v>0.5625</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D485" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E485" s="2">
         <v>175</v>
@@ -18862,10 +19018,10 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="D486" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E486" s="2">
         <v>128</v>
@@ -18894,10 +19050,10 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="E487" s="2">
         <v>74</v>
@@ -18926,10 +19082,10 @@
         <v>0.625</v>
       </c>
       <c r="C488" s="2" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="D488" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E488" s="2">
         <v>157.5</v>
@@ -18958,10 +19114,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="D489" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E489" s="2">
         <v>77</v>
@@ -18990,10 +19146,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="D490" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E490" s="2">
         <v>670</v>
@@ -19022,10 +19178,10 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="C491" s="2" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="D491" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E491" s="2">
         <v>175</v>
@@ -19054,10 +19210,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="D492" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E492" s="2">
         <v>77</v>
@@ -19086,10 +19242,10 @@
         <v>0.375</v>
       </c>
       <c r="C493" s="2" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="D493" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E493" s="2">
         <v>155</v>
@@ -19118,7 +19274,7 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="C494" s="2" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="D494" s="2" t="s">
         <v>32</v>
@@ -19150,10 +19306,10 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="C495" s="2" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="D495" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E495" s="2">
         <v>380</v>
@@ -19182,10 +19338,10 @@
         <v>0.5625</v>
       </c>
       <c r="C496" s="2" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="D496" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E496" s="2">
         <v>175</v>
@@ -19214,10 +19370,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="C497" s="2" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="D497" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E497" s="2">
         <v>77</v>
@@ -19246,10 +19402,10 @@
         <v>0.6875</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="D498" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E498" s="2">
         <v>128</v>
@@ -19278,10 +19434,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="C499" s="2" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="D499" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E499" s="2">
         <v>670</v>
@@ -19310,10 +19466,10 @@
         <v>0.8125</v>
       </c>
       <c r="C500" s="2" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="D500" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E500" s="2">
         <v>78.75</v>
@@ -19332,6 +19488,1478 @@
       </c>
       <c r="J500" s="2">
         <v>7.5</v>
+      </c>
+    </row>
+    <row r="501" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A501" s="16">
+        <v>46002</v>
+      </c>
+      <c r="B501" s="17">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C501" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="D501" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E501" s="2">
+        <v>77</v>
+      </c>
+      <c r="F501" s="2">
+        <v>2</v>
+      </c>
+      <c r="G501" s="2">
+        <v>11</v>
+      </c>
+      <c r="H501" s="2">
+        <v>2</v>
+      </c>
+      <c r="I501" s="2">
+        <v>7</v>
+      </c>
+      <c r="J501" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="502" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A502" s="16">
+        <v>46002</v>
+      </c>
+      <c r="B502" s="17">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C502" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="D502" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E502" s="2">
+        <v>175</v>
+      </c>
+      <c r="F502" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G502" s="2">
+        <v>20</v>
+      </c>
+      <c r="H502" s="2">
+        <v>2</v>
+      </c>
+      <c r="I502" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J502" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="503" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A503" s="16">
+        <v>46002</v>
+      </c>
+      <c r="B503" s="17">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C503" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="D503" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E503" s="2">
+        <v>128</v>
+      </c>
+      <c r="F503" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G503" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H503" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I503" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J503" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="504" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A504" s="16">
+        <v>46002</v>
+      </c>
+      <c r="B504" s="17">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C504" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="D504" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E504" s="2">
+        <v>290</v>
+      </c>
+      <c r="F504" s="2">
+        <v>11</v>
+      </c>
+      <c r="G504" s="2">
+        <v>18</v>
+      </c>
+      <c r="H504" s="2">
+        <v>18</v>
+      </c>
+      <c r="I504" s="2">
+        <v>0</v>
+      </c>
+      <c r="J504" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="505" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A505" s="16">
+        <v>46002</v>
+      </c>
+      <c r="B505" s="17">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C505" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="D505" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E505" s="2">
+        <v>670</v>
+      </c>
+      <c r="F505" s="2">
+        <v>42</v>
+      </c>
+      <c r="G505" s="2">
+        <v>66</v>
+      </c>
+      <c r="H505" s="2">
+        <v>26</v>
+      </c>
+      <c r="I505" s="2">
+        <v>5</v>
+      </c>
+      <c r="J505" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="506" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A506" s="16">
+        <v>46002</v>
+      </c>
+      <c r="B506" s="17">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C506" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="D506" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="E506" s="2">
+        <v>270</v>
+      </c>
+      <c r="F506" s="2">
+        <v>6</v>
+      </c>
+      <c r="G506" s="2">
+        <v>35</v>
+      </c>
+      <c r="H506" s="2">
+        <v>12</v>
+      </c>
+      <c r="I506" s="2">
+        <v>1</v>
+      </c>
+      <c r="J506" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="507" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A507" s="16">
+        <v>46002</v>
+      </c>
+      <c r="B507" s="17">
+        <v>0.8125</v>
+      </c>
+      <c r="C507" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="D507" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E507" s="2">
+        <v>78.75</v>
+      </c>
+      <c r="F507" s="2">
+        <v>1.95</v>
+      </c>
+      <c r="G507" s="2">
+        <v>16.8</v>
+      </c>
+      <c r="H507" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I507" s="2">
+        <v>11.25</v>
+      </c>
+      <c r="J507" s="2">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="508" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A508" s="16">
+        <v>46002</v>
+      </c>
+      <c r="B508" s="17">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C508" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="D508" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E508" s="2">
+        <v>128</v>
+      </c>
+      <c r="F508" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G508" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H508" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I508" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J508" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="509" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A509" s="16">
+        <v>46003</v>
+      </c>
+      <c r="B509" s="17">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C509" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="D509" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E509" s="2">
+        <v>77</v>
+      </c>
+      <c r="F509" s="2">
+        <v>2</v>
+      </c>
+      <c r="G509" s="2">
+        <v>11</v>
+      </c>
+      <c r="H509" s="2">
+        <v>2</v>
+      </c>
+      <c r="I509" s="2">
+        <v>7</v>
+      </c>
+      <c r="J509" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="510" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A510" s="16">
+        <v>46003</v>
+      </c>
+      <c r="B510" s="17">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C510" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="D510" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E510" s="2">
+        <v>128</v>
+      </c>
+      <c r="F510" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G510" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H510" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I510" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J510" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="511" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A511" s="16">
+        <v>46003</v>
+      </c>
+      <c r="B511" s="17">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C511" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="D511" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E511" s="2">
+        <v>290</v>
+      </c>
+      <c r="F511" s="2">
+        <v>11</v>
+      </c>
+      <c r="G511" s="2">
+        <v>18</v>
+      </c>
+      <c r="H511" s="2">
+        <v>18</v>
+      </c>
+      <c r="I511" s="2">
+        <v>0</v>
+      </c>
+      <c r="J511" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="512" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A512" s="16">
+        <v>46003</v>
+      </c>
+      <c r="B512" s="17">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C512" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="D512" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E512" s="2">
+        <v>380</v>
+      </c>
+      <c r="F512" s="2">
+        <v>25</v>
+      </c>
+      <c r="G512" s="2">
+        <v>46</v>
+      </c>
+      <c r="H512" s="2">
+        <v>10</v>
+      </c>
+      <c r="I512" s="2">
+        <v>2</v>
+      </c>
+      <c r="J512" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="513" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A513" s="16">
+        <v>46003</v>
+      </c>
+      <c r="B513" s="17">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C513" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="D513" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E513" s="2">
+        <v>175</v>
+      </c>
+      <c r="F513" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G513" s="2">
+        <v>20</v>
+      </c>
+      <c r="H513" s="2">
+        <v>2</v>
+      </c>
+      <c r="I513" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J513" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="514" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A514" s="16">
+        <v>46003</v>
+      </c>
+      <c r="B514" s="17">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C514" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="D514" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E514" s="2">
+        <v>77</v>
+      </c>
+      <c r="F514" s="2">
+        <v>2</v>
+      </c>
+      <c r="G514" s="2">
+        <v>11</v>
+      </c>
+      <c r="H514" s="2">
+        <v>2</v>
+      </c>
+      <c r="I514" s="2">
+        <v>7</v>
+      </c>
+      <c r="J514" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="515" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A515" s="16">
+        <v>46003</v>
+      </c>
+      <c r="B515" s="17">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C515" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="D515" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="E515" s="2">
+        <v>60</v>
+      </c>
+      <c r="F515" s="2">
+        <v>3</v>
+      </c>
+      <c r="G515" s="2">
+        <v>6</v>
+      </c>
+      <c r="H515" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="I515" s="2">
+        <v>3</v>
+      </c>
+      <c r="J515" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="516" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A516" s="16">
+        <v>46003</v>
+      </c>
+      <c r="B516" s="17">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C516" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="D516" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E516" s="2">
+        <v>225</v>
+      </c>
+      <c r="F516" s="2">
+        <v>15</v>
+      </c>
+      <c r="G516" s="2">
+        <v>25</v>
+      </c>
+      <c r="H516" s="2">
+        <v>8</v>
+      </c>
+      <c r="I516" s="2">
+        <v>3</v>
+      </c>
+      <c r="J516" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="517" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A517" s="16">
+        <v>46003</v>
+      </c>
+      <c r="B517" s="17">
+        <v>0.875</v>
+      </c>
+      <c r="C517" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="D517" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E517" s="2">
+        <v>670</v>
+      </c>
+      <c r="F517" s="2">
+        <v>42</v>
+      </c>
+      <c r="G517" s="2">
+        <v>66</v>
+      </c>
+      <c r="H517" s="2">
+        <v>26</v>
+      </c>
+      <c r="I517" s="2">
+        <v>5</v>
+      </c>
+      <c r="J517" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="518" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A518" s="16">
+        <v>46003</v>
+      </c>
+      <c r="B518" s="17">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C518" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="D518" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E518" s="2">
+        <v>128</v>
+      </c>
+      <c r="F518" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G518" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H518" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I518" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J518" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="519" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A519" s="16">
+        <v>46004</v>
+      </c>
+      <c r="B519" s="17">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C519" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="D519" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E519" s="2">
+        <v>128</v>
+      </c>
+      <c r="F519" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G519" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H519" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I519" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J519" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="520" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A520" s="16">
+        <v>46004</v>
+      </c>
+      <c r="B520" s="17">
+        <v>0.3125</v>
+      </c>
+      <c r="C520" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="D520" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="E520" s="2">
+        <v>158</v>
+      </c>
+      <c r="F520" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="G520" s="2">
+        <v>18.3</v>
+      </c>
+      <c r="H520" s="2">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="I520" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="J520" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="521" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A521" s="16">
+        <v>46004</v>
+      </c>
+      <c r="B521" s="17">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C521" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="D521" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E521" s="2">
+        <v>77</v>
+      </c>
+      <c r="F521" s="2">
+        <v>2</v>
+      </c>
+      <c r="G521" s="2">
+        <v>11</v>
+      </c>
+      <c r="H521" s="2">
+        <v>2</v>
+      </c>
+      <c r="I521" s="2">
+        <v>7</v>
+      </c>
+      <c r="J521" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A522" s="16">
+        <v>46004</v>
+      </c>
+      <c r="B522" s="17">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C522" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="D522" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E522" s="2">
+        <v>290</v>
+      </c>
+      <c r="F522" s="2">
+        <v>11</v>
+      </c>
+      <c r="G522" s="2">
+        <v>18</v>
+      </c>
+      <c r="H522" s="2">
+        <v>18</v>
+      </c>
+      <c r="I522" s="2">
+        <v>0</v>
+      </c>
+      <c r="J522" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="523" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A523" s="16">
+        <v>46004</v>
+      </c>
+      <c r="B523" s="17">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C523" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="D523" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E523" s="2">
+        <v>670</v>
+      </c>
+      <c r="F523" s="2">
+        <v>42</v>
+      </c>
+      <c r="G523" s="2">
+        <v>66</v>
+      </c>
+      <c r="H523" s="2">
+        <v>26</v>
+      </c>
+      <c r="I523" s="2">
+        <v>5</v>
+      </c>
+      <c r="J523" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="524" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A524" s="16">
+        <v>46004</v>
+      </c>
+      <c r="B524" s="17">
+        <v>0.625</v>
+      </c>
+      <c r="C524" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="D524" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E524" s="2">
+        <v>175</v>
+      </c>
+      <c r="F524" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G524" s="2">
+        <v>20</v>
+      </c>
+      <c r="H524" s="2">
+        <v>2</v>
+      </c>
+      <c r="I524" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J524" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="525" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A525" s="16">
+        <v>46004</v>
+      </c>
+      <c r="B525" s="17">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="C525" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="D525" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="E525" s="2">
+        <v>720</v>
+      </c>
+      <c r="F525" s="2">
+        <v>36</v>
+      </c>
+      <c r="G525" s="2">
+        <v>72</v>
+      </c>
+      <c r="H525" s="2">
+        <v>30</v>
+      </c>
+      <c r="I525" s="2">
+        <v>6</v>
+      </c>
+      <c r="J525" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="526" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A526" s="16">
+        <v>46004</v>
+      </c>
+      <c r="B526" s="17">
+        <v>0.9375</v>
+      </c>
+      <c r="C526" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="D526" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="E526" s="2">
+        <v>165</v>
+      </c>
+      <c r="F526" s="2">
+        <v>31</v>
+      </c>
+      <c r="G526" s="2">
+        <v>0</v>
+      </c>
+      <c r="H526" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="I526" s="2">
+        <v>0</v>
+      </c>
+      <c r="J526" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="527" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A527" s="16">
+        <v>46004</v>
+      </c>
+      <c r="B527" s="17">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="C527" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="D527" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E527" s="2">
+        <v>128</v>
+      </c>
+      <c r="F527" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G527" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H527" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I527" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J527" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="528" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A528" s="16">
+        <v>46005</v>
+      </c>
+      <c r="B528" s="17">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C528" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="D528" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E528" s="2">
+        <v>77</v>
+      </c>
+      <c r="F528" s="2">
+        <v>2</v>
+      </c>
+      <c r="G528" s="2">
+        <v>11</v>
+      </c>
+      <c r="H528" s="2">
+        <v>2</v>
+      </c>
+      <c r="I528" s="2">
+        <v>7</v>
+      </c>
+      <c r="J528" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A529" s="16">
+        <v>46005</v>
+      </c>
+      <c r="B529" s="17">
+        <v>0.375</v>
+      </c>
+      <c r="C529" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="D529" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E529" s="2">
+        <v>77</v>
+      </c>
+      <c r="F529" s="2">
+        <v>2</v>
+      </c>
+      <c r="G529" s="2">
+        <v>11</v>
+      </c>
+      <c r="H529" s="2">
+        <v>2</v>
+      </c>
+      <c r="I529" s="2">
+        <v>7</v>
+      </c>
+      <c r="J529" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A530" s="16">
+        <v>46005</v>
+      </c>
+      <c r="B530" s="17">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C530" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="D530" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="E530" s="2">
+        <v>158</v>
+      </c>
+      <c r="F530" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="G530" s="2">
+        <v>18.3</v>
+      </c>
+      <c r="H530" s="2">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="I530" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="J530" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="531" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A531" s="16">
+        <v>46005</v>
+      </c>
+      <c r="B531" s="17">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C531" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="D531" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E531" s="2">
+        <v>128</v>
+      </c>
+      <c r="F531" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G531" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H531" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I531" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J531" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="532" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A532" s="16">
+        <v>46005</v>
+      </c>
+      <c r="B532" s="17">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C532" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="D532" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E532" s="2">
+        <v>290</v>
+      </c>
+      <c r="F532" s="2">
+        <v>11</v>
+      </c>
+      <c r="G532" s="2">
+        <v>18</v>
+      </c>
+      <c r="H532" s="2">
+        <v>18</v>
+      </c>
+      <c r="I532" s="2">
+        <v>0</v>
+      </c>
+      <c r="J532" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="533" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A533" s="16">
+        <v>46005</v>
+      </c>
+      <c r="B533" s="17">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C533" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="D533" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E533" s="2">
+        <v>175</v>
+      </c>
+      <c r="F533" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G533" s="2">
+        <v>20</v>
+      </c>
+      <c r="H533" s="2">
+        <v>2</v>
+      </c>
+      <c r="I533" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J533" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="534" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A534" s="16">
+        <v>46005</v>
+      </c>
+      <c r="B534" s="17">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C534" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="D534" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E534" s="2">
+        <v>670</v>
+      </c>
+      <c r="F534" s="2">
+        <v>42</v>
+      </c>
+      <c r="G534" s="2">
+        <v>66</v>
+      </c>
+      <c r="H534" s="2">
+        <v>26</v>
+      </c>
+      <c r="I534" s="2">
+        <v>5</v>
+      </c>
+      <c r="J534" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="535" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A535" s="16">
+        <v>46005</v>
+      </c>
+      <c r="B535" s="17">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C535" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="D535" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E535" s="2">
+        <v>175</v>
+      </c>
+      <c r="F535" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G535" s="2">
+        <v>20</v>
+      </c>
+      <c r="H535" s="2">
+        <v>2</v>
+      </c>
+      <c r="I535" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J535" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="536" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A536" s="16">
+        <v>46005</v>
+      </c>
+      <c r="B536" s="17">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C536" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="D536" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E536" s="2">
+        <v>380</v>
+      </c>
+      <c r="F536" s="2">
+        <v>25</v>
+      </c>
+      <c r="G536" s="2">
+        <v>46</v>
+      </c>
+      <c r="H536" s="2">
+        <v>10</v>
+      </c>
+      <c r="I536" s="2">
+        <v>2</v>
+      </c>
+      <c r="J536" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="537" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A537" s="16">
+        <v>46005</v>
+      </c>
+      <c r="B537" s="17">
+        <v>0.8125</v>
+      </c>
+      <c r="C537" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="D537" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="E537" s="2">
+        <v>71</v>
+      </c>
+      <c r="F537" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="G537" s="2">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="H537" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="I537" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="J537" s="2">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="538" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A538" s="16">
+        <v>46005</v>
+      </c>
+      <c r="B538" s="17">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C538" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="D538" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E538" s="2">
+        <v>256</v>
+      </c>
+      <c r="F538" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="G538" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="H538" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="I538" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="J538" s="2">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="539" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A539" s="16">
+        <v>46005</v>
+      </c>
+      <c r="B539" s="17">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C539" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="D539" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="E539" s="2">
+        <v>230</v>
+      </c>
+      <c r="F539" s="2">
+        <v>18</v>
+      </c>
+      <c r="G539" s="2">
+        <v>25</v>
+      </c>
+      <c r="H539" s="2">
+        <v>8</v>
+      </c>
+      <c r="I539" s="2">
+        <v>1</v>
+      </c>
+      <c r="J539" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="540" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A540" s="16">
+        <v>46006</v>
+      </c>
+      <c r="B540" s="17">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C540" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="D540" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E540" s="2">
+        <v>77</v>
+      </c>
+      <c r="F540" s="2">
+        <v>2</v>
+      </c>
+      <c r="G540" s="2">
+        <v>11</v>
+      </c>
+      <c r="H540" s="2">
+        <v>2</v>
+      </c>
+      <c r="I540" s="2">
+        <v>7</v>
+      </c>
+      <c r="J540" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="541" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A541" s="16">
+        <v>46006</v>
+      </c>
+      <c r="B541" s="17">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C541" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="D541" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E541" s="2">
+        <v>290</v>
+      </c>
+      <c r="F541" s="2">
+        <v>11</v>
+      </c>
+      <c r="G541" s="2">
+        <v>18</v>
+      </c>
+      <c r="H541" s="2">
+        <v>18</v>
+      </c>
+      <c r="I541" s="2">
+        <v>0</v>
+      </c>
+      <c r="J541" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="542" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A542" s="16">
+        <v>46006</v>
+      </c>
+      <c r="B542" s="17">
+        <v>0.5625</v>
+      </c>
+      <c r="C542" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="D542" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E542" s="2">
+        <v>155</v>
+      </c>
+      <c r="F542" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G542" s="2">
+        <v>15</v>
+      </c>
+      <c r="H542" s="2">
+        <v>2</v>
+      </c>
+      <c r="I542" s="2">
+        <v>7</v>
+      </c>
+      <c r="J542" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="543" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A543" s="16">
+        <v>46006</v>
+      </c>
+      <c r="B543" s="17">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C543" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="D543" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E543" s="2">
+        <v>175</v>
+      </c>
+      <c r="F543" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G543" s="2">
+        <v>20</v>
+      </c>
+      <c r="H543" s="2">
+        <v>2</v>
+      </c>
+      <c r="I543" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J543" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="544" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A544" s="16">
+        <v>46006</v>
+      </c>
+      <c r="B544" s="17">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C544" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="D544" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E544" s="2">
+        <v>290</v>
+      </c>
+      <c r="F544" s="2">
+        <v>11</v>
+      </c>
+      <c r="G544" s="2">
+        <v>18</v>
+      </c>
+      <c r="H544" s="2">
+        <v>18</v>
+      </c>
+      <c r="I544" s="2">
+        <v>0</v>
+      </c>
+      <c r="J544" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="545" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A545" s="16">
+        <v>46006</v>
+      </c>
+      <c r="B545" s="17">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C545" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="D545" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E545" s="2">
+        <v>670</v>
+      </c>
+      <c r="F545" s="2">
+        <v>42</v>
+      </c>
+      <c r="G545" s="2">
+        <v>66</v>
+      </c>
+      <c r="H545" s="2">
+        <v>26</v>
+      </c>
+      <c r="I545" s="2">
+        <v>5</v>
+      </c>
+      <c r="J545" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="546" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A546" s="16">
+        <v>46006</v>
+      </c>
+      <c r="B546" s="17">
+        <v>0.8125</v>
+      </c>
+      <c r="C546" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="D546" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E546" s="2">
+        <v>256</v>
+      </c>
+      <c r="F546" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="G546" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="H546" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="I546" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="J546" s="2">
+        <v>5.4</v>
       </c>
     </row>
   </sheetData>
@@ -19345,7 +20973,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F24E0C0-BC77-4AA4-801C-82B038A8B8E4}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -19356,29 +20984,29 @@
     <col min="6" max="6" width="32.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>130</v>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="16">
+        <v>45922</v>
       </c>
       <c r="B2" s="2">
         <v>102.8</v>
@@ -19393,12 +21021,12 @@
         <v>51.6</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>93</v>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="16">
+        <v>45926</v>
       </c>
       <c r="B3" s="2">
         <v>101.8</v>
@@ -19413,12 +21041,12 @@
         <v>51.4</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>99</v>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="16">
+        <v>45929</v>
       </c>
       <c r="B4" s="2">
         <v>101.6</v>
@@ -19433,12 +21061,12 @@
         <v>51.3</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>103</v>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="16">
+        <v>45931</v>
       </c>
       <c r="B5" s="2">
         <v>101.6</v>
@@ -19453,12 +21081,12 @@
         <v>52.1</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>117</v>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="16">
+        <v>45938</v>
       </c>
       <c r="B6" s="2">
         <v>101.5</v>
@@ -19473,12 +21101,12 @@
         <v>50.1</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>119</v>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="16">
+        <v>45939</v>
       </c>
       <c r="B7" s="2">
         <v>101.2</v>
@@ -19493,12 +21121,12 @@
         <v>50.6</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>58</v>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="16">
+        <v>45945</v>
       </c>
       <c r="B8" s="2">
         <v>101.1</v>
@@ -19513,10 +21141,10 @@
         <v>51</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>45950</v>
       </c>
@@ -19533,10 +21161,10 @@
         <v>50.7</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>45954</v>
       </c>
@@ -19553,10 +21181,10 @@
         <v>51.3</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
         <v>45955</v>
       </c>
@@ -19573,10 +21201,10 @@
         <v>50.6</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
         <v>45959</v>
       </c>
@@ -19595,9 +21223,8 @@
       <c r="F12" s="10"/>
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
         <v>45961</v>
       </c>
@@ -19616,9 +21243,8 @@
       <c r="F13" s="10"/>
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
         <v>45965</v>
       </c>
@@ -19635,10 +21261,10 @@
         <v>50.9</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
         <v>45968</v>
       </c>
@@ -19655,10 +21281,10 @@
         <v>50.8</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
         <v>45969</v>
       </c>
@@ -19675,7 +21301,7 @@
         <v>50.1</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -19695,7 +21321,7 @@
         <v>49.8</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -19715,7 +21341,7 @@
         <v>50.2</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -19735,7 +21361,7 @@
         <v>50.2</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -19755,7 +21381,7 @@
         <v>50.2</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -19775,7 +21401,7 @@
         <v>49.3</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -19795,7 +21421,7 @@
         <v>50.2</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -19815,7 +21441,7 @@
         <v>48.9</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -19835,7 +21461,27 @@
         <v>49.7</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>792</v>
+        <v>790</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="16">
+        <v>46004</v>
+      </c>
+      <c r="B25" s="2">
+        <v>97.9</v>
+      </c>
+      <c r="C25" s="2">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="D25" s="2">
+        <v>28.9</v>
+      </c>
+      <c r="E25" s="2">
+        <v>50.6</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>842</v>
       </c>
     </row>
   </sheetData>
@@ -19846,7 +21492,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D2F321-D2D4-48D2-B6F9-E306604CF730}">
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -19858,22 +21504,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="D1" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="E1" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="F1" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="G1" s="18" t="s">
         <v>162</v>
-      </c>
-      <c r="F1" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="G1" s="18" t="s">
-        <v>164</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>2</v>
@@ -19884,10 +21530,10 @@
         <v>45949</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D2" s="22">
         <v>58</v>
@@ -19908,10 +21554,10 @@
         <v>45950</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D3" s="22">
         <v>45</v>
@@ -19932,10 +21578,10 @@
         <v>45952</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D4" s="22">
         <v>46</v>
@@ -19944,7 +21590,7 @@
         <v>371</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G4" s="23">
         <v>0.28472222222222221</v>
@@ -19956,10 +21602,10 @@
         <v>45953</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D5" s="22">
         <v>49</v>
@@ -19980,10 +21626,10 @@
         <v>45954</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D6" s="22">
         <v>51</v>
@@ -19992,7 +21638,7 @@
         <v>431</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G6" s="23">
         <v>0.31111111111111112</v>
@@ -20004,10 +21650,10 @@
         <v>45955</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D7" s="22">
         <v>26</v>
@@ -20029,7 +21675,7 @@
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D8" s="22">
         <v>44</v>
@@ -20038,11 +21684,11 @@
         <v>407</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="24" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -20051,7 +21697,7 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="21" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D9" s="2">
         <v>48</v>
@@ -20060,11 +21706,11 @@
         <v>418</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="24" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -20073,7 +21719,7 @@
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D10" s="2">
         <v>43</v>
@@ -20082,11 +21728,11 @@
         <v>390</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="24" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -20095,7 +21741,7 @@
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" s="2">
         <v>63</v>
@@ -20104,11 +21750,11 @@
         <v>463</v>
       </c>
       <c r="F11" s="24" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="24" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -20117,7 +21763,7 @@
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="21" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D12" s="2">
         <v>54</v>
@@ -20126,22 +21772,22 @@
         <v>442</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="24" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D13" s="2">
         <v>61</v>
@@ -20153,21 +21799,21 @@
         <v>17820</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D14" s="2">
         <v>62</v>
@@ -20179,21 +21825,21 @@
         <v>17620</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D15" s="2">
         <v>46</v>
@@ -20205,21 +21851,21 @@
         <v>700</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D16" s="2">
         <v>67</v>
@@ -20231,21 +21877,21 @@
         <v>18070</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D17" s="2">
         <v>59</v>
@@ -20255,10 +21901,10 @@
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -20266,10 +21912,10 @@
         <v>45970</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D18" s="2">
         <v>57</v>
@@ -20284,7 +21930,7 @@
         <v>0.28888888888888886</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -20292,10 +21938,10 @@
         <v>45972</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D19" s="2">
         <v>48</v>
@@ -20304,13 +21950,13 @@
         <v>362</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="G19" s="26">
         <v>0.2638888888888889</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
@@ -20318,10 +21964,10 @@
         <v>45985</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D20" s="2">
         <v>49</v>
@@ -20334,7 +21980,7 @@
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -20342,10 +21988,10 @@
         <v>45986</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D21" s="2">
         <v>50</v>
@@ -20358,7 +22004,7 @@
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -20366,10 +22012,10 @@
         <v>45987</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D22" s="2">
         <v>30</v>
@@ -20378,7 +22024,7 @@
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
@@ -20386,10 +22032,10 @@
         <v>45987</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D23" s="2">
         <v>51</v>
@@ -20400,7 +22046,7 @@
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
@@ -20408,10 +22054,10 @@
         <v>45989</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D24" s="2">
         <v>44</v>
@@ -20426,7 +22072,7 @@
         <v>0.25138888888888888</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
@@ -20434,10 +22080,10 @@
         <v>45990</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D25" s="2">
         <v>48</v>
@@ -20452,7 +22098,7 @@
         <v>0.25138888888888888</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -20460,10 +22106,10 @@
         <v>45991</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D26" s="2">
         <v>38</v>
@@ -20478,7 +22124,7 @@
         <v>0.30069444444444443</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
@@ -20486,10 +22132,10 @@
         <v>45997</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D27" s="2">
         <v>72</v>
@@ -20502,7 +22148,55 @@
         <v>0.30972222222222223</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="16">
+        <v>46001</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D28" s="2">
+        <v>38</v>
+      </c>
+      <c r="E28" s="2">
+        <v>331</v>
+      </c>
+      <c r="F28" s="2">
+        <v>750</v>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="16">
+        <v>46003</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D29" s="2">
+        <v>39</v>
+      </c>
+      <c r="E29" s="2">
+        <v>353</v>
+      </c>
+      <c r="F29" s="2">
+        <v>750</v>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2" t="s">
+        <v>844</v>
       </c>
     </row>
   </sheetData>
@@ -20522,28 +22216,28 @@
   <sheetData>
     <row r="1" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>176</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -20551,7 +22245,7 @@
         <v>32</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C2" s="10">
         <v>290</v>
@@ -20574,10 +22268,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C3" s="10">
         <v>530</v>
@@ -20600,10 +22294,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C4" s="10">
         <v>670</v>
@@ -20626,10 +22320,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C5" s="10">
         <v>380</v>
@@ -20652,10 +22346,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C6" s="10">
         <v>242</v>
@@ -20678,10 +22372,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C7" s="10">
         <v>155</v>
@@ -20704,10 +22398,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C8" s="10">
         <v>175</v>
@@ -20730,10 +22424,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C9" s="10">
         <v>77</v>
@@ -20756,10 +22450,10 @@
     </row>
     <row r="10" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C10" s="10">
         <v>256</v>
@@ -20782,10 +22476,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C11" s="10">
         <v>615</v>
@@ -20822,28 +22516,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -20869,7 +22563,7 @@
         <v>14.5</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -20919,14 +22613,14 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="E2" s="2">
         <v>1962</v>
@@ -20939,14 +22633,14 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E3" s="2">
         <v>2269</v>
@@ -20959,14 +22653,14 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E4" s="2">
         <v>1728</v>
@@ -20989,14 +22683,14 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E5" s="2">
         <v>2009</v>
@@ -21019,14 +22713,14 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E6" s="2">
         <v>1682</v>
@@ -21049,14 +22743,14 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E7" s="2">
         <v>2221</v>
@@ -21079,14 +22773,14 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E8" s="2">
         <v>1938</v>
@@ -21109,14 +22803,14 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E9" s="2">
         <v>2092</v>
@@ -21139,14 +22833,14 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E10" s="2">
         <v>2783</v>
@@ -21169,14 +22863,14 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E11" s="2">
         <v>1796</v>
@@ -21199,14 +22893,14 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E12" s="2">
         <v>1698</v>
@@ -21229,14 +22923,14 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E13" s="2">
         <v>2099</v>
@@ -21259,14 +22953,14 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E14" s="2">
         <v>2774</v>
@@ -21289,14 +22983,14 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E15" s="2">
         <v>1880</v>
@@ -21319,14 +23013,14 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E16" s="2">
         <v>1634</v>
@@ -21349,14 +23043,14 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E17" s="2">
         <v>2001</v>
@@ -21379,14 +23073,14 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E18" s="2">
         <v>1878</v>
@@ -21409,14 +23103,14 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E19" s="2">
         <v>2257</v>
@@ -21439,14 +23133,14 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E20" s="2">
         <v>2909</v>

--- a/Food Log Main.xlsx
+++ b/Food Log Main.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91998\VS\Food Log Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F1EEBD-A345-4042-BEEC-EF52AA19AD77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{109D1D15-3DDC-403C-8A36-C8D828244616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main Format 12 oct" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="845">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1693" uniqueCount="897">
   <si>
     <t>date</t>
   </si>
@@ -2593,6 +2593,162 @@
   </si>
   <si>
     <t>WK20241212-p750</t>
+  </si>
+  <si>
+    <t>FD20241216-0800-q5r6</t>
+  </si>
+  <si>
+    <t>FD20241216-0900-s7t8</t>
+  </si>
+  <si>
+    <t>FD20241216-1200-u9v0</t>
+  </si>
+  <si>
+    <t>FD20241216-1230-w1x2</t>
+  </si>
+  <si>
+    <t>FD20241216-1500-y3z4</t>
+  </si>
+  <si>
+    <t>FD20241216-1830-a5b6</t>
+  </si>
+  <si>
+    <t>FD20241216-1900-c7d8</t>
+  </si>
+  <si>
+    <t>½ Starter 1</t>
+  </si>
+  <si>
+    <t>FD20241216-1930-e9f0</t>
+  </si>
+  <si>
+    <t>FD20241216-2100-g1h2</t>
+  </si>
+  <si>
+    <t>FD20241217-0730-i3j4</t>
+  </si>
+  <si>
+    <t>FD20241217-1000-k5l6</t>
+  </si>
+  <si>
+    <t>FD20241217-1300-m7n8</t>
+  </si>
+  <si>
+    <t>FD20241217-1300-o9p0</t>
+  </si>
+  <si>
+    <t>FD20241217-1400-q1r2</t>
+  </si>
+  <si>
+    <t>FD20241217-2130-s3t4</t>
+  </si>
+  <si>
+    <t>FD20241217-2200-u5v6</t>
+  </si>
+  <si>
+    <t>FD20241217-2230-w7x8</t>
+  </si>
+  <si>
+    <t>FD20241217-2330-y9z0</t>
+  </si>
+  <si>
+    <t>2 rotis with butter and 10g jaggery</t>
+  </si>
+  <si>
+    <t>FD20241218-0830-a1b2</t>
+  </si>
+  <si>
+    <t>FD20241218-0900-c3d4</t>
+  </si>
+  <si>
+    <t>FD20241218-1300-e5f6</t>
+  </si>
+  <si>
+    <t>FD20241218-1330-g7h8</t>
+  </si>
+  <si>
+    <t>FD20241218-1900-i9j0</t>
+  </si>
+  <si>
+    <t>FD20241218-1930-k1l2</t>
+  </si>
+  <si>
+    <t>FD20241218-2000-m3n4</t>
+  </si>
+  <si>
+    <t>FD20241218-2030-o5p6</t>
+  </si>
+  <si>
+    <t>FD20241219-0800-q7r8</t>
+  </si>
+  <si>
+    <t>FD20241219-0900-y5z6</t>
+  </si>
+  <si>
+    <t>FD20241219-1300-s9t0</t>
+  </si>
+  <si>
+    <t>FD20241219-1330-u1v2</t>
+  </si>
+  <si>
+    <t>FD20241219-1400-w3x4</t>
+  </si>
+  <si>
+    <t>FD20241219-1430-a7b8</t>
+  </si>
+  <si>
+    <t>FD20241219-1600-c9d0</t>
+  </si>
+  <si>
+    <t>FD20241219-1830-e1f2</t>
+  </si>
+  <si>
+    <t>FD20241219-1900-g3h4</t>
+  </si>
+  <si>
+    <t>FD20241219-1930-i5j6</t>
+  </si>
+  <si>
+    <t>FD20241219-2200-k7l8</t>
+  </si>
+  <si>
+    <t>FD20241220-0800-m7n8</t>
+  </si>
+  <si>
+    <t>FD20241220-1400-o9p0</t>
+  </si>
+  <si>
+    <t>3 servings of Brownie</t>
+  </si>
+  <si>
+    <t>FD20241220-1800-q1r2</t>
+  </si>
+  <si>
+    <t>FD20241220-1830-s3t4</t>
+  </si>
+  <si>
+    <t>FD20241220-1900-u5v6</t>
+  </si>
+  <si>
+    <t>2 rotis with butter and jaggery powder</t>
+  </si>
+  <si>
+    <t>1000133317.jpg</t>
+  </si>
+  <si>
+    <t>1000133851.jpg</t>
+  </si>
+  <si>
+    <t>WK20241216-p750</t>
+  </si>
+  <si>
+    <t>WK20241217-p1300</t>
+  </si>
+  <si>
+    <t>WK20241219-p925</t>
+  </si>
+  <si>
+    <t>WK20241220-wm</t>
   </si>
 </sst>
 </file>
@@ -3037,7 +3193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K546"/>
+  <dimension ref="A1:K588"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -20962,6 +21118,1350 @@
         <v>5.4</v>
       </c>
     </row>
+    <row r="547" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A547" s="16">
+        <v>46007</v>
+      </c>
+      <c r="B547" s="17">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C547" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="D547" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E547" s="2">
+        <v>77</v>
+      </c>
+      <c r="F547" s="2">
+        <v>2</v>
+      </c>
+      <c r="G547" s="2">
+        <v>11</v>
+      </c>
+      <c r="H547" s="2">
+        <v>2</v>
+      </c>
+      <c r="I547" s="2">
+        <v>7</v>
+      </c>
+      <c r="J547" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A548" s="16">
+        <v>46007</v>
+      </c>
+      <c r="B548" s="17">
+        <v>0.375</v>
+      </c>
+      <c r="C548" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="D548" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E548" s="2">
+        <v>256</v>
+      </c>
+      <c r="F548" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="G548" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="H548" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="I548" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="J548" s="2">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="549" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A549" s="16">
+        <v>46007</v>
+      </c>
+      <c r="B549" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="C549" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="D549" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E549" s="2">
+        <v>290</v>
+      </c>
+      <c r="F549" s="2">
+        <v>11</v>
+      </c>
+      <c r="G549" s="2">
+        <v>18</v>
+      </c>
+      <c r="H549" s="2">
+        <v>18</v>
+      </c>
+      <c r="I549" s="2">
+        <v>0</v>
+      </c>
+      <c r="J549" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="550" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A550" s="16">
+        <v>46007</v>
+      </c>
+      <c r="B550" s="17">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C550" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="D550" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E550" s="2">
+        <v>155</v>
+      </c>
+      <c r="F550" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G550" s="2">
+        <v>15</v>
+      </c>
+      <c r="H550" s="2">
+        <v>2</v>
+      </c>
+      <c r="I550" s="2">
+        <v>7</v>
+      </c>
+      <c r="J550" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="551" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A551" s="16">
+        <v>46007</v>
+      </c>
+      <c r="B551" s="17">
+        <v>0.625</v>
+      </c>
+      <c r="C551" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="D551" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E551" s="2">
+        <v>77</v>
+      </c>
+      <c r="F551" s="2">
+        <v>2</v>
+      </c>
+      <c r="G551" s="2">
+        <v>11</v>
+      </c>
+      <c r="H551" s="2">
+        <v>2</v>
+      </c>
+      <c r="I551" s="2">
+        <v>7</v>
+      </c>
+      <c r="J551" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="552" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A552" s="16">
+        <v>46007</v>
+      </c>
+      <c r="B552" s="17">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C552" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="D552" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E552" s="2">
+        <v>670</v>
+      </c>
+      <c r="F552" s="2">
+        <v>42</v>
+      </c>
+      <c r="G552" s="2">
+        <v>66</v>
+      </c>
+      <c r="H552" s="2">
+        <v>26</v>
+      </c>
+      <c r="I552" s="2">
+        <v>5</v>
+      </c>
+      <c r="J552" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="553" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A553" s="16">
+        <v>46007</v>
+      </c>
+      <c r="B553" s="17">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C553" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="D553" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="E553" s="2">
+        <v>145</v>
+      </c>
+      <c r="F553" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="G553" s="2">
+        <v>9</v>
+      </c>
+      <c r="H553" s="2">
+        <v>9</v>
+      </c>
+      <c r="I553" s="2">
+        <v>0</v>
+      </c>
+      <c r="J553" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="554" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A554" s="16">
+        <v>46007</v>
+      </c>
+      <c r="B554" s="17">
+        <v>0.8125</v>
+      </c>
+      <c r="C554" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="D554" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E554" s="2">
+        <v>175</v>
+      </c>
+      <c r="F554" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G554" s="2">
+        <v>20</v>
+      </c>
+      <c r="H554" s="2">
+        <v>2</v>
+      </c>
+      <c r="I554" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J554" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="555" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A555" s="16">
+        <v>46007</v>
+      </c>
+      <c r="B555" s="17">
+        <v>0.875</v>
+      </c>
+      <c r="C555" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="D555" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E555" s="2">
+        <v>128</v>
+      </c>
+      <c r="F555" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G555" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H555" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I555" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J555" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="556" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A556" s="16">
+        <v>46008</v>
+      </c>
+      <c r="B556" s="17">
+        <v>0.3125</v>
+      </c>
+      <c r="C556" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="D556" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E556" s="2">
+        <v>77</v>
+      </c>
+      <c r="F556" s="2">
+        <v>2</v>
+      </c>
+      <c r="G556" s="2">
+        <v>11</v>
+      </c>
+      <c r="H556" s="2">
+        <v>2</v>
+      </c>
+      <c r="I556" s="2">
+        <v>7</v>
+      </c>
+      <c r="J556" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="557" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A557" s="16">
+        <v>46008</v>
+      </c>
+      <c r="B557" s="17">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C557" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D557" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E557" s="2">
+        <v>128</v>
+      </c>
+      <c r="F557" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G557" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H557" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I557" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J557" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="558" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A558" s="16">
+        <v>46008</v>
+      </c>
+      <c r="B558" s="17">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C558" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="D558" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E558" s="2">
+        <v>290</v>
+      </c>
+      <c r="F558" s="2">
+        <v>11</v>
+      </c>
+      <c r="G558" s="2">
+        <v>18</v>
+      </c>
+      <c r="H558" s="2">
+        <v>18</v>
+      </c>
+      <c r="I558" s="2">
+        <v>0</v>
+      </c>
+      <c r="J558" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="559" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A559" s="16">
+        <v>46008</v>
+      </c>
+      <c r="B559" s="17">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C559" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="D559" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E559" s="2">
+        <v>380</v>
+      </c>
+      <c r="F559" s="2">
+        <v>25</v>
+      </c>
+      <c r="G559" s="2">
+        <v>46</v>
+      </c>
+      <c r="H559" s="2">
+        <v>10</v>
+      </c>
+      <c r="I559" s="2">
+        <v>2</v>
+      </c>
+      <c r="J559" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="560" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A560" s="16">
+        <v>46008</v>
+      </c>
+      <c r="B560" s="17">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C560" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="D560" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E560" s="2">
+        <v>175</v>
+      </c>
+      <c r="F560" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G560" s="2">
+        <v>20</v>
+      </c>
+      <c r="H560" s="2">
+        <v>2</v>
+      </c>
+      <c r="I560" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J560" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="561" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A561" s="16">
+        <v>46008</v>
+      </c>
+      <c r="B561" s="17">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C561" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="D561" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E561" s="2">
+        <v>670</v>
+      </c>
+      <c r="F561" s="2">
+        <v>42</v>
+      </c>
+      <c r="G561" s="2">
+        <v>66</v>
+      </c>
+      <c r="H561" s="2">
+        <v>26</v>
+      </c>
+      <c r="I561" s="2">
+        <v>5</v>
+      </c>
+      <c r="J561" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="562" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A562" s="16">
+        <v>46008</v>
+      </c>
+      <c r="B562" s="17">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="C562" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="D562" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E562" s="2">
+        <v>175</v>
+      </c>
+      <c r="F562" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G562" s="2">
+        <v>20</v>
+      </c>
+      <c r="H562" s="2">
+        <v>2</v>
+      </c>
+      <c r="I562" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J562" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="563" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A563" s="16">
+        <v>46008</v>
+      </c>
+      <c r="B563" s="17">
+        <v>0.9375</v>
+      </c>
+      <c r="C563" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="D563" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E563" s="2">
+        <v>256</v>
+      </c>
+      <c r="F563" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="G563" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="H563" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="I563" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="J563" s="2">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="564" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A564" s="16">
+        <v>46008</v>
+      </c>
+      <c r="B564" s="17">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="C564" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="D564" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="E564" s="2">
+        <v>370</v>
+      </c>
+      <c r="F564" s="2">
+        <v>6</v>
+      </c>
+      <c r="G564" s="2">
+        <v>55</v>
+      </c>
+      <c r="H564" s="2">
+        <v>13</v>
+      </c>
+      <c r="I564" s="2">
+        <v>21</v>
+      </c>
+      <c r="J564" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="565" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A565" s="16">
+        <v>46009</v>
+      </c>
+      <c r="B565" s="17">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C565" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="D565" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E565" s="2">
+        <v>77</v>
+      </c>
+      <c r="F565" s="2">
+        <v>2</v>
+      </c>
+      <c r="G565" s="2">
+        <v>11</v>
+      </c>
+      <c r="H565" s="2">
+        <v>2</v>
+      </c>
+      <c r="I565" s="2">
+        <v>7</v>
+      </c>
+      <c r="J565" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="566" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A566" s="16">
+        <v>46009</v>
+      </c>
+      <c r="B566" s="17">
+        <v>0.375</v>
+      </c>
+      <c r="C566" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="D566" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E566" s="2">
+        <v>256</v>
+      </c>
+      <c r="F566" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="G566" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="H566" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="I566" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="J566" s="2">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="567" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A567" s="16">
+        <v>46009</v>
+      </c>
+      <c r="B567" s="17">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C567" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="D567" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E567" s="2">
+        <v>290</v>
+      </c>
+      <c r="F567" s="2">
+        <v>11</v>
+      </c>
+      <c r="G567" s="2">
+        <v>18</v>
+      </c>
+      <c r="H567" s="2">
+        <v>18</v>
+      </c>
+      <c r="I567" s="2">
+        <v>0</v>
+      </c>
+      <c r="J567" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="568" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A568" s="16">
+        <v>46009</v>
+      </c>
+      <c r="B568" s="17">
+        <v>0.5625</v>
+      </c>
+      <c r="C568" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="D568" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E568" s="2">
+        <v>155</v>
+      </c>
+      <c r="F568" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G568" s="2">
+        <v>15</v>
+      </c>
+      <c r="H568" s="2">
+        <v>2</v>
+      </c>
+      <c r="I568" s="2">
+        <v>7</v>
+      </c>
+      <c r="J568" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="569" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A569" s="16">
+        <v>46009</v>
+      </c>
+      <c r="B569" s="17">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C569" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="D569" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E569" s="2">
+        <v>670</v>
+      </c>
+      <c r="F569" s="2">
+        <v>42</v>
+      </c>
+      <c r="G569" s="2">
+        <v>66</v>
+      </c>
+      <c r="H569" s="2">
+        <v>26</v>
+      </c>
+      <c r="I569" s="2">
+        <v>5</v>
+      </c>
+      <c r="J569" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="570" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A570" s="16">
+        <v>46009</v>
+      </c>
+      <c r="B570" s="17">
+        <v>0.8125</v>
+      </c>
+      <c r="C570" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="D570" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="E570" s="2">
+        <v>145</v>
+      </c>
+      <c r="F570" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="G570" s="2">
+        <v>9</v>
+      </c>
+      <c r="H570" s="2">
+        <v>9</v>
+      </c>
+      <c r="I570" s="2">
+        <v>0</v>
+      </c>
+      <c r="J570" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="571" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A571" s="16">
+        <v>46009</v>
+      </c>
+      <c r="B571" s="17">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C571" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="D571" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E571" s="2">
+        <v>175</v>
+      </c>
+      <c r="F571" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G571" s="2">
+        <v>20</v>
+      </c>
+      <c r="H571" s="2">
+        <v>2</v>
+      </c>
+      <c r="I571" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J571" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="572" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A572" s="16">
+        <v>46009</v>
+      </c>
+      <c r="B572" s="17">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C572" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="D572" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E572" s="2">
+        <v>256</v>
+      </c>
+      <c r="F572" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="G572" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="H572" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="I572" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="J572" s="2">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="573" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A573" s="16">
+        <v>46010</v>
+      </c>
+      <c r="B573" s="17">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C573" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="D573" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E573" s="2">
+        <v>77</v>
+      </c>
+      <c r="F573" s="2">
+        <v>2</v>
+      </c>
+      <c r="G573" s="2">
+        <v>11</v>
+      </c>
+      <c r="H573" s="2">
+        <v>2</v>
+      </c>
+      <c r="I573" s="2">
+        <v>7</v>
+      </c>
+      <c r="J573" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="574" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A574" s="16">
+        <v>46010</v>
+      </c>
+      <c r="B574" s="17">
+        <v>0.375</v>
+      </c>
+      <c r="C574" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="D574" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="E574" s="2">
+        <v>105</v>
+      </c>
+      <c r="F574" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="G574" s="2">
+        <v>21</v>
+      </c>
+      <c r="H574" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="I574" s="2">
+        <v>14</v>
+      </c>
+      <c r="J574" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="575" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A575" s="16">
+        <v>46010</v>
+      </c>
+      <c r="B575" s="17">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C575" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="D575" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E575" s="2">
+        <v>290</v>
+      </c>
+      <c r="F575" s="2">
+        <v>11</v>
+      </c>
+      <c r="G575" s="2">
+        <v>18</v>
+      </c>
+      <c r="H575" s="2">
+        <v>18</v>
+      </c>
+      <c r="I575" s="2">
+        <v>0</v>
+      </c>
+      <c r="J575" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="576" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A576" s="16">
+        <v>46010</v>
+      </c>
+      <c r="B576" s="17">
+        <v>0.5625</v>
+      </c>
+      <c r="C576" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="D576" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E576" s="2">
+        <v>380</v>
+      </c>
+      <c r="F576" s="2">
+        <v>25</v>
+      </c>
+      <c r="G576" s="2">
+        <v>46</v>
+      </c>
+      <c r="H576" s="2">
+        <v>10</v>
+      </c>
+      <c r="I576" s="2">
+        <v>2</v>
+      </c>
+      <c r="J576" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="577" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A577" s="16">
+        <v>46010</v>
+      </c>
+      <c r="B577" s="17">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C577" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="D577" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E577" s="2">
+        <v>155</v>
+      </c>
+      <c r="F577" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G577" s="2">
+        <v>15</v>
+      </c>
+      <c r="H577" s="2">
+        <v>2</v>
+      </c>
+      <c r="I577" s="2">
+        <v>7</v>
+      </c>
+      <c r="J577" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="578" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A578" s="16">
+        <v>46010</v>
+      </c>
+      <c r="B578" s="17">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C578" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="D578" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="E578" s="2">
+        <v>105</v>
+      </c>
+      <c r="F578" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="G578" s="2">
+        <v>21</v>
+      </c>
+      <c r="H578" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="I578" s="2">
+        <v>14</v>
+      </c>
+      <c r="J578" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="579" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A579" s="16">
+        <v>46010</v>
+      </c>
+      <c r="B579" s="17">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C579" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="D579" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E579" s="2">
+        <v>77</v>
+      </c>
+      <c r="F579" s="2">
+        <v>2</v>
+      </c>
+      <c r="G579" s="2">
+        <v>11</v>
+      </c>
+      <c r="H579" s="2">
+        <v>2</v>
+      </c>
+      <c r="I579" s="2">
+        <v>7</v>
+      </c>
+      <c r="J579" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="580" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A580" s="16">
+        <v>46010</v>
+      </c>
+      <c r="B580" s="17">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C580" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="D580" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E580" s="2">
+        <v>670</v>
+      </c>
+      <c r="F580" s="2">
+        <v>42</v>
+      </c>
+      <c r="G580" s="2">
+        <v>66</v>
+      </c>
+      <c r="H580" s="2">
+        <v>26</v>
+      </c>
+      <c r="I580" s="2">
+        <v>5</v>
+      </c>
+      <c r="J580" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="581" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A581" s="16">
+        <v>46010</v>
+      </c>
+      <c r="B581" s="17">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C581" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="D581" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="E581" s="2">
+        <v>145</v>
+      </c>
+      <c r="F581" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="G581" s="2">
+        <v>9</v>
+      </c>
+      <c r="H581" s="2">
+        <v>9</v>
+      </c>
+      <c r="I581" s="2">
+        <v>0</v>
+      </c>
+      <c r="J581" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="582" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A582" s="16">
+        <v>46010</v>
+      </c>
+      <c r="B582" s="17">
+        <v>0.8125</v>
+      </c>
+      <c r="C582" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="D582" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E582" s="2">
+        <v>128</v>
+      </c>
+      <c r="F582" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G582" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H582" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I582" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J582" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="583" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A583" s="16">
+        <v>46010</v>
+      </c>
+      <c r="B583" s="17">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="C583" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="D583" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="E583" s="2">
+        <v>158</v>
+      </c>
+      <c r="F583" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="G583" s="2">
+        <v>18.3</v>
+      </c>
+      <c r="H583" s="2">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="I583" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="J583" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="584" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A584" s="16">
+        <v>46011</v>
+      </c>
+      <c r="B584" s="17">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C584" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="D584" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E584" s="2">
+        <v>77</v>
+      </c>
+      <c r="F584" s="2">
+        <v>2</v>
+      </c>
+      <c r="G584" s="2">
+        <v>11</v>
+      </c>
+      <c r="H584" s="2">
+        <v>2</v>
+      </c>
+      <c r="I584" s="2">
+        <v>7</v>
+      </c>
+      <c r="J584" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="585" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A585" s="16">
+        <v>46011</v>
+      </c>
+      <c r="B585" s="17">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C585" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="D585" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="E585" s="2">
+        <v>918</v>
+      </c>
+      <c r="F585" s="2">
+        <v>12.9</v>
+      </c>
+      <c r="G585" s="2">
+        <v>102.9</v>
+      </c>
+      <c r="H585" s="2">
+        <v>53.1</v>
+      </c>
+      <c r="I585" s="2">
+        <v>60</v>
+      </c>
+      <c r="J585" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="586" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A586" s="16">
+        <v>46011</v>
+      </c>
+      <c r="B586" s="17">
+        <v>0.75</v>
+      </c>
+      <c r="C586" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="D586" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E586" s="2">
+        <v>670</v>
+      </c>
+      <c r="F586" s="2">
+        <v>42</v>
+      </c>
+      <c r="G586" s="2">
+        <v>66</v>
+      </c>
+      <c r="H586" s="2">
+        <v>26</v>
+      </c>
+      <c r="I586" s="2">
+        <v>5</v>
+      </c>
+      <c r="J586" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="587" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A587" s="16">
+        <v>46011</v>
+      </c>
+      <c r="B587" s="17">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C587" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="D587" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E587" s="2">
+        <v>175</v>
+      </c>
+      <c r="F587" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G587" s="2">
+        <v>20</v>
+      </c>
+      <c r="H587" s="2">
+        <v>2</v>
+      </c>
+      <c r="I587" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J587" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="588" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A588" s="16">
+        <v>46011</v>
+      </c>
+      <c r="B588" s="17">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C588" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="D588" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="E588" s="2">
+        <v>310</v>
+      </c>
+      <c r="F588" s="2">
+        <v>6</v>
+      </c>
+      <c r="G588" s="2">
+        <v>45</v>
+      </c>
+      <c r="H588" s="2">
+        <v>12</v>
+      </c>
+      <c r="I588" s="2">
+        <v>11</v>
+      </c>
+      <c r="J588" s="2">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C277:C1048576 C1:C211 C217:C265">
@@ -20973,7 +22473,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F24E0C0-BC77-4AA4-801C-82B038A8B8E4}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -21484,6 +22984,46 @@
         <v>842</v>
       </c>
     </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="16">
+        <v>46008</v>
+      </c>
+      <c r="B26" s="2">
+        <v>97.5</v>
+      </c>
+      <c r="C26" s="2">
+        <v>35.9</v>
+      </c>
+      <c r="D26" s="2">
+        <v>30.5</v>
+      </c>
+      <c r="E26" s="2">
+        <v>49.1</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="16">
+        <v>46011</v>
+      </c>
+      <c r="B27" s="2">
+        <v>97.9</v>
+      </c>
+      <c r="C27" s="2">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="D27" s="2">
+        <v>28.9</v>
+      </c>
+      <c r="E27" s="2">
+        <v>50.6</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>892</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21492,7 +23032,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D2F321-D2D4-48D2-B6F9-E306604CF730}">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -22020,7 +23560,9 @@
       <c r="D22" s="2">
         <v>30</v>
       </c>
-      <c r="E22" s="2"/>
+      <c r="E22" s="2">
+        <v>304</v>
+      </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2" t="s">
@@ -22040,7 +23582,9 @@
       <c r="D23" s="2">
         <v>51</v>
       </c>
-      <c r="E23" s="2"/>
+      <c r="E23" s="2">
+        <v>451</v>
+      </c>
       <c r="F23" s="2">
         <v>1075</v>
       </c>
@@ -22197,6 +23741,100 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2" t="s">
         <v>844</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="16">
+        <v>46007</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D30" s="2">
+        <v>40</v>
+      </c>
+      <c r="E30" s="2">
+        <v>370</v>
+      </c>
+      <c r="F30" s="2">
+        <v>750</v>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="16">
+        <v>46008</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D31" s="2">
+        <v>50</v>
+      </c>
+      <c r="E31" s="2">
+        <v>518</v>
+      </c>
+      <c r="F31" s="2">
+        <v>1300</v>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="16">
+        <v>46010</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D32" s="2">
+        <v>39</v>
+      </c>
+      <c r="E32" s="2">
+        <v>392</v>
+      </c>
+      <c r="F32" s="2">
+        <v>925</v>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="16">
+        <v>46011</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D33" s="2">
+        <v>50</v>
+      </c>
+      <c r="E33" s="2">
+        <v>374</v>
+      </c>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2" t="s">
+        <v>896</v>
       </c>
     </row>
   </sheetData>

--- a/Food Log Main.xlsx
+++ b/Food Log Main.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91998\VS\Food Log Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4AB6178-FC85-4492-98B4-0C517ED08E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78ACF91D-606E-4E2F-8582-5E558C6F226E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main Format 12 oct" sheetId="1" r:id="rId1"/>
     <sheet name="Weight Tracker 23sep" sheetId="3" r:id="rId2"/>
     <sheet name="Workouts 19oct" sheetId="6" r:id="rId3"/>
     <sheet name="Std Meals with Mac" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="8" r:id="rId5"/>
-    <sheet name="Body Measurements" sheetId="5" r:id="rId6"/>
+    <sheet name="Body Measurements" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId6"/>
     <sheet name="Daily 23 to 11oct" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Main Format 12 oct'!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sheet1!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Sheet1!$A$1:$K$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Weight Tracker 23sep'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Workouts 19oct'!$A$1:$H$1</definedName>
   </definedNames>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="1103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2198" uniqueCount="1103">
   <si>
     <t>date</t>
   </si>
@@ -3520,7 +3520,27 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -27610,13 +27630,19 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C1:C211 C217:C265">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C277:C588">
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C656:C664">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C665:C680">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C589:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  <conditionalFormatting sqref="C760:C1048576 C589:C655 C681:C743">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -29514,2901 +29540,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB0140AB-465A-4E35-8F6E-65CE935EFC2A}">
-  <dimension ref="A1:J95"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="29">
-        <v>46020</v>
-      </c>
-      <c r="B2" s="30">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="C2" t="s">
-        <v>989</v>
-      </c>
-      <c r="D2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E2">
-        <v>77</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>11</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>7</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="29">
-        <v>46020</v>
-      </c>
-      <c r="B3" s="30">
-        <v>0.5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>990</v>
-      </c>
-      <c r="D3" t="s">
-        <v>991</v>
-      </c>
-      <c r="E3">
-        <v>285</v>
-      </c>
-      <c r="F3">
-        <v>25</v>
-      </c>
-      <c r="G3">
-        <v>15</v>
-      </c>
-      <c r="H3">
-        <v>15</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="29">
-        <v>46020</v>
-      </c>
-      <c r="B4" s="30">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="C4" t="s">
-        <v>992</v>
-      </c>
-      <c r="D4" t="s">
-        <v>993</v>
-      </c>
-      <c r="E4">
-        <v>130</v>
-      </c>
-      <c r="F4">
-        <v>5</v>
-      </c>
-      <c r="G4">
-        <v>25</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="29">
-        <v>46020</v>
-      </c>
-      <c r="B5" s="30">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="C5" t="s">
-        <v>994</v>
-      </c>
-      <c r="D5" t="s">
-        <v>995</v>
-      </c>
-      <c r="E5">
-        <v>180</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>25</v>
-      </c>
-      <c r="H5">
-        <v>8</v>
-      </c>
-      <c r="I5">
-        <v>15</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="29">
-        <v>46020</v>
-      </c>
-      <c r="B6" s="30">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="C6" t="s">
-        <v>996</v>
-      </c>
-      <c r="D6" t="s">
-        <v>997</v>
-      </c>
-      <c r="E6">
-        <v>240</v>
-      </c>
-      <c r="F6">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>24</v>
-      </c>
-      <c r="H6">
-        <v>12</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="29">
-        <v>46020</v>
-      </c>
-      <c r="B7" s="30">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="C7" t="s">
-        <v>998</v>
-      </c>
-      <c r="D7" t="s">
-        <v>102</v>
-      </c>
-      <c r="E7">
-        <v>77</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7">
-        <v>11</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="29">
-        <v>46020</v>
-      </c>
-      <c r="B8" s="30">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="C8" t="s">
-        <v>999</v>
-      </c>
-      <c r="D8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8">
-        <v>290</v>
-      </c>
-      <c r="F8">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>18</v>
-      </c>
-      <c r="H8">
-        <v>18</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="29">
-        <v>46020</v>
-      </c>
-      <c r="B9" s="30">
-        <v>0.75</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1000</v>
-      </c>
-      <c r="D9" t="s">
-        <v>932</v>
-      </c>
-      <c r="E9">
-        <v>335</v>
-      </c>
-      <c r="F9">
-        <v>21</v>
-      </c>
-      <c r="G9">
-        <v>33</v>
-      </c>
-      <c r="H9">
-        <v>13</v>
-      </c>
-      <c r="I9">
-        <v>2.5</v>
-      </c>
-      <c r="J9">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="29">
-        <v>46020</v>
-      </c>
-      <c r="B10" s="30">
-        <v>0.8125</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1001</v>
-      </c>
-      <c r="D10" t="s">
-        <v>139</v>
-      </c>
-      <c r="E10">
-        <v>175</v>
-      </c>
-      <c r="F10">
-        <v>15.5</v>
-      </c>
-      <c r="G10">
-        <v>20</v>
-      </c>
-      <c r="H10">
-        <v>2</v>
-      </c>
-      <c r="I10">
-        <v>11.5</v>
-      </c>
-      <c r="J10">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" t="s">
-        <v>4</v>
-      </c>
-      <c r="F16" t="s">
-        <v>5</v>
-      </c>
-      <c r="G16" t="s">
-        <v>6</v>
-      </c>
-      <c r="H16" t="s">
-        <v>7</v>
-      </c>
-      <c r="I16" t="s">
-        <v>8</v>
-      </c>
-      <c r="J16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="29">
-        <v>46021</v>
-      </c>
-      <c r="B17" s="30">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="C17" t="s">
-        <v>1002</v>
-      </c>
-      <c r="D17" t="s">
-        <v>102</v>
-      </c>
-      <c r="E17">
-        <v>77</v>
-      </c>
-      <c r="F17">
-        <v>2</v>
-      </c>
-      <c r="G17">
-        <v>11</v>
-      </c>
-      <c r="H17">
-        <v>2</v>
-      </c>
-      <c r="I17">
-        <v>7</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="29">
-        <v>46021</v>
-      </c>
-      <c r="B18" s="30">
-        <v>0.5</v>
-      </c>
-      <c r="C18" t="s">
-        <v>1003</v>
-      </c>
-      <c r="D18" t="s">
-        <v>116</v>
-      </c>
-      <c r="E18">
-        <v>155</v>
-      </c>
-      <c r="F18">
-        <v>15.5</v>
-      </c>
-      <c r="G18">
-        <v>15</v>
-      </c>
-      <c r="H18">
-        <v>2</v>
-      </c>
-      <c r="I18">
-        <v>7</v>
-      </c>
-      <c r="J18">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="29">
-        <v>46021</v>
-      </c>
-      <c r="B19" s="30">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C19" t="s">
-        <v>1004</v>
-      </c>
-      <c r="D19" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19">
-        <v>290</v>
-      </c>
-      <c r="F19">
-        <v>11</v>
-      </c>
-      <c r="G19">
-        <v>18</v>
-      </c>
-      <c r="H19">
-        <v>18</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="29">
-        <v>46021</v>
-      </c>
-      <c r="B20" s="30">
-        <v>0.8125</v>
-      </c>
-      <c r="C20" t="s">
-        <v>1005</v>
-      </c>
-      <c r="D20" t="s">
-        <v>1006</v>
-      </c>
-      <c r="E20">
-        <v>800</v>
-      </c>
-      <c r="F20">
-        <v>40</v>
-      </c>
-      <c r="G20">
-        <v>100</v>
-      </c>
-      <c r="H20">
-        <v>25</v>
-      </c>
-      <c r="I20">
-        <v>5</v>
-      </c>
-      <c r="J20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="29">
-        <v>46021</v>
-      </c>
-      <c r="B21" s="30">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="C21" t="s">
-        <v>1007</v>
-      </c>
-      <c r="D21" t="s">
-        <v>365</v>
-      </c>
-      <c r="E21">
-        <v>256</v>
-      </c>
-      <c r="F21">
-        <v>13.2</v>
-      </c>
-      <c r="G21">
-        <v>19.2</v>
-      </c>
-      <c r="H21">
-        <v>10.6</v>
-      </c>
-      <c r="I21">
-        <v>10.6</v>
-      </c>
-      <c r="J21">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="29">
-        <v>46021</v>
-      </c>
-      <c r="B22" s="30">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="C22" t="s">
-        <v>1008</v>
-      </c>
-      <c r="D22" t="s">
-        <v>1009</v>
-      </c>
-      <c r="E22">
-        <v>175</v>
-      </c>
-      <c r="F22">
-        <v>15.5</v>
-      </c>
-      <c r="G22">
-        <v>20</v>
-      </c>
-      <c r="H22">
-        <v>2</v>
-      </c>
-      <c r="I22">
-        <v>11.5</v>
-      </c>
-      <c r="J22">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="29">
-        <v>46021</v>
-      </c>
-      <c r="B23" s="30">
-        <v>0.875</v>
-      </c>
-      <c r="C23" t="s">
-        <v>1010</v>
-      </c>
-      <c r="D23" t="s">
-        <v>1011</v>
-      </c>
-      <c r="E23">
-        <v>310</v>
-      </c>
-      <c r="F23">
-        <v>6</v>
-      </c>
-      <c r="G23">
-        <v>45</v>
-      </c>
-      <c r="H23">
-        <v>12</v>
-      </c>
-      <c r="I23">
-        <v>11</v>
-      </c>
-      <c r="J23">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="29">
-        <v>46022</v>
-      </c>
-      <c r="B24" s="30">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="C24" t="s">
-        <v>1012</v>
-      </c>
-      <c r="D24" t="s">
-        <v>102</v>
-      </c>
-      <c r="E24">
-        <v>77</v>
-      </c>
-      <c r="F24">
-        <v>2</v>
-      </c>
-      <c r="G24">
-        <v>11</v>
-      </c>
-      <c r="H24">
-        <v>2</v>
-      </c>
-      <c r="I24">
-        <v>7</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="29">
-        <v>46022</v>
-      </c>
-      <c r="B25" s="30">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="C25" t="s">
-        <v>1013</v>
-      </c>
-      <c r="D25" t="s">
-        <v>258</v>
-      </c>
-      <c r="E25">
-        <v>128</v>
-      </c>
-      <c r="F25">
-        <v>6.6</v>
-      </c>
-      <c r="G25">
-        <v>9.6</v>
-      </c>
-      <c r="H25">
-        <v>5.3</v>
-      </c>
-      <c r="I25">
-        <v>5.3</v>
-      </c>
-      <c r="J25">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="29">
-        <v>46022</v>
-      </c>
-      <c r="B26" s="30">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="C26" t="s">
-        <v>1014</v>
-      </c>
-      <c r="D26" t="s">
-        <v>1006</v>
-      </c>
-      <c r="E26">
-        <v>800</v>
-      </c>
-      <c r="F26">
-        <v>40</v>
-      </c>
-      <c r="G26">
-        <v>100</v>
-      </c>
-      <c r="H26">
-        <v>25</v>
-      </c>
-      <c r="I26">
-        <v>5</v>
-      </c>
-      <c r="J26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="29">
-        <v>46022</v>
-      </c>
-      <c r="B27" s="30">
-        <v>0.5</v>
-      </c>
-      <c r="C27" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D27" t="s">
-        <v>116</v>
-      </c>
-      <c r="E27">
-        <v>155</v>
-      </c>
-      <c r="F27">
-        <v>15.5</v>
-      </c>
-      <c r="G27">
-        <v>15</v>
-      </c>
-      <c r="H27">
-        <v>2</v>
-      </c>
-      <c r="I27">
-        <v>7</v>
-      </c>
-      <c r="J27">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="29">
-        <v>46022</v>
-      </c>
-      <c r="B28" s="30">
-        <v>0.6875</v>
-      </c>
-      <c r="C28" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D28" t="s">
-        <v>102</v>
-      </c>
-      <c r="E28">
-        <v>77</v>
-      </c>
-      <c r="F28">
-        <v>2</v>
-      </c>
-      <c r="G28">
-        <v>11</v>
-      </c>
-      <c r="H28">
-        <v>2</v>
-      </c>
-      <c r="I28">
-        <v>7</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="29">
-        <v>46022</v>
-      </c>
-      <c r="B29" s="30">
-        <v>0.75</v>
-      </c>
-      <c r="C29" t="s">
-        <v>1017</v>
-      </c>
-      <c r="D29" t="s">
-        <v>32</v>
-      </c>
-      <c r="E29">
-        <v>290</v>
-      </c>
-      <c r="F29">
-        <v>11</v>
-      </c>
-      <c r="G29">
-        <v>18</v>
-      </c>
-      <c r="H29">
-        <v>18</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="29">
-        <v>46022</v>
-      </c>
-      <c r="B30" s="30">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="C30" t="s">
-        <v>1018</v>
-      </c>
-      <c r="D30" t="s">
-        <v>98</v>
-      </c>
-      <c r="E30">
-        <v>380</v>
-      </c>
-      <c r="F30">
-        <v>25</v>
-      </c>
-      <c r="G30">
-        <v>46</v>
-      </c>
-      <c r="H30">
-        <v>10</v>
-      </c>
-      <c r="I30">
-        <v>2</v>
-      </c>
-      <c r="J30">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="29">
-        <v>46022</v>
-      </c>
-      <c r="B31" s="30">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C31" t="s">
-        <v>1019</v>
-      </c>
-      <c r="D31" t="s">
-        <v>139</v>
-      </c>
-      <c r="E31">
-        <v>175</v>
-      </c>
-      <c r="F31">
-        <v>15.5</v>
-      </c>
-      <c r="G31">
-        <v>20</v>
-      </c>
-      <c r="H31">
-        <v>2</v>
-      </c>
-      <c r="I31">
-        <v>11.5</v>
-      </c>
-      <c r="J31">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="29">
-        <v>46022</v>
-      </c>
-      <c r="B32" s="30">
-        <v>0.8125</v>
-      </c>
-      <c r="C32" t="s">
-        <v>1020</v>
-      </c>
-      <c r="D32" t="s">
-        <v>1021</v>
-      </c>
-      <c r="E32">
-        <v>165</v>
-      </c>
-      <c r="F32">
-        <v>5</v>
-      </c>
-      <c r="G32">
-        <v>9</v>
-      </c>
-      <c r="H32">
-        <v>13.5</v>
-      </c>
-      <c r="I32">
-        <v>1.5</v>
-      </c>
-      <c r="J32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="29">
-        <v>46023</v>
-      </c>
-      <c r="B33" s="30">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="C33" t="s">
-        <v>1022</v>
-      </c>
-      <c r="D33" t="s">
-        <v>102</v>
-      </c>
-      <c r="E33">
-        <v>77</v>
-      </c>
-      <c r="F33">
-        <v>2</v>
-      </c>
-      <c r="G33">
-        <v>11</v>
-      </c>
-      <c r="H33">
-        <v>2</v>
-      </c>
-      <c r="I33">
-        <v>7</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="29">
-        <v>46023</v>
-      </c>
-      <c r="B34" s="30">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="C34" t="s">
-        <v>1023</v>
-      </c>
-      <c r="D34" t="s">
-        <v>1021</v>
-      </c>
-      <c r="E34">
-        <v>165</v>
-      </c>
-      <c r="F34">
-        <v>5</v>
-      </c>
-      <c r="G34">
-        <v>9</v>
-      </c>
-      <c r="H34">
-        <v>13.5</v>
-      </c>
-      <c r="I34">
-        <v>1.5</v>
-      </c>
-      <c r="J34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="29">
-        <v>46023</v>
-      </c>
-      <c r="B35" s="30">
-        <v>0.375</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1024</v>
-      </c>
-      <c r="D35" t="s">
-        <v>258</v>
-      </c>
-      <c r="E35">
-        <v>128</v>
-      </c>
-      <c r="F35">
-        <v>6.6</v>
-      </c>
-      <c r="G35">
-        <v>9.6</v>
-      </c>
-      <c r="H35">
-        <v>5.3</v>
-      </c>
-      <c r="I35">
-        <v>5.3</v>
-      </c>
-      <c r="J35">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="29">
-        <v>46023</v>
-      </c>
-      <c r="B36" s="30">
-        <v>0.4375</v>
-      </c>
-      <c r="C36" t="s">
-        <v>1025</v>
-      </c>
-      <c r="D36" t="s">
-        <v>102</v>
-      </c>
-      <c r="E36">
-        <v>77</v>
-      </c>
-      <c r="F36">
-        <v>2</v>
-      </c>
-      <c r="G36">
-        <v>11</v>
-      </c>
-      <c r="H36">
-        <v>2</v>
-      </c>
-      <c r="I36">
-        <v>7</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="29">
-        <v>46023</v>
-      </c>
-      <c r="B37" s="30">
-        <v>0.5</v>
-      </c>
-      <c r="C37" t="s">
-        <v>1026</v>
-      </c>
-      <c r="D37" t="s">
-        <v>32</v>
-      </c>
-      <c r="E37">
-        <v>290</v>
-      </c>
-      <c r="F37">
-        <v>11</v>
-      </c>
-      <c r="G37">
-        <v>18</v>
-      </c>
-      <c r="H37">
-        <v>18</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="29">
-        <v>46023</v>
-      </c>
-      <c r="B38" s="30">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="C38" t="s">
-        <v>1027</v>
-      </c>
-      <c r="D38" t="s">
-        <v>258</v>
-      </c>
-      <c r="E38">
-        <v>128</v>
-      </c>
-      <c r="F38">
-        <v>6.6</v>
-      </c>
-      <c r="G38">
-        <v>9.6</v>
-      </c>
-      <c r="H38">
-        <v>5.3</v>
-      </c>
-      <c r="I38">
-        <v>5.3</v>
-      </c>
-      <c r="J38">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="29">
-        <v>46023</v>
-      </c>
-      <c r="B39" s="30">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="C39" t="s">
-        <v>1028</v>
-      </c>
-      <c r="D39" t="s">
-        <v>116</v>
-      </c>
-      <c r="E39">
-        <v>155</v>
-      </c>
-      <c r="F39">
-        <v>15.5</v>
-      </c>
-      <c r="G39">
-        <v>15</v>
-      </c>
-      <c r="H39">
-        <v>2</v>
-      </c>
-      <c r="I39">
-        <v>7</v>
-      </c>
-      <c r="J39">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="29">
-        <v>46023</v>
-      </c>
-      <c r="B40" s="30">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="C40" t="s">
-        <v>1029</v>
-      </c>
-      <c r="D40" t="s">
-        <v>808</v>
-      </c>
-      <c r="E40">
-        <v>145</v>
-      </c>
-      <c r="F40">
-        <v>5.5</v>
-      </c>
-      <c r="G40">
-        <v>9</v>
-      </c>
-      <c r="H40">
-        <v>9</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="29">
-        <v>46023</v>
-      </c>
-      <c r="B41" s="30">
-        <v>0.75</v>
-      </c>
-      <c r="C41" t="s">
-        <v>1030</v>
-      </c>
-      <c r="D41" t="s">
-        <v>932</v>
-      </c>
-      <c r="E41">
-        <v>335</v>
-      </c>
-      <c r="F41">
-        <v>21</v>
-      </c>
-      <c r="G41">
-        <v>33</v>
-      </c>
-      <c r="H41">
-        <v>13</v>
-      </c>
-      <c r="I41">
-        <v>2.5</v>
-      </c>
-      <c r="J41">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="29">
-        <v>46023</v>
-      </c>
-      <c r="B42" s="30">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="C42" t="s">
-        <v>1031</v>
-      </c>
-      <c r="D42" t="s">
-        <v>1032</v>
-      </c>
-      <c r="E42">
-        <v>155</v>
-      </c>
-      <c r="F42">
-        <v>3</v>
-      </c>
-      <c r="G42">
-        <v>22.5</v>
-      </c>
-      <c r="H42">
-        <v>6</v>
-      </c>
-      <c r="I42">
-        <v>5.5</v>
-      </c>
-      <c r="J42">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" s="29">
-        <v>46023</v>
-      </c>
-      <c r="B43" s="30">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C43" t="s">
-        <v>1033</v>
-      </c>
-      <c r="D43" t="s">
-        <v>1034</v>
-      </c>
-      <c r="E43">
-        <v>136.5</v>
-      </c>
-      <c r="F43">
-        <v>3.4</v>
-      </c>
-      <c r="G43">
-        <v>27.3</v>
-      </c>
-      <c r="H43">
-        <v>0.9</v>
-      </c>
-      <c r="I43">
-        <v>18.2</v>
-      </c>
-      <c r="J43">
-        <v>10.4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="29">
-        <v>46023</v>
-      </c>
-      <c r="B44" s="30">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="C44" t="s">
-        <v>1035</v>
-      </c>
-      <c r="D44" t="s">
-        <v>1032</v>
-      </c>
-      <c r="E44">
-        <v>155</v>
-      </c>
-      <c r="F44">
-        <v>3</v>
-      </c>
-      <c r="G44">
-        <v>22.5</v>
-      </c>
-      <c r="H44">
-        <v>6</v>
-      </c>
-      <c r="I44">
-        <v>5.5</v>
-      </c>
-      <c r="J44">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="29">
-        <v>46024</v>
-      </c>
-      <c r="B45" s="30">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="C45" t="s">
-        <v>1036</v>
-      </c>
-      <c r="D45" t="s">
-        <v>102</v>
-      </c>
-      <c r="E45">
-        <v>77</v>
-      </c>
-      <c r="F45">
-        <v>2</v>
-      </c>
-      <c r="G45">
-        <v>11</v>
-      </c>
-      <c r="H45">
-        <v>2</v>
-      </c>
-      <c r="I45">
-        <v>7</v>
-      </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" s="29">
-        <v>46024</v>
-      </c>
-      <c r="B46" s="30">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="C46" t="s">
-        <v>1037</v>
-      </c>
-      <c r="D46" t="s">
-        <v>1021</v>
-      </c>
-      <c r="E46">
-        <v>165</v>
-      </c>
-      <c r="F46">
-        <v>5</v>
-      </c>
-      <c r="G46">
-        <v>9</v>
-      </c>
-      <c r="H46">
-        <v>13.5</v>
-      </c>
-      <c r="I46">
-        <v>1.5</v>
-      </c>
-      <c r="J46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="29">
-        <v>46024</v>
-      </c>
-      <c r="B47" s="30">
-        <v>0.375</v>
-      </c>
-      <c r="C47" t="s">
-        <v>1038</v>
-      </c>
-      <c r="D47" t="s">
-        <v>258</v>
-      </c>
-      <c r="E47">
-        <v>128</v>
-      </c>
-      <c r="F47">
-        <v>6.6</v>
-      </c>
-      <c r="G47">
-        <v>9.6</v>
-      </c>
-      <c r="H47">
-        <v>5.3</v>
-      </c>
-      <c r="I47">
-        <v>5.3</v>
-      </c>
-      <c r="J47">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" s="29">
-        <v>46024</v>
-      </c>
-      <c r="B48" s="30">
-        <v>0.5625</v>
-      </c>
-      <c r="C48" t="s">
-        <v>1039</v>
-      </c>
-      <c r="D48" t="s">
-        <v>32</v>
-      </c>
-      <c r="E48">
-        <v>290</v>
-      </c>
-      <c r="F48">
-        <v>11</v>
-      </c>
-      <c r="G48">
-        <v>18</v>
-      </c>
-      <c r="H48">
-        <v>18</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" s="29">
-        <v>46024</v>
-      </c>
-      <c r="B49" s="30">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="C49" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D49" t="s">
-        <v>808</v>
-      </c>
-      <c r="E49">
-        <v>145</v>
-      </c>
-      <c r="F49">
-        <v>5.5</v>
-      </c>
-      <c r="G49">
-        <v>9</v>
-      </c>
-      <c r="H49">
-        <v>9</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="29">
-        <v>46024</v>
-      </c>
-      <c r="B50" s="30">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C50" t="s">
-        <v>1041</v>
-      </c>
-      <c r="D50" t="s">
-        <v>1042</v>
-      </c>
-      <c r="E50">
-        <v>800</v>
-      </c>
-      <c r="F50">
-        <v>40</v>
-      </c>
-      <c r="G50">
-        <v>100</v>
-      </c>
-      <c r="H50">
-        <v>25</v>
-      </c>
-      <c r="I50">
-        <v>5</v>
-      </c>
-      <c r="J50">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="29">
-        <v>46024</v>
-      </c>
-      <c r="B51" s="30">
-        <v>0.8125</v>
-      </c>
-      <c r="C51" t="s">
-        <v>1043</v>
-      </c>
-      <c r="D51" t="s">
-        <v>365</v>
-      </c>
-      <c r="E51">
-        <v>256</v>
-      </c>
-      <c r="F51">
-        <v>13.2</v>
-      </c>
-      <c r="G51">
-        <v>19.2</v>
-      </c>
-      <c r="H51">
-        <v>10.6</v>
-      </c>
-      <c r="I51">
-        <v>10.6</v>
-      </c>
-      <c r="J51">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="29">
-        <v>46025</v>
-      </c>
-      <c r="B52" s="30">
-        <v>0.375</v>
-      </c>
-      <c r="C52" t="s">
-        <v>1044</v>
-      </c>
-      <c r="D52" t="s">
-        <v>102</v>
-      </c>
-      <c r="E52">
-        <v>77</v>
-      </c>
-      <c r="F52">
-        <v>2</v>
-      </c>
-      <c r="G52">
-        <v>11</v>
-      </c>
-      <c r="H52">
-        <v>2</v>
-      </c>
-      <c r="I52">
-        <v>7</v>
-      </c>
-      <c r="J52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" s="29">
-        <v>46025</v>
-      </c>
-      <c r="B53" s="30">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="C53" t="s">
-        <v>1045</v>
-      </c>
-      <c r="D53" t="s">
-        <v>258</v>
-      </c>
-      <c r="E53">
-        <v>128</v>
-      </c>
-      <c r="F53">
-        <v>6.6</v>
-      </c>
-      <c r="G53">
-        <v>9.6</v>
-      </c>
-      <c r="H53">
-        <v>5.3</v>
-      </c>
-      <c r="I53">
-        <v>5.3</v>
-      </c>
-      <c r="J53">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" s="29">
-        <v>46025</v>
-      </c>
-      <c r="B54" s="30">
-        <v>0.5</v>
-      </c>
-      <c r="C54" t="s">
-        <v>1046</v>
-      </c>
-      <c r="D54" t="s">
-        <v>32</v>
-      </c>
-      <c r="E54">
-        <v>290</v>
-      </c>
-      <c r="F54">
-        <v>11</v>
-      </c>
-      <c r="G54">
-        <v>18</v>
-      </c>
-      <c r="H54">
-        <v>18</v>
-      </c>
-      <c r="I54">
-        <v>0</v>
-      </c>
-      <c r="J54">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="29">
-        <v>46025</v>
-      </c>
-      <c r="B55" s="30">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="C55" t="s">
-        <v>1047</v>
-      </c>
-      <c r="D55" t="s">
-        <v>98</v>
-      </c>
-      <c r="E55">
-        <v>380</v>
-      </c>
-      <c r="F55">
-        <v>25</v>
-      </c>
-      <c r="G55">
-        <v>46</v>
-      </c>
-      <c r="H55">
-        <v>10</v>
-      </c>
-      <c r="I55">
-        <v>2</v>
-      </c>
-      <c r="J55">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56" s="29">
-        <v>46025</v>
-      </c>
-      <c r="B56" s="30">
-        <v>0.5625</v>
-      </c>
-      <c r="C56" t="s">
-        <v>1048</v>
-      </c>
-      <c r="D56" t="s">
-        <v>116</v>
-      </c>
-      <c r="E56">
-        <v>155</v>
-      </c>
-      <c r="F56">
-        <v>15.5</v>
-      </c>
-      <c r="G56">
-        <v>15</v>
-      </c>
-      <c r="H56">
-        <v>2</v>
-      </c>
-      <c r="I56">
-        <v>7</v>
-      </c>
-      <c r="J56">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" s="29">
-        <v>46025</v>
-      </c>
-      <c r="B57" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="C57" t="s">
-        <v>1049</v>
-      </c>
-      <c r="D57" t="s">
-        <v>102</v>
-      </c>
-      <c r="E57">
-        <v>77</v>
-      </c>
-      <c r="F57">
-        <v>2</v>
-      </c>
-      <c r="G57">
-        <v>11</v>
-      </c>
-      <c r="H57">
-        <v>2</v>
-      </c>
-      <c r="I57">
-        <v>7</v>
-      </c>
-      <c r="J57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" s="29">
-        <v>46025</v>
-      </c>
-      <c r="B58" s="30">
-        <v>0.6875</v>
-      </c>
-      <c r="C58" t="s">
-        <v>1050</v>
-      </c>
-      <c r="D58" t="s">
-        <v>808</v>
-      </c>
-      <c r="E58">
-        <v>145</v>
-      </c>
-      <c r="F58">
-        <v>5.5</v>
-      </c>
-      <c r="G58">
-        <v>9</v>
-      </c>
-      <c r="H58">
-        <v>9</v>
-      </c>
-      <c r="I58">
-        <v>0</v>
-      </c>
-      <c r="J58">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59" s="29">
-        <v>46025</v>
-      </c>
-      <c r="B59" s="30">
-        <v>0.75</v>
-      </c>
-      <c r="C59" t="s">
-        <v>1051</v>
-      </c>
-      <c r="D59" t="s">
-        <v>932</v>
-      </c>
-      <c r="E59">
-        <v>335</v>
-      </c>
-      <c r="F59">
-        <v>21</v>
-      </c>
-      <c r="G59">
-        <v>33</v>
-      </c>
-      <c r="H59">
-        <v>13</v>
-      </c>
-      <c r="I59">
-        <v>2.5</v>
-      </c>
-      <c r="J59">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A60" s="29">
-        <v>46025</v>
-      </c>
-      <c r="B60" s="30">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="C60" t="s">
-        <v>1052</v>
-      </c>
-      <c r="D60" t="s">
-        <v>116</v>
-      </c>
-      <c r="E60">
-        <v>155</v>
-      </c>
-      <c r="F60">
-        <v>15.5</v>
-      </c>
-      <c r="G60">
-        <v>15</v>
-      </c>
-      <c r="H60">
-        <v>2</v>
-      </c>
-      <c r="I60">
-        <v>7</v>
-      </c>
-      <c r="J60">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A61" s="29">
-        <v>46025</v>
-      </c>
-      <c r="B61" s="30">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C61" t="s">
-        <v>1053</v>
-      </c>
-      <c r="D61" t="s">
-        <v>205</v>
-      </c>
-      <c r="E61">
-        <v>78.75</v>
-      </c>
-      <c r="F61">
-        <v>1.95</v>
-      </c>
-      <c r="G61">
-        <v>16.8</v>
-      </c>
-      <c r="H61">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="I61">
-        <v>11.25</v>
-      </c>
-      <c r="J61">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A62" s="29">
-        <v>46025</v>
-      </c>
-      <c r="B62" s="30">
-        <v>0.875</v>
-      </c>
-      <c r="C62" t="s">
-        <v>1054</v>
-      </c>
-      <c r="D62" t="s">
-        <v>205</v>
-      </c>
-      <c r="E62">
-        <v>78.75</v>
-      </c>
-      <c r="F62">
-        <v>1.95</v>
-      </c>
-      <c r="G62">
-        <v>16.8</v>
-      </c>
-      <c r="H62">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="I62">
-        <v>11.25</v>
-      </c>
-      <c r="J62">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A63" s="29">
-        <v>46025</v>
-      </c>
-      <c r="B63" s="30">
-        <v>0.89583333333333337</v>
-      </c>
-      <c r="C63" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D63" t="s">
-        <v>1056</v>
-      </c>
-      <c r="E63">
-        <v>165</v>
-      </c>
-      <c r="F63">
-        <v>5</v>
-      </c>
-      <c r="G63">
-        <v>9</v>
-      </c>
-      <c r="H63">
-        <v>13.5</v>
-      </c>
-      <c r="I63">
-        <v>1.5</v>
-      </c>
-      <c r="J63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A64" s="29">
-        <v>46026</v>
-      </c>
-      <c r="B64" s="30">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="C64" t="s">
-        <v>1057</v>
-      </c>
-      <c r="D64" t="s">
-        <v>102</v>
-      </c>
-      <c r="E64">
-        <v>77</v>
-      </c>
-      <c r="F64">
-        <v>2</v>
-      </c>
-      <c r="G64">
-        <v>11</v>
-      </c>
-      <c r="H64">
-        <v>2</v>
-      </c>
-      <c r="I64">
-        <v>7</v>
-      </c>
-      <c r="J64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A65" s="29">
-        <v>46026</v>
-      </c>
-      <c r="B65" s="30">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="C65" t="s">
-        <v>1058</v>
-      </c>
-      <c r="D65" t="s">
-        <v>1059</v>
-      </c>
-      <c r="E65">
-        <v>300</v>
-      </c>
-      <c r="F65">
-        <v>5</v>
-      </c>
-      <c r="G65">
-        <v>30</v>
-      </c>
-      <c r="H65">
-        <v>15</v>
-      </c>
-      <c r="I65">
-        <v>5</v>
-      </c>
-      <c r="J65">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A66" s="29">
-        <v>46026</v>
-      </c>
-      <c r="B66" s="30">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="C66" t="s">
-        <v>1060</v>
-      </c>
-      <c r="D66" t="s">
-        <v>32</v>
-      </c>
-      <c r="E66">
-        <v>290</v>
-      </c>
-      <c r="F66">
-        <v>11</v>
-      </c>
-      <c r="G66">
-        <v>18</v>
-      </c>
-      <c r="H66">
-        <v>18</v>
-      </c>
-      <c r="I66">
-        <v>0</v>
-      </c>
-      <c r="J66">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A67" s="29">
-        <v>46026</v>
-      </c>
-      <c r="B67" s="30">
-        <v>0.5625</v>
-      </c>
-      <c r="C67" t="s">
-        <v>1061</v>
-      </c>
-      <c r="D67" t="s">
-        <v>1062</v>
-      </c>
-      <c r="E67">
-        <v>335</v>
-      </c>
-      <c r="F67">
-        <v>20</v>
-      </c>
-      <c r="G67">
-        <v>40</v>
-      </c>
-      <c r="H67">
-        <v>10</v>
-      </c>
-      <c r="I67">
-        <v>2</v>
-      </c>
-      <c r="J67">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A68" s="29">
-        <v>46026</v>
-      </c>
-      <c r="B68" s="30">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="C68" t="s">
-        <v>1063</v>
-      </c>
-      <c r="D68" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E68">
-        <v>310</v>
-      </c>
-      <c r="F68">
-        <v>6</v>
-      </c>
-      <c r="G68">
-        <v>45</v>
-      </c>
-      <c r="H68">
-        <v>12</v>
-      </c>
-      <c r="I68">
-        <v>11</v>
-      </c>
-      <c r="J68">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A69" s="29">
-        <v>46026</v>
-      </c>
-      <c r="B69" s="30">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="C69" t="s">
-        <v>1065</v>
-      </c>
-      <c r="D69" t="s">
-        <v>116</v>
-      </c>
-      <c r="E69">
-        <v>155</v>
-      </c>
-      <c r="F69">
-        <v>15.5</v>
-      </c>
-      <c r="G69">
-        <v>15</v>
-      </c>
-      <c r="H69">
-        <v>2</v>
-      </c>
-      <c r="I69">
-        <v>7</v>
-      </c>
-      <c r="J69">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A70" s="29">
-        <v>46026</v>
-      </c>
-      <c r="B70" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="C70" t="s">
-        <v>1066</v>
-      </c>
-      <c r="D70" t="s">
-        <v>102</v>
-      </c>
-      <c r="E70">
-        <v>77</v>
-      </c>
-      <c r="F70">
-        <v>2</v>
-      </c>
-      <c r="G70">
-        <v>11</v>
-      </c>
-      <c r="H70">
-        <v>2</v>
-      </c>
-      <c r="I70">
-        <v>7</v>
-      </c>
-      <c r="J70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A71" s="29">
-        <v>46026</v>
-      </c>
-      <c r="B71" s="30">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="C71" t="s">
-        <v>1067</v>
-      </c>
-      <c r="D71" t="s">
-        <v>1068</v>
-      </c>
-      <c r="E71">
-        <v>567</v>
-      </c>
-      <c r="F71">
-        <v>43.3</v>
-      </c>
-      <c r="G71">
-        <v>40</v>
-      </c>
-      <c r="H71">
-        <v>23.3</v>
-      </c>
-      <c r="I71">
-        <v>3.3</v>
-      </c>
-      <c r="J71">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A72" s="29">
-        <v>46026</v>
-      </c>
-      <c r="B72" s="30">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C72" t="s">
-        <v>1069</v>
-      </c>
-      <c r="D72" t="s">
-        <v>116</v>
-      </c>
-      <c r="E72">
-        <v>155</v>
-      </c>
-      <c r="F72">
-        <v>15.5</v>
-      </c>
-      <c r="G72">
-        <v>15</v>
-      </c>
-      <c r="H72">
-        <v>2</v>
-      </c>
-      <c r="I72">
-        <v>7</v>
-      </c>
-      <c r="J72">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A73" s="29">
-        <v>46027</v>
-      </c>
-      <c r="B73" s="30">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="C73" t="s">
-        <v>1070</v>
-      </c>
-      <c r="D73" t="s">
-        <v>116</v>
-      </c>
-      <c r="E73">
-        <v>155</v>
-      </c>
-      <c r="F73">
-        <v>15.5</v>
-      </c>
-      <c r="G73">
-        <v>15</v>
-      </c>
-      <c r="H73">
-        <v>2</v>
-      </c>
-      <c r="I73">
-        <v>7</v>
-      </c>
-      <c r="J73">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A74" s="29">
-        <v>46027</v>
-      </c>
-      <c r="B74" s="30">
-        <v>0.375</v>
-      </c>
-      <c r="C74" t="s">
-        <v>1071</v>
-      </c>
-      <c r="D74" t="s">
-        <v>102</v>
-      </c>
-      <c r="E74">
-        <v>77</v>
-      </c>
-      <c r="F74">
-        <v>2</v>
-      </c>
-      <c r="G74">
-        <v>11</v>
-      </c>
-      <c r="H74">
-        <v>2</v>
-      </c>
-      <c r="I74">
-        <v>7</v>
-      </c>
-      <c r="J74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A75" s="29">
-        <v>46027</v>
-      </c>
-      <c r="B75" s="30">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="C75" t="s">
-        <v>1072</v>
-      </c>
-      <c r="D75" t="s">
-        <v>808</v>
-      </c>
-      <c r="E75">
-        <v>145</v>
-      </c>
-      <c r="F75">
-        <v>5.5</v>
-      </c>
-      <c r="G75">
-        <v>9</v>
-      </c>
-      <c r="H75">
-        <v>9</v>
-      </c>
-      <c r="I75">
-        <v>0</v>
-      </c>
-      <c r="J75">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A76" s="29">
-        <v>46027</v>
-      </c>
-      <c r="B76" s="30">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="C76" t="s">
-        <v>1073</v>
-      </c>
-      <c r="D76" t="s">
-        <v>372</v>
-      </c>
-      <c r="E76">
-        <v>89</v>
-      </c>
-      <c r="F76">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="G76">
-        <v>23</v>
-      </c>
-      <c r="H76">
-        <v>0.3</v>
-      </c>
-      <c r="I76">
-        <v>12</v>
-      </c>
-      <c r="J76">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A77" s="29">
-        <v>46027</v>
-      </c>
-      <c r="B77" s="30">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="C77" t="s">
-        <v>1074</v>
-      </c>
-      <c r="D77" t="s">
-        <v>932</v>
-      </c>
-      <c r="E77">
-        <v>335</v>
-      </c>
-      <c r="F77">
-        <v>21</v>
-      </c>
-      <c r="G77">
-        <v>33</v>
-      </c>
-      <c r="H77">
-        <v>13</v>
-      </c>
-      <c r="I77">
-        <v>2.5</v>
-      </c>
-      <c r="J77">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A78" s="29">
-        <v>46027</v>
-      </c>
-      <c r="B78" s="30">
-        <v>0.5625</v>
-      </c>
-      <c r="C78" t="s">
-        <v>1075</v>
-      </c>
-      <c r="D78" t="s">
-        <v>205</v>
-      </c>
-      <c r="E78">
-        <v>78.75</v>
-      </c>
-      <c r="F78">
-        <v>1.95</v>
-      </c>
-      <c r="G78">
-        <v>16.8</v>
-      </c>
-      <c r="H78">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="I78">
-        <v>11.25</v>
-      </c>
-      <c r="J78">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A79" s="29">
-        <v>46027</v>
-      </c>
-      <c r="B79" s="30">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="C79" t="s">
-        <v>1076</v>
-      </c>
-      <c r="D79" t="s">
-        <v>1021</v>
-      </c>
-      <c r="E79">
-        <v>165</v>
-      </c>
-      <c r="F79">
-        <v>5</v>
-      </c>
-      <c r="G79">
-        <v>9</v>
-      </c>
-      <c r="H79">
-        <v>13.5</v>
-      </c>
-      <c r="I79">
-        <v>1.5</v>
-      </c>
-      <c r="J79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A80" s="29">
-        <v>46027</v>
-      </c>
-      <c r="B80" s="30">
-        <v>0.625</v>
-      </c>
-      <c r="C80" t="s">
-        <v>1077</v>
-      </c>
-      <c r="D80" t="s">
-        <v>808</v>
-      </c>
-      <c r="E80">
-        <v>145</v>
-      </c>
-      <c r="F80">
-        <v>5.5</v>
-      </c>
-      <c r="G80">
-        <v>9</v>
-      </c>
-      <c r="H80">
-        <v>9</v>
-      </c>
-      <c r="I80">
-        <v>0</v>
-      </c>
-      <c r="J80">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A81" s="29">
-        <v>46027</v>
-      </c>
-      <c r="B81" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="C81" t="s">
-        <v>1078</v>
-      </c>
-      <c r="D81" t="s">
-        <v>116</v>
-      </c>
-      <c r="E81">
-        <v>155</v>
-      </c>
-      <c r="F81">
-        <v>15.5</v>
-      </c>
-      <c r="G81">
-        <v>15</v>
-      </c>
-      <c r="H81">
-        <v>2</v>
-      </c>
-      <c r="I81">
-        <v>7</v>
-      </c>
-      <c r="J81">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A82" s="29">
-        <v>46027</v>
-      </c>
-      <c r="B82" s="30">
-        <v>0.6875</v>
-      </c>
-      <c r="C82" t="s">
-        <v>1079</v>
-      </c>
-      <c r="D82" t="s">
-        <v>258</v>
-      </c>
-      <c r="E82">
-        <v>128</v>
-      </c>
-      <c r="F82">
-        <v>6.6</v>
-      </c>
-      <c r="G82">
-        <v>9.6</v>
-      </c>
-      <c r="H82">
-        <v>5.3</v>
-      </c>
-      <c r="I82">
-        <v>5.3</v>
-      </c>
-      <c r="J82">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A83" s="29">
-        <v>46027</v>
-      </c>
-      <c r="B83" s="30">
-        <v>0.75</v>
-      </c>
-      <c r="C83" t="s">
-        <v>1080</v>
-      </c>
-      <c r="D83" t="s">
-        <v>1081</v>
-      </c>
-      <c r="E83">
-        <v>440</v>
-      </c>
-      <c r="F83">
-        <v>22</v>
-      </c>
-      <c r="G83">
-        <v>50</v>
-      </c>
-      <c r="H83">
-        <v>16</v>
-      </c>
-      <c r="I83">
-        <v>3</v>
-      </c>
-      <c r="J83">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A84" s="29">
-        <v>46027</v>
-      </c>
-      <c r="B84" s="30">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="C84" t="s">
-        <v>1082</v>
-      </c>
-      <c r="D84" t="s">
-        <v>1083</v>
-      </c>
-      <c r="E84">
-        <v>240</v>
-      </c>
-      <c r="F84">
-        <v>16</v>
-      </c>
-      <c r="G84">
-        <v>20</v>
-      </c>
-      <c r="H84">
-        <v>12</v>
-      </c>
-      <c r="I84">
-        <v>20</v>
-      </c>
-      <c r="J84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A85" s="29">
-        <v>46028</v>
-      </c>
-      <c r="B85" s="30">
-        <v>0.375</v>
-      </c>
-      <c r="C85" t="s">
-        <v>1084</v>
-      </c>
-      <c r="D85" t="s">
-        <v>1085</v>
-      </c>
-      <c r="E85">
-        <v>450</v>
-      </c>
-      <c r="F85">
-        <v>12</v>
-      </c>
-      <c r="G85">
-        <v>48.5</v>
-      </c>
-      <c r="H85">
-        <v>27.8</v>
-      </c>
-      <c r="I85">
-        <v>3.9</v>
-      </c>
-      <c r="J85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A86" s="29">
-        <v>46028</v>
-      </c>
-      <c r="B86" s="30">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="C86" t="s">
-        <v>1086</v>
-      </c>
-      <c r="D86" t="s">
-        <v>27</v>
-      </c>
-      <c r="E86">
-        <v>210</v>
-      </c>
-      <c r="F86">
-        <v>5.2</v>
-      </c>
-      <c r="G86">
-        <v>42</v>
-      </c>
-      <c r="H86">
-        <v>1.4</v>
-      </c>
-      <c r="I86">
-        <v>28</v>
-      </c>
-      <c r="J86">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A87" s="29">
-        <v>46028</v>
-      </c>
-      <c r="B87" s="30">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="C87" t="s">
-        <v>1087</v>
-      </c>
-      <c r="D87" t="s">
-        <v>365</v>
-      </c>
-      <c r="E87">
-        <v>256</v>
-      </c>
-      <c r="F87">
-        <v>13.2</v>
-      </c>
-      <c r="G87">
-        <v>19.2</v>
-      </c>
-      <c r="H87">
-        <v>10.6</v>
-      </c>
-      <c r="I87">
-        <v>10.6</v>
-      </c>
-      <c r="J87">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A88" s="29">
-        <v>46028</v>
-      </c>
-      <c r="B88" s="30">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="C88" t="s">
-        <v>1088</v>
-      </c>
-      <c r="D88" t="s">
-        <v>932</v>
-      </c>
-      <c r="E88">
-        <v>335</v>
-      </c>
-      <c r="F88">
-        <v>21</v>
-      </c>
-      <c r="G88">
-        <v>33</v>
-      </c>
-      <c r="H88">
-        <v>13</v>
-      </c>
-      <c r="I88">
-        <v>2.5</v>
-      </c>
-      <c r="J88">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A89" s="29">
-        <v>46028</v>
-      </c>
-      <c r="B89" s="30">
-        <v>0.5625</v>
-      </c>
-      <c r="C89" t="s">
-        <v>1089</v>
-      </c>
-      <c r="D89" t="s">
-        <v>1021</v>
-      </c>
-      <c r="E89">
-        <v>165</v>
-      </c>
-      <c r="F89">
-        <v>5</v>
-      </c>
-      <c r="G89">
-        <v>9</v>
-      </c>
-      <c r="H89">
-        <v>13.5</v>
-      </c>
-      <c r="I89">
-        <v>1.5</v>
-      </c>
-      <c r="J89">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A90" s="29">
-        <v>46028</v>
-      </c>
-      <c r="B90" s="30">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="C90" t="s">
-        <v>1090</v>
-      </c>
-      <c r="D90" t="s">
-        <v>1091</v>
-      </c>
-      <c r="E90">
-        <v>263.3</v>
-      </c>
-      <c r="F90">
-        <v>2.8</v>
-      </c>
-      <c r="G90">
-        <v>30.5</v>
-      </c>
-      <c r="H90">
-        <v>14.7</v>
-      </c>
-      <c r="I90">
-        <v>3</v>
-      </c>
-      <c r="J90">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A91" s="29">
-        <v>46028</v>
-      </c>
-      <c r="B91" s="30">
-        <v>0.75</v>
-      </c>
-      <c r="C91" t="s">
-        <v>1092</v>
-      </c>
-      <c r="D91" t="s">
-        <v>372</v>
-      </c>
-      <c r="E91">
-        <v>89</v>
-      </c>
-      <c r="F91">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="G91">
-        <v>23</v>
-      </c>
-      <c r="H91">
-        <v>0.3</v>
-      </c>
-      <c r="I91">
-        <v>12</v>
-      </c>
-      <c r="J91">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A92" s="29">
-        <v>46028</v>
-      </c>
-      <c r="B92" s="30">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="C92" t="s">
-        <v>1093</v>
-      </c>
-      <c r="D92" t="s">
-        <v>102</v>
-      </c>
-      <c r="E92">
-        <v>77</v>
-      </c>
-      <c r="F92">
-        <v>2</v>
-      </c>
-      <c r="G92">
-        <v>11</v>
-      </c>
-      <c r="H92">
-        <v>2</v>
-      </c>
-      <c r="I92">
-        <v>7</v>
-      </c>
-      <c r="J92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A93" s="29">
-        <v>46028</v>
-      </c>
-      <c r="B93" s="30">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C93" t="s">
-        <v>1094</v>
-      </c>
-      <c r="D93" t="s">
-        <v>1095</v>
-      </c>
-      <c r="E93">
-        <v>300</v>
-      </c>
-      <c r="F93">
-        <v>25</v>
-      </c>
-      <c r="G93">
-        <v>20</v>
-      </c>
-      <c r="H93">
-        <v>15</v>
-      </c>
-      <c r="I93">
-        <v>3</v>
-      </c>
-      <c r="J93">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A94" s="29">
-        <v>46028</v>
-      </c>
-      <c r="B94" s="30">
-        <v>0.8125</v>
-      </c>
-      <c r="C94" t="s">
-        <v>1096</v>
-      </c>
-      <c r="D94" t="s">
-        <v>1021</v>
-      </c>
-      <c r="E94">
-        <v>165</v>
-      </c>
-      <c r="F94">
-        <v>5</v>
-      </c>
-      <c r="G94">
-        <v>9</v>
-      </c>
-      <c r="H94">
-        <v>13.5</v>
-      </c>
-      <c r="I94">
-        <v>1.5</v>
-      </c>
-      <c r="J94">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A95" s="29">
-        <v>46028</v>
-      </c>
-      <c r="B95" s="30">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="C95" t="s">
-        <v>1097</v>
-      </c>
-      <c r="D95" t="s">
-        <v>1091</v>
-      </c>
-      <c r="E95">
-        <v>263.3</v>
-      </c>
-      <c r="F95">
-        <v>2.8</v>
-      </c>
-      <c r="G95">
-        <v>30.5</v>
-      </c>
-      <c r="H95">
-        <v>14.7</v>
-      </c>
-      <c r="I95">
-        <v>3</v>
-      </c>
-      <c r="J95">
-        <v>1.3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC2BD037-7A04-4BEA-B100-A47D0614F32C}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -32492,6 +29623,2613 @@
         <v>14</v>
       </c>
       <c r="H3" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB0140AB-465A-4E35-8F6E-65CE935EFC2A}">
+  <dimension ref="A1:J111"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" t="s">
+        <v>6</v>
+      </c>
+      <c r="H32" t="s">
+        <v>7</v>
+      </c>
+      <c r="I32" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="29">
+        <v>46021</v>
+      </c>
+      <c r="B33" s="30">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D33" t="s">
+        <v>102</v>
+      </c>
+      <c r="E33">
+        <v>77</v>
+      </c>
+      <c r="F33">
+        <v>2</v>
+      </c>
+      <c r="G33">
+        <v>11</v>
+      </c>
+      <c r="H33">
+        <v>2</v>
+      </c>
+      <c r="I33">
+        <v>7</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" s="29">
+        <v>46021</v>
+      </c>
+      <c r="B34" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D34" t="s">
+        <v>116</v>
+      </c>
+      <c r="E34">
+        <v>155</v>
+      </c>
+      <c r="F34">
+        <v>15.5</v>
+      </c>
+      <c r="G34">
+        <v>15</v>
+      </c>
+      <c r="H34">
+        <v>2</v>
+      </c>
+      <c r="I34">
+        <v>7</v>
+      </c>
+      <c r="J34">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" s="29">
+        <v>46021</v>
+      </c>
+      <c r="B35" s="30">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D35" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35">
+        <v>290</v>
+      </c>
+      <c r="F35">
+        <v>11</v>
+      </c>
+      <c r="G35">
+        <v>18</v>
+      </c>
+      <c r="H35">
+        <v>18</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="29">
+        <v>46021</v>
+      </c>
+      <c r="B36" s="30">
+        <v>0.8125</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E36">
+        <v>800</v>
+      </c>
+      <c r="F36">
+        <v>40</v>
+      </c>
+      <c r="G36">
+        <v>100</v>
+      </c>
+      <c r="H36">
+        <v>25</v>
+      </c>
+      <c r="I36">
+        <v>5</v>
+      </c>
+      <c r="J36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" s="29">
+        <v>46021</v>
+      </c>
+      <c r="B37" s="30">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D37" t="s">
+        <v>365</v>
+      </c>
+      <c r="E37">
+        <v>256</v>
+      </c>
+      <c r="F37">
+        <v>13.2</v>
+      </c>
+      <c r="G37">
+        <v>19.2</v>
+      </c>
+      <c r="H37">
+        <v>10.6</v>
+      </c>
+      <c r="I37">
+        <v>10.6</v>
+      </c>
+      <c r="J37">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="29">
+        <v>46021</v>
+      </c>
+      <c r="B38" s="30">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D38" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E38">
+        <v>175</v>
+      </c>
+      <c r="F38">
+        <v>15.5</v>
+      </c>
+      <c r="G38">
+        <v>20</v>
+      </c>
+      <c r="H38">
+        <v>2</v>
+      </c>
+      <c r="I38">
+        <v>11.5</v>
+      </c>
+      <c r="J38">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" s="29">
+        <v>46021</v>
+      </c>
+      <c r="B39" s="30">
+        <v>0.875</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E39">
+        <v>310</v>
+      </c>
+      <c r="F39">
+        <v>6</v>
+      </c>
+      <c r="G39">
+        <v>45</v>
+      </c>
+      <c r="H39">
+        <v>12</v>
+      </c>
+      <c r="I39">
+        <v>11</v>
+      </c>
+      <c r="J39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" s="29">
+        <v>46022</v>
+      </c>
+      <c r="B40" s="30">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D40" t="s">
+        <v>102</v>
+      </c>
+      <c r="E40">
+        <v>77</v>
+      </c>
+      <c r="F40">
+        <v>2</v>
+      </c>
+      <c r="G40">
+        <v>11</v>
+      </c>
+      <c r="H40">
+        <v>2</v>
+      </c>
+      <c r="I40">
+        <v>7</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" s="29">
+        <v>46022</v>
+      </c>
+      <c r="B41" s="30">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D41" t="s">
+        <v>258</v>
+      </c>
+      <c r="E41">
+        <v>128</v>
+      </c>
+      <c r="F41">
+        <v>6.6</v>
+      </c>
+      <c r="G41">
+        <v>9.6</v>
+      </c>
+      <c r="H41">
+        <v>5.3</v>
+      </c>
+      <c r="I41">
+        <v>5.3</v>
+      </c>
+      <c r="J41">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" s="29">
+        <v>46022</v>
+      </c>
+      <c r="B42" s="30">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D42" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E42">
+        <v>800</v>
+      </c>
+      <c r="F42">
+        <v>40</v>
+      </c>
+      <c r="G42">
+        <v>100</v>
+      </c>
+      <c r="H42">
+        <v>25</v>
+      </c>
+      <c r="I42">
+        <v>5</v>
+      </c>
+      <c r="J42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" s="29">
+        <v>46022</v>
+      </c>
+      <c r="B43" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D43" t="s">
+        <v>116</v>
+      </c>
+      <c r="E43">
+        <v>155</v>
+      </c>
+      <c r="F43">
+        <v>15.5</v>
+      </c>
+      <c r="G43">
+        <v>15</v>
+      </c>
+      <c r="H43">
+        <v>2</v>
+      </c>
+      <c r="I43">
+        <v>7</v>
+      </c>
+      <c r="J43">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" s="29">
+        <v>46022</v>
+      </c>
+      <c r="B44" s="30">
+        <v>0.6875</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D44" t="s">
+        <v>102</v>
+      </c>
+      <c r="E44">
+        <v>77</v>
+      </c>
+      <c r="F44">
+        <v>2</v>
+      </c>
+      <c r="G44">
+        <v>11</v>
+      </c>
+      <c r="H44">
+        <v>2</v>
+      </c>
+      <c r="I44">
+        <v>7</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" s="29">
+        <v>46022</v>
+      </c>
+      <c r="B45" s="30">
+        <v>0.75</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D45" t="s">
+        <v>32</v>
+      </c>
+      <c r="E45">
+        <v>290</v>
+      </c>
+      <c r="F45">
+        <v>11</v>
+      </c>
+      <c r="G45">
+        <v>18</v>
+      </c>
+      <c r="H45">
+        <v>18</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" s="29">
+        <v>46022</v>
+      </c>
+      <c r="B46" s="30">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D46" t="s">
+        <v>98</v>
+      </c>
+      <c r="E46">
+        <v>380</v>
+      </c>
+      <c r="F46">
+        <v>25</v>
+      </c>
+      <c r="G46">
+        <v>46</v>
+      </c>
+      <c r="H46">
+        <v>10</v>
+      </c>
+      <c r="I46">
+        <v>2</v>
+      </c>
+      <c r="J46">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" s="29">
+        <v>46022</v>
+      </c>
+      <c r="B47" s="30">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D47" t="s">
+        <v>139</v>
+      </c>
+      <c r="E47">
+        <v>175</v>
+      </c>
+      <c r="F47">
+        <v>15.5</v>
+      </c>
+      <c r="G47">
+        <v>20</v>
+      </c>
+      <c r="H47">
+        <v>2</v>
+      </c>
+      <c r="I47">
+        <v>11.5</v>
+      </c>
+      <c r="J47">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" s="29">
+        <v>46022</v>
+      </c>
+      <c r="B48" s="30">
+        <v>0.8125</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D48" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E48">
+        <v>165</v>
+      </c>
+      <c r="F48">
+        <v>5</v>
+      </c>
+      <c r="G48">
+        <v>9</v>
+      </c>
+      <c r="H48">
+        <v>13.5</v>
+      </c>
+      <c r="I48">
+        <v>1.5</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" s="29">
+        <v>46023</v>
+      </c>
+      <c r="B49" s="30">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C49" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D49" t="s">
+        <v>102</v>
+      </c>
+      <c r="E49">
+        <v>77</v>
+      </c>
+      <c r="F49">
+        <v>2</v>
+      </c>
+      <c r="G49">
+        <v>11</v>
+      </c>
+      <c r="H49">
+        <v>2</v>
+      </c>
+      <c r="I49">
+        <v>7</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" s="29">
+        <v>46023</v>
+      </c>
+      <c r="B50" s="30">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D50" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E50">
+        <v>165</v>
+      </c>
+      <c r="F50">
+        <v>5</v>
+      </c>
+      <c r="G50">
+        <v>9</v>
+      </c>
+      <c r="H50">
+        <v>13.5</v>
+      </c>
+      <c r="I50">
+        <v>1.5</v>
+      </c>
+      <c r="J50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" s="29">
+        <v>46023</v>
+      </c>
+      <c r="B51" s="30">
+        <v>0.375</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D51" t="s">
+        <v>258</v>
+      </c>
+      <c r="E51">
+        <v>128</v>
+      </c>
+      <c r="F51">
+        <v>6.6</v>
+      </c>
+      <c r="G51">
+        <v>9.6</v>
+      </c>
+      <c r="H51">
+        <v>5.3</v>
+      </c>
+      <c r="I51">
+        <v>5.3</v>
+      </c>
+      <c r="J51">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" s="29">
+        <v>46023</v>
+      </c>
+      <c r="B52" s="30">
+        <v>0.4375</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D52" t="s">
+        <v>102</v>
+      </c>
+      <c r="E52">
+        <v>77</v>
+      </c>
+      <c r="F52">
+        <v>2</v>
+      </c>
+      <c r="G52">
+        <v>11</v>
+      </c>
+      <c r="H52">
+        <v>2</v>
+      </c>
+      <c r="I52">
+        <v>7</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53" s="29">
+        <v>46023</v>
+      </c>
+      <c r="B53" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D53" t="s">
+        <v>32</v>
+      </c>
+      <c r="E53">
+        <v>290</v>
+      </c>
+      <c r="F53">
+        <v>11</v>
+      </c>
+      <c r="G53">
+        <v>18</v>
+      </c>
+      <c r="H53">
+        <v>18</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" s="29">
+        <v>46023</v>
+      </c>
+      <c r="B54" s="30">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D54" t="s">
+        <v>258</v>
+      </c>
+      <c r="E54">
+        <v>128</v>
+      </c>
+      <c r="F54">
+        <v>6.6</v>
+      </c>
+      <c r="G54">
+        <v>9.6</v>
+      </c>
+      <c r="H54">
+        <v>5.3</v>
+      </c>
+      <c r="I54">
+        <v>5.3</v>
+      </c>
+      <c r="J54">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" s="29">
+        <v>46023</v>
+      </c>
+      <c r="B55" s="30">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D55" t="s">
+        <v>116</v>
+      </c>
+      <c r="E55">
+        <v>155</v>
+      </c>
+      <c r="F55">
+        <v>15.5</v>
+      </c>
+      <c r="G55">
+        <v>15</v>
+      </c>
+      <c r="H55">
+        <v>2</v>
+      </c>
+      <c r="I55">
+        <v>7</v>
+      </c>
+      <c r="J55">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" s="29">
+        <v>46023</v>
+      </c>
+      <c r="B56" s="30">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D56" t="s">
+        <v>808</v>
+      </c>
+      <c r="E56">
+        <v>145</v>
+      </c>
+      <c r="F56">
+        <v>5.5</v>
+      </c>
+      <c r="G56">
+        <v>9</v>
+      </c>
+      <c r="H56">
+        <v>9</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" s="29">
+        <v>46023</v>
+      </c>
+      <c r="B57" s="30">
+        <v>0.75</v>
+      </c>
+      <c r="C57" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D57" t="s">
+        <v>932</v>
+      </c>
+      <c r="E57">
+        <v>335</v>
+      </c>
+      <c r="F57">
+        <v>21</v>
+      </c>
+      <c r="G57">
+        <v>33</v>
+      </c>
+      <c r="H57">
+        <v>13</v>
+      </c>
+      <c r="I57">
+        <v>2.5</v>
+      </c>
+      <c r="J57">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" s="29">
+        <v>46023</v>
+      </c>
+      <c r="B58" s="30">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D58" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E58">
+        <v>155</v>
+      </c>
+      <c r="F58">
+        <v>3</v>
+      </c>
+      <c r="G58">
+        <v>22.5</v>
+      </c>
+      <c r="H58">
+        <v>6</v>
+      </c>
+      <c r="I58">
+        <v>5.5</v>
+      </c>
+      <c r="J58">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" s="29">
+        <v>46023</v>
+      </c>
+      <c r="B59" s="30">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D59" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E59">
+        <v>136.5</v>
+      </c>
+      <c r="F59">
+        <v>3.4</v>
+      </c>
+      <c r="G59">
+        <v>27.3</v>
+      </c>
+      <c r="H59">
+        <v>0.9</v>
+      </c>
+      <c r="I59">
+        <v>18.2</v>
+      </c>
+      <c r="J59">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" s="29">
+        <v>46023</v>
+      </c>
+      <c r="B60" s="30">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D60" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E60">
+        <v>155</v>
+      </c>
+      <c r="F60">
+        <v>3</v>
+      </c>
+      <c r="G60">
+        <v>22.5</v>
+      </c>
+      <c r="H60">
+        <v>6</v>
+      </c>
+      <c r="I60">
+        <v>5.5</v>
+      </c>
+      <c r="J60">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61" s="29">
+        <v>46024</v>
+      </c>
+      <c r="B61" s="30">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C61" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D61" t="s">
+        <v>102</v>
+      </c>
+      <c r="E61">
+        <v>77</v>
+      </c>
+      <c r="F61">
+        <v>2</v>
+      </c>
+      <c r="G61">
+        <v>11</v>
+      </c>
+      <c r="H61">
+        <v>2</v>
+      </c>
+      <c r="I61">
+        <v>7</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62" s="29">
+        <v>46024</v>
+      </c>
+      <c r="B62" s="30">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D62" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E62">
+        <v>165</v>
+      </c>
+      <c r="F62">
+        <v>5</v>
+      </c>
+      <c r="G62">
+        <v>9</v>
+      </c>
+      <c r="H62">
+        <v>13.5</v>
+      </c>
+      <c r="I62">
+        <v>1.5</v>
+      </c>
+      <c r="J62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63" s="29">
+        <v>46024</v>
+      </c>
+      <c r="B63" s="30">
+        <v>0.375</v>
+      </c>
+      <c r="C63" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D63" t="s">
+        <v>258</v>
+      </c>
+      <c r="E63">
+        <v>128</v>
+      </c>
+      <c r="F63">
+        <v>6.6</v>
+      </c>
+      <c r="G63">
+        <v>9.6</v>
+      </c>
+      <c r="H63">
+        <v>5.3</v>
+      </c>
+      <c r="I63">
+        <v>5.3</v>
+      </c>
+      <c r="J63">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A64" s="29">
+        <v>46024</v>
+      </c>
+      <c r="B64" s="30">
+        <v>0.5625</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D64" t="s">
+        <v>32</v>
+      </c>
+      <c r="E64">
+        <v>290</v>
+      </c>
+      <c r="F64">
+        <v>11</v>
+      </c>
+      <c r="G64">
+        <v>18</v>
+      </c>
+      <c r="H64">
+        <v>18</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A65" s="29">
+        <v>46024</v>
+      </c>
+      <c r="B65" s="30">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D65" t="s">
+        <v>808</v>
+      </c>
+      <c r="E65">
+        <v>145</v>
+      </c>
+      <c r="F65">
+        <v>5.5</v>
+      </c>
+      <c r="G65">
+        <v>9</v>
+      </c>
+      <c r="H65">
+        <v>9</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A66" s="29">
+        <v>46024</v>
+      </c>
+      <c r="B66" s="30">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D66" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E66">
+        <v>800</v>
+      </c>
+      <c r="F66">
+        <v>40</v>
+      </c>
+      <c r="G66">
+        <v>100</v>
+      </c>
+      <c r="H66">
+        <v>25</v>
+      </c>
+      <c r="I66">
+        <v>5</v>
+      </c>
+      <c r="J66">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A67" s="29">
+        <v>46024</v>
+      </c>
+      <c r="B67" s="30">
+        <v>0.8125</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D67" t="s">
+        <v>365</v>
+      </c>
+      <c r="E67">
+        <v>256</v>
+      </c>
+      <c r="F67">
+        <v>13.2</v>
+      </c>
+      <c r="G67">
+        <v>19.2</v>
+      </c>
+      <c r="H67">
+        <v>10.6</v>
+      </c>
+      <c r="I67">
+        <v>10.6</v>
+      </c>
+      <c r="J67">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A68" s="29">
+        <v>46025</v>
+      </c>
+      <c r="B68" s="30">
+        <v>0.375</v>
+      </c>
+      <c r="C68" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D68" t="s">
+        <v>102</v>
+      </c>
+      <c r="E68">
+        <v>77</v>
+      </c>
+      <c r="F68">
+        <v>2</v>
+      </c>
+      <c r="G68">
+        <v>11</v>
+      </c>
+      <c r="H68">
+        <v>2</v>
+      </c>
+      <c r="I68">
+        <v>7</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A69" s="29">
+        <v>46025</v>
+      </c>
+      <c r="B69" s="30">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D69" t="s">
+        <v>258</v>
+      </c>
+      <c r="E69">
+        <v>128</v>
+      </c>
+      <c r="F69">
+        <v>6.6</v>
+      </c>
+      <c r="G69">
+        <v>9.6</v>
+      </c>
+      <c r="H69">
+        <v>5.3</v>
+      </c>
+      <c r="I69">
+        <v>5.3</v>
+      </c>
+      <c r="J69">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A70" s="29">
+        <v>46025</v>
+      </c>
+      <c r="B70" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="C70" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D70" t="s">
+        <v>32</v>
+      </c>
+      <c r="E70">
+        <v>290</v>
+      </c>
+      <c r="F70">
+        <v>11</v>
+      </c>
+      <c r="G70">
+        <v>18</v>
+      </c>
+      <c r="H70">
+        <v>18</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A71" s="29">
+        <v>46025</v>
+      </c>
+      <c r="B71" s="30">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D71" t="s">
+        <v>98</v>
+      </c>
+      <c r="E71">
+        <v>380</v>
+      </c>
+      <c r="F71">
+        <v>25</v>
+      </c>
+      <c r="G71">
+        <v>46</v>
+      </c>
+      <c r="H71">
+        <v>10</v>
+      </c>
+      <c r="I71">
+        <v>2</v>
+      </c>
+      <c r="J71">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A72" s="29">
+        <v>46025</v>
+      </c>
+      <c r="B72" s="30">
+        <v>0.5625</v>
+      </c>
+      <c r="C72" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D72" t="s">
+        <v>116</v>
+      </c>
+      <c r="E72">
+        <v>155</v>
+      </c>
+      <c r="F72">
+        <v>15.5</v>
+      </c>
+      <c r="G72">
+        <v>15</v>
+      </c>
+      <c r="H72">
+        <v>2</v>
+      </c>
+      <c r="I72">
+        <v>7</v>
+      </c>
+      <c r="J72">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A73" s="29">
+        <v>46025</v>
+      </c>
+      <c r="B73" s="30">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D73" t="s">
+        <v>102</v>
+      </c>
+      <c r="E73">
+        <v>77</v>
+      </c>
+      <c r="F73">
+        <v>2</v>
+      </c>
+      <c r="G73">
+        <v>11</v>
+      </c>
+      <c r="H73">
+        <v>2</v>
+      </c>
+      <c r="I73">
+        <v>7</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74" s="29">
+        <v>46025</v>
+      </c>
+      <c r="B74" s="30">
+        <v>0.6875</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D74" t="s">
+        <v>808</v>
+      </c>
+      <c r="E74">
+        <v>145</v>
+      </c>
+      <c r="F74">
+        <v>5.5</v>
+      </c>
+      <c r="G74">
+        <v>9</v>
+      </c>
+      <c r="H74">
+        <v>9</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A75" s="29">
+        <v>46025</v>
+      </c>
+      <c r="B75" s="30">
+        <v>0.75</v>
+      </c>
+      <c r="C75" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D75" t="s">
+        <v>932</v>
+      </c>
+      <c r="E75">
+        <v>335</v>
+      </c>
+      <c r="F75">
+        <v>21</v>
+      </c>
+      <c r="G75">
+        <v>33</v>
+      </c>
+      <c r="H75">
+        <v>13</v>
+      </c>
+      <c r="I75">
+        <v>2.5</v>
+      </c>
+      <c r="J75">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A76" s="29">
+        <v>46025</v>
+      </c>
+      <c r="B76" s="30">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D76" t="s">
+        <v>116</v>
+      </c>
+      <c r="E76">
+        <v>155</v>
+      </c>
+      <c r="F76">
+        <v>15.5</v>
+      </c>
+      <c r="G76">
+        <v>15</v>
+      </c>
+      <c r="H76">
+        <v>2</v>
+      </c>
+      <c r="I76">
+        <v>7</v>
+      </c>
+      <c r="J76">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A77" s="29">
+        <v>46025</v>
+      </c>
+      <c r="B77" s="30">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C77" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D77" t="s">
+        <v>205</v>
+      </c>
+      <c r="E77">
+        <v>78.75</v>
+      </c>
+      <c r="F77">
+        <v>1.95</v>
+      </c>
+      <c r="G77">
+        <v>16.8</v>
+      </c>
+      <c r="H77">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I77">
+        <v>11.25</v>
+      </c>
+      <c r="J77">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78" s="29">
+        <v>46025</v>
+      </c>
+      <c r="B78" s="30">
+        <v>0.875</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D78" t="s">
+        <v>205</v>
+      </c>
+      <c r="E78">
+        <v>78.75</v>
+      </c>
+      <c r="F78">
+        <v>1.95</v>
+      </c>
+      <c r="G78">
+        <v>16.8</v>
+      </c>
+      <c r="H78">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I78">
+        <v>11.25</v>
+      </c>
+      <c r="J78">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79" s="29">
+        <v>46025</v>
+      </c>
+      <c r="B79" s="30">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D79" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E79">
+        <v>165</v>
+      </c>
+      <c r="F79">
+        <v>5</v>
+      </c>
+      <c r="G79">
+        <v>9</v>
+      </c>
+      <c r="H79">
+        <v>13.5</v>
+      </c>
+      <c r="I79">
+        <v>1.5</v>
+      </c>
+      <c r="J79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A80" s="29">
+        <v>46026</v>
+      </c>
+      <c r="B80" s="30">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D80" t="s">
+        <v>102</v>
+      </c>
+      <c r="E80">
+        <v>77</v>
+      </c>
+      <c r="F80">
+        <v>2</v>
+      </c>
+      <c r="G80">
+        <v>11</v>
+      </c>
+      <c r="H80">
+        <v>2</v>
+      </c>
+      <c r="I80">
+        <v>7</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A81" s="29">
+        <v>46026</v>
+      </c>
+      <c r="B81" s="30">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D81" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E81">
+        <v>300</v>
+      </c>
+      <c r="F81">
+        <v>5</v>
+      </c>
+      <c r="G81">
+        <v>30</v>
+      </c>
+      <c r="H81">
+        <v>15</v>
+      </c>
+      <c r="I81">
+        <v>5</v>
+      </c>
+      <c r="J81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A82" s="29">
+        <v>46026</v>
+      </c>
+      <c r="B82" s="30">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C82" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D82" t="s">
+        <v>32</v>
+      </c>
+      <c r="E82">
+        <v>290</v>
+      </c>
+      <c r="F82">
+        <v>11</v>
+      </c>
+      <c r="G82">
+        <v>18</v>
+      </c>
+      <c r="H82">
+        <v>18</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A83" s="29">
+        <v>46026</v>
+      </c>
+      <c r="B83" s="30">
+        <v>0.5625</v>
+      </c>
+      <c r="C83" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D83" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E83">
+        <v>335</v>
+      </c>
+      <c r="F83">
+        <v>20</v>
+      </c>
+      <c r="G83">
+        <v>40</v>
+      </c>
+      <c r="H83">
+        <v>10</v>
+      </c>
+      <c r="I83">
+        <v>2</v>
+      </c>
+      <c r="J83">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A84" s="29">
+        <v>46026</v>
+      </c>
+      <c r="B84" s="30">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C84" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D84" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E84">
+        <v>310</v>
+      </c>
+      <c r="F84">
+        <v>6</v>
+      </c>
+      <c r="G84">
+        <v>45</v>
+      </c>
+      <c r="H84">
+        <v>12</v>
+      </c>
+      <c r="I84">
+        <v>11</v>
+      </c>
+      <c r="J84">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A85" s="29">
+        <v>46026</v>
+      </c>
+      <c r="B85" s="30">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C85" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D85" t="s">
+        <v>116</v>
+      </c>
+      <c r="E85">
+        <v>155</v>
+      </c>
+      <c r="F85">
+        <v>15.5</v>
+      </c>
+      <c r="G85">
+        <v>15</v>
+      </c>
+      <c r="H85">
+        <v>2</v>
+      </c>
+      <c r="I85">
+        <v>7</v>
+      </c>
+      <c r="J85">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A86" s="29">
+        <v>46026</v>
+      </c>
+      <c r="B86" s="30">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D86" t="s">
+        <v>102</v>
+      </c>
+      <c r="E86">
+        <v>77</v>
+      </c>
+      <c r="F86">
+        <v>2</v>
+      </c>
+      <c r="G86">
+        <v>11</v>
+      </c>
+      <c r="H86">
+        <v>2</v>
+      </c>
+      <c r="I86">
+        <v>7</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A87" s="29">
+        <v>46026</v>
+      </c>
+      <c r="B87" s="30">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D87" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E87">
+        <v>567</v>
+      </c>
+      <c r="F87">
+        <v>43.3</v>
+      </c>
+      <c r="G87">
+        <v>40</v>
+      </c>
+      <c r="H87">
+        <v>23.3</v>
+      </c>
+      <c r="I87">
+        <v>3.3</v>
+      </c>
+      <c r="J87">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A88" s="29">
+        <v>46026</v>
+      </c>
+      <c r="B88" s="30">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C88" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D88" t="s">
+        <v>116</v>
+      </c>
+      <c r="E88">
+        <v>155</v>
+      </c>
+      <c r="F88">
+        <v>15.5</v>
+      </c>
+      <c r="G88">
+        <v>15</v>
+      </c>
+      <c r="H88">
+        <v>2</v>
+      </c>
+      <c r="I88">
+        <v>7</v>
+      </c>
+      <c r="J88">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A89" s="29">
+        <v>46027</v>
+      </c>
+      <c r="B89" s="30">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C89" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D89" t="s">
+        <v>116</v>
+      </c>
+      <c r="E89">
+        <v>155</v>
+      </c>
+      <c r="F89">
+        <v>15.5</v>
+      </c>
+      <c r="G89">
+        <v>15</v>
+      </c>
+      <c r="H89">
+        <v>2</v>
+      </c>
+      <c r="I89">
+        <v>7</v>
+      </c>
+      <c r="J89">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A90" s="29">
+        <v>46027</v>
+      </c>
+      <c r="B90" s="30">
+        <v>0.375</v>
+      </c>
+      <c r="C90" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D90" t="s">
+        <v>102</v>
+      </c>
+      <c r="E90">
+        <v>77</v>
+      </c>
+      <c r="F90">
+        <v>2</v>
+      </c>
+      <c r="G90">
+        <v>11</v>
+      </c>
+      <c r="H90">
+        <v>2</v>
+      </c>
+      <c r="I90">
+        <v>7</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A91" s="29">
+        <v>46027</v>
+      </c>
+      <c r="B91" s="30">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C91" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D91" t="s">
+        <v>808</v>
+      </c>
+      <c r="E91">
+        <v>145</v>
+      </c>
+      <c r="F91">
+        <v>5.5</v>
+      </c>
+      <c r="G91">
+        <v>9</v>
+      </c>
+      <c r="H91">
+        <v>9</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A92" s="29">
+        <v>46027</v>
+      </c>
+      <c r="B92" s="30">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C92" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D92" t="s">
+        <v>372</v>
+      </c>
+      <c r="E92">
+        <v>89</v>
+      </c>
+      <c r="F92">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G92">
+        <v>23</v>
+      </c>
+      <c r="H92">
+        <v>0.3</v>
+      </c>
+      <c r="I92">
+        <v>12</v>
+      </c>
+      <c r="J92">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A93" s="29">
+        <v>46027</v>
+      </c>
+      <c r="B93" s="30">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C93" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D93" t="s">
+        <v>932</v>
+      </c>
+      <c r="E93">
+        <v>335</v>
+      </c>
+      <c r="F93">
+        <v>21</v>
+      </c>
+      <c r="G93">
+        <v>33</v>
+      </c>
+      <c r="H93">
+        <v>13</v>
+      </c>
+      <c r="I93">
+        <v>2.5</v>
+      </c>
+      <c r="J93">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A94" s="29">
+        <v>46027</v>
+      </c>
+      <c r="B94" s="30">
+        <v>0.5625</v>
+      </c>
+      <c r="C94" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D94" t="s">
+        <v>205</v>
+      </c>
+      <c r="E94">
+        <v>78.75</v>
+      </c>
+      <c r="F94">
+        <v>1.95</v>
+      </c>
+      <c r="G94">
+        <v>16.8</v>
+      </c>
+      <c r="H94">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I94">
+        <v>11.25</v>
+      </c>
+      <c r="J94">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A95" s="29">
+        <v>46027</v>
+      </c>
+      <c r="B95" s="30">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D95" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E95">
+        <v>165</v>
+      </c>
+      <c r="F95">
+        <v>5</v>
+      </c>
+      <c r="G95">
+        <v>9</v>
+      </c>
+      <c r="H95">
+        <v>13.5</v>
+      </c>
+      <c r="I95">
+        <v>1.5</v>
+      </c>
+      <c r="J95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A96" s="29">
+        <v>46027</v>
+      </c>
+      <c r="B96" s="30">
+        <v>0.625</v>
+      </c>
+      <c r="C96" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D96" t="s">
+        <v>808</v>
+      </c>
+      <c r="E96">
+        <v>145</v>
+      </c>
+      <c r="F96">
+        <v>5.5</v>
+      </c>
+      <c r="G96">
+        <v>9</v>
+      </c>
+      <c r="H96">
+        <v>9</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A97" s="29">
+        <v>46027</v>
+      </c>
+      <c r="B97" s="30">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C97" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D97" t="s">
+        <v>116</v>
+      </c>
+      <c r="E97">
+        <v>155</v>
+      </c>
+      <c r="F97">
+        <v>15.5</v>
+      </c>
+      <c r="G97">
+        <v>15</v>
+      </c>
+      <c r="H97">
+        <v>2</v>
+      </c>
+      <c r="I97">
+        <v>7</v>
+      </c>
+      <c r="J97">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A98" s="29">
+        <v>46027</v>
+      </c>
+      <c r="B98" s="30">
+        <v>0.6875</v>
+      </c>
+      <c r="C98" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D98" t="s">
+        <v>258</v>
+      </c>
+      <c r="E98">
+        <v>128</v>
+      </c>
+      <c r="F98">
+        <v>6.6</v>
+      </c>
+      <c r="G98">
+        <v>9.6</v>
+      </c>
+      <c r="H98">
+        <v>5.3</v>
+      </c>
+      <c r="I98">
+        <v>5.3</v>
+      </c>
+      <c r="J98">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A99" s="29">
+        <v>46027</v>
+      </c>
+      <c r="B99" s="30">
+        <v>0.75</v>
+      </c>
+      <c r="C99" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D99" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E99">
+        <v>440</v>
+      </c>
+      <c r="F99">
+        <v>22</v>
+      </c>
+      <c r="G99">
+        <v>50</v>
+      </c>
+      <c r="H99">
+        <v>16</v>
+      </c>
+      <c r="I99">
+        <v>3</v>
+      </c>
+      <c r="J99">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A100" s="29">
+        <v>46027</v>
+      </c>
+      <c r="B100" s="30">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C100" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D100" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E100">
+        <v>240</v>
+      </c>
+      <c r="F100">
+        <v>16</v>
+      </c>
+      <c r="G100">
+        <v>20</v>
+      </c>
+      <c r="H100">
+        <v>12</v>
+      </c>
+      <c r="I100">
+        <v>20</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A101" s="29">
+        <v>46028</v>
+      </c>
+      <c r="B101" s="30">
+        <v>0.375</v>
+      </c>
+      <c r="C101" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D101" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E101">
+        <v>450</v>
+      </c>
+      <c r="F101">
+        <v>12</v>
+      </c>
+      <c r="G101">
+        <v>48.5</v>
+      </c>
+      <c r="H101">
+        <v>27.8</v>
+      </c>
+      <c r="I101">
+        <v>3.9</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A102" s="29">
+        <v>46028</v>
+      </c>
+      <c r="B102" s="30">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C102" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D102" t="s">
+        <v>27</v>
+      </c>
+      <c r="E102">
+        <v>210</v>
+      </c>
+      <c r="F102">
+        <v>5.2</v>
+      </c>
+      <c r="G102">
+        <v>42</v>
+      </c>
+      <c r="H102">
+        <v>1.4</v>
+      </c>
+      <c r="I102">
+        <v>28</v>
+      </c>
+      <c r="J102">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A103" s="29">
+        <v>46028</v>
+      </c>
+      <c r="B103" s="30">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C103" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D103" t="s">
+        <v>365</v>
+      </c>
+      <c r="E103">
+        <v>256</v>
+      </c>
+      <c r="F103">
+        <v>13.2</v>
+      </c>
+      <c r="G103">
+        <v>19.2</v>
+      </c>
+      <c r="H103">
+        <v>10.6</v>
+      </c>
+      <c r="I103">
+        <v>10.6</v>
+      </c>
+      <c r="J103">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A104" s="29">
+        <v>46028</v>
+      </c>
+      <c r="B104" s="30">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C104" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D104" t="s">
+        <v>932</v>
+      </c>
+      <c r="E104">
+        <v>335</v>
+      </c>
+      <c r="F104">
+        <v>21</v>
+      </c>
+      <c r="G104">
+        <v>33</v>
+      </c>
+      <c r="H104">
+        <v>13</v>
+      </c>
+      <c r="I104">
+        <v>2.5</v>
+      </c>
+      <c r="J104">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A105" s="29">
+        <v>46028</v>
+      </c>
+      <c r="B105" s="30">
+        <v>0.5625</v>
+      </c>
+      <c r="C105" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D105" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E105">
+        <v>165</v>
+      </c>
+      <c r="F105">
+        <v>5</v>
+      </c>
+      <c r="G105">
+        <v>9</v>
+      </c>
+      <c r="H105">
+        <v>13.5</v>
+      </c>
+      <c r="I105">
+        <v>1.5</v>
+      </c>
+      <c r="J105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A106" s="29">
+        <v>46028</v>
+      </c>
+      <c r="B106" s="30">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C106" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D106" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E106">
+        <v>263.3</v>
+      </c>
+      <c r="F106">
+        <v>2.8</v>
+      </c>
+      <c r="G106">
+        <v>30.5</v>
+      </c>
+      <c r="H106">
+        <v>14.7</v>
+      </c>
+      <c r="I106">
+        <v>3</v>
+      </c>
+      <c r="J106">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A107" s="29">
+        <v>46028</v>
+      </c>
+      <c r="B107" s="30">
+        <v>0.75</v>
+      </c>
+      <c r="C107" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D107" t="s">
+        <v>372</v>
+      </c>
+      <c r="E107">
+        <v>89</v>
+      </c>
+      <c r="F107">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G107">
+        <v>23</v>
+      </c>
+      <c r="H107">
+        <v>0.3</v>
+      </c>
+      <c r="I107">
+        <v>12</v>
+      </c>
+      <c r="J107">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A108" s="29">
+        <v>46028</v>
+      </c>
+      <c r="B108" s="30">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C108" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D108" t="s">
+        <v>102</v>
+      </c>
+      <c r="E108">
+        <v>77</v>
+      </c>
+      <c r="F108">
+        <v>2</v>
+      </c>
+      <c r="G108">
+        <v>11</v>
+      </c>
+      <c r="H108">
+        <v>2</v>
+      </c>
+      <c r="I108">
+        <v>7</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A109" s="29">
+        <v>46028</v>
+      </c>
+      <c r="B109" s="30">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C109" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D109" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E109">
+        <v>300</v>
+      </c>
+      <c r="F109">
+        <v>25</v>
+      </c>
+      <c r="G109">
+        <v>20</v>
+      </c>
+      <c r="H109">
+        <v>15</v>
+      </c>
+      <c r="I109">
+        <v>3</v>
+      </c>
+      <c r="J109">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A110" s="29">
+        <v>46028</v>
+      </c>
+      <c r="B110" s="30">
+        <v>0.8125</v>
+      </c>
+      <c r="C110" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D110" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E110">
+        <v>165</v>
+      </c>
+      <c r="F110">
+        <v>5</v>
+      </c>
+      <c r="G110">
+        <v>9</v>
+      </c>
+      <c r="H110">
+        <v>13.5</v>
+      </c>
+      <c r="I110">
+        <v>1.5</v>
+      </c>
+      <c r="J110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A111" s="29">
+        <v>46028</v>
+      </c>
+      <c r="B111" s="30">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C111" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D111" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E111">
+        <v>263.3</v>
+      </c>
+      <c r="F111">
+        <v>2.8</v>
+      </c>
+      <c r="G111">
+        <v>30.5</v>
+      </c>
+      <c r="H111">
+        <v>14.7</v>
+      </c>
+      <c r="I111">
+        <v>3</v>
+      </c>
+      <c r="J111">
+        <v>1.3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Food Log Main.xlsx
+++ b/Food Log Main.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91998\VS\Food Log Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78ACF91D-606E-4E2F-8582-5E558C6F226E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{731D474C-26BC-428D-9DE9-4D61943C3C90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main Format 12 oct" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2198" uniqueCount="1103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2353" uniqueCount="1185">
   <si>
     <t>date</t>
   </si>
@@ -3369,6 +3369,252 @@
   </si>
   <si>
     <t>WK20260103-wm</t>
+  </si>
+  <si>
+    <t>FD20260107-0800-u5v6</t>
+  </si>
+  <si>
+    <t>FD20260107-1200-w7x8</t>
+  </si>
+  <si>
+    <t>FD20260107-1300-y9z0</t>
+  </si>
+  <si>
+    <t>FD20260107-1330-a1b2</t>
+  </si>
+  <si>
+    <t>FD20260107-1400-c3d4</t>
+  </si>
+  <si>
+    <t>FD20260107-1530-e5f6</t>
+  </si>
+  <si>
+    <t>FD20260107-1930-g7h8</t>
+  </si>
+  <si>
+    <t>FD20260107-2000-i9j0</t>
+  </si>
+  <si>
+    <t>FD20260108-0800-k1l2</t>
+  </si>
+  <si>
+    <t>FD20260108-0830-m3n4</t>
+  </si>
+  <si>
+    <t>FD20260108-0900-o5p6</t>
+  </si>
+  <si>
+    <t>Roasted cashew (15 g)</t>
+  </si>
+  <si>
+    <t>FD20260108-1230-q7r8</t>
+  </si>
+  <si>
+    <t>FD20260108-1530-s9t0</t>
+  </si>
+  <si>
+    <t>FD20260108-1600-u1v2</t>
+  </si>
+  <si>
+    <t>FD20260108-1730-w3x4</t>
+  </si>
+  <si>
+    <t>FD20260108-1800-y5z6</t>
+  </si>
+  <si>
+    <t>FD20260108-1830-a7b8</t>
+  </si>
+  <si>
+    <t>FD20260108-1900-c9d0</t>
+  </si>
+  <si>
+    <t>FD20260109-0830-e1f2</t>
+  </si>
+  <si>
+    <t>FD20260109-0930-g3h4</t>
+  </si>
+  <si>
+    <t>FD20260109-1130-i5j6</t>
+  </si>
+  <si>
+    <t>FD20260109-1400-k7l8</t>
+  </si>
+  <si>
+    <t>FD20260109-1800-m9n0</t>
+  </si>
+  <si>
+    <t>Chicken sandwich</t>
+  </si>
+  <si>
+    <t>FD20260109-1830-o1p2</t>
+  </si>
+  <si>
+    <t>FD20260109-1900-q3r4</t>
+  </si>
+  <si>
+    <t>FD20260110-0800-s5t6</t>
+  </si>
+  <si>
+    <t>FD20260110-0830-u7v8</t>
+  </si>
+  <si>
+    <t>FD20260110-1400-w9x0</t>
+  </si>
+  <si>
+    <t>FD20260110-1430-y1z2</t>
+  </si>
+  <si>
+    <t>FD20260110-1500-a3b4</t>
+  </si>
+  <si>
+    <t>FD20260110-1630-c5d6</t>
+  </si>
+  <si>
+    <t>FD20260110-1700-e7f8</t>
+  </si>
+  <si>
+    <t>FD20260110-1930-g9h0</t>
+  </si>
+  <si>
+    <t>100g grilled beef and 2 rotis</t>
+  </si>
+  <si>
+    <t>WK20260104-b</t>
+  </si>
+  <si>
+    <t>WK20260107-wm</t>
+  </si>
+  <si>
+    <t>WK20260108-w1</t>
+  </si>
+  <si>
+    <t>WK20260108-w2</t>
+  </si>
+  <si>
+    <t>WK20260109-b</t>
+  </si>
+  <si>
+    <t>WK20260110-wm</t>
+  </si>
+  <si>
+    <t>FD20260111-0800-i1j2</t>
+  </si>
+  <si>
+    <t>FD20260111-0830-k3l4</t>
+  </si>
+  <si>
+    <t>FD20260111-1000-m5n6</t>
+  </si>
+  <si>
+    <t>FD20260111-1200-o7p8</t>
+  </si>
+  <si>
+    <t>FD20260111-1230-q9r0</t>
+  </si>
+  <si>
+    <t>FD20260111-1330-s1t2</t>
+  </si>
+  <si>
+    <t>50g grilled beef and 2 rotis</t>
+  </si>
+  <si>
+    <t>FD20260111-1600-u3v4</t>
+  </si>
+  <si>
+    <t>FD20260111-1630-w5x6</t>
+  </si>
+  <si>
+    <t>FD20260111-1700-y7z8</t>
+  </si>
+  <si>
+    <t>FD20260111-1830-a9b0</t>
+  </si>
+  <si>
+    <t>FD20260111-2000-c1d2</t>
+  </si>
+  <si>
+    <t>Apple (150 g)</t>
+  </si>
+  <si>
+    <t>FD20260111-2030-e3f4</t>
+  </si>
+  <si>
+    <t>100g chicken popcorn and 100g lettuce</t>
+  </si>
+  <si>
+    <t>FD20260112-0800-g5h6</t>
+  </si>
+  <si>
+    <t>FD20260112-0830-i7j8</t>
+  </si>
+  <si>
+    <t>FD20260112-0900-k9l0</t>
+  </si>
+  <si>
+    <t>FD20260112-1200-m1n2</t>
+  </si>
+  <si>
+    <t>100g chicken popcorn and 1 roti with butter</t>
+  </si>
+  <si>
+    <t>FD20260112-1700-o3p4</t>
+  </si>
+  <si>
+    <t>FD20260112-1830-q5r6</t>
+  </si>
+  <si>
+    <t>Chicken and mushroom cream soup (330g) with 19g breadsticks</t>
+  </si>
+  <si>
+    <t>FD20260112-1900-s7t8</t>
+  </si>
+  <si>
+    <t>FD20260112-1930-u9v0</t>
+  </si>
+  <si>
+    <t>FD20260113-0800-w1x2</t>
+  </si>
+  <si>
+    <t>FD20260113-0830-y3z4</t>
+  </si>
+  <si>
+    <t>FD20260113-0900-a5b6</t>
+  </si>
+  <si>
+    <t>FD20260113-0930-c7d8</t>
+  </si>
+  <si>
+    <t>FD20260113-1000-e9f0</t>
+  </si>
+  <si>
+    <t>2 rotis with 16g ketchup</t>
+  </si>
+  <si>
+    <t>FD20260113-1230-g1h2</t>
+  </si>
+  <si>
+    <t>FD20260113-1700-i3j4</t>
+  </si>
+  <si>
+    <t>FD20260113-1730-k5l6</t>
+  </si>
+  <si>
+    <t>FD20260113-1800-m7n8</t>
+  </si>
+  <si>
+    <t>Walking (Auto)</t>
+  </si>
+  <si>
+    <t>WK20260110-w</t>
+  </si>
+  <si>
+    <t>WK20260111-b</t>
+  </si>
+  <si>
+    <t>WK20260113-b</t>
+  </si>
+  <si>
+    <t>1000140850.jpg</t>
   </si>
 </sst>
 </file>
@@ -3438,7 +3684,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -3516,6 +3762,7 @@
     <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3847,7 +4094,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J743"/>
+  <dimension ref="A1:J805"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -27625,6 +27872,1990 @@
       </c>
       <c r="J743" s="2">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="744" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A744" s="29">
+        <v>46029</v>
+      </c>
+      <c r="B744" s="30">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C744" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D744" t="s">
+        <v>102</v>
+      </c>
+      <c r="E744">
+        <v>77</v>
+      </c>
+      <c r="F744">
+        <v>2</v>
+      </c>
+      <c r="G744">
+        <v>11</v>
+      </c>
+      <c r="H744">
+        <v>2</v>
+      </c>
+      <c r="I744">
+        <v>7</v>
+      </c>
+      <c r="J744">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="745" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A745" s="29">
+        <v>46029</v>
+      </c>
+      <c r="B745" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="C745" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D745" t="s">
+        <v>32</v>
+      </c>
+      <c r="E745">
+        <v>290</v>
+      </c>
+      <c r="F745">
+        <v>11</v>
+      </c>
+      <c r="G745">
+        <v>18</v>
+      </c>
+      <c r="H745">
+        <v>18</v>
+      </c>
+      <c r="I745">
+        <v>0</v>
+      </c>
+      <c r="J745">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="746" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A746" s="29">
+        <v>46029</v>
+      </c>
+      <c r="B746" s="30">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C746" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D746" t="s">
+        <v>917</v>
+      </c>
+      <c r="E746">
+        <v>502.5</v>
+      </c>
+      <c r="F746">
+        <v>31.5</v>
+      </c>
+      <c r="G746">
+        <v>49.5</v>
+      </c>
+      <c r="H746">
+        <v>19.5</v>
+      </c>
+      <c r="I746">
+        <v>3.75</v>
+      </c>
+      <c r="J746">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="747" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A747" s="29">
+        <v>46029</v>
+      </c>
+      <c r="B747" s="30">
+        <v>0.5625</v>
+      </c>
+      <c r="C747" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D747" t="s">
+        <v>116</v>
+      </c>
+      <c r="E747">
+        <v>155</v>
+      </c>
+      <c r="F747">
+        <v>15.5</v>
+      </c>
+      <c r="G747">
+        <v>15</v>
+      </c>
+      <c r="H747">
+        <v>2</v>
+      </c>
+      <c r="I747">
+        <v>7</v>
+      </c>
+      <c r="J747">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="748" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A748" s="29">
+        <v>46029</v>
+      </c>
+      <c r="B748" s="30">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C748" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D748" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E748">
+        <v>165</v>
+      </c>
+      <c r="F748">
+        <v>5</v>
+      </c>
+      <c r="G748">
+        <v>9</v>
+      </c>
+      <c r="H748">
+        <v>13.5</v>
+      </c>
+      <c r="I748">
+        <v>1.5</v>
+      </c>
+      <c r="J748">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="749" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A749" s="29">
+        <v>46029</v>
+      </c>
+      <c r="B749" s="30">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C749" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D749" t="s">
+        <v>102</v>
+      </c>
+      <c r="E749">
+        <v>77</v>
+      </c>
+      <c r="F749">
+        <v>2</v>
+      </c>
+      <c r="G749">
+        <v>11</v>
+      </c>
+      <c r="H749">
+        <v>2</v>
+      </c>
+      <c r="I749">
+        <v>7</v>
+      </c>
+      <c r="J749">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="750" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A750" s="29">
+        <v>46029</v>
+      </c>
+      <c r="B750" s="30">
+        <v>0.8125</v>
+      </c>
+      <c r="C750" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D750" t="s">
+        <v>98</v>
+      </c>
+      <c r="E750">
+        <v>380</v>
+      </c>
+      <c r="F750">
+        <v>25</v>
+      </c>
+      <c r="G750">
+        <v>46</v>
+      </c>
+      <c r="H750">
+        <v>10</v>
+      </c>
+      <c r="I750">
+        <v>2</v>
+      </c>
+      <c r="J750">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="751" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A751" s="29">
+        <v>46029</v>
+      </c>
+      <c r="B751" s="30">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C751" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D751" t="s">
+        <v>116</v>
+      </c>
+      <c r="E751">
+        <v>155</v>
+      </c>
+      <c r="F751">
+        <v>15.5</v>
+      </c>
+      <c r="G751">
+        <v>15</v>
+      </c>
+      <c r="H751">
+        <v>2</v>
+      </c>
+      <c r="I751">
+        <v>7</v>
+      </c>
+      <c r="J751">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="752" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A752" s="29">
+        <v>46030</v>
+      </c>
+      <c r="B752" s="30">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C752" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D752" t="s">
+        <v>102</v>
+      </c>
+      <c r="E752">
+        <v>77</v>
+      </c>
+      <c r="F752">
+        <v>2</v>
+      </c>
+      <c r="G752">
+        <v>11</v>
+      </c>
+      <c r="H752">
+        <v>2</v>
+      </c>
+      <c r="I752">
+        <v>7</v>
+      </c>
+      <c r="J752">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="753" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A753" s="29">
+        <v>46030</v>
+      </c>
+      <c r="B753" s="30">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C753" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D753" t="s">
+        <v>258</v>
+      </c>
+      <c r="E753">
+        <v>128</v>
+      </c>
+      <c r="F753">
+        <v>6.6</v>
+      </c>
+      <c r="G753">
+        <v>9.6</v>
+      </c>
+      <c r="H753">
+        <v>5.3</v>
+      </c>
+      <c r="I753">
+        <v>5.3</v>
+      </c>
+      <c r="J753">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="754" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A754" s="29">
+        <v>46030</v>
+      </c>
+      <c r="B754" s="30">
+        <v>0.375</v>
+      </c>
+      <c r="C754" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D754" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E754">
+        <v>82.5</v>
+      </c>
+      <c r="F754">
+        <v>2.5</v>
+      </c>
+      <c r="G754">
+        <v>4.5</v>
+      </c>
+      <c r="H754">
+        <v>6.75</v>
+      </c>
+      <c r="I754">
+        <v>0.75</v>
+      </c>
+      <c r="J754">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="755" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A755" s="29">
+        <v>46030</v>
+      </c>
+      <c r="B755" s="30">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C755" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D755" t="s">
+        <v>32</v>
+      </c>
+      <c r="E755">
+        <v>290</v>
+      </c>
+      <c r="F755">
+        <v>11</v>
+      </c>
+      <c r="G755">
+        <v>18</v>
+      </c>
+      <c r="H755">
+        <v>18</v>
+      </c>
+      <c r="I755">
+        <v>0</v>
+      </c>
+      <c r="J755">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="756" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A756" s="29">
+        <v>46030</v>
+      </c>
+      <c r="B756" s="30">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C756" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D756" t="s">
+        <v>98</v>
+      </c>
+      <c r="E756">
+        <v>380</v>
+      </c>
+      <c r="F756">
+        <v>25</v>
+      </c>
+      <c r="G756">
+        <v>46</v>
+      </c>
+      <c r="H756">
+        <v>10</v>
+      </c>
+      <c r="I756">
+        <v>2</v>
+      </c>
+      <c r="J756">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="757" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A757" s="29">
+        <v>46030</v>
+      </c>
+      <c r="B757" s="30">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C757" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D757" t="s">
+        <v>116</v>
+      </c>
+      <c r="E757">
+        <v>155</v>
+      </c>
+      <c r="F757">
+        <v>15.5</v>
+      </c>
+      <c r="G757">
+        <v>15</v>
+      </c>
+      <c r="H757">
+        <v>2</v>
+      </c>
+      <c r="I757">
+        <v>7</v>
+      </c>
+      <c r="J757">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="758" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A758" s="29">
+        <v>46030</v>
+      </c>
+      <c r="B758" s="30">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C758" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D758" t="s">
+        <v>102</v>
+      </c>
+      <c r="E758">
+        <v>77</v>
+      </c>
+      <c r="F758">
+        <v>2</v>
+      </c>
+      <c r="G758">
+        <v>11</v>
+      </c>
+      <c r="H758">
+        <v>2</v>
+      </c>
+      <c r="I758">
+        <v>7</v>
+      </c>
+      <c r="J758">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="759" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A759" s="29">
+        <v>46030</v>
+      </c>
+      <c r="B759" s="30">
+        <v>0.75</v>
+      </c>
+      <c r="C759" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D759" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E759">
+        <v>82.5</v>
+      </c>
+      <c r="F759">
+        <v>2.5</v>
+      </c>
+      <c r="G759">
+        <v>4.5</v>
+      </c>
+      <c r="H759">
+        <v>6.75</v>
+      </c>
+      <c r="I759">
+        <v>0.75</v>
+      </c>
+      <c r="J759">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="760" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A760" s="29">
+        <v>46030</v>
+      </c>
+      <c r="B760" s="30">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C760" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D760" t="s">
+        <v>808</v>
+      </c>
+      <c r="E760">
+        <v>145</v>
+      </c>
+      <c r="F760">
+        <v>5.5</v>
+      </c>
+      <c r="G760">
+        <v>9</v>
+      </c>
+      <c r="H760">
+        <v>9</v>
+      </c>
+      <c r="I760">
+        <v>0</v>
+      </c>
+      <c r="J760">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="761" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A761" s="29">
+        <v>46030</v>
+      </c>
+      <c r="B761" s="30">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C761" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D761" t="s">
+        <v>932</v>
+      </c>
+      <c r="E761">
+        <v>335</v>
+      </c>
+      <c r="F761">
+        <v>21</v>
+      </c>
+      <c r="G761">
+        <v>33</v>
+      </c>
+      <c r="H761">
+        <v>13</v>
+      </c>
+      <c r="I761">
+        <v>2.5</v>
+      </c>
+      <c r="J761">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="762" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A762" s="29">
+        <v>46031</v>
+      </c>
+      <c r="B762" s="30">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C762" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D762" t="s">
+        <v>102</v>
+      </c>
+      <c r="E762">
+        <v>77</v>
+      </c>
+      <c r="F762">
+        <v>2</v>
+      </c>
+      <c r="G762">
+        <v>11</v>
+      </c>
+      <c r="H762">
+        <v>2</v>
+      </c>
+      <c r="I762">
+        <v>7</v>
+      </c>
+      <c r="J762">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="763" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A763" s="29">
+        <v>46031</v>
+      </c>
+      <c r="B763" s="30">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C763" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D763" t="s">
+        <v>258</v>
+      </c>
+      <c r="E763">
+        <v>128</v>
+      </c>
+      <c r="F763">
+        <v>6.6</v>
+      </c>
+      <c r="G763">
+        <v>9.6</v>
+      </c>
+      <c r="H763">
+        <v>5.3</v>
+      </c>
+      <c r="I763">
+        <v>5.3</v>
+      </c>
+      <c r="J763">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="764" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A764" s="29">
+        <v>46031</v>
+      </c>
+      <c r="B764" s="30">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C764" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D764" t="s">
+        <v>116</v>
+      </c>
+      <c r="E764">
+        <v>155</v>
+      </c>
+      <c r="F764">
+        <v>15.5</v>
+      </c>
+      <c r="G764">
+        <v>15</v>
+      </c>
+      <c r="H764">
+        <v>2</v>
+      </c>
+      <c r="I764">
+        <v>7</v>
+      </c>
+      <c r="J764">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="765" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A765" s="29">
+        <v>46031</v>
+      </c>
+      <c r="B765" s="30">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C765" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D765" t="s">
+        <v>32</v>
+      </c>
+      <c r="E765">
+        <v>290</v>
+      </c>
+      <c r="F765">
+        <v>11</v>
+      </c>
+      <c r="G765">
+        <v>18</v>
+      </c>
+      <c r="H765">
+        <v>18</v>
+      </c>
+      <c r="I765">
+        <v>0</v>
+      </c>
+      <c r="J765">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="766" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A766" s="29">
+        <v>46031</v>
+      </c>
+      <c r="B766" s="30">
+        <v>0.75</v>
+      </c>
+      <c r="C766" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D766" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E766">
+        <v>400</v>
+      </c>
+      <c r="F766">
+        <v>25</v>
+      </c>
+      <c r="G766">
+        <v>40</v>
+      </c>
+      <c r="H766">
+        <v>15</v>
+      </c>
+      <c r="I766">
+        <v>5</v>
+      </c>
+      <c r="J766">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="767" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A767" s="29">
+        <v>46031</v>
+      </c>
+      <c r="B767" s="30">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C767" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D767" t="s">
+        <v>917</v>
+      </c>
+      <c r="E767">
+        <v>502.5</v>
+      </c>
+      <c r="F767">
+        <v>31.5</v>
+      </c>
+      <c r="G767">
+        <v>49.5</v>
+      </c>
+      <c r="H767">
+        <v>19.5</v>
+      </c>
+      <c r="I767">
+        <v>3.75</v>
+      </c>
+      <c r="J767">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="768" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A768" s="29">
+        <v>46031</v>
+      </c>
+      <c r="B768" s="30">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C768" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D768" t="s">
+        <v>116</v>
+      </c>
+      <c r="E768">
+        <v>155</v>
+      </c>
+      <c r="F768">
+        <v>15.5</v>
+      </c>
+      <c r="G768">
+        <v>15</v>
+      </c>
+      <c r="H768">
+        <v>2</v>
+      </c>
+      <c r="I768">
+        <v>7</v>
+      </c>
+      <c r="J768">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="769" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A769" s="29">
+        <v>46032</v>
+      </c>
+      <c r="B769" s="30">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C769" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D769" t="s">
+        <v>102</v>
+      </c>
+      <c r="E769">
+        <v>77</v>
+      </c>
+      <c r="F769">
+        <v>2</v>
+      </c>
+      <c r="G769">
+        <v>11</v>
+      </c>
+      <c r="H769">
+        <v>2</v>
+      </c>
+      <c r="I769">
+        <v>7</v>
+      </c>
+      <c r="J769">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="770" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A770" s="29">
+        <v>46032</v>
+      </c>
+      <c r="B770" s="30">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C770" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D770" t="s">
+        <v>258</v>
+      </c>
+      <c r="E770">
+        <v>128</v>
+      </c>
+      <c r="F770">
+        <v>6.6</v>
+      </c>
+      <c r="G770">
+        <v>9.6</v>
+      </c>
+      <c r="H770">
+        <v>5.3</v>
+      </c>
+      <c r="I770">
+        <v>5.3</v>
+      </c>
+      <c r="J770">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="771" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A771" s="29">
+        <v>46032</v>
+      </c>
+      <c r="B771" s="30">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C771" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D771" t="s">
+        <v>32</v>
+      </c>
+      <c r="E771">
+        <v>290</v>
+      </c>
+      <c r="F771">
+        <v>11</v>
+      </c>
+      <c r="G771">
+        <v>18</v>
+      </c>
+      <c r="H771">
+        <v>18</v>
+      </c>
+      <c r="I771">
+        <v>0</v>
+      </c>
+      <c r="J771">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="772" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A772" s="29">
+        <v>46032</v>
+      </c>
+      <c r="B772" s="30">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C772" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D772" t="s">
+        <v>205</v>
+      </c>
+      <c r="E772">
+        <v>78.75</v>
+      </c>
+      <c r="F772">
+        <v>1.95</v>
+      </c>
+      <c r="G772">
+        <v>16.8</v>
+      </c>
+      <c r="H772">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I772">
+        <v>11.25</v>
+      </c>
+      <c r="J772">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="773" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A773" s="29">
+        <v>46032</v>
+      </c>
+      <c r="B773" s="30">
+        <v>0.625</v>
+      </c>
+      <c r="C773" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D773" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E773">
+        <v>82.5</v>
+      </c>
+      <c r="F773">
+        <v>2.5</v>
+      </c>
+      <c r="G773">
+        <v>4.5</v>
+      </c>
+      <c r="H773">
+        <v>6.75</v>
+      </c>
+      <c r="I773">
+        <v>0.75</v>
+      </c>
+      <c r="J773">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="774" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A774" s="29">
+        <v>46032</v>
+      </c>
+      <c r="B774" s="30">
+        <v>0.6875</v>
+      </c>
+      <c r="C774" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D774" t="s">
+        <v>932</v>
+      </c>
+      <c r="E774">
+        <v>335</v>
+      </c>
+      <c r="F774">
+        <v>21</v>
+      </c>
+      <c r="G774">
+        <v>33</v>
+      </c>
+      <c r="H774">
+        <v>13</v>
+      </c>
+      <c r="I774">
+        <v>2.5</v>
+      </c>
+      <c r="J774">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="775" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A775" s="29">
+        <v>46032</v>
+      </c>
+      <c r="B775" s="30">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C775" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D775" t="s">
+        <v>116</v>
+      </c>
+      <c r="E775">
+        <v>155</v>
+      </c>
+      <c r="F775">
+        <v>15.5</v>
+      </c>
+      <c r="G775">
+        <v>15</v>
+      </c>
+      <c r="H775">
+        <v>2</v>
+      </c>
+      <c r="I775">
+        <v>7</v>
+      </c>
+      <c r="J775">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="776" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A776" s="29">
+        <v>46032</v>
+      </c>
+      <c r="B776" s="30">
+        <v>0.8125</v>
+      </c>
+      <c r="C776" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D776" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E776">
+        <v>460</v>
+      </c>
+      <c r="F776">
+        <v>30</v>
+      </c>
+      <c r="G776">
+        <v>50</v>
+      </c>
+      <c r="H776">
+        <v>15</v>
+      </c>
+      <c r="I776">
+        <v>2</v>
+      </c>
+      <c r="J776">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="777" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A777" s="29">
+        <v>46033</v>
+      </c>
+      <c r="B777" s="30">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C777" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D777" t="s">
+        <v>102</v>
+      </c>
+      <c r="E777">
+        <v>77</v>
+      </c>
+      <c r="F777">
+        <v>2</v>
+      </c>
+      <c r="G777">
+        <v>11</v>
+      </c>
+      <c r="H777">
+        <v>2</v>
+      </c>
+      <c r="I777">
+        <v>7</v>
+      </c>
+      <c r="J777">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="778" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A778" s="29">
+        <v>46033</v>
+      </c>
+      <c r="B778" s="30">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C778" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D778" t="s">
+        <v>258</v>
+      </c>
+      <c r="E778">
+        <v>128</v>
+      </c>
+      <c r="F778">
+        <v>6.6</v>
+      </c>
+      <c r="G778">
+        <v>9.6</v>
+      </c>
+      <c r="H778">
+        <v>5.3</v>
+      </c>
+      <c r="I778">
+        <v>5.3</v>
+      </c>
+      <c r="J778">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="779" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A779" s="29">
+        <v>46033</v>
+      </c>
+      <c r="B779" s="30">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C779" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D779" t="s">
+        <v>205</v>
+      </c>
+      <c r="E779">
+        <v>78.75</v>
+      </c>
+      <c r="F779">
+        <v>1.95</v>
+      </c>
+      <c r="G779">
+        <v>16.8</v>
+      </c>
+      <c r="H779">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I779">
+        <v>11.25</v>
+      </c>
+      <c r="J779">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="780" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A780" s="29">
+        <v>46033</v>
+      </c>
+      <c r="B780" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="C780" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D780" t="s">
+        <v>32</v>
+      </c>
+      <c r="E780">
+        <v>290</v>
+      </c>
+      <c r="F780">
+        <v>11</v>
+      </c>
+      <c r="G780">
+        <v>18</v>
+      </c>
+      <c r="H780">
+        <v>18</v>
+      </c>
+      <c r="I780">
+        <v>0</v>
+      </c>
+      <c r="J780">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="781" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A781" s="29">
+        <v>46033</v>
+      </c>
+      <c r="B781" s="30">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C781" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D781" t="s">
+        <v>139</v>
+      </c>
+      <c r="E781">
+        <v>175</v>
+      </c>
+      <c r="F781">
+        <v>15.5</v>
+      </c>
+      <c r="G781">
+        <v>20</v>
+      </c>
+      <c r="H781">
+        <v>2</v>
+      </c>
+      <c r="I781">
+        <v>11.5</v>
+      </c>
+      <c r="J781">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="782" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A782" s="29">
+        <v>46033</v>
+      </c>
+      <c r="B782" s="30">
+        <v>0.5625</v>
+      </c>
+      <c r="C782" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D782" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E782">
+        <v>330</v>
+      </c>
+      <c r="F782">
+        <v>20</v>
+      </c>
+      <c r="G782">
+        <v>50</v>
+      </c>
+      <c r="H782">
+        <v>8</v>
+      </c>
+      <c r="I782">
+        <v>2</v>
+      </c>
+      <c r="J782">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="783" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A783" s="29">
+        <v>46033</v>
+      </c>
+      <c r="B783" s="30">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C783" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D783" t="s">
+        <v>102</v>
+      </c>
+      <c r="E783">
+        <v>77</v>
+      </c>
+      <c r="F783">
+        <v>2</v>
+      </c>
+      <c r="G783">
+        <v>11</v>
+      </c>
+      <c r="H783">
+        <v>2</v>
+      </c>
+      <c r="I783">
+        <v>7</v>
+      </c>
+      <c r="J783">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="784" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A784" s="29">
+        <v>46033</v>
+      </c>
+      <c r="B784" s="30">
+        <v>0.6875</v>
+      </c>
+      <c r="C784" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D784" t="s">
+        <v>452</v>
+      </c>
+      <c r="E784">
+        <v>44.5</v>
+      </c>
+      <c r="F784">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G784">
+        <v>11.5</v>
+      </c>
+      <c r="H784">
+        <v>0.15</v>
+      </c>
+      <c r="I784">
+        <v>6</v>
+      </c>
+      <c r="J784">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="785" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A785" s="29">
+        <v>46033</v>
+      </c>
+      <c r="B785" s="30">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C785" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D785" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E785">
+        <v>82.5</v>
+      </c>
+      <c r="F785">
+        <v>2.5</v>
+      </c>
+      <c r="G785">
+        <v>4.5</v>
+      </c>
+      <c r="H785">
+        <v>6.75</v>
+      </c>
+      <c r="I785">
+        <v>0.75</v>
+      </c>
+      <c r="J785">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="786" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A786" s="29">
+        <v>46033</v>
+      </c>
+      <c r="B786" s="30">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C786" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D786" t="s">
+        <v>932</v>
+      </c>
+      <c r="E786">
+        <v>335</v>
+      </c>
+      <c r="F786">
+        <v>21</v>
+      </c>
+      <c r="G786">
+        <v>33</v>
+      </c>
+      <c r="H786">
+        <v>13</v>
+      </c>
+      <c r="I786">
+        <v>2.5</v>
+      </c>
+      <c r="J786">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="787" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A787" s="29">
+        <v>46033</v>
+      </c>
+      <c r="B787" s="30">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C787" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D787" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E787">
+        <v>78</v>
+      </c>
+      <c r="F787">
+        <v>0.6</v>
+      </c>
+      <c r="G787">
+        <v>20.8</v>
+      </c>
+      <c r="H787">
+        <v>0.2</v>
+      </c>
+      <c r="I787">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="J787">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="788" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A788" s="29">
+        <v>46033</v>
+      </c>
+      <c r="B788" s="30">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C788" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D788" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E788">
+        <v>300</v>
+      </c>
+      <c r="F788">
+        <v>18</v>
+      </c>
+      <c r="G788">
+        <v>20</v>
+      </c>
+      <c r="H788">
+        <v>18</v>
+      </c>
+      <c r="I788">
+        <v>2</v>
+      </c>
+      <c r="J788">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="789" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A789" s="29">
+        <v>46034</v>
+      </c>
+      <c r="B789" s="30">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C789" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D789" t="s">
+        <v>102</v>
+      </c>
+      <c r="E789">
+        <v>77</v>
+      </c>
+      <c r="F789">
+        <v>2</v>
+      </c>
+      <c r="G789">
+        <v>11</v>
+      </c>
+      <c r="H789">
+        <v>2</v>
+      </c>
+      <c r="I789">
+        <v>7</v>
+      </c>
+      <c r="J789">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="790" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A790" s="29">
+        <v>46034</v>
+      </c>
+      <c r="B790" s="30">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C790" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D790" t="s">
+        <v>258</v>
+      </c>
+      <c r="E790">
+        <v>128</v>
+      </c>
+      <c r="F790">
+        <v>6.6</v>
+      </c>
+      <c r="G790">
+        <v>9.6</v>
+      </c>
+      <c r="H790">
+        <v>5.3</v>
+      </c>
+      <c r="I790">
+        <v>5.3</v>
+      </c>
+      <c r="J790">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="791" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A791" s="29">
+        <v>46034</v>
+      </c>
+      <c r="B791" s="30">
+        <v>0.375</v>
+      </c>
+      <c r="C791" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D791" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E791">
+        <v>82.5</v>
+      </c>
+      <c r="F791">
+        <v>2.5</v>
+      </c>
+      <c r="G791">
+        <v>4.5</v>
+      </c>
+      <c r="H791">
+        <v>6.75</v>
+      </c>
+      <c r="I791">
+        <v>0.75</v>
+      </c>
+      <c r="J791">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="792" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A792" s="29">
+        <v>46034</v>
+      </c>
+      <c r="B792" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="C792" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D792" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E792">
+        <v>340</v>
+      </c>
+      <c r="F792">
+        <v>18</v>
+      </c>
+      <c r="G792">
+        <v>30</v>
+      </c>
+      <c r="H792">
+        <v>17</v>
+      </c>
+      <c r="I792">
+        <v>2</v>
+      </c>
+      <c r="J792">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="793" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A793" s="29">
+        <v>46034</v>
+      </c>
+      <c r="B793" s="30">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C793" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D793" t="s">
+        <v>102</v>
+      </c>
+      <c r="E793">
+        <v>77</v>
+      </c>
+      <c r="F793">
+        <v>2</v>
+      </c>
+      <c r="G793">
+        <v>11</v>
+      </c>
+      <c r="H793">
+        <v>2</v>
+      </c>
+      <c r="I793">
+        <v>7</v>
+      </c>
+      <c r="J793">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="794" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A794" s="29">
+        <v>46034</v>
+      </c>
+      <c r="B794" s="30">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C794" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D794" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E794">
+        <v>343</v>
+      </c>
+      <c r="F794">
+        <v>20</v>
+      </c>
+      <c r="G794">
+        <v>35</v>
+      </c>
+      <c r="H794">
+        <v>15</v>
+      </c>
+      <c r="I794">
+        <v>5</v>
+      </c>
+      <c r="J794">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="795" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A795" s="29">
+        <v>46034</v>
+      </c>
+      <c r="B795" s="30">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C795" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D795" t="s">
+        <v>932</v>
+      </c>
+      <c r="E795">
+        <v>335</v>
+      </c>
+      <c r="F795">
+        <v>21</v>
+      </c>
+      <c r="G795">
+        <v>33</v>
+      </c>
+      <c r="H795">
+        <v>13</v>
+      </c>
+      <c r="I795">
+        <v>2.5</v>
+      </c>
+      <c r="J795">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="796" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A796" s="29">
+        <v>46034</v>
+      </c>
+      <c r="B796" s="30">
+        <v>0.8125</v>
+      </c>
+      <c r="C796" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D796" t="s">
+        <v>139</v>
+      </c>
+      <c r="E796">
+        <v>175</v>
+      </c>
+      <c r="F796">
+        <v>15.5</v>
+      </c>
+      <c r="G796">
+        <v>20</v>
+      </c>
+      <c r="H796">
+        <v>2</v>
+      </c>
+      <c r="I796">
+        <v>11.5</v>
+      </c>
+      <c r="J796">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="797" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A797" s="29">
+        <v>46035</v>
+      </c>
+      <c r="B797" s="30">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C797" t="s">
+        <v>1170</v>
+      </c>
+      <c r="D797" t="s">
+        <v>102</v>
+      </c>
+      <c r="E797">
+        <v>77</v>
+      </c>
+      <c r="F797">
+        <v>2</v>
+      </c>
+      <c r="G797">
+        <v>11</v>
+      </c>
+      <c r="H797">
+        <v>2</v>
+      </c>
+      <c r="I797">
+        <v>7</v>
+      </c>
+      <c r="J797">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="798" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A798" s="29">
+        <v>46035</v>
+      </c>
+      <c r="B798" s="30">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C798" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D798" t="s">
+        <v>258</v>
+      </c>
+      <c r="E798">
+        <v>128</v>
+      </c>
+      <c r="F798">
+        <v>6.6</v>
+      </c>
+      <c r="G798">
+        <v>9.6</v>
+      </c>
+      <c r="H798">
+        <v>5.3</v>
+      </c>
+      <c r="I798">
+        <v>5.3</v>
+      </c>
+      <c r="J798">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="799" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A799" s="29">
+        <v>46035</v>
+      </c>
+      <c r="B799" s="30">
+        <v>0.375</v>
+      </c>
+      <c r="C799" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D799" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E799">
+        <v>82.5</v>
+      </c>
+      <c r="F799">
+        <v>2.5</v>
+      </c>
+      <c r="G799">
+        <v>4.5</v>
+      </c>
+      <c r="H799">
+        <v>6.75</v>
+      </c>
+      <c r="I799">
+        <v>0.75</v>
+      </c>
+      <c r="J799">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="800" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A800" s="29">
+        <v>46035</v>
+      </c>
+      <c r="B800" s="30">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C800" t="s">
+        <v>1173</v>
+      </c>
+      <c r="D800" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E800">
+        <v>78</v>
+      </c>
+      <c r="F800">
+        <v>0.6</v>
+      </c>
+      <c r="G800">
+        <v>20.8</v>
+      </c>
+      <c r="H800">
+        <v>0.2</v>
+      </c>
+      <c r="I800">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="J800">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="801" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A801" s="29">
+        <v>46035</v>
+      </c>
+      <c r="B801" s="30">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C801" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D801" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E801">
+        <v>240</v>
+      </c>
+      <c r="F801">
+        <v>6</v>
+      </c>
+      <c r="G801">
+        <v>40</v>
+      </c>
+      <c r="H801">
+        <v>6</v>
+      </c>
+      <c r="I801">
+        <v>8</v>
+      </c>
+      <c r="J801">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="802" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A802" s="29">
+        <v>46035</v>
+      </c>
+      <c r="B802" s="30">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C802" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D802" t="s">
+        <v>32</v>
+      </c>
+      <c r="E802">
+        <v>290</v>
+      </c>
+      <c r="F802">
+        <v>11</v>
+      </c>
+      <c r="G802">
+        <v>18</v>
+      </c>
+      <c r="H802">
+        <v>18</v>
+      </c>
+      <c r="I802">
+        <v>0</v>
+      </c>
+      <c r="J802">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="803" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A803" s="29">
+        <v>46035</v>
+      </c>
+      <c r="B803" s="30">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C803" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D803" t="s">
+        <v>808</v>
+      </c>
+      <c r="E803">
+        <v>145</v>
+      </c>
+      <c r="F803">
+        <v>5.5</v>
+      </c>
+      <c r="G803">
+        <v>9</v>
+      </c>
+      <c r="H803">
+        <v>9</v>
+      </c>
+      <c r="I803">
+        <v>0</v>
+      </c>
+      <c r="J803">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="804" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A804" s="29">
+        <v>46035</v>
+      </c>
+      <c r="B804" s="30">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C804" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D804" t="s">
+        <v>932</v>
+      </c>
+      <c r="E804">
+        <v>335</v>
+      </c>
+      <c r="F804">
+        <v>21</v>
+      </c>
+      <c r="G804">
+        <v>33</v>
+      </c>
+      <c r="H804">
+        <v>13</v>
+      </c>
+      <c r="I804">
+        <v>2.5</v>
+      </c>
+      <c r="J804">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="805" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A805" s="29">
+        <v>46035</v>
+      </c>
+      <c r="B805" s="30">
+        <v>0.75</v>
+      </c>
+      <c r="C805" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D805" t="s">
+        <v>139</v>
+      </c>
+      <c r="E805">
+        <v>175</v>
+      </c>
+      <c r="F805">
+        <v>15.5</v>
+      </c>
+      <c r="G805">
+        <v>20</v>
+      </c>
+      <c r="H805">
+        <v>2</v>
+      </c>
+      <c r="I805">
+        <v>11.5</v>
+      </c>
+      <c r="J805">
+        <v>1.8</v>
       </c>
     </row>
   </sheetData>
@@ -27641,7 +29872,7 @@
   <conditionalFormatting sqref="C665:C680">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C760:C1048576 C589:C655 C681:C743">
+  <conditionalFormatting sqref="C758:C1048576 C589:C655 C681:C743">
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -27650,7 +29881,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F24E0C0-BC77-4AA4-801C-82B038A8B8E4}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -28281,6 +30512,62 @@
         <v>1099</v>
       </c>
     </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="16">
+        <v>46031</v>
+      </c>
+      <c r="B32" s="31">
+        <v>97.7</v>
+      </c>
+      <c r="C32" s="31">
+        <v>35.9</v>
+      </c>
+      <c r="D32" s="31">
+        <v>30.7</v>
+      </c>
+      <c r="E32" s="31">
+        <v>49.1</v>
+      </c>
+      <c r="F32" s="2"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="16">
+        <v>46033</v>
+      </c>
+      <c r="B33" s="31">
+        <v>97.3</v>
+      </c>
+      <c r="C33" s="31">
+        <v>36.4</v>
+      </c>
+      <c r="D33" s="31">
+        <v>29.5</v>
+      </c>
+      <c r="E33" s="31">
+        <v>49.7</v>
+      </c>
+      <c r="F33" s="2"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="16">
+        <v>46035</v>
+      </c>
+      <c r="B34" s="2">
+        <v>97.1</v>
+      </c>
+      <c r="C34" s="2">
+        <v>37.1</v>
+      </c>
+      <c r="D34" s="2">
+        <v>28.3</v>
+      </c>
+      <c r="E34" s="2">
+        <v>50.4</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>1184</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -28289,7 +30576,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D2F321-D2D4-48D2-B6F9-E306604CF730}">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -29230,6 +31517,234 @@
       <c r="G39" s="2"/>
       <c r="H39" s="2" t="s">
         <v>1102</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="16">
+        <v>46025</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D40" s="2">
+        <v>80</v>
+      </c>
+      <c r="E40" s="2">
+        <v>703</v>
+      </c>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="16">
+        <v>46026</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D41" s="2">
+        <v>64</v>
+      </c>
+      <c r="E41" s="2">
+        <v>478</v>
+      </c>
+      <c r="F41" s="2">
+        <v>14880</v>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="16">
+        <v>46029</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D42" s="2">
+        <v>52</v>
+      </c>
+      <c r="E42" s="2">
+        <v>494</v>
+      </c>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="16">
+        <v>46030</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D43" s="2">
+        <v>39</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2">
+        <v>2640</v>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="16">
+        <v>46030</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D44" s="2">
+        <v>51</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2">
+        <v>3470</v>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="16">
+        <v>46031</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D45" s="2">
+        <v>53</v>
+      </c>
+      <c r="E45" s="2">
+        <v>347</v>
+      </c>
+      <c r="F45" s="2">
+        <v>13520</v>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" s="16">
+        <v>46032</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D46" s="2">
+        <v>102</v>
+      </c>
+      <c r="E46" s="2">
+        <v>863</v>
+      </c>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" s="16">
+        <v>46032</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D47" s="2">
+        <v>18</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2">
+        <v>1280</v>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="16">
+        <v>46033</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D48" s="2">
+        <v>74</v>
+      </c>
+      <c r="E48" s="2">
+        <v>546</v>
+      </c>
+      <c r="F48" s="2">
+        <v>20030</v>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="16">
+        <v>46035</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D49" s="2">
+        <v>62</v>
+      </c>
+      <c r="E49" s="2">
+        <v>528</v>
+      </c>
+      <c r="F49" s="2">
+        <v>17950</v>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2" t="s">
+        <v>1183</v>
       </c>
     </row>
   </sheetData>

--- a/Food Log Main.xlsx
+++ b/Food Log Main.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91998\VS\Food Log Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{731D474C-26BC-428D-9DE9-4D61943C3C90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EBABBD4-2BC1-46B1-9BDD-880EAFD590C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main Format 12 oct" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="Daily 23 to 11oct" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Main Format 12 oct'!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Main Format 12 oct'!$A$806:$J$838</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Sheet1!$A$1:$K$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Weight Tracker 23sep'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Workouts 19oct'!$A$1:$H$1</definedName>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2353" uniqueCount="1185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2435" uniqueCount="1232">
   <si>
     <t>date</t>
   </si>
@@ -3615,6 +3615,147 @@
   </si>
   <si>
     <t>1000140850.jpg</t>
+  </si>
+  <si>
+    <t>FD20260114-0800-7f1a</t>
+  </si>
+  <si>
+    <t>FD20260114-0830-8g2b</t>
+  </si>
+  <si>
+    <t>FD20260114-1130-9h3c</t>
+  </si>
+  <si>
+    <t>FD20260114-1200-0i4d</t>
+  </si>
+  <si>
+    <t>FD20260114-1500-1j5e</t>
+  </si>
+  <si>
+    <t>2 boiled eggs</t>
+  </si>
+  <si>
+    <t>FD20260114-1530-2k6f</t>
+  </si>
+  <si>
+    <t>FD20260114-2000-3l7g</t>
+  </si>
+  <si>
+    <t>Banana (100g)</t>
+  </si>
+  <si>
+    <t>FD20260114-2030-4m8h</t>
+  </si>
+  <si>
+    <t>FD20260114-2130-5n9i</t>
+  </si>
+  <si>
+    <t>Chicken mushroom cream soup (330g) + breadsticks (19g)</t>
+  </si>
+  <si>
+    <t>FD20260114-2200-6o0j</t>
+  </si>
+  <si>
+    <t>FD20260114-2200-7p1k</t>
+  </si>
+  <si>
+    <t>FD20260115-0800-8q2l</t>
+  </si>
+  <si>
+    <t>FD20260115-0830-9r3m</t>
+  </si>
+  <si>
+    <t>FD20260115-1030-0s4n</t>
+  </si>
+  <si>
+    <t>Guava (150g)</t>
+  </si>
+  <si>
+    <t>FD20260115-1430-1t5o</t>
+  </si>
+  <si>
+    <t>FD20260115-1500-2u6p</t>
+  </si>
+  <si>
+    <t>FD20260115-1530-3v7q</t>
+  </si>
+  <si>
+    <t>FD20260115-1800-4w8r</t>
+  </si>
+  <si>
+    <t>FD20260115-2000-5x9s</t>
+  </si>
+  <si>
+    <t>Shake 2 (with 5g sugar)</t>
+  </si>
+  <si>
+    <t>FD20260115-2030-6y0t</t>
+  </si>
+  <si>
+    <t>FD20260116-0700-7z1u</t>
+  </si>
+  <si>
+    <t>FD20260116-0730-8a2v</t>
+  </si>
+  <si>
+    <t>FD20260116-0800-9b3w</t>
+  </si>
+  <si>
+    <t>FD20260116-0830-0c4x</t>
+  </si>
+  <si>
+    <t>1 roti with butter and jaggery</t>
+  </si>
+  <si>
+    <t>FD20260116-1100-1d5y</t>
+  </si>
+  <si>
+    <t>Milk coffee with 5g sugar</t>
+  </si>
+  <si>
+    <t>FD20260116-1130-2e6z</t>
+  </si>
+  <si>
+    <t>FD20260116-1200-3f7a</t>
+  </si>
+  <si>
+    <t>FD20260116-1400-4g8b</t>
+  </si>
+  <si>
+    <t>FD20260116-1700-5h9c</t>
+  </si>
+  <si>
+    <t>FD20260116-1730-6i0d</t>
+  </si>
+  <si>
+    <t>FD20260116-1800-7j1e</t>
+  </si>
+  <si>
+    <t>FD20260116-1830-8k2f</t>
+  </si>
+  <si>
+    <t>Mad Angles (30g)</t>
+  </si>
+  <si>
+    <t>FD20260116-1900-9l3g</t>
+  </si>
+  <si>
+    <t>1000139603.jpg</t>
+  </si>
+  <si>
+    <t>1000142235.jpg</t>
+  </si>
+  <si>
+    <t>WK20260114-wm</t>
+  </si>
+  <si>
+    <t>WK20260115-w</t>
+  </si>
+  <si>
+    <t>WK20260115-b</t>
+  </si>
+  <si>
+    <t>WK20260117-wm</t>
   </si>
 </sst>
 </file>
@@ -3684,7 +3825,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -3762,7 +3903,6 @@
     <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4094,7 +4234,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J805"/>
+  <dimension ref="A1:J838"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -27875,1987 +28015,3043 @@
       </c>
     </row>
     <row r="744" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A744" s="29">
+      <c r="A744" s="16">
         <v>46029</v>
       </c>
-      <c r="B744" s="30">
+      <c r="B744" s="17">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C744" t="s">
+      <c r="C744" s="2" t="s">
         <v>1103</v>
       </c>
-      <c r="D744" t="s">
+      <c r="D744" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E744">
+      <c r="E744" s="2">
         <v>77</v>
       </c>
-      <c r="F744">
-        <v>2</v>
-      </c>
-      <c r="G744">
+      <c r="F744" s="2">
+        <v>2</v>
+      </c>
+      <c r="G744" s="2">
         <v>11</v>
       </c>
-      <c r="H744">
-        <v>2</v>
-      </c>
-      <c r="I744">
+      <c r="H744" s="2">
+        <v>2</v>
+      </c>
+      <c r="I744" s="2">
         <v>7</v>
       </c>
-      <c r="J744">
+      <c r="J744" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="745" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A745" s="29">
+      <c r="A745" s="16">
         <v>46029</v>
       </c>
-      <c r="B745" s="30">
+      <c r="B745" s="17">
         <v>0.5</v>
       </c>
-      <c r="C745" t="s">
+      <c r="C745" s="2" t="s">
         <v>1104</v>
       </c>
-      <c r="D745" t="s">
+      <c r="D745" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E745">
+      <c r="E745" s="2">
         <v>290</v>
       </c>
-      <c r="F745">
+      <c r="F745" s="2">
         <v>11</v>
       </c>
-      <c r="G745">
+      <c r="G745" s="2">
         <v>18</v>
       </c>
-      <c r="H745">
+      <c r="H745" s="2">
         <v>18</v>
       </c>
-      <c r="I745">
+      <c r="I745" s="2">
         <v>0</v>
       </c>
-      <c r="J745">
+      <c r="J745" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="746" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A746" s="29">
+      <c r="A746" s="16">
         <v>46029</v>
       </c>
-      <c r="B746" s="30">
+      <c r="B746" s="17">
         <v>0.54166666666666663</v>
       </c>
-      <c r="C746" t="s">
+      <c r="C746" s="2" t="s">
         <v>1105</v>
       </c>
-      <c r="D746" t="s">
+      <c r="D746" s="2" t="s">
         <v>917</v>
       </c>
-      <c r="E746">
+      <c r="E746" s="2">
         <v>502.5</v>
       </c>
-      <c r="F746">
+      <c r="F746" s="2">
         <v>31.5</v>
       </c>
-      <c r="G746">
+      <c r="G746" s="2">
         <v>49.5</v>
       </c>
-      <c r="H746">
+      <c r="H746" s="2">
         <v>19.5</v>
       </c>
-      <c r="I746">
+      <c r="I746" s="2">
         <v>3.75</v>
       </c>
-      <c r="J746">
+      <c r="J746" s="2">
         <v>3.75</v>
       </c>
     </row>
     <row r="747" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A747" s="29">
+      <c r="A747" s="16">
         <v>46029</v>
       </c>
-      <c r="B747" s="30">
+      <c r="B747" s="17">
         <v>0.5625</v>
       </c>
-      <c r="C747" t="s">
+      <c r="C747" s="2" t="s">
         <v>1106</v>
       </c>
-      <c r="D747" t="s">
+      <c r="D747" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E747">
+      <c r="E747" s="2">
         <v>155</v>
       </c>
-      <c r="F747">
+      <c r="F747" s="2">
         <v>15.5</v>
       </c>
-      <c r="G747">
+      <c r="G747" s="2">
         <v>15</v>
       </c>
-      <c r="H747">
-        <v>2</v>
-      </c>
-      <c r="I747">
+      <c r="H747" s="2">
+        <v>2</v>
+      </c>
+      <c r="I747" s="2">
         <v>7</v>
       </c>
-      <c r="J747">
+      <c r="J747" s="2">
         <v>1.8</v>
       </c>
     </row>
     <row r="748" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A748" s="29">
+      <c r="A748" s="16">
         <v>46029</v>
       </c>
-      <c r="B748" s="30">
+      <c r="B748" s="17">
         <v>0.58333333333333337</v>
       </c>
-      <c r="C748" t="s">
+      <c r="C748" s="2" t="s">
         <v>1107</v>
       </c>
-      <c r="D748" t="s">
+      <c r="D748" s="2" t="s">
         <v>1056</v>
       </c>
-      <c r="E748">
+      <c r="E748" s="2">
         <v>165</v>
       </c>
-      <c r="F748">
+      <c r="F748" s="2">
         <v>5</v>
       </c>
-      <c r="G748">
+      <c r="G748" s="2">
         <v>9</v>
       </c>
-      <c r="H748">
+      <c r="H748" s="2">
         <v>13.5</v>
       </c>
-      <c r="I748">
+      <c r="I748" s="2">
         <v>1.5</v>
       </c>
-      <c r="J748">
+      <c r="J748" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="749" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A749" s="29">
+      <c r="A749" s="16">
         <v>46029</v>
       </c>
-      <c r="B749" s="30">
+      <c r="B749" s="17">
         <v>0.64583333333333337</v>
       </c>
-      <c r="C749" t="s">
+      <c r="C749" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="D749" t="s">
+      <c r="D749" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E749">
+      <c r="E749" s="2">
         <v>77</v>
       </c>
-      <c r="F749">
-        <v>2</v>
-      </c>
-      <c r="G749">
+      <c r="F749" s="2">
+        <v>2</v>
+      </c>
+      <c r="G749" s="2">
         <v>11</v>
       </c>
-      <c r="H749">
-        <v>2</v>
-      </c>
-      <c r="I749">
+      <c r="H749" s="2">
+        <v>2</v>
+      </c>
+      <c r="I749" s="2">
         <v>7</v>
       </c>
-      <c r="J749">
+      <c r="J749" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="750" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A750" s="29">
+      <c r="A750" s="16">
         <v>46029</v>
       </c>
-      <c r="B750" s="30">
+      <c r="B750" s="17">
         <v>0.8125</v>
       </c>
-      <c r="C750" t="s">
+      <c r="C750" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="D750" t="s">
+      <c r="D750" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E750">
+      <c r="E750" s="2">
         <v>380</v>
       </c>
-      <c r="F750">
+      <c r="F750" s="2">
         <v>25</v>
       </c>
-      <c r="G750">
+      <c r="G750" s="2">
         <v>46</v>
       </c>
-      <c r="H750">
+      <c r="H750" s="2">
         <v>10</v>
       </c>
-      <c r="I750">
-        <v>2</v>
-      </c>
-      <c r="J750">
+      <c r="I750" s="2">
+        <v>2</v>
+      </c>
+      <c r="J750" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="751" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A751" s="29">
+      <c r="A751" s="16">
         <v>46029</v>
       </c>
-      <c r="B751" s="30">
+      <c r="B751" s="17">
         <v>0.83333333333333337</v>
       </c>
-      <c r="C751" t="s">
+      <c r="C751" s="2" t="s">
         <v>1110</v>
       </c>
-      <c r="D751" t="s">
+      <c r="D751" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E751">
+      <c r="E751" s="2">
         <v>155</v>
       </c>
-      <c r="F751">
+      <c r="F751" s="2">
         <v>15.5</v>
       </c>
-      <c r="G751">
+      <c r="G751" s="2">
         <v>15</v>
       </c>
-      <c r="H751">
-        <v>2</v>
-      </c>
-      <c r="I751">
+      <c r="H751" s="2">
+        <v>2</v>
+      </c>
+      <c r="I751" s="2">
         <v>7</v>
       </c>
-      <c r="J751">
+      <c r="J751" s="2">
         <v>1.8</v>
       </c>
     </row>
     <row r="752" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A752" s="29">
+      <c r="A752" s="16">
         <v>46030</v>
       </c>
-      <c r="B752" s="30">
+      <c r="B752" s="17">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C752" t="s">
+      <c r="C752" s="2" t="s">
         <v>1111</v>
       </c>
-      <c r="D752" t="s">
+      <c r="D752" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E752">
+      <c r="E752" s="2">
         <v>77</v>
       </c>
-      <c r="F752">
-        <v>2</v>
-      </c>
-      <c r="G752">
+      <c r="F752" s="2">
+        <v>2</v>
+      </c>
+      <c r="G752" s="2">
         <v>11</v>
       </c>
-      <c r="H752">
-        <v>2</v>
-      </c>
-      <c r="I752">
+      <c r="H752" s="2">
+        <v>2</v>
+      </c>
+      <c r="I752" s="2">
         <v>7</v>
       </c>
-      <c r="J752">
+      <c r="J752" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="753" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A753" s="29">
+      <c r="A753" s="16">
         <v>46030</v>
       </c>
-      <c r="B753" s="30">
+      <c r="B753" s="17">
         <v>0.35416666666666669</v>
       </c>
-      <c r="C753" t="s">
+      <c r="C753" s="2" t="s">
         <v>1112</v>
       </c>
-      <c r="D753" t="s">
+      <c r="D753" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E753">
+      <c r="E753" s="2">
         <v>128</v>
       </c>
-      <c r="F753">
+      <c r="F753" s="2">
         <v>6.6</v>
       </c>
-      <c r="G753">
+      <c r="G753" s="2">
         <v>9.6</v>
       </c>
-      <c r="H753">
+      <c r="H753" s="2">
         <v>5.3</v>
       </c>
-      <c r="I753">
+      <c r="I753" s="2">
         <v>5.3</v>
       </c>
-      <c r="J753">
+      <c r="J753" s="2">
         <v>2.7</v>
       </c>
     </row>
     <row r="754" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A754" s="29">
+      <c r="A754" s="16">
         <v>46030</v>
       </c>
-      <c r="B754" s="30">
+      <c r="B754" s="17">
         <v>0.375</v>
       </c>
-      <c r="C754" t="s">
+      <c r="C754" s="2" t="s">
         <v>1113</v>
       </c>
-      <c r="D754" t="s">
+      <c r="D754" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="E754">
+      <c r="E754" s="2">
         <v>82.5</v>
       </c>
-      <c r="F754">
+      <c r="F754" s="2">
         <v>2.5</v>
       </c>
-      <c r="G754">
+      <c r="G754" s="2">
         <v>4.5</v>
       </c>
-      <c r="H754">
+      <c r="H754" s="2">
         <v>6.75</v>
       </c>
-      <c r="I754">
+      <c r="I754" s="2">
         <v>0.75</v>
       </c>
-      <c r="J754">
+      <c r="J754" s="2">
         <v>0.5</v>
       </c>
     </row>
     <row r="755" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A755" s="29">
+      <c r="A755" s="16">
         <v>46030</v>
       </c>
-      <c r="B755" s="30">
+      <c r="B755" s="17">
         <v>0.52083333333333337</v>
       </c>
-      <c r="C755" t="s">
+      <c r="C755" s="2" t="s">
         <v>1115</v>
       </c>
-      <c r="D755" t="s">
+      <c r="D755" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E755">
+      <c r="E755" s="2">
         <v>290</v>
       </c>
-      <c r="F755">
+      <c r="F755" s="2">
         <v>11</v>
       </c>
-      <c r="G755">
+      <c r="G755" s="2">
         <v>18</v>
       </c>
-      <c r="H755">
+      <c r="H755" s="2">
         <v>18</v>
       </c>
-      <c r="I755">
+      <c r="I755" s="2">
         <v>0</v>
       </c>
-      <c r="J755">
+      <c r="J755" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="756" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A756" s="29">
+      <c r="A756" s="16">
         <v>46030</v>
       </c>
-      <c r="B756" s="30">
+      <c r="B756" s="17">
         <v>0.64583333333333337</v>
       </c>
-      <c r="C756" t="s">
+      <c r="C756" s="2" t="s">
         <v>1116</v>
       </c>
-      <c r="D756" t="s">
+      <c r="D756" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E756">
+      <c r="E756" s="2">
         <v>380</v>
       </c>
-      <c r="F756">
+      <c r="F756" s="2">
         <v>25</v>
       </c>
-      <c r="G756">
+      <c r="G756" s="2">
         <v>46</v>
       </c>
-      <c r="H756">
+      <c r="H756" s="2">
         <v>10</v>
       </c>
-      <c r="I756">
-        <v>2</v>
-      </c>
-      <c r="J756">
+      <c r="I756" s="2">
+        <v>2</v>
+      </c>
+      <c r="J756" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="757" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A757" s="29">
+      <c r="A757" s="16">
         <v>46030</v>
       </c>
-      <c r="B757" s="30">
+      <c r="B757" s="17">
         <v>0.66666666666666663</v>
       </c>
-      <c r="C757" t="s">
+      <c r="C757" s="2" t="s">
         <v>1117</v>
       </c>
-      <c r="D757" t="s">
+      <c r="D757" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E757">
+      <c r="E757" s="2">
         <v>155</v>
       </c>
-      <c r="F757">
+      <c r="F757" s="2">
         <v>15.5</v>
       </c>
-      <c r="G757">
+      <c r="G757" s="2">
         <v>15</v>
       </c>
-      <c r="H757">
-        <v>2</v>
-      </c>
-      <c r="I757">
+      <c r="H757" s="2">
+        <v>2</v>
+      </c>
+      <c r="I757" s="2">
         <v>7</v>
       </c>
-      <c r="J757">
+      <c r="J757" s="2">
         <v>1.8</v>
       </c>
     </row>
     <row r="758" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A758" s="29">
+      <c r="A758" s="16">
         <v>46030</v>
       </c>
-      <c r="B758" s="30">
+      <c r="B758" s="17">
         <v>0.72916666666666663</v>
       </c>
-      <c r="C758" t="s">
+      <c r="C758" s="2" t="s">
         <v>1118</v>
       </c>
-      <c r="D758" t="s">
+      <c r="D758" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E758">
+      <c r="E758" s="2">
         <v>77</v>
       </c>
-      <c r="F758">
-        <v>2</v>
-      </c>
-      <c r="G758">
+      <c r="F758" s="2">
+        <v>2</v>
+      </c>
+      <c r="G758" s="2">
         <v>11</v>
       </c>
-      <c r="H758">
-        <v>2</v>
-      </c>
-      <c r="I758">
+      <c r="H758" s="2">
+        <v>2</v>
+      </c>
+      <c r="I758" s="2">
         <v>7</v>
       </c>
-      <c r="J758">
+      <c r="J758" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="759" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A759" s="29">
+      <c r="A759" s="16">
         <v>46030</v>
       </c>
-      <c r="B759" s="30">
+      <c r="B759" s="17">
         <v>0.75</v>
       </c>
-      <c r="C759" t="s">
+      <c r="C759" s="2" t="s">
         <v>1119</v>
       </c>
-      <c r="D759" t="s">
+      <c r="D759" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="E759">
+      <c r="E759" s="2">
         <v>82.5</v>
       </c>
-      <c r="F759">
+      <c r="F759" s="2">
         <v>2.5</v>
       </c>
-      <c r="G759">
+      <c r="G759" s="2">
         <v>4.5</v>
       </c>
-      <c r="H759">
+      <c r="H759" s="2">
         <v>6.75</v>
       </c>
-      <c r="I759">
+      <c r="I759" s="2">
         <v>0.75</v>
       </c>
-      <c r="J759">
+      <c r="J759" s="2">
         <v>0.5</v>
       </c>
     </row>
     <row r="760" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A760" s="29">
+      <c r="A760" s="16">
         <v>46030</v>
       </c>
-      <c r="B760" s="30">
+      <c r="B760" s="17">
         <v>0.77083333333333337</v>
       </c>
-      <c r="C760" t="s">
+      <c r="C760" s="2" t="s">
         <v>1120</v>
       </c>
-      <c r="D760" t="s">
+      <c r="D760" s="2" t="s">
         <v>808</v>
       </c>
-      <c r="E760">
+      <c r="E760" s="2">
         <v>145</v>
       </c>
-      <c r="F760">
+      <c r="F760" s="2">
         <v>5.5</v>
       </c>
-      <c r="G760">
+      <c r="G760" s="2">
         <v>9</v>
       </c>
-      <c r="H760">
+      <c r="H760" s="2">
         <v>9</v>
       </c>
-      <c r="I760">
+      <c r="I760" s="2">
         <v>0</v>
       </c>
-      <c r="J760">
+      <c r="J760" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="761" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A761" s="29">
+      <c r="A761" s="16">
         <v>46030</v>
       </c>
-      <c r="B761" s="30">
+      <c r="B761" s="17">
         <v>0.79166666666666663</v>
       </c>
-      <c r="C761" t="s">
+      <c r="C761" s="2" t="s">
         <v>1121</v>
       </c>
-      <c r="D761" t="s">
+      <c r="D761" s="2" t="s">
         <v>932</v>
       </c>
-      <c r="E761">
+      <c r="E761" s="2">
         <v>335</v>
       </c>
-      <c r="F761">
+      <c r="F761" s="2">
         <v>21</v>
       </c>
-      <c r="G761">
+      <c r="G761" s="2">
         <v>33</v>
       </c>
-      <c r="H761">
+      <c r="H761" s="2">
         <v>13</v>
       </c>
-      <c r="I761">
+      <c r="I761" s="2">
         <v>2.5</v>
       </c>
-      <c r="J761">
+      <c r="J761" s="2">
         <v>2.5</v>
       </c>
     </row>
     <row r="762" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A762" s="29">
+      <c r="A762" s="16">
         <v>46031</v>
       </c>
-      <c r="B762" s="30">
+      <c r="B762" s="17">
         <v>0.35416666666666669</v>
       </c>
-      <c r="C762" t="s">
+      <c r="C762" s="2" t="s">
         <v>1122</v>
       </c>
-      <c r="D762" t="s">
+      <c r="D762" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E762">
+      <c r="E762" s="2">
         <v>77</v>
       </c>
-      <c r="F762">
-        <v>2</v>
-      </c>
-      <c r="G762">
+      <c r="F762" s="2">
+        <v>2</v>
+      </c>
+      <c r="G762" s="2">
         <v>11</v>
       </c>
-      <c r="H762">
-        <v>2</v>
-      </c>
-      <c r="I762">
+      <c r="H762" s="2">
+        <v>2</v>
+      </c>
+      <c r="I762" s="2">
         <v>7</v>
       </c>
-      <c r="J762">
+      <c r="J762" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="763" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A763" s="29">
+      <c r="A763" s="16">
         <v>46031</v>
       </c>
-      <c r="B763" s="30">
+      <c r="B763" s="17">
         <v>0.39583333333333331</v>
       </c>
-      <c r="C763" t="s">
+      <c r="C763" s="2" t="s">
         <v>1123</v>
       </c>
-      <c r="D763" t="s">
+      <c r="D763" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E763">
+      <c r="E763" s="2">
         <v>128</v>
       </c>
-      <c r="F763">
+      <c r="F763" s="2">
         <v>6.6</v>
       </c>
-      <c r="G763">
+      <c r="G763" s="2">
         <v>9.6</v>
       </c>
-      <c r="H763">
+      <c r="H763" s="2">
         <v>5.3</v>
       </c>
-      <c r="I763">
+      <c r="I763" s="2">
         <v>5.3</v>
       </c>
-      <c r="J763">
+      <c r="J763" s="2">
         <v>2.7</v>
       </c>
     </row>
     <row r="764" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A764" s="29">
+      <c r="A764" s="16">
         <v>46031</v>
       </c>
-      <c r="B764" s="30">
+      <c r="B764" s="17">
         <v>0.47916666666666669</v>
       </c>
-      <c r="C764" t="s">
+      <c r="C764" s="2" t="s">
         <v>1124</v>
       </c>
-      <c r="D764" t="s">
+      <c r="D764" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E764">
+      <c r="E764" s="2">
         <v>155</v>
       </c>
-      <c r="F764">
+      <c r="F764" s="2">
         <v>15.5</v>
       </c>
-      <c r="G764">
+      <c r="G764" s="2">
         <v>15</v>
       </c>
-      <c r="H764">
-        <v>2</v>
-      </c>
-      <c r="I764">
+      <c r="H764" s="2">
+        <v>2</v>
+      </c>
+      <c r="I764" s="2">
         <v>7</v>
       </c>
-      <c r="J764">
+      <c r="J764" s="2">
         <v>1.8</v>
       </c>
     </row>
     <row r="765" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A765" s="29">
+      <c r="A765" s="16">
         <v>46031</v>
       </c>
-      <c r="B765" s="30">
+      <c r="B765" s="17">
         <v>0.58333333333333337</v>
       </c>
-      <c r="C765" t="s">
+      <c r="C765" s="2" t="s">
         <v>1125</v>
       </c>
-      <c r="D765" t="s">
+      <c r="D765" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E765">
+      <c r="E765" s="2">
         <v>290</v>
       </c>
-      <c r="F765">
+      <c r="F765" s="2">
         <v>11</v>
       </c>
-      <c r="G765">
+      <c r="G765" s="2">
         <v>18</v>
       </c>
-      <c r="H765">
+      <c r="H765" s="2">
         <v>18</v>
       </c>
-      <c r="I765">
+      <c r="I765" s="2">
         <v>0</v>
       </c>
-      <c r="J765">
+      <c r="J765" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="766" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A766" s="29">
+      <c r="A766" s="16">
         <v>46031</v>
       </c>
-      <c r="B766" s="30">
+      <c r="B766" s="17">
         <v>0.75</v>
       </c>
-      <c r="C766" t="s">
+      <c r="C766" s="2" t="s">
         <v>1126</v>
       </c>
-      <c r="D766" t="s">
+      <c r="D766" s="2" t="s">
         <v>1127</v>
       </c>
-      <c r="E766">
+      <c r="E766" s="2">
         <v>400</v>
       </c>
-      <c r="F766">
+      <c r="F766" s="2">
         <v>25</v>
       </c>
-      <c r="G766">
+      <c r="G766" s="2">
         <v>40</v>
       </c>
-      <c r="H766">
+      <c r="H766" s="2">
         <v>15</v>
       </c>
-      <c r="I766">
+      <c r="I766" s="2">
         <v>5</v>
       </c>
-      <c r="J766">
+      <c r="J766" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="767" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A767" s="29">
+      <c r="A767" s="16">
         <v>46031</v>
       </c>
-      <c r="B767" s="30">
+      <c r="B767" s="17">
         <v>0.77083333333333337</v>
       </c>
-      <c r="C767" t="s">
+      <c r="C767" s="2" t="s">
         <v>1128</v>
       </c>
-      <c r="D767" t="s">
+      <c r="D767" s="2" t="s">
         <v>917</v>
       </c>
-      <c r="E767">
+      <c r="E767" s="2">
         <v>502.5</v>
       </c>
-      <c r="F767">
+      <c r="F767" s="2">
         <v>31.5</v>
       </c>
-      <c r="G767">
+      <c r="G767" s="2">
         <v>49.5</v>
       </c>
-      <c r="H767">
+      <c r="H767" s="2">
         <v>19.5</v>
       </c>
-      <c r="I767">
+      <c r="I767" s="2">
         <v>3.75</v>
       </c>
-      <c r="J767">
+      <c r="J767" s="2">
         <v>3.75</v>
       </c>
     </row>
     <row r="768" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A768" s="29">
+      <c r="A768" s="16">
         <v>46031</v>
       </c>
-      <c r="B768" s="30">
+      <c r="B768" s="17">
         <v>0.79166666666666663</v>
       </c>
-      <c r="C768" t="s">
+      <c r="C768" s="2" t="s">
         <v>1129</v>
       </c>
-      <c r="D768" t="s">
+      <c r="D768" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E768">
+      <c r="E768" s="2">
         <v>155</v>
       </c>
-      <c r="F768">
+      <c r="F768" s="2">
         <v>15.5</v>
       </c>
-      <c r="G768">
+      <c r="G768" s="2">
         <v>15</v>
       </c>
-      <c r="H768">
-        <v>2</v>
-      </c>
-      <c r="I768">
+      <c r="H768" s="2">
+        <v>2</v>
+      </c>
+      <c r="I768" s="2">
         <v>7</v>
       </c>
-      <c r="J768">
+      <c r="J768" s="2">
         <v>1.8</v>
       </c>
     </row>
     <row r="769" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A769" s="29">
+      <c r="A769" s="16">
         <v>46032</v>
       </c>
-      <c r="B769" s="30">
+      <c r="B769" s="17">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C769" t="s">
+      <c r="C769" s="2" t="s">
         <v>1130</v>
       </c>
-      <c r="D769" t="s">
+      <c r="D769" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E769">
+      <c r="E769" s="2">
         <v>77</v>
       </c>
-      <c r="F769">
-        <v>2</v>
-      </c>
-      <c r="G769">
+      <c r="F769" s="2">
+        <v>2</v>
+      </c>
+      <c r="G769" s="2">
         <v>11</v>
       </c>
-      <c r="H769">
-        <v>2</v>
-      </c>
-      <c r="I769">
+      <c r="H769" s="2">
+        <v>2</v>
+      </c>
+      <c r="I769" s="2">
         <v>7</v>
       </c>
-      <c r="J769">
+      <c r="J769" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="770" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A770" s="29">
+      <c r="A770" s="16">
         <v>46032</v>
       </c>
-      <c r="B770" s="30">
+      <c r="B770" s="17">
         <v>0.35416666666666669</v>
       </c>
-      <c r="C770" t="s">
+      <c r="C770" s="2" t="s">
         <v>1131</v>
       </c>
-      <c r="D770" t="s">
+      <c r="D770" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E770">
+      <c r="E770" s="2">
         <v>128</v>
       </c>
-      <c r="F770">
+      <c r="F770" s="2">
         <v>6.6</v>
       </c>
-      <c r="G770">
+      <c r="G770" s="2">
         <v>9.6</v>
       </c>
-      <c r="H770">
+      <c r="H770" s="2">
         <v>5.3</v>
       </c>
-      <c r="I770">
+      <c r="I770" s="2">
         <v>5.3</v>
       </c>
-      <c r="J770">
+      <c r="J770" s="2">
         <v>2.7</v>
       </c>
     </row>
     <row r="771" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A771" s="29">
+      <c r="A771" s="16">
         <v>46032</v>
       </c>
-      <c r="B771" s="30">
+      <c r="B771" s="17">
         <v>0.58333333333333337</v>
       </c>
-      <c r="C771" t="s">
+      <c r="C771" s="2" t="s">
         <v>1132</v>
       </c>
-      <c r="D771" t="s">
+      <c r="D771" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E771">
+      <c r="E771" s="2">
         <v>290</v>
       </c>
-      <c r="F771">
+      <c r="F771" s="2">
         <v>11</v>
       </c>
-      <c r="G771">
+      <c r="G771" s="2">
         <v>18</v>
       </c>
-      <c r="H771">
+      <c r="H771" s="2">
         <v>18</v>
       </c>
-      <c r="I771">
+      <c r="I771" s="2">
         <v>0</v>
       </c>
-      <c r="J771">
+      <c r="J771" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="772" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A772" s="29">
+      <c r="A772" s="16">
         <v>46032</v>
       </c>
-      <c r="B772" s="30">
+      <c r="B772" s="17">
         <v>0.60416666666666663</v>
       </c>
-      <c r="C772" t="s">
+      <c r="C772" s="2" t="s">
         <v>1133</v>
       </c>
-      <c r="D772" t="s">
+      <c r="D772" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="E772">
+      <c r="E772" s="2">
         <v>78.75</v>
       </c>
-      <c r="F772">
+      <c r="F772" s="2">
         <v>1.95</v>
       </c>
-      <c r="G772">
+      <c r="G772" s="2">
         <v>16.8</v>
       </c>
-      <c r="H772">
+      <c r="H772" s="2">
         <v>0.55000000000000004</v>
       </c>
-      <c r="I772">
+      <c r="I772" s="2">
         <v>11.25</v>
       </c>
-      <c r="J772">
+      <c r="J772" s="2">
         <v>7.5</v>
       </c>
     </row>
     <row r="773" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A773" s="29">
+      <c r="A773" s="16">
         <v>46032</v>
       </c>
-      <c r="B773" s="30">
+      <c r="B773" s="17">
         <v>0.625</v>
       </c>
-      <c r="C773" t="s">
+      <c r="C773" s="2" t="s">
         <v>1134</v>
       </c>
-      <c r="D773" t="s">
+      <c r="D773" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="E773">
+      <c r="E773" s="2">
         <v>82.5</v>
       </c>
-      <c r="F773">
+      <c r="F773" s="2">
         <v>2.5</v>
       </c>
-      <c r="G773">
+      <c r="G773" s="2">
         <v>4.5</v>
       </c>
-      <c r="H773">
+      <c r="H773" s="2">
         <v>6.75</v>
       </c>
-      <c r="I773">
+      <c r="I773" s="2">
         <v>0.75</v>
       </c>
-      <c r="J773">
+      <c r="J773" s="2">
         <v>0.5</v>
       </c>
     </row>
     <row r="774" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A774" s="29">
+      <c r="A774" s="16">
         <v>46032</v>
       </c>
-      <c r="B774" s="30">
+      <c r="B774" s="17">
         <v>0.6875</v>
       </c>
-      <c r="C774" t="s">
+      <c r="C774" s="2" t="s">
         <v>1135</v>
       </c>
-      <c r="D774" t="s">
+      <c r="D774" s="2" t="s">
         <v>932</v>
       </c>
-      <c r="E774">
+      <c r="E774" s="2">
         <v>335</v>
       </c>
-      <c r="F774">
+      <c r="F774" s="2">
         <v>21</v>
       </c>
-      <c r="G774">
+      <c r="G774" s="2">
         <v>33</v>
       </c>
-      <c r="H774">
+      <c r="H774" s="2">
         <v>13</v>
       </c>
-      <c r="I774">
+      <c r="I774" s="2">
         <v>2.5</v>
       </c>
-      <c r="J774">
+      <c r="J774" s="2">
         <v>2.5</v>
       </c>
     </row>
     <row r="775" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A775" s="29">
+      <c r="A775" s="16">
         <v>46032</v>
       </c>
-      <c r="B775" s="30">
+      <c r="B775" s="17">
         <v>0.70833333333333337</v>
       </c>
-      <c r="C775" t="s">
+      <c r="C775" s="2" t="s">
         <v>1136</v>
       </c>
-      <c r="D775" t="s">
+      <c r="D775" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E775">
+      <c r="E775" s="2">
         <v>155</v>
       </c>
-      <c r="F775">
+      <c r="F775" s="2">
         <v>15.5</v>
       </c>
-      <c r="G775">
+      <c r="G775" s="2">
         <v>15</v>
       </c>
-      <c r="H775">
-        <v>2</v>
-      </c>
-      <c r="I775">
+      <c r="H775" s="2">
+        <v>2</v>
+      </c>
+      <c r="I775" s="2">
         <v>7</v>
       </c>
-      <c r="J775">
+      <c r="J775" s="2">
         <v>1.8</v>
       </c>
     </row>
     <row r="776" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A776" s="29">
+      <c r="A776" s="16">
         <v>46032</v>
       </c>
-      <c r="B776" s="30">
+      <c r="B776" s="17">
         <v>0.8125</v>
       </c>
-      <c r="C776" t="s">
+      <c r="C776" s="2" t="s">
         <v>1137</v>
       </c>
-      <c r="D776" t="s">
+      <c r="D776" s="2" t="s">
         <v>1138</v>
       </c>
-      <c r="E776">
+      <c r="E776" s="2">
         <v>460</v>
       </c>
-      <c r="F776">
+      <c r="F776" s="2">
         <v>30</v>
       </c>
-      <c r="G776">
+      <c r="G776" s="2">
         <v>50</v>
       </c>
-      <c r="H776">
+      <c r="H776" s="2">
         <v>15</v>
       </c>
-      <c r="I776">
-        <v>2</v>
-      </c>
-      <c r="J776">
+      <c r="I776" s="2">
+        <v>2</v>
+      </c>
+      <c r="J776" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="777" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A777" s="29">
+      <c r="A777" s="16">
         <v>46033</v>
       </c>
-      <c r="B777" s="30">
+      <c r="B777" s="17">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C777" t="s">
+      <c r="C777" s="2" t="s">
         <v>1145</v>
       </c>
-      <c r="D777" t="s">
+      <c r="D777" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E777">
+      <c r="E777" s="2">
         <v>77</v>
       </c>
-      <c r="F777">
-        <v>2</v>
-      </c>
-      <c r="G777">
+      <c r="F777" s="2">
+        <v>2</v>
+      </c>
+      <c r="G777" s="2">
         <v>11</v>
       </c>
-      <c r="H777">
-        <v>2</v>
-      </c>
-      <c r="I777">
+      <c r="H777" s="2">
+        <v>2</v>
+      </c>
+      <c r="I777" s="2">
         <v>7</v>
       </c>
-      <c r="J777">
+      <c r="J777" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="778" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A778" s="29">
+      <c r="A778" s="16">
         <v>46033</v>
       </c>
-      <c r="B778" s="30">
+      <c r="B778" s="17">
         <v>0.35416666666666669</v>
       </c>
-      <c r="C778" t="s">
+      <c r="C778" s="2" t="s">
         <v>1146</v>
       </c>
-      <c r="D778" t="s">
+      <c r="D778" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E778">
+      <c r="E778" s="2">
         <v>128</v>
       </c>
-      <c r="F778">
+      <c r="F778" s="2">
         <v>6.6</v>
       </c>
-      <c r="G778">
+      <c r="G778" s="2">
         <v>9.6</v>
       </c>
-      <c r="H778">
+      <c r="H778" s="2">
         <v>5.3</v>
       </c>
-      <c r="I778">
+      <c r="I778" s="2">
         <v>5.3</v>
       </c>
-      <c r="J778">
+      <c r="J778" s="2">
         <v>2.7</v>
       </c>
     </row>
     <row r="779" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A779" s="29">
+      <c r="A779" s="16">
         <v>46033</v>
       </c>
-      <c r="B779" s="30">
+      <c r="B779" s="17">
         <v>0.41666666666666669</v>
       </c>
-      <c r="C779" t="s">
+      <c r="C779" s="2" t="s">
         <v>1147</v>
       </c>
-      <c r="D779" t="s">
+      <c r="D779" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="E779">
+      <c r="E779" s="2">
         <v>78.75</v>
       </c>
-      <c r="F779">
+      <c r="F779" s="2">
         <v>1.95</v>
       </c>
-      <c r="G779">
+      <c r="G779" s="2">
         <v>16.8</v>
       </c>
-      <c r="H779">
+      <c r="H779" s="2">
         <v>0.55000000000000004</v>
       </c>
-      <c r="I779">
+      <c r="I779" s="2">
         <v>11.25</v>
       </c>
-      <c r="J779">
+      <c r="J779" s="2">
         <v>7.5</v>
       </c>
     </row>
     <row r="780" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A780" s="29">
+      <c r="A780" s="16">
         <v>46033</v>
       </c>
-      <c r="B780" s="30">
+      <c r="B780" s="17">
         <v>0.5</v>
       </c>
-      <c r="C780" t="s">
+      <c r="C780" s="2" t="s">
         <v>1148</v>
       </c>
-      <c r="D780" t="s">
+      <c r="D780" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E780">
+      <c r="E780" s="2">
         <v>290</v>
       </c>
-      <c r="F780">
+      <c r="F780" s="2">
         <v>11</v>
       </c>
-      <c r="G780">
+      <c r="G780" s="2">
         <v>18</v>
       </c>
-      <c r="H780">
+      <c r="H780" s="2">
         <v>18</v>
       </c>
-      <c r="I780">
+      <c r="I780" s="2">
         <v>0</v>
       </c>
-      <c r="J780">
+      <c r="J780" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="781" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A781" s="29">
+      <c r="A781" s="16">
         <v>46033</v>
       </c>
-      <c r="B781" s="30">
+      <c r="B781" s="17">
         <v>0.52083333333333337</v>
       </c>
-      <c r="C781" t="s">
+      <c r="C781" s="2" t="s">
         <v>1149</v>
       </c>
-      <c r="D781" t="s">
+      <c r="D781" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="E781">
+      <c r="E781" s="2">
         <v>175</v>
       </c>
-      <c r="F781">
+      <c r="F781" s="2">
         <v>15.5</v>
       </c>
-      <c r="G781">
+      <c r="G781" s="2">
         <v>20</v>
       </c>
-      <c r="H781">
-        <v>2</v>
-      </c>
-      <c r="I781">
+      <c r="H781" s="2">
+        <v>2</v>
+      </c>
+      <c r="I781" s="2">
         <v>11.5</v>
       </c>
-      <c r="J781">
+      <c r="J781" s="2">
         <v>1.8</v>
       </c>
     </row>
     <row r="782" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A782" s="29">
+      <c r="A782" s="16">
         <v>46033</v>
       </c>
-      <c r="B782" s="30">
+      <c r="B782" s="17">
         <v>0.5625</v>
       </c>
-      <c r="C782" t="s">
+      <c r="C782" s="2" t="s">
         <v>1150</v>
       </c>
-      <c r="D782" t="s">
+      <c r="D782" s="2" t="s">
         <v>1151</v>
       </c>
-      <c r="E782">
+      <c r="E782" s="2">
         <v>330</v>
       </c>
-      <c r="F782">
+      <c r="F782" s="2">
         <v>20</v>
       </c>
-      <c r="G782">
+      <c r="G782" s="2">
         <v>50</v>
       </c>
-      <c r="H782">
+      <c r="H782" s="2">
         <v>8</v>
       </c>
-      <c r="I782">
-        <v>2</v>
-      </c>
-      <c r="J782">
+      <c r="I782" s="2">
+        <v>2</v>
+      </c>
+      <c r="J782" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="783" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A783" s="29">
+      <c r="A783" s="16">
         <v>46033</v>
       </c>
-      <c r="B783" s="30">
+      <c r="B783" s="17">
         <v>0.66666666666666663</v>
       </c>
-      <c r="C783" t="s">
+      <c r="C783" s="2" t="s">
         <v>1152</v>
       </c>
-      <c r="D783" t="s">
+      <c r="D783" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E783">
+      <c r="E783" s="2">
         <v>77</v>
       </c>
-      <c r="F783">
-        <v>2</v>
-      </c>
-      <c r="G783">
+      <c r="F783" s="2">
+        <v>2</v>
+      </c>
+      <c r="G783" s="2">
         <v>11</v>
       </c>
-      <c r="H783">
-        <v>2</v>
-      </c>
-      <c r="I783">
+      <c r="H783" s="2">
+        <v>2</v>
+      </c>
+      <c r="I783" s="2">
         <v>7</v>
       </c>
-      <c r="J783">
+      <c r="J783" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="784" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A784" s="29">
+      <c r="A784" s="16">
         <v>46033</v>
       </c>
-      <c r="B784" s="30">
+      <c r="B784" s="17">
         <v>0.6875</v>
       </c>
-      <c r="C784" t="s">
+      <c r="C784" s="2" t="s">
         <v>1153</v>
       </c>
-      <c r="D784" t="s">
+      <c r="D784" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="E784">
+      <c r="E784" s="2">
         <v>44.5</v>
       </c>
-      <c r="F784">
+      <c r="F784" s="2">
         <v>0.55000000000000004</v>
       </c>
-      <c r="G784">
+      <c r="G784" s="2">
         <v>11.5</v>
       </c>
-      <c r="H784">
+      <c r="H784" s="2">
         <v>0.15</v>
       </c>
-      <c r="I784">
+      <c r="I784" s="2">
         <v>6</v>
       </c>
-      <c r="J784">
+      <c r="J784" s="2">
         <v>1.3</v>
       </c>
     </row>
     <row r="785" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A785" s="29">
+      <c r="A785" s="16">
         <v>46033</v>
       </c>
-      <c r="B785" s="30">
+      <c r="B785" s="17">
         <v>0.70833333333333337</v>
       </c>
-      <c r="C785" t="s">
+      <c r="C785" s="2" t="s">
         <v>1154</v>
       </c>
-      <c r="D785" t="s">
+      <c r="D785" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="E785">
+      <c r="E785" s="2">
         <v>82.5</v>
       </c>
-      <c r="F785">
+      <c r="F785" s="2">
         <v>2.5</v>
       </c>
-      <c r="G785">
+      <c r="G785" s="2">
         <v>4.5</v>
       </c>
-      <c r="H785">
+      <c r="H785" s="2">
         <v>6.75</v>
       </c>
-      <c r="I785">
+      <c r="I785" s="2">
         <v>0.75</v>
       </c>
-      <c r="J785">
+      <c r="J785" s="2">
         <v>0.5</v>
       </c>
     </row>
     <row r="786" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A786" s="29">
+      <c r="A786" s="16">
         <v>46033</v>
       </c>
-      <c r="B786" s="30">
+      <c r="B786" s="17">
         <v>0.77083333333333337</v>
       </c>
-      <c r="C786" t="s">
+      <c r="C786" s="2" t="s">
         <v>1155</v>
       </c>
-      <c r="D786" t="s">
+      <c r="D786" s="2" t="s">
         <v>932</v>
       </c>
-      <c r="E786">
+      <c r="E786" s="2">
         <v>335</v>
       </c>
-      <c r="F786">
+      <c r="F786" s="2">
         <v>21</v>
       </c>
-      <c r="G786">
+      <c r="G786" s="2">
         <v>33</v>
       </c>
-      <c r="H786">
+      <c r="H786" s="2">
         <v>13</v>
       </c>
-      <c r="I786">
+      <c r="I786" s="2">
         <v>2.5</v>
       </c>
-      <c r="J786">
+      <c r="J786" s="2">
         <v>2.5</v>
       </c>
     </row>
     <row r="787" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A787" s="29">
+      <c r="A787" s="16">
         <v>46033</v>
       </c>
-      <c r="B787" s="30">
+      <c r="B787" s="17">
         <v>0.83333333333333337</v>
       </c>
-      <c r="C787" t="s">
+      <c r="C787" s="2" t="s">
         <v>1156</v>
       </c>
-      <c r="D787" t="s">
+      <c r="D787" s="2" t="s">
         <v>1157</v>
       </c>
-      <c r="E787">
+      <c r="E787" s="2">
         <v>78</v>
       </c>
-      <c r="F787">
+      <c r="F787" s="2">
         <v>0.6</v>
       </c>
-      <c r="G787">
+      <c r="G787" s="2">
         <v>20.8</v>
       </c>
-      <c r="H787">
+      <c r="H787" s="2">
         <v>0.2</v>
       </c>
-      <c r="I787">
+      <c r="I787" s="2">
         <v>16.100000000000001</v>
       </c>
-      <c r="J787">
+      <c r="J787" s="2">
         <v>3.5</v>
       </c>
     </row>
     <row r="788" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A788" s="29">
+      <c r="A788" s="16">
         <v>46033</v>
       </c>
-      <c r="B788" s="30">
+      <c r="B788" s="17">
         <v>0.85416666666666663</v>
       </c>
-      <c r="C788" t="s">
+      <c r="C788" s="2" t="s">
         <v>1158</v>
       </c>
-      <c r="D788" t="s">
+      <c r="D788" s="2" t="s">
         <v>1159</v>
       </c>
-      <c r="E788">
+      <c r="E788" s="2">
         <v>300</v>
       </c>
-      <c r="F788">
+      <c r="F788" s="2">
         <v>18</v>
       </c>
-      <c r="G788">
+      <c r="G788" s="2">
         <v>20</v>
       </c>
-      <c r="H788">
+      <c r="H788" s="2">
         <v>18</v>
       </c>
-      <c r="I788">
-        <v>2</v>
-      </c>
-      <c r="J788">
+      <c r="I788" s="2">
+        <v>2</v>
+      </c>
+      <c r="J788" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="789" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A789" s="29">
+      <c r="A789" s="16">
         <v>46034</v>
       </c>
-      <c r="B789" s="30">
+      <c r="B789" s="17">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C789" t="s">
+      <c r="C789" s="2" t="s">
         <v>1160</v>
       </c>
-      <c r="D789" t="s">
+      <c r="D789" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E789">
+      <c r="E789" s="2">
         <v>77</v>
       </c>
-      <c r="F789">
-        <v>2</v>
-      </c>
-      <c r="G789">
+      <c r="F789" s="2">
+        <v>2</v>
+      </c>
+      <c r="G789" s="2">
         <v>11</v>
       </c>
-      <c r="H789">
-        <v>2</v>
-      </c>
-      <c r="I789">
+      <c r="H789" s="2">
+        <v>2</v>
+      </c>
+      <c r="I789" s="2">
         <v>7</v>
       </c>
-      <c r="J789">
+      <c r="J789" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="790" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A790" s="29">
+      <c r="A790" s="16">
         <v>46034</v>
       </c>
-      <c r="B790" s="30">
+      <c r="B790" s="17">
         <v>0.35416666666666669</v>
       </c>
-      <c r="C790" t="s">
+      <c r="C790" s="2" t="s">
         <v>1161</v>
       </c>
-      <c r="D790" t="s">
+      <c r="D790" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E790">
+      <c r="E790" s="2">
         <v>128</v>
       </c>
-      <c r="F790">
+      <c r="F790" s="2">
         <v>6.6</v>
       </c>
-      <c r="G790">
+      <c r="G790" s="2">
         <v>9.6</v>
       </c>
-      <c r="H790">
+      <c r="H790" s="2">
         <v>5.3</v>
       </c>
-      <c r="I790">
+      <c r="I790" s="2">
         <v>5.3</v>
       </c>
-      <c r="J790">
+      <c r="J790" s="2">
         <v>2.7</v>
       </c>
     </row>
     <row r="791" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A791" s="29">
+      <c r="A791" s="16">
         <v>46034</v>
       </c>
-      <c r="B791" s="30">
+      <c r="B791" s="17">
         <v>0.375</v>
       </c>
-      <c r="C791" t="s">
+      <c r="C791" s="2" t="s">
         <v>1162</v>
       </c>
-      <c r="D791" t="s">
+      <c r="D791" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="E791">
+      <c r="E791" s="2">
         <v>82.5</v>
       </c>
-      <c r="F791">
+      <c r="F791" s="2">
         <v>2.5</v>
       </c>
-      <c r="G791">
+      <c r="G791" s="2">
         <v>4.5</v>
       </c>
-      <c r="H791">
+      <c r="H791" s="2">
         <v>6.75</v>
       </c>
-      <c r="I791">
+      <c r="I791" s="2">
         <v>0.75</v>
       </c>
-      <c r="J791">
+      <c r="J791" s="2">
         <v>0.5</v>
       </c>
     </row>
     <row r="792" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A792" s="29">
+      <c r="A792" s="16">
         <v>46034</v>
       </c>
-      <c r="B792" s="30">
+      <c r="B792" s="17">
         <v>0.5</v>
       </c>
-      <c r="C792" t="s">
+      <c r="C792" s="2" t="s">
         <v>1163</v>
       </c>
-      <c r="D792" t="s">
+      <c r="D792" s="2" t="s">
         <v>1164</v>
       </c>
-      <c r="E792">
+      <c r="E792" s="2">
         <v>340</v>
       </c>
-      <c r="F792">
+      <c r="F792" s="2">
         <v>18</v>
       </c>
-      <c r="G792">
+      <c r="G792" s="2">
         <v>30</v>
       </c>
-      <c r="H792">
+      <c r="H792" s="2">
         <v>17</v>
       </c>
-      <c r="I792">
-        <v>2</v>
-      </c>
-      <c r="J792">
+      <c r="I792" s="2">
+        <v>2</v>
+      </c>
+      <c r="J792" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="793" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A793" s="29">
+      <c r="A793" s="16">
         <v>46034</v>
       </c>
-      <c r="B793" s="30">
+      <c r="B793" s="17">
         <v>0.70833333333333337</v>
       </c>
-      <c r="C793" t="s">
+      <c r="C793" s="2" t="s">
         <v>1165</v>
       </c>
-      <c r="D793" t="s">
+      <c r="D793" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E793">
+      <c r="E793" s="2">
         <v>77</v>
       </c>
-      <c r="F793">
-        <v>2</v>
-      </c>
-      <c r="G793">
+      <c r="F793" s="2">
+        <v>2</v>
+      </c>
+      <c r="G793" s="2">
         <v>11</v>
       </c>
-      <c r="H793">
-        <v>2</v>
-      </c>
-      <c r="I793">
+      <c r="H793" s="2">
+        <v>2</v>
+      </c>
+      <c r="I793" s="2">
         <v>7</v>
       </c>
-      <c r="J793">
+      <c r="J793" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="794" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A794" s="29">
+      <c r="A794" s="16">
         <v>46034</v>
       </c>
-      <c r="B794" s="30">
+      <c r="B794" s="17">
         <v>0.77083333333333337</v>
       </c>
-      <c r="C794" t="s">
+      <c r="C794" s="2" t="s">
         <v>1166</v>
       </c>
-      <c r="D794" t="s">
+      <c r="D794" s="2" t="s">
         <v>1167</v>
       </c>
-      <c r="E794">
+      <c r="E794" s="2">
         <v>343</v>
       </c>
-      <c r="F794">
+      <c r="F794" s="2">
         <v>20</v>
       </c>
-      <c r="G794">
+      <c r="G794" s="2">
         <v>35</v>
       </c>
-      <c r="H794">
+      <c r="H794" s="2">
         <v>15</v>
       </c>
-      <c r="I794">
+      <c r="I794" s="2">
         <v>5</v>
       </c>
-      <c r="J794">
+      <c r="J794" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="795" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A795" s="29">
+      <c r="A795" s="16">
         <v>46034</v>
       </c>
-      <c r="B795" s="30">
+      <c r="B795" s="17">
         <v>0.79166666666666663</v>
       </c>
-      <c r="C795" t="s">
+      <c r="C795" s="2" t="s">
         <v>1168</v>
       </c>
-      <c r="D795" t="s">
+      <c r="D795" s="2" t="s">
         <v>932</v>
       </c>
-      <c r="E795">
+      <c r="E795" s="2">
         <v>335</v>
       </c>
-      <c r="F795">
+      <c r="F795" s="2">
         <v>21</v>
       </c>
-      <c r="G795">
+      <c r="G795" s="2">
         <v>33</v>
       </c>
-      <c r="H795">
+      <c r="H795" s="2">
         <v>13</v>
       </c>
-      <c r="I795">
+      <c r="I795" s="2">
         <v>2.5</v>
       </c>
-      <c r="J795">
+      <c r="J795" s="2">
         <v>2.5</v>
       </c>
     </row>
     <row r="796" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A796" s="29">
+      <c r="A796" s="16">
         <v>46034</v>
       </c>
-      <c r="B796" s="30">
+      <c r="B796" s="17">
         <v>0.8125</v>
       </c>
-      <c r="C796" t="s">
+      <c r="C796" s="2" t="s">
         <v>1169</v>
       </c>
-      <c r="D796" t="s">
+      <c r="D796" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="E796">
+      <c r="E796" s="2">
         <v>175</v>
       </c>
-      <c r="F796">
+      <c r="F796" s="2">
         <v>15.5</v>
       </c>
-      <c r="G796">
+      <c r="G796" s="2">
         <v>20</v>
       </c>
-      <c r="H796">
-        <v>2</v>
-      </c>
-      <c r="I796">
+      <c r="H796" s="2">
+        <v>2</v>
+      </c>
+      <c r="I796" s="2">
         <v>11.5</v>
       </c>
-      <c r="J796">
+      <c r="J796" s="2">
         <v>1.8</v>
       </c>
     </row>
     <row r="797" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A797" s="29">
+      <c r="A797" s="16">
         <v>46035</v>
       </c>
-      <c r="B797" s="30">
+      <c r="B797" s="17">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C797" t="s">
+      <c r="C797" s="2" t="s">
         <v>1170</v>
       </c>
-      <c r="D797" t="s">
+      <c r="D797" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E797">
+      <c r="E797" s="2">
         <v>77</v>
       </c>
-      <c r="F797">
-        <v>2</v>
-      </c>
-      <c r="G797">
+      <c r="F797" s="2">
+        <v>2</v>
+      </c>
+      <c r="G797" s="2">
         <v>11</v>
       </c>
-      <c r="H797">
-        <v>2</v>
-      </c>
-      <c r="I797">
+      <c r="H797" s="2">
+        <v>2</v>
+      </c>
+      <c r="I797" s="2">
         <v>7</v>
       </c>
-      <c r="J797">
+      <c r="J797" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="798" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A798" s="29">
+      <c r="A798" s="16">
         <v>46035</v>
       </c>
-      <c r="B798" s="30">
+      <c r="B798" s="17">
         <v>0.35416666666666669</v>
       </c>
-      <c r="C798" t="s">
+      <c r="C798" s="2" t="s">
         <v>1171</v>
       </c>
-      <c r="D798" t="s">
+      <c r="D798" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E798">
+      <c r="E798" s="2">
         <v>128</v>
       </c>
-      <c r="F798">
+      <c r="F798" s="2">
         <v>6.6</v>
       </c>
-      <c r="G798">
+      <c r="G798" s="2">
         <v>9.6</v>
       </c>
-      <c r="H798">
+      <c r="H798" s="2">
         <v>5.3</v>
       </c>
-      <c r="I798">
+      <c r="I798" s="2">
         <v>5.3</v>
       </c>
-      <c r="J798">
+      <c r="J798" s="2">
         <v>2.7</v>
       </c>
     </row>
     <row r="799" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A799" s="29">
+      <c r="A799" s="16">
         <v>46035</v>
       </c>
-      <c r="B799" s="30">
+      <c r="B799" s="17">
         <v>0.375</v>
       </c>
-      <c r="C799" t="s">
+      <c r="C799" s="2" t="s">
         <v>1172</v>
       </c>
-      <c r="D799" t="s">
+      <c r="D799" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="E799">
+      <c r="E799" s="2">
         <v>82.5</v>
       </c>
-      <c r="F799">
+      <c r="F799" s="2">
         <v>2.5</v>
       </c>
-      <c r="G799">
+      <c r="G799" s="2">
         <v>4.5</v>
       </c>
-      <c r="H799">
+      <c r="H799" s="2">
         <v>6.75</v>
       </c>
-      <c r="I799">
+      <c r="I799" s="2">
         <v>0.75</v>
       </c>
-      <c r="J799">
+      <c r="J799" s="2">
         <v>0.5</v>
       </c>
     </row>
     <row r="800" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A800" s="29">
+      <c r="A800" s="16">
         <v>46035</v>
       </c>
-      <c r="B800" s="30">
+      <c r="B800" s="17">
         <v>0.39583333333333331</v>
       </c>
-      <c r="C800" t="s">
+      <c r="C800" s="2" t="s">
         <v>1173</v>
       </c>
-      <c r="D800" t="s">
+      <c r="D800" s="2" t="s">
         <v>1157</v>
       </c>
-      <c r="E800">
+      <c r="E800" s="2">
         <v>78</v>
       </c>
-      <c r="F800">
+      <c r="F800" s="2">
         <v>0.6</v>
       </c>
-      <c r="G800">
+      <c r="G800" s="2">
         <v>20.8</v>
       </c>
-      <c r="H800">
+      <c r="H800" s="2">
         <v>0.2</v>
       </c>
-      <c r="I800">
+      <c r="I800" s="2">
         <v>16.100000000000001</v>
       </c>
-      <c r="J800">
+      <c r="J800" s="2">
         <v>3.5</v>
       </c>
     </row>
     <row r="801" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A801" s="29">
+      <c r="A801" s="16">
         <v>46035</v>
       </c>
-      <c r="B801" s="30">
+      <c r="B801" s="17">
         <v>0.41666666666666669</v>
       </c>
-      <c r="C801" t="s">
+      <c r="C801" s="2" t="s">
         <v>1174</v>
       </c>
-      <c r="D801" t="s">
+      <c r="D801" s="2" t="s">
         <v>1175</v>
       </c>
-      <c r="E801">
+      <c r="E801" s="2">
         <v>240</v>
       </c>
-      <c r="F801">
+      <c r="F801" s="2">
         <v>6</v>
       </c>
-      <c r="G801">
+      <c r="G801" s="2">
         <v>40</v>
       </c>
-      <c r="H801">
+      <c r="H801" s="2">
         <v>6</v>
       </c>
-      <c r="I801">
+      <c r="I801" s="2">
         <v>8</v>
       </c>
-      <c r="J801">
+      <c r="J801" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="802" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A802" s="29">
+      <c r="A802" s="16">
         <v>46035</v>
       </c>
-      <c r="B802" s="30">
+      <c r="B802" s="17">
         <v>0.52083333333333337</v>
       </c>
-      <c r="C802" t="s">
+      <c r="C802" s="2" t="s">
         <v>1176</v>
       </c>
-      <c r="D802" t="s">
+      <c r="D802" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E802">
+      <c r="E802" s="2">
         <v>290</v>
       </c>
-      <c r="F802">
+      <c r="F802" s="2">
         <v>11</v>
       </c>
-      <c r="G802">
+      <c r="G802" s="2">
         <v>18</v>
       </c>
-      <c r="H802">
+      <c r="H802" s="2">
         <v>18</v>
       </c>
-      <c r="I802">
+      <c r="I802" s="2">
         <v>0</v>
       </c>
-      <c r="J802">
+      <c r="J802" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="803" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A803" s="29">
+      <c r="A803" s="16">
         <v>46035</v>
       </c>
-      <c r="B803" s="30">
+      <c r="B803" s="17">
         <v>0.70833333333333337</v>
       </c>
-      <c r="C803" t="s">
+      <c r="C803" s="2" t="s">
         <v>1177</v>
       </c>
-      <c r="D803" t="s">
+      <c r="D803" s="2" t="s">
         <v>808</v>
       </c>
-      <c r="E803">
+      <c r="E803" s="2">
         <v>145</v>
       </c>
-      <c r="F803">
+      <c r="F803" s="2">
         <v>5.5</v>
       </c>
-      <c r="G803">
+      <c r="G803" s="2">
         <v>9</v>
       </c>
-      <c r="H803">
+      <c r="H803" s="2">
         <v>9</v>
       </c>
-      <c r="I803">
+      <c r="I803" s="2">
         <v>0</v>
       </c>
-      <c r="J803">
+      <c r="J803" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="804" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A804" s="29">
+      <c r="A804" s="16">
         <v>46035</v>
       </c>
-      <c r="B804" s="30">
+      <c r="B804" s="17">
         <v>0.72916666666666663</v>
       </c>
-      <c r="C804" t="s">
+      <c r="C804" s="2" t="s">
         <v>1178</v>
       </c>
-      <c r="D804" t="s">
+      <c r="D804" s="2" t="s">
         <v>932</v>
       </c>
-      <c r="E804">
+      <c r="E804" s="2">
         <v>335</v>
       </c>
-      <c r="F804">
+      <c r="F804" s="2">
         <v>21</v>
       </c>
-      <c r="G804">
+      <c r="G804" s="2">
         <v>33</v>
       </c>
-      <c r="H804">
+      <c r="H804" s="2">
         <v>13</v>
       </c>
-      <c r="I804">
+      <c r="I804" s="2">
         <v>2.5</v>
       </c>
-      <c r="J804">
+      <c r="J804" s="2">
         <v>2.5</v>
       </c>
     </row>
     <row r="805" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A805" s="29">
+      <c r="A805" s="16">
         <v>46035</v>
       </c>
-      <c r="B805" s="30">
+      <c r="B805" s="17">
         <v>0.75</v>
       </c>
-      <c r="C805" t="s">
+      <c r="C805" s="2" t="s">
         <v>1179</v>
       </c>
-      <c r="D805" t="s">
+      <c r="D805" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="E805">
+      <c r="E805" s="2">
         <v>175</v>
       </c>
-      <c r="F805">
+      <c r="F805" s="2">
         <v>15.5</v>
       </c>
-      <c r="G805">
+      <c r="G805" s="2">
         <v>20</v>
       </c>
-      <c r="H805">
-        <v>2</v>
-      </c>
-      <c r="I805">
+      <c r="H805" s="2">
+        <v>2</v>
+      </c>
+      <c r="I805" s="2">
         <v>11.5</v>
       </c>
-      <c r="J805">
+      <c r="J805" s="2">
         <v>1.8</v>
+      </c>
+    </row>
+    <row r="806" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A806" s="16">
+        <v>46036</v>
+      </c>
+      <c r="B806" s="17">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C806" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D806" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E806" s="2">
+        <v>77</v>
+      </c>
+      <c r="F806" s="2">
+        <v>2</v>
+      </c>
+      <c r="G806" s="2">
+        <v>11</v>
+      </c>
+      <c r="H806" s="2">
+        <v>2</v>
+      </c>
+      <c r="I806" s="2">
+        <v>7</v>
+      </c>
+      <c r="J806" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="807" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A807" s="16">
+        <v>46036</v>
+      </c>
+      <c r="B807" s="17">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C807" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D807" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E807" s="2">
+        <v>256</v>
+      </c>
+      <c r="F807" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="G807" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="H807" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="I807" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="J807" s="2">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="808" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A808" s="16">
+        <v>46036</v>
+      </c>
+      <c r="B808" s="17">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C808" s="2" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D808" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E808" s="2">
+        <v>290</v>
+      </c>
+      <c r="F808" s="2">
+        <v>11</v>
+      </c>
+      <c r="G808" s="2">
+        <v>18</v>
+      </c>
+      <c r="H808" s="2">
+        <v>18</v>
+      </c>
+      <c r="I808" s="2">
+        <v>0</v>
+      </c>
+      <c r="J808" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="809" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A809" s="16">
+        <v>46036</v>
+      </c>
+      <c r="B809" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="C809" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D809" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="E809" s="2">
+        <v>503</v>
+      </c>
+      <c r="F809" s="2">
+        <v>31.5</v>
+      </c>
+      <c r="G809" s="2">
+        <v>49.5</v>
+      </c>
+      <c r="H809" s="2">
+        <v>19.5</v>
+      </c>
+      <c r="I809" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="J809" s="2">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="810" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A810" s="16">
+        <v>46036</v>
+      </c>
+      <c r="B810" s="17">
+        <v>0.625</v>
+      </c>
+      <c r="C810" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D810" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E810" s="2">
+        <v>156</v>
+      </c>
+      <c r="F810" s="2">
+        <v>12.6</v>
+      </c>
+      <c r="G810" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="H810" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="I810" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="J810" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="811" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A811" s="16">
+        <v>46036</v>
+      </c>
+      <c r="B811" s="17">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C811" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D811" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E811" s="2">
+        <v>77</v>
+      </c>
+      <c r="F811" s="2">
+        <v>2</v>
+      </c>
+      <c r="G811" s="2">
+        <v>11</v>
+      </c>
+      <c r="H811" s="2">
+        <v>2</v>
+      </c>
+      <c r="I811" s="2">
+        <v>7</v>
+      </c>
+      <c r="J811" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="812" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A812" s="16">
+        <v>46036</v>
+      </c>
+      <c r="B812" s="17">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C812" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D812" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E812" s="2">
+        <v>89</v>
+      </c>
+      <c r="F812" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G812" s="2">
+        <v>23</v>
+      </c>
+      <c r="H812" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="I812" s="2">
+        <v>12</v>
+      </c>
+      <c r="J812" s="2">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="813" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A813" s="16">
+        <v>46036</v>
+      </c>
+      <c r="B813" s="17">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C813" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D813" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E813" s="2">
+        <v>155</v>
+      </c>
+      <c r="F813" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G813" s="2">
+        <v>15</v>
+      </c>
+      <c r="H813" s="2">
+        <v>2</v>
+      </c>
+      <c r="I813" s="2">
+        <v>7</v>
+      </c>
+      <c r="J813" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="814" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A814" s="16">
+        <v>46036</v>
+      </c>
+      <c r="B814" s="17">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C814" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D814" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E814" s="2">
+        <v>243</v>
+      </c>
+      <c r="F814" s="2">
+        <v>12</v>
+      </c>
+      <c r="G814" s="2">
+        <v>19</v>
+      </c>
+      <c r="H814" s="2">
+        <v>13</v>
+      </c>
+      <c r="I814" s="2">
+        <v>5</v>
+      </c>
+      <c r="J814" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="815" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A815" s="16">
+        <v>46036</v>
+      </c>
+      <c r="B815" s="17">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="C815" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D815" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="E815" s="2">
+        <v>270</v>
+      </c>
+      <c r="F815" s="2">
+        <v>6</v>
+      </c>
+      <c r="G815" s="2">
+        <v>35</v>
+      </c>
+      <c r="H815" s="2">
+        <v>12</v>
+      </c>
+      <c r="I815" s="2">
+        <v>1</v>
+      </c>
+      <c r="J815" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="816" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A816" s="16">
+        <v>46036</v>
+      </c>
+      <c r="B816" s="17">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="C816" s="2" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D816" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E816" s="2">
+        <v>128</v>
+      </c>
+      <c r="F816" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G816" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H816" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I816" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J816" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="817" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A817" s="16">
+        <v>46037</v>
+      </c>
+      <c r="B817" s="17">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C817" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D817" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E817" s="2">
+        <v>77</v>
+      </c>
+      <c r="F817" s="2">
+        <v>2</v>
+      </c>
+      <c r="G817" s="2">
+        <v>11</v>
+      </c>
+      <c r="H817" s="2">
+        <v>2</v>
+      </c>
+      <c r="I817" s="2">
+        <v>7</v>
+      </c>
+      <c r="J817" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="818" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A818" s="16">
+        <v>46037</v>
+      </c>
+      <c r="B818" s="17">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C818" s="2" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D818" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E818" s="2">
+        <v>128</v>
+      </c>
+      <c r="F818" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G818" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H818" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I818" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J818" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="819" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A819" s="16">
+        <v>46037</v>
+      </c>
+      <c r="B819" s="17">
+        <v>0.4375</v>
+      </c>
+      <c r="C819" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D819" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E819" s="2">
+        <v>90</v>
+      </c>
+      <c r="F819" s="2">
+        <v>2</v>
+      </c>
+      <c r="G819" s="2">
+        <v>21</v>
+      </c>
+      <c r="H819" s="2">
+        <v>1</v>
+      </c>
+      <c r="I819" s="2">
+        <v>14</v>
+      </c>
+      <c r="J819" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="820" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A820" s="16">
+        <v>46037</v>
+      </c>
+      <c r="B820" s="17">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C820" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D820" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E820" s="2">
+        <v>290</v>
+      </c>
+      <c r="F820" s="2">
+        <v>11</v>
+      </c>
+      <c r="G820" s="2">
+        <v>18</v>
+      </c>
+      <c r="H820" s="2">
+        <v>18</v>
+      </c>
+      <c r="I820" s="2">
+        <v>0</v>
+      </c>
+      <c r="J820" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="821" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A821" s="16">
+        <v>46037</v>
+      </c>
+      <c r="B821" s="17">
+        <v>0.625</v>
+      </c>
+      <c r="C821" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="D821" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E821" s="2">
+        <v>335</v>
+      </c>
+      <c r="F821" s="2">
+        <v>21</v>
+      </c>
+      <c r="G821" s="2">
+        <v>33</v>
+      </c>
+      <c r="H821" s="2">
+        <v>13</v>
+      </c>
+      <c r="I821" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J821" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="822" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A822" s="16">
+        <v>46037</v>
+      </c>
+      <c r="B822" s="17">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C822" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D822" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E822" s="2">
+        <v>77</v>
+      </c>
+      <c r="F822" s="2">
+        <v>2</v>
+      </c>
+      <c r="G822" s="2">
+        <v>11</v>
+      </c>
+      <c r="H822" s="2">
+        <v>2</v>
+      </c>
+      <c r="I822" s="2">
+        <v>7</v>
+      </c>
+      <c r="J822" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="823" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A823" s="16">
+        <v>46037</v>
+      </c>
+      <c r="B823" s="17">
+        <v>0.75</v>
+      </c>
+      <c r="C823" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="D823" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E823" s="2">
+        <v>380</v>
+      </c>
+      <c r="F823" s="2">
+        <v>25</v>
+      </c>
+      <c r="G823" s="2">
+        <v>46</v>
+      </c>
+      <c r="H823" s="2">
+        <v>10</v>
+      </c>
+      <c r="I823" s="2">
+        <v>2</v>
+      </c>
+      <c r="J823" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="824" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A824" s="16">
+        <v>46037</v>
+      </c>
+      <c r="B824" s="17">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C824" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D824" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E824" s="2">
+        <v>175</v>
+      </c>
+      <c r="F824" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G824" s="2">
+        <v>20</v>
+      </c>
+      <c r="H824" s="2">
+        <v>2</v>
+      </c>
+      <c r="I824" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J824" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="825" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A825" s="16">
+        <v>46037</v>
+      </c>
+      <c r="B825" s="17">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C825" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D825" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E825" s="2">
+        <v>156</v>
+      </c>
+      <c r="F825" s="2">
+        <v>12.6</v>
+      </c>
+      <c r="G825" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="H825" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="I825" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="J825" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="826" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A826" s="16">
+        <v>46038</v>
+      </c>
+      <c r="B826" s="17">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C826" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D826" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E826" s="2">
+        <v>77</v>
+      </c>
+      <c r="F826" s="2">
+        <v>2</v>
+      </c>
+      <c r="G826" s="2">
+        <v>11</v>
+      </c>
+      <c r="H826" s="2">
+        <v>2</v>
+      </c>
+      <c r="I826" s="2">
+        <v>7</v>
+      </c>
+      <c r="J826" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="827" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A827" s="16">
+        <v>46038</v>
+      </c>
+      <c r="B827" s="17">
+        <v>0.3125</v>
+      </c>
+      <c r="C827" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D827" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E827" s="2">
+        <v>128</v>
+      </c>
+      <c r="F827" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G827" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H827" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I827" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J827" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="828" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A828" s="16">
+        <v>46038</v>
+      </c>
+      <c r="B828" s="17">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C828" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D828" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E828" s="2">
+        <v>90</v>
+      </c>
+      <c r="F828" s="2">
+        <v>2</v>
+      </c>
+      <c r="G828" s="2">
+        <v>21</v>
+      </c>
+      <c r="H828" s="2">
+        <v>1</v>
+      </c>
+      <c r="I828" s="2">
+        <v>14</v>
+      </c>
+      <c r="J828" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="829" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A829" s="16">
+        <v>46038</v>
+      </c>
+      <c r="B829" s="17">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C829" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D829" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E829" s="2">
+        <v>175</v>
+      </c>
+      <c r="F829" s="2">
+        <v>4</v>
+      </c>
+      <c r="G829" s="2">
+        <v>28</v>
+      </c>
+      <c r="H829" s="2">
+        <v>6</v>
+      </c>
+      <c r="I829" s="2">
+        <v>12</v>
+      </c>
+      <c r="J829" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="830" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A830" s="16">
+        <v>46038</v>
+      </c>
+      <c r="B830" s="17">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C830" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D830" s="2" t="s">
+        <v>1216</v>
+      </c>
+      <c r="E830" s="2">
+        <v>90</v>
+      </c>
+      <c r="F830" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="G830" s="2">
+        <v>10</v>
+      </c>
+      <c r="H830" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="I830" s="2">
+        <v>9</v>
+      </c>
+      <c r="J830" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="831" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A831" s="16">
+        <v>46038</v>
+      </c>
+      <c r="B831" s="17">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C831" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D831" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E831" s="2">
+        <v>290</v>
+      </c>
+      <c r="F831" s="2">
+        <v>11</v>
+      </c>
+      <c r="G831" s="2">
+        <v>18</v>
+      </c>
+      <c r="H831" s="2">
+        <v>18</v>
+      </c>
+      <c r="I831" s="2">
+        <v>0</v>
+      </c>
+      <c r="J831" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="832" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A832" s="16">
+        <v>46038</v>
+      </c>
+      <c r="B832" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="C832" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="D832" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E832" s="2">
+        <v>155</v>
+      </c>
+      <c r="F832" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G832" s="2">
+        <v>15</v>
+      </c>
+      <c r="H832" s="2">
+        <v>2</v>
+      </c>
+      <c r="I832" s="2">
+        <v>7</v>
+      </c>
+      <c r="J832" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="833" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A833" s="16">
+        <v>46038</v>
+      </c>
+      <c r="B833" s="17">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C833" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D833" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E833" s="2">
+        <v>145</v>
+      </c>
+      <c r="F833" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="G833" s="2">
+        <v>9</v>
+      </c>
+      <c r="H833" s="2">
+        <v>9</v>
+      </c>
+      <c r="I833" s="2">
+        <v>0</v>
+      </c>
+      <c r="J833" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="834" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A834" s="16">
+        <v>46038</v>
+      </c>
+      <c r="B834" s="17">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C834" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D834" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E834" s="2">
+        <v>243</v>
+      </c>
+      <c r="F834" s="2">
+        <v>12</v>
+      </c>
+      <c r="G834" s="2">
+        <v>19</v>
+      </c>
+      <c r="H834" s="2">
+        <v>13</v>
+      </c>
+      <c r="I834" s="2">
+        <v>5</v>
+      </c>
+      <c r="J834" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="835" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A835" s="16">
+        <v>46038</v>
+      </c>
+      <c r="B835" s="17">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C835" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D835" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E835" s="2">
+        <v>335</v>
+      </c>
+      <c r="F835" s="2">
+        <v>21</v>
+      </c>
+      <c r="G835" s="2">
+        <v>33</v>
+      </c>
+      <c r="H835" s="2">
+        <v>13</v>
+      </c>
+      <c r="I835" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J835" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="836" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A836" s="16">
+        <v>46038</v>
+      </c>
+      <c r="B836" s="17">
+        <v>0.75</v>
+      </c>
+      <c r="C836" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D836" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="E836" s="2">
+        <v>270</v>
+      </c>
+      <c r="F836" s="2">
+        <v>6</v>
+      </c>
+      <c r="G836" s="2">
+        <v>35</v>
+      </c>
+      <c r="H836" s="2">
+        <v>12</v>
+      </c>
+      <c r="I836" s="2">
+        <v>1</v>
+      </c>
+      <c r="J836" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="837" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A837" s="16">
+        <v>46038</v>
+      </c>
+      <c r="B837" s="17">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C837" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D837" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="E837" s="2">
+        <v>158</v>
+      </c>
+      <c r="F837" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="G837" s="2">
+        <v>18.3</v>
+      </c>
+      <c r="H837" s="2">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="I837" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="J837" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="838" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A838" s="16">
+        <v>46038</v>
+      </c>
+      <c r="B838" s="17">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C838" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D838" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E838" s="2">
+        <v>128</v>
+      </c>
+      <c r="F838" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G838" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H838" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I838" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J838" s="2">
+        <v>2.7</v>
       </c>
     </row>
   </sheetData>
@@ -29876,12 +31072,13 @@
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F24E0C0-BC77-4AA4-801C-82B038A8B8E4}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -30516,16 +31713,16 @@
       <c r="A32" s="16">
         <v>46031</v>
       </c>
-      <c r="B32" s="31">
+      <c r="B32" s="2">
         <v>97.7</v>
       </c>
-      <c r="C32" s="31">
+      <c r="C32" s="2">
         <v>35.9</v>
       </c>
-      <c r="D32" s="31">
+      <c r="D32" s="2">
         <v>30.7</v>
       </c>
-      <c r="E32" s="31">
+      <c r="E32" s="2">
         <v>49.1</v>
       </c>
       <c r="F32" s="2"/>
@@ -30534,16 +31731,16 @@
       <c r="A33" s="16">
         <v>46033</v>
       </c>
-      <c r="B33" s="31">
+      <c r="B33" s="2">
         <v>97.3</v>
       </c>
-      <c r="C33" s="31">
+      <c r="C33" s="2">
         <v>36.4</v>
       </c>
-      <c r="D33" s="31">
+      <c r="D33" s="2">
         <v>29.5</v>
       </c>
-      <c r="E33" s="31">
+      <c r="E33" s="2">
         <v>49.7</v>
       </c>
       <c r="F33" s="2"/>
@@ -30566,6 +31763,86 @@
       </c>
       <c r="F34" s="2" t="s">
         <v>1184</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="16">
+        <v>46025</v>
+      </c>
+      <c r="B35" s="2">
+        <v>97.4</v>
+      </c>
+      <c r="C35" s="2">
+        <v>35.9</v>
+      </c>
+      <c r="D35" s="2">
+        <v>30.5</v>
+      </c>
+      <c r="E35" s="2">
+        <v>49.1</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="16">
+        <v>46031</v>
+      </c>
+      <c r="B36" s="2">
+        <v>97.7</v>
+      </c>
+      <c r="C36" s="2">
+        <v>35.9</v>
+      </c>
+      <c r="D36" s="2">
+        <v>30.7</v>
+      </c>
+      <c r="E36" s="2">
+        <v>49.1</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="16">
+        <v>46035</v>
+      </c>
+      <c r="B37" s="2">
+        <v>97.1</v>
+      </c>
+      <c r="C37" s="2">
+        <v>37.1</v>
+      </c>
+      <c r="D37" s="2">
+        <v>28.3</v>
+      </c>
+      <c r="E37" s="2">
+        <v>50.4</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="16">
+        <v>46039</v>
+      </c>
+      <c r="B38" s="2">
+        <v>97.5</v>
+      </c>
+      <c r="C38" s="2">
+        <v>37.299999999999997</v>
+      </c>
+      <c r="D38" s="2">
+        <v>28.4</v>
+      </c>
+      <c r="E38" s="2">
+        <v>50.6</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>1227</v>
       </c>
     </row>
   </sheetData>
@@ -30576,7 +31853,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D2F321-D2D4-48D2-B6F9-E306604CF730}">
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -31745,6 +33022,94 @@
       <c r="G49" s="2"/>
       <c r="H49" s="2" t="s">
         <v>1183</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="16">
+        <v>46036</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D50" s="2">
+        <v>54</v>
+      </c>
+      <c r="E50" s="2">
+        <v>523</v>
+      </c>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" s="16">
+        <v>46037</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D51" s="2">
+        <v>42</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2">
+        <v>2720</v>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" s="16">
+        <v>46037</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D52" s="2">
+        <v>58</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2">
+        <v>13520</v>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" s="16">
+        <v>46039</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D53" s="2">
+        <v>50</v>
+      </c>
+      <c r="E53" s="2">
+        <v>490</v>
+      </c>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2" t="s">
+        <v>1231</v>
       </c>
     </row>
   </sheetData>

--- a/Food Log Main.xlsx
+++ b/Food Log Main.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91998\VS\Food Log Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EBABBD4-2BC1-46B1-9BDD-880EAFD590C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41EDE104-701D-4296-BECB-A9231775E0E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main Format 12 oct" sheetId="1" r:id="rId1"/>
@@ -32877,7 +32877,10 @@
       <c r="D43" s="2">
         <v>39</v>
       </c>
-      <c r="E43" s="2"/>
+      <c r="E43" s="2">
+        <f>609/2</f>
+        <v>304.5</v>
+      </c>
       <c r="F43" s="2">
         <v>2640</v>
       </c>
@@ -32899,7 +32902,10 @@
       <c r="D44" s="2">
         <v>51</v>
       </c>
-      <c r="E44" s="2"/>
+      <c r="E44" s="2">
+        <f>609/2</f>
+        <v>304.5</v>
+      </c>
       <c r="F44" s="2">
         <v>3470</v>
       </c>
@@ -32967,7 +32973,10 @@
       <c r="D47" s="2">
         <v>18</v>
       </c>
-      <c r="E47" s="2"/>
+      <c r="E47" s="2">
+        <f>73+88</f>
+        <v>161</v>
+      </c>
       <c r="F47" s="2">
         <v>1280</v>
       </c>
@@ -33059,7 +33068,9 @@
       <c r="D51" s="2">
         <v>42</v>
       </c>
-      <c r="E51" s="2"/>
+      <c r="E51" s="2">
+        <v>284</v>
+      </c>
       <c r="F51" s="2">
         <v>2720</v>
       </c>
@@ -33081,7 +33092,9 @@
       <c r="D52" s="2">
         <v>58</v>
       </c>
-      <c r="E52" s="2"/>
+      <c r="E52" s="2">
+        <v>326</v>
+      </c>
       <c r="F52" s="2">
         <v>13520</v>
       </c>
@@ -33113,7 +33126,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{06D2F321-D2D4-48D2-B6F9-E306604CF730}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Food Log Main.xlsx
+++ b/Food Log Main.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91998\VS\Food Log Project Jan 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E682E3D6-F212-4594-87B4-265059F89019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1242103B-7848-4090-BCE6-1005E95662BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main Format 12 oct" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2738" uniqueCount="1418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2860" uniqueCount="1489">
   <si>
     <t>date</t>
   </si>
@@ -4314,6 +4314,219 @@
   </si>
   <si>
     <t>200g rice + 200g pork</t>
+  </si>
+  <si>
+    <t>1000148344.jpg</t>
+  </si>
+  <si>
+    <t>WK20260204-wm</t>
+  </si>
+  <si>
+    <t>WK20260205-w</t>
+  </si>
+  <si>
+    <t>WK20260206-w</t>
+  </si>
+  <si>
+    <t>WK20260207-wm</t>
+  </si>
+  <si>
+    <t>FD20260203-0800-8u2p</t>
+  </si>
+  <si>
+    <t>FD20260203-0900-9v3q</t>
+  </si>
+  <si>
+    <t>FD20260203-1230-0w4r</t>
+  </si>
+  <si>
+    <t>FD20260203-1300-1x5s</t>
+  </si>
+  <si>
+    <t>FD20260203-1500-2y6t</t>
+  </si>
+  <si>
+    <t>130g beef fry + 100g rice</t>
+  </si>
+  <si>
+    <t>FD20260203-1600-3z7u</t>
+  </si>
+  <si>
+    <t>FD20260203-1730-4a8v</t>
+  </si>
+  <si>
+    <t>Guava (250g)</t>
+  </si>
+  <si>
+    <t>FD20260203-1800-5b9w</t>
+  </si>
+  <si>
+    <t>100ml milk with coffee + 5g sugar</t>
+  </si>
+  <si>
+    <t>FD20260203-1830-6c0x</t>
+  </si>
+  <si>
+    <t>Beef fry (130g)</t>
+  </si>
+  <si>
+    <t>FD20260203-1900-7d1y</t>
+  </si>
+  <si>
+    <t>FD20260203-2100-8e2z</t>
+  </si>
+  <si>
+    <t>2 rotis with butter + 5g jaggery powder</t>
+  </si>
+  <si>
+    <t>FD20260204-0800-9f3a</t>
+  </si>
+  <si>
+    <t>FD20260204-0900-0g4b</t>
+  </si>
+  <si>
+    <t>FD20260204-0930-1h5c</t>
+  </si>
+  <si>
+    <t>FD20260204-1200-2i6d</t>
+  </si>
+  <si>
+    <t>130g chicken curry + 200g rice</t>
+  </si>
+  <si>
+    <t>FD20260204-1230-3j7e</t>
+  </si>
+  <si>
+    <t>FD20260204-1300-4k8f</t>
+  </si>
+  <si>
+    <t>Banana (120g)</t>
+  </si>
+  <si>
+    <t>FD20260204-1500-5l9g</t>
+  </si>
+  <si>
+    <t>FD20260204-1900-6m0h</t>
+  </si>
+  <si>
+    <t>FD20260204-1930-7n1i</t>
+  </si>
+  <si>
+    <t>FD20260204-1930-8o2j</t>
+  </si>
+  <si>
+    <t>FD20260205-0800-9p3k</t>
+  </si>
+  <si>
+    <t>FD20260205-0900-0q4l</t>
+  </si>
+  <si>
+    <t>FD20260205-1200-1r5m</t>
+  </si>
+  <si>
+    <t>FD20260205-1230-2s6n</t>
+  </si>
+  <si>
+    <t>FD20260205-1300-3t7o</t>
+  </si>
+  <si>
+    <t>FD20260205-1630-4u8p</t>
+  </si>
+  <si>
+    <t>FD20260205-1700-5v9q</t>
+  </si>
+  <si>
+    <t>FD20260205-1730-6w0r</t>
+  </si>
+  <si>
+    <t>FD20260205-2030-7x1s</t>
+  </si>
+  <si>
+    <t>FD20260205-2100-8y2t</t>
+  </si>
+  <si>
+    <t>FD20260206-0800-9z3u</t>
+  </si>
+  <si>
+    <t>FD20260206-0900-0a4v</t>
+  </si>
+  <si>
+    <t>FD20260206-1100-1b5w</t>
+  </si>
+  <si>
+    <t>Orange (130g)</t>
+  </si>
+  <si>
+    <t>FD20260206-1230-2c6x</t>
+  </si>
+  <si>
+    <t>FD20260206-1300-3d7y</t>
+  </si>
+  <si>
+    <t>FD20260206-1330-4e8z</t>
+  </si>
+  <si>
+    <t>FD20260206-1400-5f9a</t>
+  </si>
+  <si>
+    <t>FD20260206-1430-6g0b</t>
+  </si>
+  <si>
+    <t>FD20260206-2030-7h1c</t>
+  </si>
+  <si>
+    <t>FD20260206-2100-8i2d</t>
+  </si>
+  <si>
+    <t>FD20260207-0900-9j3e</t>
+  </si>
+  <si>
+    <t>FD20260207-0930-0k4f</t>
+  </si>
+  <si>
+    <t>½ Chai</t>
+  </si>
+  <si>
+    <t>FD20260207-1000-1l5g</t>
+  </si>
+  <si>
+    <t>FD20260207-1030-2m6h</t>
+  </si>
+  <si>
+    <t>FD20260207-1100-3n7i</t>
+  </si>
+  <si>
+    <t>FD20260207-1430-4o8j</t>
+  </si>
+  <si>
+    <t>Black coffee with 5g sugar</t>
+  </si>
+  <si>
+    <t>FD20260207-1500-5p9k</t>
+  </si>
+  <si>
+    <t>Orange (120g)</t>
+  </si>
+  <si>
+    <t>FD20260207-1530-6q0l</t>
+  </si>
+  <si>
+    <t>FD20260207-1600-7r1m</t>
+  </si>
+  <si>
+    <t>FD20260207-1630-9t3o</t>
+  </si>
+  <si>
+    <t>FD20260207-1700-8s2n</t>
+  </si>
+  <si>
+    <t>FD20260207-2000-0u4p</t>
+  </si>
+  <si>
+    <t>FD20260207-2030-1v5q</t>
+  </si>
+  <si>
+    <t>FD20260207-2100-2w6r</t>
   </si>
 </sst>
 </file>
@@ -4363,7 +4576,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -4387,38 +4600,23 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
+      <left style="thin">
+        <color auto="1"/>
       </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
+      <right style="thin">
+        <color auto="1"/>
       </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
+      <top style="thin">
+        <color auto="1"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -4483,9 +4681,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -4495,10 +4690,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4830,7 +5022,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J977"/>
+  <dimension ref="A1:J1032"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -36096,6 +36288,1766 @@
       </c>
       <c r="J977">
         <v>10</v>
+      </c>
+    </row>
+    <row r="978" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A978" s="25">
+        <v>46056</v>
+      </c>
+      <c r="B978" s="24">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C978" t="s">
+        <v>1423</v>
+      </c>
+      <c r="D978" t="s">
+        <v>102</v>
+      </c>
+      <c r="E978">
+        <v>77</v>
+      </c>
+      <c r="F978">
+        <v>2</v>
+      </c>
+      <c r="G978">
+        <v>11</v>
+      </c>
+      <c r="H978">
+        <v>2</v>
+      </c>
+      <c r="I978">
+        <v>7</v>
+      </c>
+      <c r="J978">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="979" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A979" s="25">
+        <v>46056</v>
+      </c>
+      <c r="B979" s="24">
+        <v>0.375</v>
+      </c>
+      <c r="C979" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D979" t="s">
+        <v>258</v>
+      </c>
+      <c r="E979">
+        <v>128</v>
+      </c>
+      <c r="F979">
+        <v>6.6</v>
+      </c>
+      <c r="G979">
+        <v>9.6</v>
+      </c>
+      <c r="H979">
+        <v>5.3</v>
+      </c>
+      <c r="I979">
+        <v>5.3</v>
+      </c>
+      <c r="J979">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="980" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A980" s="25">
+        <v>46056</v>
+      </c>
+      <c r="B980" s="24">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C980" t="s">
+        <v>1425</v>
+      </c>
+      <c r="D980" t="s">
+        <v>32</v>
+      </c>
+      <c r="E980">
+        <v>290</v>
+      </c>
+      <c r="F980">
+        <v>11</v>
+      </c>
+      <c r="G980">
+        <v>18</v>
+      </c>
+      <c r="H980">
+        <v>18</v>
+      </c>
+      <c r="I980">
+        <v>0</v>
+      </c>
+      <c r="J980">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="981" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A981" s="25">
+        <v>46056</v>
+      </c>
+      <c r="B981" s="24">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C981" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D981" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E981">
+        <v>175</v>
+      </c>
+      <c r="F981">
+        <v>15.5</v>
+      </c>
+      <c r="G981">
+        <v>20</v>
+      </c>
+      <c r="H981">
+        <v>2</v>
+      </c>
+      <c r="I981">
+        <v>11.5</v>
+      </c>
+      <c r="J981">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="982" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A982" s="25">
+        <v>46056</v>
+      </c>
+      <c r="B982" s="24">
+        <v>0.625</v>
+      </c>
+      <c r="C982" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D982" t="s">
+        <v>1428</v>
+      </c>
+      <c r="E982">
+        <v>390</v>
+      </c>
+      <c r="F982">
+        <v>28.5</v>
+      </c>
+      <c r="G982">
+        <v>32</v>
+      </c>
+      <c r="H982">
+        <v>15.9</v>
+      </c>
+      <c r="I982">
+        <v>1</v>
+      </c>
+      <c r="J982">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="983" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A983" s="25">
+        <v>46056</v>
+      </c>
+      <c r="B983" s="24">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C983" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D983" t="s">
+        <v>102</v>
+      </c>
+      <c r="E983">
+        <v>77</v>
+      </c>
+      <c r="F983">
+        <v>2</v>
+      </c>
+      <c r="G983">
+        <v>11</v>
+      </c>
+      <c r="H983">
+        <v>2</v>
+      </c>
+      <c r="I983">
+        <v>7</v>
+      </c>
+      <c r="J983">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="984" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A984" s="25">
+        <v>46056</v>
+      </c>
+      <c r="B984" s="24">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C984" t="s">
+        <v>1430</v>
+      </c>
+      <c r="D984" t="s">
+        <v>1431</v>
+      </c>
+      <c r="E984">
+        <v>150</v>
+      </c>
+      <c r="F984">
+        <v>3.3</v>
+      </c>
+      <c r="G984">
+        <v>35</v>
+      </c>
+      <c r="H984">
+        <v>1.7</v>
+      </c>
+      <c r="I984">
+        <v>23.3</v>
+      </c>
+      <c r="J984">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="985" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A985" s="25">
+        <v>46056</v>
+      </c>
+      <c r="B985" s="24">
+        <v>0.75</v>
+      </c>
+      <c r="C985" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D985" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E985">
+        <v>90</v>
+      </c>
+      <c r="F985">
+        <v>3.3</v>
+      </c>
+      <c r="G985">
+        <v>10</v>
+      </c>
+      <c r="H985">
+        <v>4.5</v>
+      </c>
+      <c r="I985">
+        <v>9</v>
+      </c>
+      <c r="J985">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="986" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A986" s="25">
+        <v>46056</v>
+      </c>
+      <c r="B986" s="24">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C986" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D986" t="s">
+        <v>1435</v>
+      </c>
+      <c r="E986">
+        <v>260</v>
+      </c>
+      <c r="F986">
+        <v>26</v>
+      </c>
+      <c r="G986">
+        <v>4</v>
+      </c>
+      <c r="H986">
+        <v>15.6</v>
+      </c>
+      <c r="I986">
+        <v>1</v>
+      </c>
+      <c r="J986">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="987" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A987" s="25">
+        <v>46056</v>
+      </c>
+      <c r="B987" s="24">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C987" t="s">
+        <v>1436</v>
+      </c>
+      <c r="D987" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E987">
+        <v>175</v>
+      </c>
+      <c r="F987">
+        <v>15.5</v>
+      </c>
+      <c r="G987">
+        <v>20</v>
+      </c>
+      <c r="H987">
+        <v>2</v>
+      </c>
+      <c r="I987">
+        <v>11.5</v>
+      </c>
+      <c r="J987">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="988" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A988" s="25">
+        <v>46056</v>
+      </c>
+      <c r="B988" s="24">
+        <v>0.875</v>
+      </c>
+      <c r="C988" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D988" t="s">
+        <v>1438</v>
+      </c>
+      <c r="E988">
+        <v>290</v>
+      </c>
+      <c r="F988">
+        <v>6</v>
+      </c>
+      <c r="G988">
+        <v>40</v>
+      </c>
+      <c r="H988">
+        <v>12</v>
+      </c>
+      <c r="I988">
+        <v>6</v>
+      </c>
+      <c r="J988">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="989" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A989" s="25">
+        <v>46057</v>
+      </c>
+      <c r="B989" s="24">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C989" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D989" t="s">
+        <v>102</v>
+      </c>
+      <c r="E989">
+        <v>77</v>
+      </c>
+      <c r="F989">
+        <v>2</v>
+      </c>
+      <c r="G989">
+        <v>11</v>
+      </c>
+      <c r="H989">
+        <v>2</v>
+      </c>
+      <c r="I989">
+        <v>7</v>
+      </c>
+      <c r="J989">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="990" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A990" s="25">
+        <v>46057</v>
+      </c>
+      <c r="B990" s="24">
+        <v>0.375</v>
+      </c>
+      <c r="C990" t="s">
+        <v>1440</v>
+      </c>
+      <c r="D990" t="s">
+        <v>102</v>
+      </c>
+      <c r="E990">
+        <v>77</v>
+      </c>
+      <c r="F990">
+        <v>2</v>
+      </c>
+      <c r="G990">
+        <v>11</v>
+      </c>
+      <c r="H990">
+        <v>2</v>
+      </c>
+      <c r="I990">
+        <v>7</v>
+      </c>
+      <c r="J990">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="991" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A991" s="25">
+        <v>46057</v>
+      </c>
+      <c r="B991" s="24">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C991" t="s">
+        <v>1441</v>
+      </c>
+      <c r="D991" t="s">
+        <v>258</v>
+      </c>
+      <c r="E991">
+        <v>128</v>
+      </c>
+      <c r="F991">
+        <v>6.6</v>
+      </c>
+      <c r="G991">
+        <v>9.6</v>
+      </c>
+      <c r="H991">
+        <v>5.3</v>
+      </c>
+      <c r="I991">
+        <v>5.3</v>
+      </c>
+      <c r="J991">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="992" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A992" s="25">
+        <v>46057</v>
+      </c>
+      <c r="B992" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="C992" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D992" t="s">
+        <v>1443</v>
+      </c>
+      <c r="E992">
+        <v>380</v>
+      </c>
+      <c r="F992">
+        <v>29</v>
+      </c>
+      <c r="G992">
+        <v>57</v>
+      </c>
+      <c r="H992">
+        <v>7.6</v>
+      </c>
+      <c r="I992">
+        <v>2</v>
+      </c>
+      <c r="J992">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="993" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A993" s="25">
+        <v>46057</v>
+      </c>
+      <c r="B993" s="24">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C993" t="s">
+        <v>1444</v>
+      </c>
+      <c r="D993" t="s">
+        <v>365</v>
+      </c>
+      <c r="E993">
+        <v>256</v>
+      </c>
+      <c r="F993">
+        <v>13.2</v>
+      </c>
+      <c r="G993">
+        <v>19.2</v>
+      </c>
+      <c r="H993">
+        <v>10.6</v>
+      </c>
+      <c r="I993">
+        <v>10.6</v>
+      </c>
+      <c r="J993">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="994" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A994" s="25">
+        <v>46057</v>
+      </c>
+      <c r="B994" s="24">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C994" t="s">
+        <v>1445</v>
+      </c>
+      <c r="D994" t="s">
+        <v>1446</v>
+      </c>
+      <c r="E994">
+        <v>107</v>
+      </c>
+      <c r="F994">
+        <v>1.3</v>
+      </c>
+      <c r="G994">
+        <v>28</v>
+      </c>
+      <c r="H994">
+        <v>0.4</v>
+      </c>
+      <c r="I994">
+        <v>14</v>
+      </c>
+      <c r="J994">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="995" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A995" s="25">
+        <v>46057</v>
+      </c>
+      <c r="B995" s="24">
+        <v>0.625</v>
+      </c>
+      <c r="C995" t="s">
+        <v>1447</v>
+      </c>
+      <c r="D995" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E995">
+        <v>175</v>
+      </c>
+      <c r="F995">
+        <v>15.5</v>
+      </c>
+      <c r="G995">
+        <v>20</v>
+      </c>
+      <c r="H995">
+        <v>2</v>
+      </c>
+      <c r="I995">
+        <v>11.5</v>
+      </c>
+      <c r="J995">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="996" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A996" s="25">
+        <v>46057</v>
+      </c>
+      <c r="B996" s="24">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C996" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D996" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E996">
+        <v>175</v>
+      </c>
+      <c r="F996">
+        <v>15.5</v>
+      </c>
+      <c r="G996">
+        <v>20</v>
+      </c>
+      <c r="H996">
+        <v>2</v>
+      </c>
+      <c r="I996">
+        <v>11.5</v>
+      </c>
+      <c r="J996">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="997" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A997" s="25">
+        <v>46057</v>
+      </c>
+      <c r="B997" s="24">
+        <v>0.8125</v>
+      </c>
+      <c r="C997" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D997" t="s">
+        <v>1259</v>
+      </c>
+      <c r="E997">
+        <v>246</v>
+      </c>
+      <c r="F997">
+        <v>15.6</v>
+      </c>
+      <c r="G997">
+        <v>19.2</v>
+      </c>
+      <c r="H997">
+        <v>11.6</v>
+      </c>
+      <c r="I997">
+        <v>1.2</v>
+      </c>
+      <c r="J997">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="998" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A998" s="25">
+        <v>46057</v>
+      </c>
+      <c r="B998" s="24">
+        <v>0.8125</v>
+      </c>
+      <c r="C998" t="s">
+        <v>1450</v>
+      </c>
+      <c r="D998" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E998">
+        <v>90</v>
+      </c>
+      <c r="F998">
+        <v>2</v>
+      </c>
+      <c r="G998">
+        <v>21</v>
+      </c>
+      <c r="H998">
+        <v>1</v>
+      </c>
+      <c r="I998">
+        <v>14</v>
+      </c>
+      <c r="J998">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="999" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A999" s="25">
+        <v>46058</v>
+      </c>
+      <c r="B999" s="24">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C999" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D999" t="s">
+        <v>102</v>
+      </c>
+      <c r="E999">
+        <v>77</v>
+      </c>
+      <c r="F999">
+        <v>2</v>
+      </c>
+      <c r="G999">
+        <v>11</v>
+      </c>
+      <c r="H999">
+        <v>2</v>
+      </c>
+      <c r="I999">
+        <v>7</v>
+      </c>
+      <c r="J999">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1000" s="25">
+        <v>46058</v>
+      </c>
+      <c r="B1000" s="24">
+        <v>0.375</v>
+      </c>
+      <c r="C1000" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D1000" t="s">
+        <v>605</v>
+      </c>
+      <c r="E1000">
+        <v>270</v>
+      </c>
+      <c r="F1000">
+        <v>6</v>
+      </c>
+      <c r="G1000">
+        <v>35</v>
+      </c>
+      <c r="H1000">
+        <v>12</v>
+      </c>
+      <c r="I1000">
+        <v>1</v>
+      </c>
+      <c r="J1000">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1001" s="25">
+        <v>46058</v>
+      </c>
+      <c r="B1001" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="C1001" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D1001" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1001">
+        <v>335</v>
+      </c>
+      <c r="F1001">
+        <v>21</v>
+      </c>
+      <c r="G1001">
+        <v>33</v>
+      </c>
+      <c r="H1001">
+        <v>13</v>
+      </c>
+      <c r="I1001">
+        <v>2.5</v>
+      </c>
+      <c r="J1001">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1002" s="25">
+        <v>46058</v>
+      </c>
+      <c r="B1002" s="24">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C1002" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1002" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1002">
+        <v>290</v>
+      </c>
+      <c r="F1002">
+        <v>11</v>
+      </c>
+      <c r="G1002">
+        <v>18</v>
+      </c>
+      <c r="H1002">
+        <v>18</v>
+      </c>
+      <c r="I1002">
+        <v>0</v>
+      </c>
+      <c r="J1002">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1003" s="25">
+        <v>46058</v>
+      </c>
+      <c r="B1003" s="24">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1003" t="s">
+        <v>1455</v>
+      </c>
+      <c r="D1003" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1003">
+        <v>335</v>
+      </c>
+      <c r="F1003">
+        <v>21</v>
+      </c>
+      <c r="G1003">
+        <v>33</v>
+      </c>
+      <c r="H1003">
+        <v>13</v>
+      </c>
+      <c r="I1003">
+        <v>2.5</v>
+      </c>
+      <c r="J1003">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1004" s="25">
+        <v>46058</v>
+      </c>
+      <c r="B1004" s="24">
+        <v>0.6875</v>
+      </c>
+      <c r="C1004" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D1004" t="s">
+        <v>1259</v>
+      </c>
+      <c r="E1004">
+        <v>246</v>
+      </c>
+      <c r="F1004">
+        <v>15.6</v>
+      </c>
+      <c r="G1004">
+        <v>19.2</v>
+      </c>
+      <c r="H1004">
+        <v>11.6</v>
+      </c>
+      <c r="I1004">
+        <v>1.2</v>
+      </c>
+      <c r="J1004">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1005" s="25">
+        <v>46058</v>
+      </c>
+      <c r="B1005" s="24">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C1005" t="s">
+        <v>1457</v>
+      </c>
+      <c r="D1005" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1005">
+        <v>155</v>
+      </c>
+      <c r="F1005">
+        <v>15.5</v>
+      </c>
+      <c r="G1005">
+        <v>15</v>
+      </c>
+      <c r="H1005">
+        <v>2</v>
+      </c>
+      <c r="I1005">
+        <v>7</v>
+      </c>
+      <c r="J1005">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1006" s="25">
+        <v>46058</v>
+      </c>
+      <c r="B1006" s="24">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C1006" t="s">
+        <v>1458</v>
+      </c>
+      <c r="D1006" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E1006">
+        <v>90</v>
+      </c>
+      <c r="F1006">
+        <v>2</v>
+      </c>
+      <c r="G1006">
+        <v>21</v>
+      </c>
+      <c r="H1006">
+        <v>1</v>
+      </c>
+      <c r="I1006">
+        <v>14</v>
+      </c>
+      <c r="J1006">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1007" s="25">
+        <v>46058</v>
+      </c>
+      <c r="B1007" s="24">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C1007" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D1007" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1007">
+        <v>335</v>
+      </c>
+      <c r="F1007">
+        <v>21</v>
+      </c>
+      <c r="G1007">
+        <v>33</v>
+      </c>
+      <c r="H1007">
+        <v>13</v>
+      </c>
+      <c r="I1007">
+        <v>2.5</v>
+      </c>
+      <c r="J1007">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1008" s="25">
+        <v>46058</v>
+      </c>
+      <c r="B1008" s="24">
+        <v>0.875</v>
+      </c>
+      <c r="C1008" t="s">
+        <v>1460</v>
+      </c>
+      <c r="D1008" t="s">
+        <v>605</v>
+      </c>
+      <c r="E1008">
+        <v>270</v>
+      </c>
+      <c r="F1008">
+        <v>6</v>
+      </c>
+      <c r="G1008">
+        <v>35</v>
+      </c>
+      <c r="H1008">
+        <v>12</v>
+      </c>
+      <c r="I1008">
+        <v>1</v>
+      </c>
+      <c r="J1008">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1009" s="25">
+        <v>46059</v>
+      </c>
+      <c r="B1009" s="24">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C1009" t="s">
+        <v>1461</v>
+      </c>
+      <c r="D1009" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1009">
+        <v>77</v>
+      </c>
+      <c r="F1009">
+        <v>2</v>
+      </c>
+      <c r="G1009">
+        <v>11</v>
+      </c>
+      <c r="H1009">
+        <v>2</v>
+      </c>
+      <c r="I1009">
+        <v>7</v>
+      </c>
+      <c r="J1009">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1010" s="25">
+        <v>46059</v>
+      </c>
+      <c r="B1010" s="24">
+        <v>0.375</v>
+      </c>
+      <c r="C1010" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D1010" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1010">
+        <v>77</v>
+      </c>
+      <c r="F1010">
+        <v>2</v>
+      </c>
+      <c r="G1010">
+        <v>11</v>
+      </c>
+      <c r="H1010">
+        <v>2</v>
+      </c>
+      <c r="I1010">
+        <v>7</v>
+      </c>
+      <c r="J1010">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1011" s="25">
+        <v>46059</v>
+      </c>
+      <c r="B1011" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C1011" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D1011" t="s">
+        <v>1464</v>
+      </c>
+      <c r="E1011">
+        <v>62</v>
+      </c>
+      <c r="F1011">
+        <v>1.2</v>
+      </c>
+      <c r="G1011">
+        <v>15</v>
+      </c>
+      <c r="H1011">
+        <v>0.2</v>
+      </c>
+      <c r="I1011">
+        <v>12</v>
+      </c>
+      <c r="J1011">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1012" s="25">
+        <v>46059</v>
+      </c>
+      <c r="B1012" s="24">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C1012" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D1012" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1012">
+        <v>290</v>
+      </c>
+      <c r="F1012">
+        <v>11</v>
+      </c>
+      <c r="G1012">
+        <v>18</v>
+      </c>
+      <c r="H1012">
+        <v>18</v>
+      </c>
+      <c r="I1012">
+        <v>0</v>
+      </c>
+      <c r="J1012">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1013" s="25">
+        <v>46059</v>
+      </c>
+      <c r="B1013" s="24">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1013" t="s">
+        <v>1466</v>
+      </c>
+      <c r="D1013" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1013">
+        <v>335</v>
+      </c>
+      <c r="F1013">
+        <v>21</v>
+      </c>
+      <c r="G1013">
+        <v>33</v>
+      </c>
+      <c r="H1013">
+        <v>13</v>
+      </c>
+      <c r="I1013">
+        <v>2.5</v>
+      </c>
+      <c r="J1013">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1014" s="25">
+        <v>46059</v>
+      </c>
+      <c r="B1014" s="24">
+        <v>0.5625</v>
+      </c>
+      <c r="C1014" t="s">
+        <v>1467</v>
+      </c>
+      <c r="D1014" t="s">
+        <v>365</v>
+      </c>
+      <c r="E1014">
+        <v>256</v>
+      </c>
+      <c r="F1014">
+        <v>13.2</v>
+      </c>
+      <c r="G1014">
+        <v>19.2</v>
+      </c>
+      <c r="H1014">
+        <v>10.6</v>
+      </c>
+      <c r="I1014">
+        <v>10.6</v>
+      </c>
+      <c r="J1014">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1015" s="25">
+        <v>46059</v>
+      </c>
+      <c r="B1015" s="24">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C1015" t="s">
+        <v>1468</v>
+      </c>
+      <c r="D1015" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E1015">
+        <v>263</v>
+      </c>
+      <c r="F1015">
+        <v>2.8</v>
+      </c>
+      <c r="G1015">
+        <v>30.5</v>
+      </c>
+      <c r="H1015">
+        <v>14.7</v>
+      </c>
+      <c r="I1015">
+        <v>3</v>
+      </c>
+      <c r="J1015">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1016" s="25">
+        <v>46059</v>
+      </c>
+      <c r="B1016" s="24">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C1016" t="s">
+        <v>1469</v>
+      </c>
+      <c r="D1016" t="s">
+        <v>605</v>
+      </c>
+      <c r="E1016">
+        <v>270</v>
+      </c>
+      <c r="F1016">
+        <v>6</v>
+      </c>
+      <c r="G1016">
+        <v>35</v>
+      </c>
+      <c r="H1016">
+        <v>12</v>
+      </c>
+      <c r="I1016">
+        <v>1</v>
+      </c>
+      <c r="J1016">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1017" s="25">
+        <v>46059</v>
+      </c>
+      <c r="B1017" s="24">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C1017" t="s">
+        <v>1470</v>
+      </c>
+      <c r="D1017" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1017">
+        <v>335</v>
+      </c>
+      <c r="F1017">
+        <v>21</v>
+      </c>
+      <c r="G1017">
+        <v>33</v>
+      </c>
+      <c r="H1017">
+        <v>13</v>
+      </c>
+      <c r="I1017">
+        <v>2.5</v>
+      </c>
+      <c r="J1017">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1018" s="25">
+        <v>46059</v>
+      </c>
+      <c r="B1018" s="24">
+        <v>0.875</v>
+      </c>
+      <c r="C1018" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D1018" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1018">
+        <v>155</v>
+      </c>
+      <c r="F1018">
+        <v>15.5</v>
+      </c>
+      <c r="G1018">
+        <v>15</v>
+      </c>
+      <c r="H1018">
+        <v>2</v>
+      </c>
+      <c r="I1018">
+        <v>7</v>
+      </c>
+      <c r="J1018">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1019" s="25">
+        <v>46060</v>
+      </c>
+      <c r="B1019" s="24">
+        <v>0.375</v>
+      </c>
+      <c r="C1019" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D1019" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1019">
+        <v>77</v>
+      </c>
+      <c r="F1019">
+        <v>2</v>
+      </c>
+      <c r="G1019">
+        <v>11</v>
+      </c>
+      <c r="H1019">
+        <v>2</v>
+      </c>
+      <c r="I1019">
+        <v>7</v>
+      </c>
+      <c r="J1019">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1020" s="25">
+        <v>46060</v>
+      </c>
+      <c r="B1020" s="24">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C1020" t="s">
+        <v>1473</v>
+      </c>
+      <c r="D1020" t="s">
+        <v>1474</v>
+      </c>
+      <c r="E1020">
+        <v>39</v>
+      </c>
+      <c r="F1020">
+        <v>1</v>
+      </c>
+      <c r="G1020">
+        <v>5.5</v>
+      </c>
+      <c r="H1020">
+        <v>1</v>
+      </c>
+      <c r="I1020">
+        <v>3.5</v>
+      </c>
+      <c r="J1020">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1021" s="25">
+        <v>46060</v>
+      </c>
+      <c r="B1021" s="24">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C1021" t="s">
+        <v>1475</v>
+      </c>
+      <c r="D1021" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E1021">
+        <v>263</v>
+      </c>
+      <c r="F1021">
+        <v>2.8</v>
+      </c>
+      <c r="G1021">
+        <v>30.5</v>
+      </c>
+      <c r="H1021">
+        <v>14.7</v>
+      </c>
+      <c r="I1021">
+        <v>3</v>
+      </c>
+      <c r="J1021">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1022" s="25">
+        <v>46060</v>
+      </c>
+      <c r="B1022" s="24">
+        <v>0.4375</v>
+      </c>
+      <c r="C1022" t="s">
+        <v>1476</v>
+      </c>
+      <c r="D1022" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1022">
+        <v>128</v>
+      </c>
+      <c r="F1022">
+        <v>6.6</v>
+      </c>
+      <c r="G1022">
+        <v>9.6</v>
+      </c>
+      <c r="H1022">
+        <v>5.3</v>
+      </c>
+      <c r="I1022">
+        <v>5.3</v>
+      </c>
+      <c r="J1022">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1023" s="25">
+        <v>46060</v>
+      </c>
+      <c r="B1023" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C1023" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D1023" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1023">
+        <v>290</v>
+      </c>
+      <c r="F1023">
+        <v>11</v>
+      </c>
+      <c r="G1023">
+        <v>18</v>
+      </c>
+      <c r="H1023">
+        <v>18</v>
+      </c>
+      <c r="I1023">
+        <v>0</v>
+      </c>
+      <c r="J1023">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1024" s="25">
+        <v>46060</v>
+      </c>
+      <c r="B1024" s="24">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C1024" t="s">
+        <v>1478</v>
+      </c>
+      <c r="D1024" t="s">
+        <v>1479</v>
+      </c>
+      <c r="E1024">
+        <v>20</v>
+      </c>
+      <c r="F1024">
+        <v>0</v>
+      </c>
+      <c r="G1024">
+        <v>5</v>
+      </c>
+      <c r="H1024">
+        <v>0</v>
+      </c>
+      <c r="I1024">
+        <v>5</v>
+      </c>
+      <c r="J1024">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1025" s="25">
+        <v>46060</v>
+      </c>
+      <c r="B1025" s="24">
+        <v>0.625</v>
+      </c>
+      <c r="C1025" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D1025" t="s">
+        <v>1481</v>
+      </c>
+      <c r="E1025">
+        <v>57</v>
+      </c>
+      <c r="F1025">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G1025">
+        <v>14</v>
+      </c>
+      <c r="H1025">
+        <v>0.2</v>
+      </c>
+      <c r="I1025">
+        <v>11</v>
+      </c>
+      <c r="J1025">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1026" s="25">
+        <v>46060</v>
+      </c>
+      <c r="B1026" s="24">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C1026" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D1026" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1026">
+        <v>175</v>
+      </c>
+      <c r="F1026">
+        <v>15.5</v>
+      </c>
+      <c r="G1026">
+        <v>20</v>
+      </c>
+      <c r="H1026">
+        <v>2</v>
+      </c>
+      <c r="I1026">
+        <v>11.5</v>
+      </c>
+      <c r="J1026">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1027" s="25">
+        <v>46060</v>
+      </c>
+      <c r="B1027" s="24">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C1027" t="s">
+        <v>1483</v>
+      </c>
+      <c r="D1027" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E1027">
+        <v>89</v>
+      </c>
+      <c r="F1027">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G1027">
+        <v>23</v>
+      </c>
+      <c r="H1027">
+        <v>0.3</v>
+      </c>
+      <c r="I1027">
+        <v>12</v>
+      </c>
+      <c r="J1027">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1028" s="25">
+        <v>46060</v>
+      </c>
+      <c r="B1028" s="24">
+        <v>0.6875</v>
+      </c>
+      <c r="C1028" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D1028" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1028">
+        <v>335</v>
+      </c>
+      <c r="F1028">
+        <v>21</v>
+      </c>
+      <c r="G1028">
+        <v>33</v>
+      </c>
+      <c r="H1028">
+        <v>13</v>
+      </c>
+      <c r="I1028">
+        <v>2.5</v>
+      </c>
+      <c r="J1028">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1029" s="25">
+        <v>46060</v>
+      </c>
+      <c r="B1029" s="24">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C1029" t="s">
+        <v>1485</v>
+      </c>
+      <c r="D1029" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1029">
+        <v>77</v>
+      </c>
+      <c r="F1029">
+        <v>2</v>
+      </c>
+      <c r="G1029">
+        <v>11</v>
+      </c>
+      <c r="H1029">
+        <v>2</v>
+      </c>
+      <c r="I1029">
+        <v>7</v>
+      </c>
+      <c r="J1029">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1030" s="25">
+        <v>46060</v>
+      </c>
+      <c r="B1030" s="24">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C1030" t="s">
+        <v>1486</v>
+      </c>
+      <c r="D1030" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1030">
+        <v>335</v>
+      </c>
+      <c r="F1030">
+        <v>21</v>
+      </c>
+      <c r="G1030">
+        <v>33</v>
+      </c>
+      <c r="H1030">
+        <v>13</v>
+      </c>
+      <c r="I1030">
+        <v>2.5</v>
+      </c>
+      <c r="J1030">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1031" s="25">
+        <v>46060</v>
+      </c>
+      <c r="B1031" s="24">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C1031" t="s">
+        <v>1487</v>
+      </c>
+      <c r="D1031" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1031">
+        <v>175</v>
+      </c>
+      <c r="F1031">
+        <v>15.5</v>
+      </c>
+      <c r="G1031">
+        <v>20</v>
+      </c>
+      <c r="H1031">
+        <v>2</v>
+      </c>
+      <c r="I1031">
+        <v>11.5</v>
+      </c>
+      <c r="J1031">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1032" s="25">
+        <v>46060</v>
+      </c>
+      <c r="B1032" s="24">
+        <v>0.875</v>
+      </c>
+      <c r="C1032" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D1032" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1032">
+        <v>128</v>
+      </c>
+      <c r="F1032">
+        <v>6.6</v>
+      </c>
+      <c r="G1032">
+        <v>9.6</v>
+      </c>
+      <c r="H1032">
+        <v>5.3</v>
+      </c>
+      <c r="I1032">
+        <v>5.3</v>
+      </c>
+      <c r="J1032">
+        <v>2.7</v>
       </c>
     </row>
   </sheetData>
@@ -36112,7 +38064,7 @@
   <conditionalFormatting sqref="C665:C680">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C758:C1048576 C589:C655 C681:C743">
+  <conditionalFormatting sqref="C1035:C1048576 C758:C1032 C589:C655 C681:C743">
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -36853,24 +38805,24 @@
       <c r="A37" s="25">
         <v>46035</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="29">
         <v>97.1</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="29">
         <v>37.1</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="29">
         <v>28.3</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="29">
         <v>50.4</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F37" s="29" t="s">
         <v>1184</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="25">
+      <c r="A38" s="22">
         <v>46039</v>
       </c>
       <c r="B38" s="2">
@@ -36890,107 +38842,112 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="25">
+      <c r="A39" s="22">
         <v>46042</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="2">
         <v>97.1</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="2">
         <v>36.299999999999997</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="2">
         <v>29.6</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="2">
         <v>49.5</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="2" t="s">
         <v>1361</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="25">
+      <c r="A40" s="22">
         <v>46043</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="2">
         <v>97.1</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="2">
         <v>36.299999999999997</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="2">
         <v>29.6</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="2">
         <v>49.5</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="2" t="s">
         <v>1361</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="25">
+      <c r="A41" s="22">
         <v>46044</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="2">
         <v>96.7</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="2">
         <v>35.9</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="2">
         <v>29.7</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="2">
         <v>49.1</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="2" t="s">
         <v>1362</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="25">
+      <c r="A42" s="22">
         <v>46050</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="2">
         <v>97.2</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="2">
         <v>36</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="2">
         <v>30.1</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="2">
         <v>49.2</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42" s="2" t="s">
         <v>1363</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="25">
+      <c r="A43" s="22">
         <v>46055</v>
       </c>
-      <c r="B43">
-        <v>97.2</v>
-      </c>
-      <c r="C43">
-        <v>36</v>
-      </c>
-      <c r="D43">
-        <v>30.1</v>
-      </c>
-      <c r="E43">
-        <v>49.2</v>
-      </c>
-      <c r="F43" t="s">
-        <v>1363</v>
+      <c r="B43" s="2">
+        <v>96.4</v>
+      </c>
+      <c r="C43" s="2">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="D43" s="2">
+        <v>28.4</v>
+      </c>
+      <c r="E43" s="2">
+        <v>49.9</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>1418</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="25"/>
+      <c r="A44" s="22"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="25"/>
@@ -38289,45 +40246,45 @@
       <c r="A54" s="22">
         <v>46040</v>
       </c>
-      <c r="B54" s="27" t="s">
+      <c r="B54" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="C54" s="27" t="s">
+      <c r="C54" s="26" t="s">
         <v>337</v>
       </c>
-      <c r="D54" s="28">
+      <c r="D54" s="27">
         <v>63</v>
       </c>
-      <c r="E54" s="28">
+      <c r="E54" s="27">
         <v>659</v>
       </c>
-      <c r="F54" s="28">
+      <c r="F54" s="27">
         <v>16500</v>
       </c>
-      <c r="G54" s="29"/>
-      <c r="H54" s="29"/>
+      <c r="G54" s="28"/>
+      <c r="H54" s="28"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="22">
         <v>46041</v>
       </c>
-      <c r="B55" s="27" t="s">
+      <c r="B55" s="26" t="s">
         <v>126</v>
       </c>
-      <c r="C55" s="27" t="s">
+      <c r="C55" s="26" t="s">
         <v>149</v>
       </c>
-      <c r="D55" s="28">
+      <c r="D55" s="27">
         <v>55</v>
       </c>
-      <c r="E55" s="28">
+      <c r="E55" s="27">
         <v>388</v>
       </c>
-      <c r="F55" s="28">
+      <c r="F55" s="27">
         <v>4130</v>
       </c>
-      <c r="G55" s="29"/>
-      <c r="H55" s="29"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="28"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="22">
@@ -38427,19 +40384,19 @@
       <c r="A60" s="22">
         <v>46051</v>
       </c>
-      <c r="B60" s="27" t="s">
+      <c r="B60" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="C60" s="27" t="s">
+      <c r="C60" s="26" t="s">
         <v>149</v>
       </c>
-      <c r="D60" s="28">
+      <c r="D60" s="27">
         <v>57</v>
       </c>
-      <c r="E60" s="28">
+      <c r="E60" s="27">
         <v>395</v>
       </c>
-      <c r="F60" s="28">
+      <c r="F60" s="27">
         <v>4180</v>
       </c>
       <c r="G60" s="2"/>
@@ -38449,35 +40406,115 @@
       <c r="A61" s="22">
         <v>46055</v>
       </c>
-      <c r="B61" s="31" t="s">
+      <c r="B61" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C61" s="27" t="s">
+      <c r="C61" s="26" t="s">
         <v>149</v>
       </c>
-      <c r="D61" s="28">
+      <c r="D61" s="27">
         <v>69</v>
       </c>
-      <c r="E61" s="28">
+      <c r="E61" s="27">
         <v>494</v>
       </c>
-      <c r="F61" s="28">
+      <c r="F61" s="27">
         <v>4600</v>
       </c>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
     </row>
-    <row r="62" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="30"/>
-    </row>
-    <row r="63" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="26"/>
-    </row>
-    <row r="64" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="26"/>
-    </row>
-    <row r="65" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="26"/>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62" s="22">
+        <v>46057</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D62" s="2">
+        <v>49</v>
+      </c>
+      <c r="E62" s="2">
+        <v>411</v>
+      </c>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" s="22">
+        <v>46058</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D63" s="2">
+        <v>76</v>
+      </c>
+      <c r="E63" s="2">
+        <v>518</v>
+      </c>
+      <c r="F63" s="2">
+        <v>5530</v>
+      </c>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" s="22">
+        <v>46059</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D64" s="2">
+        <v>54</v>
+      </c>
+      <c r="E64" s="2">
+        <v>381</v>
+      </c>
+      <c r="F64" s="2">
+        <v>3940</v>
+      </c>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65" s="22">
+        <v>46060</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D65" s="2">
+        <v>72</v>
+      </c>
+      <c r="E65" s="2">
+        <v>658</v>
+      </c>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2" t="s">
+        <v>1422</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Food Log Main.xlsx
+++ b/Food Log Main.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91998\VS\Food Log Project Jan 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1242103B-7848-4090-BCE6-1005E95662BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06331675-F13D-46C4-80DA-0D30BD48DCA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main Format 12 oct" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2860" uniqueCount="1489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2992" uniqueCount="1565">
   <si>
     <t>date</t>
   </si>
@@ -4527,6 +4527,234 @@
   </si>
   <si>
     <t>FD20260207-2100-2w6r</t>
+  </si>
+  <si>
+    <t>FD20260208-0900-3x7s</t>
+  </si>
+  <si>
+    <t>FD20260208-0930-4y8t</t>
+  </si>
+  <si>
+    <t>FD20260208-1030-5z9u</t>
+  </si>
+  <si>
+    <t>FD20260208-1100-6a0v</t>
+  </si>
+  <si>
+    <t>FD20260208-1130-7b1w</t>
+  </si>
+  <si>
+    <t>FD20260208-1200-8c2x</t>
+  </si>
+  <si>
+    <t>FD20260208-1300-9d3y</t>
+  </si>
+  <si>
+    <t>100ml milk + 5g sugar + coffee</t>
+  </si>
+  <si>
+    <t>FD20260208-1330-0e4z</t>
+  </si>
+  <si>
+    <t>FD20260208-1400-1f5a</t>
+  </si>
+  <si>
+    <t>FD20260208-1530-2g6b</t>
+  </si>
+  <si>
+    <t>Onion rings (one portion)</t>
+  </si>
+  <si>
+    <t>FD20260208-1630-3h7c</t>
+  </si>
+  <si>
+    <t>FD20260208-1800-4i8d</t>
+  </si>
+  <si>
+    <t>FD20260208-1830-5j9e</t>
+  </si>
+  <si>
+    <t>Shawarma roll</t>
+  </si>
+  <si>
+    <t>FD20260208-1900-6k0f</t>
+  </si>
+  <si>
+    <t>FD20260209-0900-7l1g</t>
+  </si>
+  <si>
+    <t>FD20260209-0930-8m2h</t>
+  </si>
+  <si>
+    <t>FD20260209-1030-9n3i</t>
+  </si>
+  <si>
+    <t>FD20260209-1200-0o4j</t>
+  </si>
+  <si>
+    <t>FD20260209-1230-1p5k</t>
+  </si>
+  <si>
+    <t>FD20260209-1500-2q6l</t>
+  </si>
+  <si>
+    <t>FD20260209-1530-3r7m</t>
+  </si>
+  <si>
+    <t>FD20260209-1700-4s8n</t>
+  </si>
+  <si>
+    <t>FD20260209-1900-5t9o</t>
+  </si>
+  <si>
+    <t>FD20260209-1930-6u0p</t>
+  </si>
+  <si>
+    <t>FD20260209-2000-7v1q</t>
+  </si>
+  <si>
+    <t>FD20260209-2030-8w2r</t>
+  </si>
+  <si>
+    <t>FD20260209-2100-9x3s</t>
+  </si>
+  <si>
+    <t>FD20260210-0900-0y4t</t>
+  </si>
+  <si>
+    <t>FD20260210-0930-1z5u</t>
+  </si>
+  <si>
+    <t>FD20260210-1030-2a6v</t>
+  </si>
+  <si>
+    <t>FD20260210-1200-3b7w</t>
+  </si>
+  <si>
+    <t>FD20260210-1230-4c8x</t>
+  </si>
+  <si>
+    <t>FD20260210-1630-5d9y</t>
+  </si>
+  <si>
+    <t>FD20260210-1830-6e0z</t>
+  </si>
+  <si>
+    <t>FD20260210-1900-7f1a</t>
+  </si>
+  <si>
+    <t>Guava (130g)</t>
+  </si>
+  <si>
+    <t>FD20260210-1930-8g2b</t>
+  </si>
+  <si>
+    <t>FD20260210-2000-9h3c</t>
+  </si>
+  <si>
+    <t>FD20260210-2100-0i4d</t>
+  </si>
+  <si>
+    <t>FD20260211-1200-1j5e</t>
+  </si>
+  <si>
+    <t>Full breakfast platter</t>
+  </si>
+  <si>
+    <t>FD20260211-1330-2k6f</t>
+  </si>
+  <si>
+    <t>Flat white coffee (no sugar)</t>
+  </si>
+  <si>
+    <t>FD20260211-1800-3l7g</t>
+  </si>
+  <si>
+    <t>2 × 500ml beers</t>
+  </si>
+  <si>
+    <t>FD20260211-1830-4m8h</t>
+  </si>
+  <si>
+    <t>Mutton roll</t>
+  </si>
+  <si>
+    <t>FD20260211-2330-5n9i</t>
+  </si>
+  <si>
+    <t>Beef burger</t>
+  </si>
+  <si>
+    <t>FD20260212-0800-6o0j</t>
+  </si>
+  <si>
+    <t>Black coffee with 10g sugar</t>
+  </si>
+  <si>
+    <t>FD20260212-0830-7p1k</t>
+  </si>
+  <si>
+    <t>Butter croissant</t>
+  </si>
+  <si>
+    <t>FD20260212-1300-8q2l</t>
+  </si>
+  <si>
+    <t>FD20260212-1330-9r3m</t>
+  </si>
+  <si>
+    <t>FD20260212-1400-0s4n</t>
+  </si>
+  <si>
+    <t>FD20260212-1430-3v7q</t>
+  </si>
+  <si>
+    <t>FD20260212-1800-1t5o</t>
+  </si>
+  <si>
+    <t>70g mozzarella + 1 onion</t>
+  </si>
+  <si>
+    <t>FD20260212-1830-2u6p</t>
+  </si>
+  <si>
+    <t>FD20260212-1900-4w8r</t>
+  </si>
+  <si>
+    <t>FD20260212-2000-5x9s</t>
+  </si>
+  <si>
+    <t>FD20260213-0900-6y0t</t>
+  </si>
+  <si>
+    <t>FD20260213-0930-7z1u</t>
+  </si>
+  <si>
+    <t>FD20260213-1030-8a2v</t>
+  </si>
+  <si>
+    <t>FD20260213-1200-9b3w</t>
+  </si>
+  <si>
+    <t>FD20260213-1230-0c4x</t>
+  </si>
+  <si>
+    <t>FD20260213-1300-1d5y</t>
+  </si>
+  <si>
+    <t>FD20260213-1330-2e6z</t>
+  </si>
+  <si>
+    <t>FD20260213-1500-3f7a</t>
+  </si>
+  <si>
+    <t>FD20260213-1530-4g8b</t>
+  </si>
+  <si>
+    <t>FD20260213-1830-5h9c</t>
+  </si>
+  <si>
+    <t>FD20260213-2130-6i0d</t>
   </si>
 </sst>
 </file>
@@ -4606,9 +4834,7 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -4690,7 +4916,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5022,7 +5248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J1032"/>
+  <dimension ref="A1:J1096"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -38048,6 +38274,2048 @@
       </c>
       <c r="J1032">
         <v>2.7</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1033" s="25">
+        <v>46061</v>
+      </c>
+      <c r="B1033" s="24">
+        <v>0.375</v>
+      </c>
+      <c r="C1033" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D1033" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1033">
+        <v>77</v>
+      </c>
+      <c r="F1033">
+        <v>2</v>
+      </c>
+      <c r="G1033">
+        <v>11</v>
+      </c>
+      <c r="H1033">
+        <v>2</v>
+      </c>
+      <c r="I1033">
+        <v>7</v>
+      </c>
+      <c r="J1033">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1034" s="25">
+        <v>46061</v>
+      </c>
+      <c r="B1034" s="24">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C1034" t="s">
+        <v>1490</v>
+      </c>
+      <c r="D1034" t="s">
+        <v>1474</v>
+      </c>
+      <c r="E1034">
+        <v>39</v>
+      </c>
+      <c r="F1034">
+        <v>1</v>
+      </c>
+      <c r="G1034">
+        <v>5.5</v>
+      </c>
+      <c r="H1034">
+        <v>1</v>
+      </c>
+      <c r="I1034">
+        <v>3.5</v>
+      </c>
+      <c r="J1034">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1035" s="25">
+        <v>46061</v>
+      </c>
+      <c r="B1035" s="24">
+        <v>0.4375</v>
+      </c>
+      <c r="C1035" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D1035" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1035">
+        <v>128</v>
+      </c>
+      <c r="F1035">
+        <v>6.6</v>
+      </c>
+      <c r="G1035">
+        <v>9.6</v>
+      </c>
+      <c r="H1035">
+        <v>5.3</v>
+      </c>
+      <c r="I1035">
+        <v>5.3</v>
+      </c>
+      <c r="J1035">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1036" s="25">
+        <v>46061</v>
+      </c>
+      <c r="B1036" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C1036" t="s">
+        <v>1492</v>
+      </c>
+      <c r="D1036" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1036">
+        <v>290</v>
+      </c>
+      <c r="F1036">
+        <v>11</v>
+      </c>
+      <c r="G1036">
+        <v>18</v>
+      </c>
+      <c r="H1036">
+        <v>18</v>
+      </c>
+      <c r="I1036">
+        <v>0</v>
+      </c>
+      <c r="J1036">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1037" s="25">
+        <v>46061</v>
+      </c>
+      <c r="B1037" s="24">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C1037" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1037" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1037">
+        <v>335</v>
+      </c>
+      <c r="F1037">
+        <v>21</v>
+      </c>
+      <c r="G1037">
+        <v>33</v>
+      </c>
+      <c r="H1037">
+        <v>13</v>
+      </c>
+      <c r="I1037">
+        <v>2.5</v>
+      </c>
+      <c r="J1037">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1038" s="25">
+        <v>46061</v>
+      </c>
+      <c r="B1038" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="C1038" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D1038" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E1038">
+        <v>89</v>
+      </c>
+      <c r="F1038">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G1038">
+        <v>23</v>
+      </c>
+      <c r="H1038">
+        <v>0.3</v>
+      </c>
+      <c r="I1038">
+        <v>12</v>
+      </c>
+      <c r="J1038">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1039" s="25">
+        <v>46061</v>
+      </c>
+      <c r="B1039" s="24">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1039" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D1039" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E1039">
+        <v>90</v>
+      </c>
+      <c r="F1039">
+        <v>3.3</v>
+      </c>
+      <c r="G1039">
+        <v>10</v>
+      </c>
+      <c r="H1039">
+        <v>4.5</v>
+      </c>
+      <c r="I1039">
+        <v>9</v>
+      </c>
+      <c r="J1039">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1040" s="25">
+        <v>46061</v>
+      </c>
+      <c r="B1040" s="24">
+        <v>0.5625</v>
+      </c>
+      <c r="C1040" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D1040" t="s">
+        <v>1481</v>
+      </c>
+      <c r="E1040">
+        <v>57</v>
+      </c>
+      <c r="F1040">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G1040">
+        <v>14</v>
+      </c>
+      <c r="H1040">
+        <v>0.2</v>
+      </c>
+      <c r="I1040">
+        <v>11</v>
+      </c>
+      <c r="J1040">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1041" s="25">
+        <v>46061</v>
+      </c>
+      <c r="B1041" s="24">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C1041" t="s">
+        <v>1498</v>
+      </c>
+      <c r="D1041" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1041">
+        <v>128</v>
+      </c>
+      <c r="F1041">
+        <v>6.6</v>
+      </c>
+      <c r="G1041">
+        <v>9.6</v>
+      </c>
+      <c r="H1041">
+        <v>5.3</v>
+      </c>
+      <c r="I1041">
+        <v>5.3</v>
+      </c>
+      <c r="J1041">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1042" s="25">
+        <v>46061</v>
+      </c>
+      <c r="B1042" s="24">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C1042" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D1042" t="s">
+        <v>1500</v>
+      </c>
+      <c r="E1042">
+        <v>191</v>
+      </c>
+      <c r="F1042">
+        <v>14</v>
+      </c>
+      <c r="G1042">
+        <v>9</v>
+      </c>
+      <c r="H1042">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1043" s="25">
+        <v>46061</v>
+      </c>
+      <c r="B1043" s="24">
+        <v>0.6875</v>
+      </c>
+      <c r="C1043" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D1043" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1043">
+        <v>335</v>
+      </c>
+      <c r="F1043">
+        <v>21</v>
+      </c>
+      <c r="G1043">
+        <v>33</v>
+      </c>
+      <c r="H1043">
+        <v>13</v>
+      </c>
+      <c r="I1043">
+        <v>2.5</v>
+      </c>
+      <c r="J1043">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1044" s="25">
+        <v>46061</v>
+      </c>
+      <c r="B1044" s="24">
+        <v>0.75</v>
+      </c>
+      <c r="C1044" t="s">
+        <v>1502</v>
+      </c>
+      <c r="D1044" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1044">
+        <v>155</v>
+      </c>
+      <c r="F1044">
+        <v>15.5</v>
+      </c>
+      <c r="G1044">
+        <v>15</v>
+      </c>
+      <c r="H1044">
+        <v>2</v>
+      </c>
+      <c r="I1044">
+        <v>7</v>
+      </c>
+      <c r="J1044">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1045" s="25">
+        <v>46061</v>
+      </c>
+      <c r="B1045" s="24">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C1045" t="s">
+        <v>1503</v>
+      </c>
+      <c r="D1045" t="s">
+        <v>1504</v>
+      </c>
+      <c r="E1045">
+        <v>350</v>
+      </c>
+      <c r="F1045">
+        <v>20</v>
+      </c>
+      <c r="G1045">
+        <v>30</v>
+      </c>
+      <c r="H1045">
+        <v>18</v>
+      </c>
+      <c r="I1045">
+        <v>3</v>
+      </c>
+      <c r="J1045">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1046" s="25">
+        <v>46061</v>
+      </c>
+      <c r="B1046" s="24">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C1046" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D1046" t="s">
+        <v>1481</v>
+      </c>
+      <c r="E1046">
+        <v>57</v>
+      </c>
+      <c r="F1046">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G1046">
+        <v>14</v>
+      </c>
+      <c r="H1046">
+        <v>0.2</v>
+      </c>
+      <c r="I1046">
+        <v>11</v>
+      </c>
+      <c r="J1046">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1047" s="25">
+        <v>46062</v>
+      </c>
+      <c r="B1047" s="24">
+        <v>0.375</v>
+      </c>
+      <c r="C1047" t="s">
+        <v>1506</v>
+      </c>
+      <c r="D1047" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1047">
+        <v>77</v>
+      </c>
+      <c r="F1047">
+        <v>2</v>
+      </c>
+      <c r="G1047">
+        <v>11</v>
+      </c>
+      <c r="H1047">
+        <v>2</v>
+      </c>
+      <c r="I1047">
+        <v>7</v>
+      </c>
+      <c r="J1047">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1048" s="25">
+        <v>46062</v>
+      </c>
+      <c r="B1048" s="24">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C1048" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D1048" t="s">
+        <v>1474</v>
+      </c>
+      <c r="E1048">
+        <v>39</v>
+      </c>
+      <c r="F1048">
+        <v>1</v>
+      </c>
+      <c r="G1048">
+        <v>5.5</v>
+      </c>
+      <c r="H1048">
+        <v>1</v>
+      </c>
+      <c r="I1048">
+        <v>3.5</v>
+      </c>
+      <c r="J1048">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1049" s="25">
+        <v>46062</v>
+      </c>
+      <c r="B1049" s="24">
+        <v>0.4375</v>
+      </c>
+      <c r="C1049" t="s">
+        <v>1508</v>
+      </c>
+      <c r="D1049" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1049">
+        <v>128</v>
+      </c>
+      <c r="F1049">
+        <v>6.6</v>
+      </c>
+      <c r="G1049">
+        <v>9.6</v>
+      </c>
+      <c r="H1049">
+        <v>5.3</v>
+      </c>
+      <c r="I1049">
+        <v>5.3</v>
+      </c>
+      <c r="J1049">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1050" s="25">
+        <v>46062</v>
+      </c>
+      <c r="B1050" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="C1050" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D1050" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1050">
+        <v>290</v>
+      </c>
+      <c r="F1050">
+        <v>11</v>
+      </c>
+      <c r="G1050">
+        <v>18</v>
+      </c>
+      <c r="H1050">
+        <v>18</v>
+      </c>
+      <c r="I1050">
+        <v>0</v>
+      </c>
+      <c r="J1050">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1051" s="25">
+        <v>46062</v>
+      </c>
+      <c r="B1051" s="24">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C1051" t="s">
+        <v>1510</v>
+      </c>
+      <c r="D1051" t="s">
+        <v>1481</v>
+      </c>
+      <c r="E1051">
+        <v>57</v>
+      </c>
+      <c r="F1051">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G1051">
+        <v>14</v>
+      </c>
+      <c r="H1051">
+        <v>0.2</v>
+      </c>
+      <c r="I1051">
+        <v>11</v>
+      </c>
+      <c r="J1051">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1052" s="25">
+        <v>46062</v>
+      </c>
+      <c r="B1052" s="24">
+        <v>0.625</v>
+      </c>
+      <c r="C1052" t="s">
+        <v>1511</v>
+      </c>
+      <c r="D1052" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1052">
+        <v>335</v>
+      </c>
+      <c r="F1052">
+        <v>21</v>
+      </c>
+      <c r="G1052">
+        <v>33</v>
+      </c>
+      <c r="H1052">
+        <v>13</v>
+      </c>
+      <c r="I1052">
+        <v>2.5</v>
+      </c>
+      <c r="J1052">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1053" s="25">
+        <v>46062</v>
+      </c>
+      <c r="B1053" s="24">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C1053" t="s">
+        <v>1512</v>
+      </c>
+      <c r="D1053" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1053">
+        <v>175</v>
+      </c>
+      <c r="F1053">
+        <v>15.5</v>
+      </c>
+      <c r="G1053">
+        <v>20</v>
+      </c>
+      <c r="H1053">
+        <v>2</v>
+      </c>
+      <c r="I1053">
+        <v>11.5</v>
+      </c>
+      <c r="J1053">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1054" s="25">
+        <v>46062</v>
+      </c>
+      <c r="B1054" s="24">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C1054" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D1054" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1054">
+        <v>77</v>
+      </c>
+      <c r="F1054">
+        <v>2</v>
+      </c>
+      <c r="G1054">
+        <v>11</v>
+      </c>
+      <c r="H1054">
+        <v>2</v>
+      </c>
+      <c r="I1054">
+        <v>7</v>
+      </c>
+      <c r="J1054">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1055" s="25">
+        <v>46062</v>
+      </c>
+      <c r="B1055" s="24">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C1055" t="s">
+        <v>1514</v>
+      </c>
+      <c r="D1055" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1055">
+        <v>335</v>
+      </c>
+      <c r="F1055">
+        <v>21</v>
+      </c>
+      <c r="G1055">
+        <v>33</v>
+      </c>
+      <c r="H1055">
+        <v>13</v>
+      </c>
+      <c r="I1055">
+        <v>2.5</v>
+      </c>
+      <c r="J1055">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1056" s="25">
+        <v>46062</v>
+      </c>
+      <c r="B1056" s="24">
+        <v>0.8125</v>
+      </c>
+      <c r="C1056" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D1056" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1056">
+        <v>175</v>
+      </c>
+      <c r="F1056">
+        <v>15.5</v>
+      </c>
+      <c r="G1056">
+        <v>20</v>
+      </c>
+      <c r="H1056">
+        <v>2</v>
+      </c>
+      <c r="I1056">
+        <v>11.5</v>
+      </c>
+      <c r="J1056">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1057" s="25">
+        <v>46062</v>
+      </c>
+      <c r="B1057" s="24">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C1057" t="s">
+        <v>1516</v>
+      </c>
+      <c r="D1057" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1057">
+        <v>128</v>
+      </c>
+      <c r="F1057">
+        <v>6.6</v>
+      </c>
+      <c r="G1057">
+        <v>9.6</v>
+      </c>
+      <c r="H1057">
+        <v>5.3</v>
+      </c>
+      <c r="I1057">
+        <v>5.3</v>
+      </c>
+      <c r="J1057">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1058" s="25">
+        <v>46062</v>
+      </c>
+      <c r="B1058" s="24">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C1058" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D1058" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E1058">
+        <v>89</v>
+      </c>
+      <c r="F1058">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G1058">
+        <v>23</v>
+      </c>
+      <c r="H1058">
+        <v>0.3</v>
+      </c>
+      <c r="I1058">
+        <v>12</v>
+      </c>
+      <c r="J1058">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1059" s="25">
+        <v>46062</v>
+      </c>
+      <c r="B1059" s="24">
+        <v>0.875</v>
+      </c>
+      <c r="C1059" t="s">
+        <v>1518</v>
+      </c>
+      <c r="D1059" t="s">
+        <v>1481</v>
+      </c>
+      <c r="E1059">
+        <v>57</v>
+      </c>
+      <c r="F1059">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G1059">
+        <v>14</v>
+      </c>
+      <c r="H1059">
+        <v>0.2</v>
+      </c>
+      <c r="I1059">
+        <v>11</v>
+      </c>
+      <c r="J1059">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1060" s="25">
+        <v>46063</v>
+      </c>
+      <c r="B1060" s="24">
+        <v>0.375</v>
+      </c>
+      <c r="C1060" t="s">
+        <v>1519</v>
+      </c>
+      <c r="D1060" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1060">
+        <v>77</v>
+      </c>
+      <c r="F1060">
+        <v>2</v>
+      </c>
+      <c r="G1060">
+        <v>11</v>
+      </c>
+      <c r="H1060">
+        <v>2</v>
+      </c>
+      <c r="I1060">
+        <v>7</v>
+      </c>
+      <c r="J1060">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1061" s="25">
+        <v>46063</v>
+      </c>
+      <c r="B1061" s="24">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C1061" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D1061" t="s">
+        <v>605</v>
+      </c>
+      <c r="E1061">
+        <v>270</v>
+      </c>
+      <c r="F1061">
+        <v>6</v>
+      </c>
+      <c r="G1061">
+        <v>35</v>
+      </c>
+      <c r="H1061">
+        <v>12</v>
+      </c>
+      <c r="I1061">
+        <v>1</v>
+      </c>
+      <c r="J1061">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1062" s="25">
+        <v>46063</v>
+      </c>
+      <c r="B1062" s="24">
+        <v>0.4375</v>
+      </c>
+      <c r="C1062" t="s">
+        <v>1521</v>
+      </c>
+      <c r="D1062" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1062">
+        <v>128</v>
+      </c>
+      <c r="F1062">
+        <v>6.6</v>
+      </c>
+      <c r="G1062">
+        <v>9.6</v>
+      </c>
+      <c r="H1062">
+        <v>5.3</v>
+      </c>
+      <c r="I1062">
+        <v>5.3</v>
+      </c>
+      <c r="J1062">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1063" s="25">
+        <v>46063</v>
+      </c>
+      <c r="B1063" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="C1063" t="s">
+        <v>1522</v>
+      </c>
+      <c r="D1063" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1063">
+        <v>290</v>
+      </c>
+      <c r="F1063">
+        <v>11</v>
+      </c>
+      <c r="G1063">
+        <v>18</v>
+      </c>
+      <c r="H1063">
+        <v>18</v>
+      </c>
+      <c r="I1063">
+        <v>0</v>
+      </c>
+      <c r="J1063">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1064" s="25">
+        <v>46063</v>
+      </c>
+      <c r="B1064" s="24">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C1064" t="s">
+        <v>1523</v>
+      </c>
+      <c r="D1064" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1064">
+        <v>175</v>
+      </c>
+      <c r="F1064">
+        <v>15.5</v>
+      </c>
+      <c r="G1064">
+        <v>20</v>
+      </c>
+      <c r="H1064">
+        <v>2</v>
+      </c>
+      <c r="I1064">
+        <v>11.5</v>
+      </c>
+      <c r="J1064">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1065" s="25">
+        <v>46063</v>
+      </c>
+      <c r="B1065" s="24">
+        <v>0.6875</v>
+      </c>
+      <c r="C1065" t="s">
+        <v>1524</v>
+      </c>
+      <c r="D1065" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E1065">
+        <v>90</v>
+      </c>
+      <c r="F1065">
+        <v>3.3</v>
+      </c>
+      <c r="G1065">
+        <v>10</v>
+      </c>
+      <c r="H1065">
+        <v>4.5</v>
+      </c>
+      <c r="I1065">
+        <v>9</v>
+      </c>
+      <c r="J1065">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1066" s="25">
+        <v>46063</v>
+      </c>
+      <c r="B1066" s="24">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C1066" t="s">
+        <v>1525</v>
+      </c>
+      <c r="D1066" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1066">
+        <v>77</v>
+      </c>
+      <c r="F1066">
+        <v>2</v>
+      </c>
+      <c r="G1066">
+        <v>11</v>
+      </c>
+      <c r="H1066">
+        <v>2</v>
+      </c>
+      <c r="I1066">
+        <v>7</v>
+      </c>
+      <c r="J1066">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1067" s="25">
+        <v>46063</v>
+      </c>
+      <c r="B1067" s="24">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C1067" t="s">
+        <v>1526</v>
+      </c>
+      <c r="D1067" t="s">
+        <v>1527</v>
+      </c>
+      <c r="E1067">
+        <v>78</v>
+      </c>
+      <c r="F1067">
+        <v>1.7</v>
+      </c>
+      <c r="G1067">
+        <v>18</v>
+      </c>
+      <c r="H1067">
+        <v>0.9</v>
+      </c>
+      <c r="I1067">
+        <v>12</v>
+      </c>
+      <c r="J1067">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1068" s="25">
+        <v>46063</v>
+      </c>
+      <c r="B1068" s="24">
+        <v>0.8125</v>
+      </c>
+      <c r="C1068" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D1068" t="s">
+        <v>917</v>
+      </c>
+      <c r="E1068">
+        <v>503</v>
+      </c>
+      <c r="F1068">
+        <v>31.5</v>
+      </c>
+      <c r="G1068">
+        <v>49.5</v>
+      </c>
+      <c r="H1068">
+        <v>19.5</v>
+      </c>
+      <c r="I1068">
+        <v>3.75</v>
+      </c>
+      <c r="J1068">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1069" s="25">
+        <v>46063</v>
+      </c>
+      <c r="B1069" s="24">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C1069" t="s">
+        <v>1529</v>
+      </c>
+      <c r="D1069" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1069">
+        <v>175</v>
+      </c>
+      <c r="F1069">
+        <v>15.5</v>
+      </c>
+      <c r="G1069">
+        <v>20</v>
+      </c>
+      <c r="H1069">
+        <v>2</v>
+      </c>
+      <c r="I1069">
+        <v>11.5</v>
+      </c>
+      <c r="J1069">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1070" s="25">
+        <v>46063</v>
+      </c>
+      <c r="B1070" s="24">
+        <v>0.875</v>
+      </c>
+      <c r="C1070" t="s">
+        <v>1530</v>
+      </c>
+      <c r="D1070" t="s">
+        <v>605</v>
+      </c>
+      <c r="E1070">
+        <v>270</v>
+      </c>
+      <c r="F1070">
+        <v>6</v>
+      </c>
+      <c r="G1070">
+        <v>35</v>
+      </c>
+      <c r="H1070">
+        <v>12</v>
+      </c>
+      <c r="I1070">
+        <v>1</v>
+      </c>
+      <c r="J1070">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1071" s="25">
+        <v>46064</v>
+      </c>
+      <c r="B1071" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="C1071" t="s">
+        <v>1531</v>
+      </c>
+      <c r="D1071" t="s">
+        <v>1532</v>
+      </c>
+      <c r="E1071">
+        <v>975</v>
+      </c>
+      <c r="F1071">
+        <v>55</v>
+      </c>
+      <c r="G1071">
+        <v>60</v>
+      </c>
+      <c r="H1071">
+        <v>45</v>
+      </c>
+      <c r="I1071">
+        <v>15</v>
+      </c>
+      <c r="J1071">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1072" s="25">
+        <v>46064</v>
+      </c>
+      <c r="B1072" s="24">
+        <v>0.5625</v>
+      </c>
+      <c r="C1072" t="s">
+        <v>1533</v>
+      </c>
+      <c r="D1072" t="s">
+        <v>1534</v>
+      </c>
+      <c r="E1072">
+        <v>71</v>
+      </c>
+      <c r="F1072">
+        <v>5.4</v>
+      </c>
+      <c r="G1072">
+        <v>8.6</v>
+      </c>
+      <c r="H1072">
+        <v>1.7</v>
+      </c>
+      <c r="I1072">
+        <v>6.1</v>
+      </c>
+      <c r="J1072">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1073" s="25">
+        <v>46064</v>
+      </c>
+      <c r="B1073" s="24">
+        <v>0.75</v>
+      </c>
+      <c r="C1073" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D1073" t="s">
+        <v>1536</v>
+      </c>
+      <c r="E1073">
+        <v>380</v>
+      </c>
+      <c r="F1073">
+        <v>3.7</v>
+      </c>
+      <c r="G1073">
+        <v>22</v>
+      </c>
+      <c r="H1073">
+        <v>0</v>
+      </c>
+      <c r="I1073">
+        <v>1</v>
+      </c>
+      <c r="J1073">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1074" s="25">
+        <v>46064</v>
+      </c>
+      <c r="B1074" s="24">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C1074" t="s">
+        <v>1537</v>
+      </c>
+      <c r="D1074" t="s">
+        <v>1538</v>
+      </c>
+      <c r="E1074">
+        <v>205</v>
+      </c>
+      <c r="F1074">
+        <v>7.75</v>
+      </c>
+      <c r="G1074">
+        <v>21.18</v>
+      </c>
+      <c r="H1074">
+        <v>9.8800000000000008</v>
+      </c>
+      <c r="I1074">
+        <v>1.77</v>
+      </c>
+      <c r="J1074">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1075" s="25">
+        <v>46064</v>
+      </c>
+      <c r="B1075" s="24">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="C1075" t="s">
+        <v>1539</v>
+      </c>
+      <c r="D1075" t="s">
+        <v>1540</v>
+      </c>
+      <c r="E1075">
+        <v>321</v>
+      </c>
+      <c r="F1075">
+        <v>27.9</v>
+      </c>
+      <c r="G1075">
+        <v>34.4</v>
+      </c>
+      <c r="H1075">
+        <v>6.7</v>
+      </c>
+      <c r="I1075">
+        <v>6.3</v>
+      </c>
+      <c r="J1075">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1076" s="25">
+        <v>46065</v>
+      </c>
+      <c r="B1076" s="24">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C1076" t="s">
+        <v>1541</v>
+      </c>
+      <c r="D1076" t="s">
+        <v>1542</v>
+      </c>
+      <c r="E1076">
+        <v>40</v>
+      </c>
+      <c r="F1076">
+        <v>0</v>
+      </c>
+      <c r="G1076">
+        <v>10</v>
+      </c>
+      <c r="H1076">
+        <v>0</v>
+      </c>
+      <c r="I1076">
+        <v>10</v>
+      </c>
+      <c r="J1076">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1077" s="25">
+        <v>46065</v>
+      </c>
+      <c r="B1077" s="24">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C1077" t="s">
+        <v>1543</v>
+      </c>
+      <c r="D1077" t="s">
+        <v>1544</v>
+      </c>
+      <c r="E1077">
+        <v>231</v>
+      </c>
+      <c r="F1077">
+        <v>4.7</v>
+      </c>
+      <c r="G1077">
+        <v>26</v>
+      </c>
+      <c r="H1077">
+        <v>12</v>
+      </c>
+      <c r="I1077">
+        <v>6</v>
+      </c>
+      <c r="J1077">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1078" s="25">
+        <v>46065</v>
+      </c>
+      <c r="B1078" s="24">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1078" t="s">
+        <v>1545</v>
+      </c>
+      <c r="D1078" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1078">
+        <v>290</v>
+      </c>
+      <c r="F1078">
+        <v>11</v>
+      </c>
+      <c r="G1078">
+        <v>18</v>
+      </c>
+      <c r="H1078">
+        <v>18</v>
+      </c>
+      <c r="I1078">
+        <v>0</v>
+      </c>
+      <c r="J1078">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1079" s="25">
+        <v>46065</v>
+      </c>
+      <c r="B1079" s="24">
+        <v>0.5625</v>
+      </c>
+      <c r="C1079" t="s">
+        <v>1546</v>
+      </c>
+      <c r="D1079" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1079">
+        <v>335</v>
+      </c>
+      <c r="F1079">
+        <v>21</v>
+      </c>
+      <c r="G1079">
+        <v>33</v>
+      </c>
+      <c r="H1079">
+        <v>13</v>
+      </c>
+      <c r="I1079">
+        <v>2.5</v>
+      </c>
+      <c r="J1079">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1080" s="25">
+        <v>46065</v>
+      </c>
+      <c r="B1080" s="24">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C1080" t="s">
+        <v>1547</v>
+      </c>
+      <c r="D1080" t="s">
+        <v>1291</v>
+      </c>
+      <c r="E1080">
+        <v>211</v>
+      </c>
+      <c r="F1080">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G1080">
+        <v>24.4</v>
+      </c>
+      <c r="H1080">
+        <v>11.7</v>
+      </c>
+      <c r="I1080">
+        <v>2.4</v>
+      </c>
+      <c r="J1080">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1081" s="25">
+        <v>46065</v>
+      </c>
+      <c r="B1081" s="24">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C1081" t="s">
+        <v>1548</v>
+      </c>
+      <c r="D1081" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1081">
+        <v>175</v>
+      </c>
+      <c r="F1081">
+        <v>15.5</v>
+      </c>
+      <c r="G1081">
+        <v>20</v>
+      </c>
+      <c r="H1081">
+        <v>2</v>
+      </c>
+      <c r="I1081">
+        <v>11.5</v>
+      </c>
+      <c r="J1081">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1082" s="25">
+        <v>46065</v>
+      </c>
+      <c r="B1082" s="24">
+        <v>0.75</v>
+      </c>
+      <c r="C1082" t="s">
+        <v>1549</v>
+      </c>
+      <c r="D1082" t="s">
+        <v>1550</v>
+      </c>
+      <c r="E1082">
+        <v>226</v>
+      </c>
+      <c r="F1082">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="G1082">
+        <v>11.5</v>
+      </c>
+      <c r="H1082">
+        <v>12.6</v>
+      </c>
+      <c r="I1082">
+        <v>6.2</v>
+      </c>
+      <c r="J1082">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1083" s="25">
+        <v>46065</v>
+      </c>
+      <c r="B1083" s="24">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C1083" t="s">
+        <v>1551</v>
+      </c>
+      <c r="D1083" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1083">
+        <v>335</v>
+      </c>
+      <c r="F1083">
+        <v>21</v>
+      </c>
+      <c r="G1083">
+        <v>33</v>
+      </c>
+      <c r="H1083">
+        <v>13</v>
+      </c>
+      <c r="I1083">
+        <v>2.5</v>
+      </c>
+      <c r="J1083">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1084" s="25">
+        <v>46065</v>
+      </c>
+      <c r="B1084" s="24">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C1084" t="s">
+        <v>1552</v>
+      </c>
+      <c r="D1084" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1084">
+        <v>175</v>
+      </c>
+      <c r="F1084">
+        <v>15.5</v>
+      </c>
+      <c r="G1084">
+        <v>20</v>
+      </c>
+      <c r="H1084">
+        <v>2</v>
+      </c>
+      <c r="I1084">
+        <v>11.5</v>
+      </c>
+      <c r="J1084">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1085" s="25">
+        <v>46065</v>
+      </c>
+      <c r="B1085" s="24">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C1085" t="s">
+        <v>1553</v>
+      </c>
+      <c r="D1085" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1085">
+        <v>128</v>
+      </c>
+      <c r="F1085">
+        <v>6.6</v>
+      </c>
+      <c r="G1085">
+        <v>9.6</v>
+      </c>
+      <c r="H1085">
+        <v>5.3</v>
+      </c>
+      <c r="I1085">
+        <v>5.3</v>
+      </c>
+      <c r="J1085">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1086" s="25">
+        <v>46066</v>
+      </c>
+      <c r="B1086" s="24">
+        <v>0.375</v>
+      </c>
+      <c r="C1086" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D1086" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1086">
+        <v>77</v>
+      </c>
+      <c r="F1086">
+        <v>2</v>
+      </c>
+      <c r="G1086">
+        <v>11</v>
+      </c>
+      <c r="H1086">
+        <v>2</v>
+      </c>
+      <c r="I1086">
+        <v>7</v>
+      </c>
+      <c r="J1086">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1087" s="25">
+        <v>46066</v>
+      </c>
+      <c r="B1087" s="24">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C1087" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D1087" t="s">
+        <v>605</v>
+      </c>
+      <c r="E1087">
+        <v>270</v>
+      </c>
+      <c r="F1087">
+        <v>6</v>
+      </c>
+      <c r="G1087">
+        <v>35</v>
+      </c>
+      <c r="H1087">
+        <v>12</v>
+      </c>
+      <c r="I1087">
+        <v>1</v>
+      </c>
+      <c r="J1087">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1088" s="25">
+        <v>46066</v>
+      </c>
+      <c r="B1088" s="24">
+        <v>0.4375</v>
+      </c>
+      <c r="C1088" t="s">
+        <v>1556</v>
+      </c>
+      <c r="D1088" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1088">
+        <v>128</v>
+      </c>
+      <c r="F1088">
+        <v>6.6</v>
+      </c>
+      <c r="G1088">
+        <v>9.6</v>
+      </c>
+      <c r="H1088">
+        <v>5.3</v>
+      </c>
+      <c r="I1088">
+        <v>5.3</v>
+      </c>
+      <c r="J1088">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1089" s="25">
+        <v>46066</v>
+      </c>
+      <c r="B1089" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="C1089" t="s">
+        <v>1557</v>
+      </c>
+      <c r="D1089" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1089">
+        <v>290</v>
+      </c>
+      <c r="F1089">
+        <v>11</v>
+      </c>
+      <c r="G1089">
+        <v>18</v>
+      </c>
+      <c r="H1089">
+        <v>18</v>
+      </c>
+      <c r="I1089">
+        <v>0</v>
+      </c>
+      <c r="J1089">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1090" s="25">
+        <v>46066</v>
+      </c>
+      <c r="B1090" s="24">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C1090" t="s">
+        <v>1558</v>
+      </c>
+      <c r="D1090" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1090">
+        <v>175</v>
+      </c>
+      <c r="F1090">
+        <v>15.5</v>
+      </c>
+      <c r="G1090">
+        <v>20</v>
+      </c>
+      <c r="H1090">
+        <v>2</v>
+      </c>
+      <c r="I1090">
+        <v>11.5</v>
+      </c>
+      <c r="J1090">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1091" s="25">
+        <v>46066</v>
+      </c>
+      <c r="B1091" s="24">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1091" t="s">
+        <v>1559</v>
+      </c>
+      <c r="D1091" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1091">
+        <v>335</v>
+      </c>
+      <c r="F1091">
+        <v>21</v>
+      </c>
+      <c r="G1091">
+        <v>33</v>
+      </c>
+      <c r="H1091">
+        <v>13</v>
+      </c>
+      <c r="I1091">
+        <v>2.5</v>
+      </c>
+      <c r="J1091">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1092" s="25">
+        <v>46066</v>
+      </c>
+      <c r="B1092" s="24">
+        <v>0.5625</v>
+      </c>
+      <c r="C1092" t="s">
+        <v>1560</v>
+      </c>
+      <c r="D1092" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E1092">
+        <v>90</v>
+      </c>
+      <c r="F1092">
+        <v>3.3</v>
+      </c>
+      <c r="G1092">
+        <v>10</v>
+      </c>
+      <c r="H1092">
+        <v>4.5</v>
+      </c>
+      <c r="I1092">
+        <v>9</v>
+      </c>
+      <c r="J1092">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1093" s="25">
+        <v>46066</v>
+      </c>
+      <c r="B1093" s="24">
+        <v>0.625</v>
+      </c>
+      <c r="C1093" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D1093" t="s">
+        <v>1527</v>
+      </c>
+      <c r="E1093">
+        <v>78</v>
+      </c>
+      <c r="F1093">
+        <v>1.7</v>
+      </c>
+      <c r="G1093">
+        <v>18</v>
+      </c>
+      <c r="H1093">
+        <v>0.9</v>
+      </c>
+      <c r="I1093">
+        <v>12</v>
+      </c>
+      <c r="J1093">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1094" s="25">
+        <v>46066</v>
+      </c>
+      <c r="B1094" s="24">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C1094" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D1094" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E1094">
+        <v>263</v>
+      </c>
+      <c r="F1094">
+        <v>2.8</v>
+      </c>
+      <c r="G1094">
+        <v>30.5</v>
+      </c>
+      <c r="H1094">
+        <v>14.7</v>
+      </c>
+      <c r="I1094">
+        <v>3</v>
+      </c>
+      <c r="J1094">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1095" s="25">
+        <v>46066</v>
+      </c>
+      <c r="B1095" s="24">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C1095" t="s">
+        <v>1563</v>
+      </c>
+      <c r="D1095" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1095">
+        <v>77</v>
+      </c>
+      <c r="F1095">
+        <v>2</v>
+      </c>
+      <c r="G1095">
+        <v>11</v>
+      </c>
+      <c r="H1095">
+        <v>2</v>
+      </c>
+      <c r="I1095">
+        <v>7</v>
+      </c>
+      <c r="J1095">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1096" s="25">
+        <v>46066</v>
+      </c>
+      <c r="B1096" s="24">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C1096" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D1096" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1096">
+        <v>175</v>
+      </c>
+      <c r="F1096">
+        <v>15.5</v>
+      </c>
+      <c r="G1096">
+        <v>20</v>
+      </c>
+      <c r="H1096">
+        <v>2</v>
+      </c>
+      <c r="I1096">
+        <v>11.5</v>
+      </c>
+      <c r="J1096">
+        <v>1.8</v>
       </c>
     </row>
   </sheetData>
@@ -38064,7 +40332,7 @@
   <conditionalFormatting sqref="C665:C680">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1035:C1048576 C758:C1032 C589:C655 C681:C743">
+  <conditionalFormatting sqref="C758:C1048576 C589:C655 C681:C743">
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -38074,7 +40342,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F24E0C0-BC77-4AA4-801C-82B038A8B8E4}">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -38106,7 +40374,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="25">
+      <c r="A2" s="22">
         <v>45922</v>
       </c>
       <c r="B2" s="2">
@@ -38126,7 +40394,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="25">
+      <c r="A3" s="22">
         <v>45926</v>
       </c>
       <c r="B3" s="2">
@@ -38146,7 +40414,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="25">
+      <c r="A4" s="22">
         <v>45929</v>
       </c>
       <c r="B4" s="2">
@@ -38166,7 +40434,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="25">
+      <c r="A5" s="22">
         <v>45931</v>
       </c>
       <c r="B5" s="2">
@@ -38186,7 +40454,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="25">
+      <c r="A6" s="22">
         <v>45938</v>
       </c>
       <c r="B6" s="2">
@@ -38206,7 +40474,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="25">
+      <c r="A7" s="22">
         <v>45939</v>
       </c>
       <c r="B7" s="2">
@@ -38226,7 +40494,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="25">
+      <c r="A8" s="22">
         <v>45945</v>
       </c>
       <c r="B8" s="2">
@@ -38246,7 +40514,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="25">
+      <c r="A9" s="22">
         <v>45950</v>
       </c>
       <c r="B9" s="10">
@@ -38266,7 +40534,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="25">
+      <c r="A10" s="22">
         <v>45954</v>
       </c>
       <c r="B10" s="10">
@@ -38286,7 +40554,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="25">
+      <c r="A11" s="22">
         <v>45955</v>
       </c>
       <c r="B11" s="10">
@@ -38306,7 +40574,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="25">
+      <c r="A12" s="22">
         <v>45959</v>
       </c>
       <c r="B12" s="10">
@@ -38326,7 +40594,7 @@
       <c r="H12" s="11"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="25">
+      <c r="A13" s="22">
         <v>45961</v>
       </c>
       <c r="B13" s="10">
@@ -38346,7 +40614,7 @@
       <c r="H13" s="11"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="25">
+      <c r="A14" s="22">
         <v>45965</v>
       </c>
       <c r="B14" s="2">
@@ -38366,7 +40634,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="25">
+      <c r="A15" s="22">
         <v>45968</v>
       </c>
       <c r="B15" s="2">
@@ -38386,7 +40654,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="25">
+      <c r="A16" s="22">
         <v>45969</v>
       </c>
       <c r="B16" s="2">
@@ -38406,7 +40674,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="25">
+      <c r="A17" s="22">
         <v>45975</v>
       </c>
       <c r="B17" s="13">
@@ -38426,7 +40694,7 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="25">
+      <c r="A18" s="22">
         <v>45976</v>
       </c>
       <c r="B18" s="2">
@@ -38446,7 +40714,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="25">
+      <c r="A19" s="22">
         <v>45979</v>
       </c>
       <c r="B19" s="13">
@@ -38466,7 +40734,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="25">
+      <c r="A20" s="22">
         <v>45983</v>
       </c>
       <c r="B20" s="13">
@@ -38486,7 +40754,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="25">
+      <c r="A21" s="22">
         <v>45986</v>
       </c>
       <c r="B21" s="2">
@@ -38506,7 +40774,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="25">
+      <c r="A22" s="22">
         <v>45990</v>
       </c>
       <c r="B22" s="2">
@@ -38526,7 +40794,7 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="25">
+      <c r="A23" s="22">
         <v>45996</v>
       </c>
       <c r="B23" s="2">
@@ -38546,7 +40814,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="25">
+      <c r="A24" s="22">
         <v>46001</v>
       </c>
       <c r="B24" s="2">
@@ -38566,7 +40834,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="25">
+      <c r="A25" s="22">
         <v>46004</v>
       </c>
       <c r="B25" s="2">
@@ -38586,7 +40854,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="25">
+      <c r="A26" s="22">
         <v>46008</v>
       </c>
       <c r="B26" s="2">
@@ -38606,7 +40874,7 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="25">
+      <c r="A27" s="22">
         <v>46011</v>
       </c>
       <c r="B27" s="2">
@@ -38626,7 +40894,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="25">
+      <c r="A28" s="22">
         <v>46013</v>
       </c>
       <c r="B28" s="2">
@@ -38646,7 +40914,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="25">
+      <c r="A29" s="22">
         <v>46015</v>
       </c>
       <c r="B29" s="2">
@@ -38666,7 +40934,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="25">
+      <c r="A30" s="22">
         <v>46021</v>
       </c>
       <c r="B30" s="2">
@@ -38686,7 +40954,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="25">
+      <c r="A31" s="22">
         <v>46025</v>
       </c>
       <c r="B31" s="2">
@@ -38706,7 +40974,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="25">
+      <c r="A32" s="22">
         <v>46031</v>
       </c>
       <c r="B32" s="2">
@@ -38724,7 +40992,7 @@
       <c r="F32" s="2"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="25">
+      <c r="A33" s="22">
         <v>46033</v>
       </c>
       <c r="B33" s="2">
@@ -38742,7 +41010,7 @@
       <c r="F33" s="2"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="25">
+      <c r="A34" s="22">
         <v>46035</v>
       </c>
       <c r="B34" s="2">
@@ -38762,7 +41030,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="25">
+      <c r="A35" s="22">
         <v>46025</v>
       </c>
       <c r="B35" s="2">
@@ -38782,7 +41050,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="25">
+      <c r="A36" s="22">
         <v>46031</v>
       </c>
       <c r="B36" s="2">
@@ -38802,22 +41070,22 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="25">
+      <c r="A37" s="22">
         <v>46035</v>
       </c>
-      <c r="B37" s="29">
+      <c r="B37" s="2">
         <v>97.1</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C37" s="2">
         <v>37.1</v>
       </c>
-      <c r="D37" s="29">
+      <c r="D37" s="2">
         <v>28.3</v>
       </c>
-      <c r="E37" s="29">
+      <c r="E37" s="2">
         <v>50.4</v>
       </c>
-      <c r="F37" s="29" t="s">
+      <c r="F37" s="2" t="s">
         <v>1184</v>
       </c>
     </row>
@@ -38942,24 +41210,40 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="22"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
+      <c r="A44" s="22">
+        <v>46063</v>
+      </c>
+      <c r="B44" s="2">
+        <v>96.6</v>
+      </c>
+      <c r="C44" s="2">
+        <v>36.1</v>
+      </c>
+      <c r="D44" s="2">
+        <v>29.3</v>
+      </c>
+      <c r="E44" s="2">
+        <v>49.3</v>
+      </c>
       <c r="F44" s="2"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="25"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="25"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="25"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="25"/>
+      <c r="A45" s="22">
+        <v>46067</v>
+      </c>
+      <c r="B45" s="2">
+        <v>96.4</v>
+      </c>
+      <c r="C45" s="2">
+        <v>35.6</v>
+      </c>
+      <c r="D45" s="2">
+        <v>29.9</v>
+      </c>
+      <c r="E45" s="2">
+        <v>48.7</v>
+      </c>
+      <c r="F45" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -38970,7 +41254,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D2F321-D2D4-48D2-B6F9-E306604CF730}">
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -40514,6 +42798,43 @@
       <c r="G65" s="2"/>
       <c r="H65" s="2" t="s">
         <v>1422</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" s="22">
+        <v>46062</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C66" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="D66" s="29">
+        <v>54</v>
+      </c>
+      <c r="E66" s="29">
+        <v>307</v>
+      </c>
+      <c r="F66" s="29">
+        <v>4650</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" s="22">
+        <v>46067</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D67" s="29">
+        <v>56</v>
+      </c>
+      <c r="E67" s="29">
+        <v>545</v>
       </c>
     </row>
   </sheetData>

--- a/Food Log Main.xlsx
+++ b/Food Log Main.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91998\VS\Food Log Project Jan 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16EC5C1D-3377-49FC-A787-2D1598421CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{878E8079-048E-45B7-A96E-F12C39D2252B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main Format 12 oct" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3247" uniqueCount="1708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3516" uniqueCount="1861">
   <si>
     <t>date</t>
   </si>
@@ -5184,6 +5184,465 @@
   </si>
   <si>
     <t>WK20260225-wm</t>
+  </si>
+  <si>
+    <t>WK20260226-w</t>
+  </si>
+  <si>
+    <t>WK20260227-wm</t>
+  </si>
+  <si>
+    <t>WK20260227-wa</t>
+  </si>
+  <si>
+    <t>WK20260228-w</t>
+  </si>
+  <si>
+    <t>WK20260228-wm</t>
+  </si>
+  <si>
+    <t>WK20260301-b</t>
+  </si>
+  <si>
+    <t>WK20260303-wm</t>
+  </si>
+  <si>
+    <t>WK20260304-wm</t>
+  </si>
+  <si>
+    <t>WK20260306-wm</t>
+  </si>
+  <si>
+    <t>WK20260307-wm</t>
+  </si>
+  <si>
+    <t>WK20260308-b</t>
+  </si>
+  <si>
+    <t>FD20260226-0730-4w8r</t>
+  </si>
+  <si>
+    <t>FD20260226-0900-5x9s</t>
+  </si>
+  <si>
+    <t>Apple (120g)</t>
+  </si>
+  <si>
+    <t>FD20260226-0930-6y0t</t>
+  </si>
+  <si>
+    <t>1 roti with butter</t>
+  </si>
+  <si>
+    <t>FD20260226-1000-7z1u</t>
+  </si>
+  <si>
+    <t>FD20260226-1200-8a2v</t>
+  </si>
+  <si>
+    <t>FD20260226-1300-9b3w</t>
+  </si>
+  <si>
+    <t>3 fried eggs + 100g rice</t>
+  </si>
+  <si>
+    <t>FD20260226-1330-0c4x</t>
+  </si>
+  <si>
+    <t>FD20260226-1600-1d5y</t>
+  </si>
+  <si>
+    <t>FD20260226-1800-2e6z</t>
+  </si>
+  <si>
+    <t>FD20260226-1900-3f7a</t>
+  </si>
+  <si>
+    <t>FD20260226-1930-4g8b</t>
+  </si>
+  <si>
+    <t>FD20260227-0730-5h9c</t>
+  </si>
+  <si>
+    <t>FD20260227-0800-6i0d</t>
+  </si>
+  <si>
+    <t>FD20260227-0930-7j1e</t>
+  </si>
+  <si>
+    <t>Cheese grill sandwich (494 kcal, 23g protein)</t>
+  </si>
+  <si>
+    <t>FD20260227-1000-8k2f</t>
+  </si>
+  <si>
+    <t>FD20260227-1030-9l3g</t>
+  </si>
+  <si>
+    <t>100ml milk coffee + 5g sugar</t>
+  </si>
+  <si>
+    <t>FD20260227-1200-0m4h</t>
+  </si>
+  <si>
+    <t>FD20260227-1330-1n5i</t>
+  </si>
+  <si>
+    <t>FD20260227-1730-2o6j</t>
+  </si>
+  <si>
+    <t>FD20260227-1800-3p7k</t>
+  </si>
+  <si>
+    <t>FD20260227-1830-4q8l</t>
+  </si>
+  <si>
+    <t>FD20260227-2000-5r9m</t>
+  </si>
+  <si>
+    <t>FD20260227-2030-6s0n</t>
+  </si>
+  <si>
+    <t>FD20260228-0730-7t1o</t>
+  </si>
+  <si>
+    <t>FD20260228-1300-8u2p</t>
+  </si>
+  <si>
+    <t>FD20260228-1630-9v3q</t>
+  </si>
+  <si>
+    <t>FD20260228-1700-0w4r</t>
+  </si>
+  <si>
+    <t>Shake 2 (with 5g sugar) + 15g isolate</t>
+  </si>
+  <si>
+    <t>FD20260228-1730-1x5s</t>
+  </si>
+  <si>
+    <t>FD20260228-2030-2y6t</t>
+  </si>
+  <si>
+    <t>FD20260228-2100-3z7u</t>
+  </si>
+  <si>
+    <t>2 rotis with butter + 10g jaggery</t>
+  </si>
+  <si>
+    <t>FD20260228-2130-4a8v</t>
+  </si>
+  <si>
+    <t>FD20260301-0730-5b9w</t>
+  </si>
+  <si>
+    <t>FD20260301-1200-6c0x</t>
+  </si>
+  <si>
+    <t>Croissant (50g)</t>
+  </si>
+  <si>
+    <t>FD20260301-1230-7d1y</t>
+  </si>
+  <si>
+    <t>FD20260301-1300-8e2z</t>
+  </si>
+  <si>
+    <t>FD20260301-1500-9f3a</t>
+  </si>
+  <si>
+    <t>50g onion + 40g mozzarella</t>
+  </si>
+  <si>
+    <t>FD20260301-1630-0g4b</t>
+  </si>
+  <si>
+    <t>FD20260301-1700-1h5c</t>
+  </si>
+  <si>
+    <t>Chicken manchow soup</t>
+  </si>
+  <si>
+    <t>FD20260301-1730-2i6d</t>
+  </si>
+  <si>
+    <t>FD20260301-1800-3j7e</t>
+  </si>
+  <si>
+    <t>Chicken pepper (100g) + rice (100g)</t>
+  </si>
+  <si>
+    <t>FD20260301-1900-4k8f</t>
+  </si>
+  <si>
+    <t>FD20260301-1930-5l9g</t>
+  </si>
+  <si>
+    <t>FD20260302-0730-6m0h</t>
+  </si>
+  <si>
+    <t>FD20260302-1230-7n1i</t>
+  </si>
+  <si>
+    <t>FD20260302-1300-8o2j</t>
+  </si>
+  <si>
+    <t>FD20260302-1330-9p3k</t>
+  </si>
+  <si>
+    <t>FD20260302-1400-0q4l</t>
+  </si>
+  <si>
+    <t>FD20260302-1430-1r5m</t>
+  </si>
+  <si>
+    <t>70g banana + 1 roti + 5g jaggery</t>
+  </si>
+  <si>
+    <t>FD20260302-1630-2s6n</t>
+  </si>
+  <si>
+    <t>FD20260302-1700-3t7o</t>
+  </si>
+  <si>
+    <t>FD20260302-1730-4u8p</t>
+  </si>
+  <si>
+    <t>FD20260302-1800-5v9q</t>
+  </si>
+  <si>
+    <t>Peanuts (50g)</t>
+  </si>
+  <si>
+    <t>FD20260302-2000-6w0r</t>
+  </si>
+  <si>
+    <t>FD20260303-0730-7x1s</t>
+  </si>
+  <si>
+    <t>FD20260303-0830-8y2t</t>
+  </si>
+  <si>
+    <t>FD20260303-0900-9z3u</t>
+  </si>
+  <si>
+    <t>1 roti with butter + 5g ketchup</t>
+  </si>
+  <si>
+    <t>FD20260303-1230-0a4v</t>
+  </si>
+  <si>
+    <t>FD20260303-1300-1b5w</t>
+  </si>
+  <si>
+    <t>FD20260303-1730-2c6x</t>
+  </si>
+  <si>
+    <t>FD20260303-1800-3d7y</t>
+  </si>
+  <si>
+    <t>FD20260303-1830-4e8z</t>
+  </si>
+  <si>
+    <t>FD20260303-2000-5f9a</t>
+  </si>
+  <si>
+    <t>FD20260303-2030-6g0b</t>
+  </si>
+  <si>
+    <t>FD20260303-2100-7h1c</t>
+  </si>
+  <si>
+    <t>FD20260304-0730-8i2d</t>
+  </si>
+  <si>
+    <t>FD20260304-0830-9j3e</t>
+  </si>
+  <si>
+    <t>FD20260304-0900-0k4f</t>
+  </si>
+  <si>
+    <t>FD20260304-1230-1l5g</t>
+  </si>
+  <si>
+    <t>FD20260304-1300-2m6h</t>
+  </si>
+  <si>
+    <t>FD20260304-1400-3n7i</t>
+  </si>
+  <si>
+    <t>Banana (90g)</t>
+  </si>
+  <si>
+    <t>FD20260304-1530-4o8j</t>
+  </si>
+  <si>
+    <t>FD20260304-1930-5p9k</t>
+  </si>
+  <si>
+    <t>½ Ham and cheese sandwich (370 kcal)</t>
+  </si>
+  <si>
+    <t>FD20260304-2000-6q0l</t>
+  </si>
+  <si>
+    <t>Coconut milk latte</t>
+  </si>
+  <si>
+    <t>FD20260304-2030-7r1m</t>
+  </si>
+  <si>
+    <t>FD20260304-2100-8s2n</t>
+  </si>
+  <si>
+    <t>FD20260305-0730-9t3o</t>
+  </si>
+  <si>
+    <t>FD20260305-0830-0u4p</t>
+  </si>
+  <si>
+    <t>FD20260305-1230-1v5q</t>
+  </si>
+  <si>
+    <t>FD20260305-1300-2w6r</t>
+  </si>
+  <si>
+    <t>FD20260305-1330-3x7s</t>
+  </si>
+  <si>
+    <t>FD20260305-1400-4y8t</t>
+  </si>
+  <si>
+    <t>FD20260305-1700-5z9u</t>
+  </si>
+  <si>
+    <t>FD20260305-1730-6a0v</t>
+  </si>
+  <si>
+    <t>FD20260305-1800-7b1w</t>
+  </si>
+  <si>
+    <t>2 rotis + 2 fried eggs</t>
+  </si>
+  <si>
+    <t>FD20260305-1900-8c2x</t>
+  </si>
+  <si>
+    <t>FD20260306-0700-9d3y</t>
+  </si>
+  <si>
+    <t>FD20260306-0730-0e4z</t>
+  </si>
+  <si>
+    <t>FD20260306-0800-1f5a</t>
+  </si>
+  <si>
+    <t>FD20260306-0830-2g6b</t>
+  </si>
+  <si>
+    <t>FD20260306-1230-3h7c</t>
+  </si>
+  <si>
+    <t>FD20260306-1300-4i8d</t>
+  </si>
+  <si>
+    <t>FD20260306-1330-5j9e</t>
+  </si>
+  <si>
+    <t>FD20260306-1700-6k0f</t>
+  </si>
+  <si>
+    <t>FD20260306-1730-7l1g</t>
+  </si>
+  <si>
+    <t>2 rotis + 100g chicken curry</t>
+  </si>
+  <si>
+    <t>FD20260306-1800-8m2h</t>
+  </si>
+  <si>
+    <t>FD20260306-1830-9n3i</t>
+  </si>
+  <si>
+    <t>Guava (170g)</t>
+  </si>
+  <si>
+    <t>FD20260307-0700-0o4j</t>
+  </si>
+  <si>
+    <t>FD20260307-0730-1p5k</t>
+  </si>
+  <si>
+    <t>FD20260307-0800-2q6l</t>
+  </si>
+  <si>
+    <t>FD20260307-0830-3r7m</t>
+  </si>
+  <si>
+    <t>FD20260307-1230-4s8n</t>
+  </si>
+  <si>
+    <t>FD20260307-1300-5t9o</t>
+  </si>
+  <si>
+    <t>FD20260307-1330-6u0p</t>
+  </si>
+  <si>
+    <t>FD20260307-1700-7v1q</t>
+  </si>
+  <si>
+    <t>FD20260307-1800-8w2r</t>
+  </si>
+  <si>
+    <t>FD20260307-1900-9x3s</t>
+  </si>
+  <si>
+    <t>FD20260307-2100-0y4t</t>
+  </si>
+  <si>
+    <t>Kolkata roll</t>
+  </si>
+  <si>
+    <t>FD20260308-0700-1z5u</t>
+  </si>
+  <si>
+    <t>Banana (80g)</t>
+  </si>
+  <si>
+    <t>FD20260308-0800-2a6v</t>
+  </si>
+  <si>
+    <t>Banana fritter (50g)</t>
+  </si>
+  <si>
+    <t>FD20260308-0830-3b7w</t>
+  </si>
+  <si>
+    <t>FD20260308-1030-4c8x</t>
+  </si>
+  <si>
+    <t>FD20260308-1300-5d9y</t>
+  </si>
+  <si>
+    <t>100g rice + 2 fried eggs</t>
+  </si>
+  <si>
+    <t>FD20260308-1330-6e0z</t>
+  </si>
+  <si>
+    <t>FD20260308-1730-7f1a</t>
+  </si>
+  <si>
+    <t>FD20260308-1800-8g2b</t>
+  </si>
+  <si>
+    <t>FD20260308-1830-9h3c</t>
+  </si>
+  <si>
+    <t>FD20260308-1930-0i4d</t>
+  </si>
+  <si>
+    <t>FD20260308-2000-1j5e</t>
   </si>
 </sst>
 </file>
@@ -5260,7 +5719,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -5333,6 +5792,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5664,7 +6124,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J1213"/>
+  <dimension ref="A1:J1331"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -44478,6 +44938,3782 @@
       </c>
       <c r="J1213" s="2">
         <v>6</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1214" s="22">
+        <v>46079</v>
+      </c>
+      <c r="B1214" s="14">
+        <v>0.3125</v>
+      </c>
+      <c r="C1214" s="2" t="s">
+        <v>1719</v>
+      </c>
+      <c r="D1214" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1214" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1214" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1214" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1214" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1214" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1214" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1215" s="22">
+        <v>46079</v>
+      </c>
+      <c r="B1215" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="C1215" s="2" t="s">
+        <v>1720</v>
+      </c>
+      <c r="D1215" s="2" t="s">
+        <v>1721</v>
+      </c>
+      <c r="E1215" s="2">
+        <v>63</v>
+      </c>
+      <c r="F1215" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G1215" s="2">
+        <v>16.8</v>
+      </c>
+      <c r="H1215" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="I1215" s="2">
+        <v>13</v>
+      </c>
+      <c r="J1215" s="2">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1216" s="22">
+        <v>46079</v>
+      </c>
+      <c r="B1216" s="14">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C1216" s="2" t="s">
+        <v>1722</v>
+      </c>
+      <c r="D1216" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="E1216" s="2">
+        <v>135</v>
+      </c>
+      <c r="F1216" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1216" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1216" s="2">
+        <v>6</v>
+      </c>
+      <c r="I1216" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1216" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1217" s="22">
+        <v>46079</v>
+      </c>
+      <c r="B1217" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C1217" s="2" t="s">
+        <v>1724</v>
+      </c>
+      <c r="D1217" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E1217" s="2">
+        <v>256</v>
+      </c>
+      <c r="F1217" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="G1217" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="H1217" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="I1217" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="J1217" s="2">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1218" s="22">
+        <v>46079</v>
+      </c>
+      <c r="B1218" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="C1218" s="2" t="s">
+        <v>1725</v>
+      </c>
+      <c r="D1218" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1218" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1218" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1218" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1218" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1218" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1218" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1219" s="22">
+        <v>46079</v>
+      </c>
+      <c r="B1219" s="14">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1219" s="2" t="s">
+        <v>1726</v>
+      </c>
+      <c r="D1219" s="2" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E1219" s="2">
+        <v>323</v>
+      </c>
+      <c r="F1219" s="2">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="G1219" s="2">
+        <v>28</v>
+      </c>
+      <c r="H1219" s="2">
+        <v>15.6</v>
+      </c>
+      <c r="I1219" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="J1219" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1220" s="22">
+        <v>46079</v>
+      </c>
+      <c r="B1220" s="14">
+        <v>0.5625</v>
+      </c>
+      <c r="C1220" s="2" t="s">
+        <v>1728</v>
+      </c>
+      <c r="D1220" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1220" s="2">
+        <v>175</v>
+      </c>
+      <c r="F1220" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G1220" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1220" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1220" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1220" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1221" s="22">
+        <v>46079</v>
+      </c>
+      <c r="B1221" s="14">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C1221" s="2" t="s">
+        <v>1729</v>
+      </c>
+      <c r="D1221" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1221" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1221" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1221" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1221" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1221" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1221" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1222" s="22">
+        <v>46079</v>
+      </c>
+      <c r="B1222" s="14">
+        <v>0.75</v>
+      </c>
+      <c r="C1222" s="2" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D1222" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E1222" s="2">
+        <v>145</v>
+      </c>
+      <c r="F1222" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="G1222" s="2">
+        <v>9</v>
+      </c>
+      <c r="H1222" s="2">
+        <v>9</v>
+      </c>
+      <c r="I1222" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1222" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1223" s="22">
+        <v>46079</v>
+      </c>
+      <c r="B1223" s="14">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C1223" s="2" t="s">
+        <v>1731</v>
+      </c>
+      <c r="D1223" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1223" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1223" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1223" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1223" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1223" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1223" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1224" s="22">
+        <v>46079</v>
+      </c>
+      <c r="B1224" s="14">
+        <v>0.8125</v>
+      </c>
+      <c r="C1224" s="2" t="s">
+        <v>1732</v>
+      </c>
+      <c r="D1224" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1224" s="2">
+        <v>175</v>
+      </c>
+      <c r="F1224" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G1224" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1224" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1224" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1224" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1225" s="22">
+        <v>46080</v>
+      </c>
+      <c r="B1225" s="14">
+        <v>0.3125</v>
+      </c>
+      <c r="C1225" s="2" t="s">
+        <v>1733</v>
+      </c>
+      <c r="D1225" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1225" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1225" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1225" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1225" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1225" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1225" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1226" s="22">
+        <v>46080</v>
+      </c>
+      <c r="B1226" s="14">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C1226" s="2" t="s">
+        <v>1734</v>
+      </c>
+      <c r="D1226" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E1226" s="2">
+        <v>90</v>
+      </c>
+      <c r="F1226" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1226" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1226" s="2">
+        <v>1</v>
+      </c>
+      <c r="I1226" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1226" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1227" s="22">
+        <v>46080</v>
+      </c>
+      <c r="B1227" s="14">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C1227" s="2" t="s">
+        <v>1735</v>
+      </c>
+      <c r="D1227" s="2" t="s">
+        <v>1736</v>
+      </c>
+      <c r="E1227" s="2">
+        <v>494</v>
+      </c>
+      <c r="F1227" s="2">
+        <v>23</v>
+      </c>
+      <c r="G1227" s="2">
+        <v>43</v>
+      </c>
+      <c r="H1227" s="2">
+        <v>27</v>
+      </c>
+      <c r="I1227" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1227" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1228" s="22">
+        <v>46080</v>
+      </c>
+      <c r="B1228" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C1228" s="2" t="s">
+        <v>1737</v>
+      </c>
+      <c r="D1228" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1228" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1228" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1228" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1228" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1228" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1228" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1229" s="22">
+        <v>46080</v>
+      </c>
+      <c r="B1229" s="14">
+        <v>0.4375</v>
+      </c>
+      <c r="C1229" s="2" t="s">
+        <v>1738</v>
+      </c>
+      <c r="D1229" s="2" t="s">
+        <v>1739</v>
+      </c>
+      <c r="E1229" s="2">
+        <v>90</v>
+      </c>
+      <c r="F1229" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="G1229" s="2">
+        <v>10</v>
+      </c>
+      <c r="H1229" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="I1229" s="2">
+        <v>9</v>
+      </c>
+      <c r="J1229" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1230" s="22">
+        <v>46080</v>
+      </c>
+      <c r="B1230" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="C1230" s="2" t="s">
+        <v>1740</v>
+      </c>
+      <c r="D1230" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1230" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1230" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1230" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1230" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1230" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1230" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1231" s="22">
+        <v>46080</v>
+      </c>
+      <c r="B1231" s="14">
+        <v>0.5625</v>
+      </c>
+      <c r="C1231" s="2" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D1231" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1231" s="2">
+        <v>175</v>
+      </c>
+      <c r="F1231" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G1231" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1231" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1231" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1231" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1232" s="22">
+        <v>46080</v>
+      </c>
+      <c r="B1232" s="14">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C1232" s="2" t="s">
+        <v>1742</v>
+      </c>
+      <c r="D1232" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1232" s="2">
+        <v>175</v>
+      </c>
+      <c r="F1232" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G1232" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1232" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1232" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1232" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1233" s="22">
+        <v>46080</v>
+      </c>
+      <c r="B1233" s="14">
+        <v>0.75</v>
+      </c>
+      <c r="C1233" s="2" t="s">
+        <v>1743</v>
+      </c>
+      <c r="D1233" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E1233" s="2">
+        <v>145</v>
+      </c>
+      <c r="F1233" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="G1233" s="2">
+        <v>9</v>
+      </c>
+      <c r="H1233" s="2">
+        <v>9</v>
+      </c>
+      <c r="I1233" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1233" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1234" s="22">
+        <v>46080</v>
+      </c>
+      <c r="B1234" s="14">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C1234" s="2" t="s">
+        <v>1744</v>
+      </c>
+      <c r="D1234" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1234" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1234" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1234" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1234" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1234" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1234" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1235" s="22">
+        <v>46080</v>
+      </c>
+      <c r="B1235" s="14">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C1235" s="2" t="s">
+        <v>1745</v>
+      </c>
+      <c r="D1235" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E1235" s="2">
+        <v>256</v>
+      </c>
+      <c r="F1235" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="G1235" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="H1235" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="I1235" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="J1235" s="2">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1236" s="22">
+        <v>46080</v>
+      </c>
+      <c r="B1236" s="14">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C1236" s="2" t="s">
+        <v>1746</v>
+      </c>
+      <c r="D1236" s="2" t="s">
+        <v>1616</v>
+      </c>
+      <c r="E1236" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1236" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1236" s="2">
+        <v>40</v>
+      </c>
+      <c r="H1236" s="2">
+        <v>12</v>
+      </c>
+      <c r="I1236" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1236" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1237" s="22">
+        <v>46081</v>
+      </c>
+      <c r="B1237" s="14">
+        <v>0.3125</v>
+      </c>
+      <c r="C1237" s="2" t="s">
+        <v>1747</v>
+      </c>
+      <c r="D1237" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1237" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1237" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1237" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1237" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1237" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1237" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1238" s="22">
+        <v>46081</v>
+      </c>
+      <c r="B1238" s="14">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1238" s="2" t="s">
+        <v>1748</v>
+      </c>
+      <c r="D1238" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1238" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1238" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1238" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1238" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1238" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1238" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1239" s="22">
+        <v>46081</v>
+      </c>
+      <c r="B1239" s="14">
+        <v>0.6875</v>
+      </c>
+      <c r="C1239" s="2" t="s">
+        <v>1749</v>
+      </c>
+      <c r="D1239" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1239" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1239" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1239" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1239" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1239" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1239" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1240" s="22">
+        <v>46081</v>
+      </c>
+      <c r="B1240" s="14">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C1240" s="2" t="s">
+        <v>1750</v>
+      </c>
+      <c r="D1240" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="E1240" s="2">
+        <v>235</v>
+      </c>
+      <c r="F1240" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="G1240" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1240" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1240" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1240" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1241" s="22">
+        <v>46081</v>
+      </c>
+      <c r="B1241" s="14">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C1241" s="2" t="s">
+        <v>1752</v>
+      </c>
+      <c r="D1241" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1241" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1241" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1241" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1241" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1241" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1241" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1242" s="22">
+        <v>46081</v>
+      </c>
+      <c r="B1242" s="14">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C1242" s="2" t="s">
+        <v>1753</v>
+      </c>
+      <c r="D1242" s="2" t="s">
+        <v>1654</v>
+      </c>
+      <c r="E1242" s="2">
+        <v>590</v>
+      </c>
+      <c r="F1242" s="2">
+        <v>47.5</v>
+      </c>
+      <c r="G1242" s="2">
+        <v>24</v>
+      </c>
+      <c r="H1242" s="2">
+        <v>42</v>
+      </c>
+      <c r="I1242" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1242" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1243" s="22">
+        <v>46081</v>
+      </c>
+      <c r="B1243" s="14">
+        <v>0.875</v>
+      </c>
+      <c r="C1243" s="2" t="s">
+        <v>1754</v>
+      </c>
+      <c r="D1243" s="2" t="s">
+        <v>1755</v>
+      </c>
+      <c r="E1243" s="2">
+        <v>320</v>
+      </c>
+      <c r="F1243" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1243" s="2">
+        <v>45</v>
+      </c>
+      <c r="H1243" s="2">
+        <v>12</v>
+      </c>
+      <c r="I1243" s="2">
+        <v>11</v>
+      </c>
+      <c r="J1243" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1244" s="22">
+        <v>46081</v>
+      </c>
+      <c r="B1244" s="14">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C1244" s="2" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D1244" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E1244" s="2">
+        <v>256</v>
+      </c>
+      <c r="F1244" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="G1244" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="H1244" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="I1244" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="J1244" s="2">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1245" s="22">
+        <v>46082</v>
+      </c>
+      <c r="B1245" s="14">
+        <v>0.3125</v>
+      </c>
+      <c r="C1245" s="2" t="s">
+        <v>1757</v>
+      </c>
+      <c r="D1245" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1245" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1245" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1245" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1245" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1245" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1245" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1246" s="22">
+        <v>46082</v>
+      </c>
+      <c r="B1246" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="C1246" s="2" t="s">
+        <v>1758</v>
+      </c>
+      <c r="D1246" s="2" t="s">
+        <v>1759</v>
+      </c>
+      <c r="E1246" s="2">
+        <v>231</v>
+      </c>
+      <c r="F1246" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="G1246" s="2">
+        <v>26</v>
+      </c>
+      <c r="H1246" s="2">
+        <v>12</v>
+      </c>
+      <c r="I1246" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1246" s="2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1247" s="22">
+        <v>46082</v>
+      </c>
+      <c r="B1247" s="14">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C1247" s="2" t="s">
+        <v>1760</v>
+      </c>
+      <c r="D1247" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1247" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1247" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1247" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1247" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1247" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1247" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1248" s="22">
+        <v>46082</v>
+      </c>
+      <c r="B1248" s="14">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1248" s="2" t="s">
+        <v>1761</v>
+      </c>
+      <c r="D1248" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1248" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1248" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1248" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1248" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1248" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1248" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1249" s="22">
+        <v>46082</v>
+      </c>
+      <c r="B1249" s="14">
+        <v>0.625</v>
+      </c>
+      <c r="C1249" s="2" t="s">
+        <v>1762</v>
+      </c>
+      <c r="D1249" s="2" t="s">
+        <v>1763</v>
+      </c>
+      <c r="E1249" s="2">
+        <v>136</v>
+      </c>
+      <c r="F1249" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="G1249" s="2">
+        <v>5</v>
+      </c>
+      <c r="H1249" s="2">
+        <v>9</v>
+      </c>
+      <c r="I1249" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="J1249" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1250" s="22">
+        <v>46082</v>
+      </c>
+      <c r="B1250" s="14">
+        <v>0.6875</v>
+      </c>
+      <c r="C1250" s="2" t="s">
+        <v>1764</v>
+      </c>
+      <c r="D1250" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1250" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1250" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1250" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1250" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1250" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1250" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1251" s="22">
+        <v>46082</v>
+      </c>
+      <c r="B1251" s="14">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C1251" s="2" t="s">
+        <v>1765</v>
+      </c>
+      <c r="D1251" s="2" t="s">
+        <v>1766</v>
+      </c>
+      <c r="E1251" s="2">
+        <v>207</v>
+      </c>
+      <c r="F1251" s="2">
+        <v>13</v>
+      </c>
+      <c r="G1251" s="2">
+        <v>25</v>
+      </c>
+      <c r="H1251" s="2">
+        <v>6</v>
+      </c>
+      <c r="I1251" s="2">
+        <v>3</v>
+      </c>
+      <c r="J1251" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1252" s="22">
+        <v>46082</v>
+      </c>
+      <c r="B1252" s="14">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C1252" s="2" t="s">
+        <v>1767</v>
+      </c>
+      <c r="D1252" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="E1252" s="2">
+        <v>68</v>
+      </c>
+      <c r="F1252" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="G1252" s="2">
+        <v>14</v>
+      </c>
+      <c r="H1252" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="I1252" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1252" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1253" s="22">
+        <v>46082</v>
+      </c>
+      <c r="B1253" s="14">
+        <v>0.75</v>
+      </c>
+      <c r="C1253" s="2" t="s">
+        <v>1768</v>
+      </c>
+      <c r="D1253" s="2" t="s">
+        <v>1769</v>
+      </c>
+      <c r="E1253" s="2">
+        <v>311</v>
+      </c>
+      <c r="F1253" s="2">
+        <v>27</v>
+      </c>
+      <c r="G1253" s="2">
+        <v>28</v>
+      </c>
+      <c r="H1253" s="2">
+        <v>8</v>
+      </c>
+      <c r="I1253" s="2">
+        <v>1</v>
+      </c>
+      <c r="J1253" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1254" s="22">
+        <v>46082</v>
+      </c>
+      <c r="B1254" s="14">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C1254" s="2" t="s">
+        <v>1770</v>
+      </c>
+      <c r="D1254" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1254" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1254" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1254" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1254" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1254" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1254" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1255" s="22">
+        <v>46082</v>
+      </c>
+      <c r="B1255" s="14">
+        <v>0.8125</v>
+      </c>
+      <c r="C1255" s="2" t="s">
+        <v>1771</v>
+      </c>
+      <c r="D1255" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="E1255" s="2">
+        <v>235</v>
+      </c>
+      <c r="F1255" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="G1255" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1255" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1255" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1255" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1256" s="22">
+        <v>46083</v>
+      </c>
+      <c r="B1256" s="14">
+        <v>0.3125</v>
+      </c>
+      <c r="C1256" s="2" t="s">
+        <v>1772</v>
+      </c>
+      <c r="D1256" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1256" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1256" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1256" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1256" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1256" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1256" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1257" s="22">
+        <v>46083</v>
+      </c>
+      <c r="B1257" s="14">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C1257" s="2" t="s">
+        <v>1773</v>
+      </c>
+      <c r="D1257" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E1257" s="2">
+        <v>145</v>
+      </c>
+      <c r="F1257" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="G1257" s="2">
+        <v>9</v>
+      </c>
+      <c r="H1257" s="2">
+        <v>9</v>
+      </c>
+      <c r="I1257" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1257" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1258" s="22">
+        <v>46083</v>
+      </c>
+      <c r="B1258" s="14">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1258" s="2" t="s">
+        <v>1774</v>
+      </c>
+      <c r="D1258" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1258" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1258" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1258" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1258" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1258" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1258" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1259" s="22">
+        <v>46083</v>
+      </c>
+      <c r="B1259" s="14">
+        <v>0.5625</v>
+      </c>
+      <c r="C1259" s="2" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D1259" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="E1259" s="2">
+        <v>235</v>
+      </c>
+      <c r="F1259" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="G1259" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1259" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1259" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1259" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1260" s="22">
+        <v>46083</v>
+      </c>
+      <c r="B1260" s="14">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C1260" s="2" t="s">
+        <v>1776</v>
+      </c>
+      <c r="D1260" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E1260" s="2">
+        <v>256</v>
+      </c>
+      <c r="F1260" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="G1260" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="H1260" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="I1260" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="J1260" s="2">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1261" s="22">
+        <v>46083</v>
+      </c>
+      <c r="B1261" s="14">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C1261" s="2" t="s">
+        <v>1777</v>
+      </c>
+      <c r="D1261" s="2" t="s">
+        <v>1778</v>
+      </c>
+      <c r="E1261" s="2">
+        <v>210</v>
+      </c>
+      <c r="F1261" s="2">
+        <v>5.8</v>
+      </c>
+      <c r="G1261" s="2">
+        <v>41.5</v>
+      </c>
+      <c r="H1261" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="I1261" s="2">
+        <v>21.5</v>
+      </c>
+      <c r="J1261" s="2">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1262" s="22">
+        <v>46083</v>
+      </c>
+      <c r="B1262" s="14">
+        <v>0.6875</v>
+      </c>
+      <c r="C1262" s="2" t="s">
+        <v>1779</v>
+      </c>
+      <c r="D1262" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1262" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1262" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1262" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1262" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1262" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1262" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1263" s="22">
+        <v>46083</v>
+      </c>
+      <c r="B1263" s="14">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C1263" s="2" t="s">
+        <v>1780</v>
+      </c>
+      <c r="D1263" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E1263" s="2">
+        <v>145</v>
+      </c>
+      <c r="F1263" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="G1263" s="2">
+        <v>9</v>
+      </c>
+      <c r="H1263" s="2">
+        <v>9</v>
+      </c>
+      <c r="I1263" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1263" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1264" s="22">
+        <v>46083</v>
+      </c>
+      <c r="B1264" s="14">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C1264" s="2" t="s">
+        <v>1781</v>
+      </c>
+      <c r="D1264" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1264" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1264" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1264" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1264" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1264" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1264" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1265" s="22">
+        <v>46083</v>
+      </c>
+      <c r="B1265" s="14">
+        <v>0.75</v>
+      </c>
+      <c r="C1265" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="D1265" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="E1265" s="2">
+        <v>284</v>
+      </c>
+      <c r="F1265" s="2">
+        <v>13</v>
+      </c>
+      <c r="G1265" s="2">
+        <v>8</v>
+      </c>
+      <c r="H1265" s="2">
+        <v>24</v>
+      </c>
+      <c r="I1265" s="2">
+        <v>2</v>
+      </c>
+      <c r="J1265" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1266" s="22">
+        <v>46083</v>
+      </c>
+      <c r="B1266" s="14">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C1266" s="2" t="s">
+        <v>1784</v>
+      </c>
+      <c r="D1266" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E1266" s="2">
+        <v>155</v>
+      </c>
+      <c r="F1266" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1266" s="2">
+        <v>23</v>
+      </c>
+      <c r="H1266" s="2">
+        <v>6</v>
+      </c>
+      <c r="I1266" s="2">
+        <v>12</v>
+      </c>
+      <c r="J1266" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1267" s="22">
+        <v>46084</v>
+      </c>
+      <c r="B1267" s="14">
+        <v>0.3125</v>
+      </c>
+      <c r="C1267" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D1267" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1267" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1267" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1267" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1267" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1267" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1267" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1268" s="22">
+        <v>46084</v>
+      </c>
+      <c r="B1268" s="14">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C1268" s="2" t="s">
+        <v>1786</v>
+      </c>
+      <c r="D1268" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E1268" s="2">
+        <v>256</v>
+      </c>
+      <c r="F1268" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="G1268" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="H1268" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="I1268" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="J1268" s="2">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1269" s="22">
+        <v>46084</v>
+      </c>
+      <c r="B1269" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="C1269" s="2" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D1269" s="2" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E1269" s="2">
+        <v>135</v>
+      </c>
+      <c r="F1269" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1269" s="2">
+        <v>19</v>
+      </c>
+      <c r="H1269" s="2">
+        <v>6</v>
+      </c>
+      <c r="I1269" s="2">
+        <v>2</v>
+      </c>
+      <c r="J1269" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1270" s="22">
+        <v>46084</v>
+      </c>
+      <c r="B1270" s="14">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C1270" s="2" t="s">
+        <v>1789</v>
+      </c>
+      <c r="D1270" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1270" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1270" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1270" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1270" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1270" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1270" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1271" s="22">
+        <v>46084</v>
+      </c>
+      <c r="B1271" s="14">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1271" s="2" t="s">
+        <v>1790</v>
+      </c>
+      <c r="D1271" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1271" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1271" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1271" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1271" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1271" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1271" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1272" s="22">
+        <v>46084</v>
+      </c>
+      <c r="B1272" s="14">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C1272" s="2" t="s">
+        <v>1791</v>
+      </c>
+      <c r="D1272" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E1272" s="2">
+        <v>145</v>
+      </c>
+      <c r="F1272" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="G1272" s="2">
+        <v>9</v>
+      </c>
+      <c r="H1272" s="2">
+        <v>9</v>
+      </c>
+      <c r="I1272" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1272" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1273" s="22">
+        <v>46084</v>
+      </c>
+      <c r="B1273" s="14">
+        <v>0.75</v>
+      </c>
+      <c r="C1273" s="2" t="s">
+        <v>1792</v>
+      </c>
+      <c r="D1273" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1273" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1273" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1273" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1273" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1273" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1273" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1274" s="22">
+        <v>46084</v>
+      </c>
+      <c r="B1274" s="14">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C1274" s="2" t="s">
+        <v>1793</v>
+      </c>
+      <c r="D1274" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="E1274" s="2">
+        <v>235</v>
+      </c>
+      <c r="F1274" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="G1274" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1274" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1274" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1274" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1275" s="22">
+        <v>46084</v>
+      </c>
+      <c r="B1275" s="14">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C1275" s="2" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D1275" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1275" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1275" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1275" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1275" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1275" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1275" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1276" s="22">
+        <v>46084</v>
+      </c>
+      <c r="B1276" s="14">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C1276" s="2" t="s">
+        <v>1795</v>
+      </c>
+      <c r="D1276" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="E1276" s="2">
+        <v>150</v>
+      </c>
+      <c r="F1276" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="G1276" s="2">
+        <v>35</v>
+      </c>
+      <c r="H1276" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="I1276" s="2">
+        <v>23.3</v>
+      </c>
+      <c r="J1276" s="2">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1277" s="22">
+        <v>46084</v>
+      </c>
+      <c r="B1277" s="14">
+        <v>0.875</v>
+      </c>
+      <c r="C1277" s="2" t="s">
+        <v>1796</v>
+      </c>
+      <c r="D1277" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E1277" s="2">
+        <v>155</v>
+      </c>
+      <c r="F1277" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1277" s="2">
+        <v>23</v>
+      </c>
+      <c r="H1277" s="2">
+        <v>6</v>
+      </c>
+      <c r="I1277" s="2">
+        <v>12</v>
+      </c>
+      <c r="J1277" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1278" s="22">
+        <v>46085</v>
+      </c>
+      <c r="B1278" s="14">
+        <v>0.3125</v>
+      </c>
+      <c r="C1278" s="2" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D1278" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1278" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1278" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1278" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1278" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1278" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1278" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1279" s="22">
+        <v>46085</v>
+      </c>
+      <c r="B1279" s="14">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C1279" s="2" t="s">
+        <v>1798</v>
+      </c>
+      <c r="D1279" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E1279" s="2">
+        <v>256</v>
+      </c>
+      <c r="F1279" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="G1279" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="H1279" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="I1279" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="J1279" s="2">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1280" s="22">
+        <v>46085</v>
+      </c>
+      <c r="B1280" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="C1280" s="2" t="s">
+        <v>1799</v>
+      </c>
+      <c r="D1280" s="2" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E1280" s="2">
+        <v>135</v>
+      </c>
+      <c r="F1280" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1280" s="2">
+        <v>19</v>
+      </c>
+      <c r="H1280" s="2">
+        <v>6</v>
+      </c>
+      <c r="I1280" s="2">
+        <v>2</v>
+      </c>
+      <c r="J1280" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1281" s="22">
+        <v>46085</v>
+      </c>
+      <c r="B1281" s="14">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C1281" s="2" t="s">
+        <v>1800</v>
+      </c>
+      <c r="D1281" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1281" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1281" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1281" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1281" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1281" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1281" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1282" s="22">
+        <v>46085</v>
+      </c>
+      <c r="B1282" s="14">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1282" s="2" t="s">
+        <v>1801</v>
+      </c>
+      <c r="D1282" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1282" s="2">
+        <v>155</v>
+      </c>
+      <c r="F1282" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G1282" s="2">
+        <v>15</v>
+      </c>
+      <c r="H1282" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1282" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1282" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1283" s="22">
+        <v>46085</v>
+      </c>
+      <c r="B1283" s="14">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C1283" s="2" t="s">
+        <v>1802</v>
+      </c>
+      <c r="D1283" s="2" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E1283" s="2">
+        <v>80</v>
+      </c>
+      <c r="F1283" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1283" s="2">
+        <v>20.7</v>
+      </c>
+      <c r="H1283" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="I1283" s="2">
+        <v>10.8</v>
+      </c>
+      <c r="J1283" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1284" s="22">
+        <v>46085</v>
+      </c>
+      <c r="B1284" s="14">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C1284" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="D1284" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1284" s="2">
+        <v>175</v>
+      </c>
+      <c r="F1284" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G1284" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1284" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1284" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1284" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1285" s="22">
+        <v>46085</v>
+      </c>
+      <c r="B1285" s="14">
+        <v>0.8125</v>
+      </c>
+      <c r="C1285" s="2" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D1285" s="2" t="s">
+        <v>1806</v>
+      </c>
+      <c r="E1285" s="2">
+        <v>370</v>
+      </c>
+      <c r="F1285" s="2">
+        <v>20</v>
+      </c>
+      <c r="G1285" s="2">
+        <v>34</v>
+      </c>
+      <c r="H1285" s="2">
+        <v>21</v>
+      </c>
+      <c r="I1285" s="2">
+        <v>3</v>
+      </c>
+      <c r="J1285" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1286" s="22">
+        <v>46085</v>
+      </c>
+      <c r="B1286" s="14">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C1286" s="2" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D1286" s="2" t="s">
+        <v>1808</v>
+      </c>
+      <c r="E1286" s="2">
+        <v>106</v>
+      </c>
+      <c r="F1286" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="G1286" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="H1286" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="I1286" s="2">
+        <v>4</v>
+      </c>
+      <c r="J1286" s="2">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1287" s="22">
+        <v>46085</v>
+      </c>
+      <c r="B1287" s="14">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C1287" s="2" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D1287" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1287" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1287" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1287" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1287" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1287" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1287" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1288" s="22">
+        <v>46085</v>
+      </c>
+      <c r="B1288" s="14">
+        <v>0.875</v>
+      </c>
+      <c r="C1288" s="2" t="s">
+        <v>1810</v>
+      </c>
+      <c r="D1288" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1288" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1288" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1288" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1288" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1288" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1288" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1289" s="22">
+        <v>46086</v>
+      </c>
+      <c r="B1289" s="14">
+        <v>0.3125</v>
+      </c>
+      <c r="C1289" s="2" t="s">
+        <v>1811</v>
+      </c>
+      <c r="D1289" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1289" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1289" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1289" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1289" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1289" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1289" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1290" s="22">
+        <v>46086</v>
+      </c>
+      <c r="B1290" s="14">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C1290" s="2" t="s">
+        <v>1812</v>
+      </c>
+      <c r="D1290" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1290" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1290" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1290" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1290" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1290" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1290" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1291" s="22">
+        <v>46086</v>
+      </c>
+      <c r="B1291" s="14">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C1291" s="2" t="s">
+        <v>1813</v>
+      </c>
+      <c r="D1291" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1291" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1291" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1291" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1291" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1291" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1291" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1292" s="22">
+        <v>46086</v>
+      </c>
+      <c r="B1292" s="14">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1292" s="2" t="s">
+        <v>1814</v>
+      </c>
+      <c r="D1292" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1292" s="2">
+        <v>175</v>
+      </c>
+      <c r="F1292" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G1292" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1292" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1292" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1292" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1293" s="22">
+        <v>46086</v>
+      </c>
+      <c r="B1293" s="14">
+        <v>0.5625</v>
+      </c>
+      <c r="C1293" s="2" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D1293" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1293" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1293" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1293" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1293" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1293" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1293" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1294" s="22">
+        <v>46086</v>
+      </c>
+      <c r="B1294" s="14">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C1294" s="2" t="s">
+        <v>1816</v>
+      </c>
+      <c r="D1294" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E1294" s="2">
+        <v>105</v>
+      </c>
+      <c r="F1294" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G1294" s="2">
+        <v>12.2</v>
+      </c>
+      <c r="H1294" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="I1294" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="J1294" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1295" s="22">
+        <v>46086</v>
+      </c>
+      <c r="B1295" s="14">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C1295" s="2" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D1295" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1295" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1295" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1295" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1295" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1295" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1295" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1296" s="22">
+        <v>46086</v>
+      </c>
+      <c r="B1296" s="14">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C1296" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="D1296" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E1296" s="2">
+        <v>145</v>
+      </c>
+      <c r="F1296" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="G1296" s="2">
+        <v>9</v>
+      </c>
+      <c r="H1296" s="2">
+        <v>9</v>
+      </c>
+      <c r="I1296" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1296" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1297" s="22">
+        <v>46086</v>
+      </c>
+      <c r="B1297" s="14">
+        <v>0.75</v>
+      </c>
+      <c r="C1297" s="2" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D1297" s="2" t="s">
+        <v>1820</v>
+      </c>
+      <c r="E1297" s="2">
+        <v>426</v>
+      </c>
+      <c r="F1297" s="2">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="G1297" s="2">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="H1297" s="2">
+        <v>22.6</v>
+      </c>
+      <c r="I1297" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="J1297" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1298" s="22">
+        <v>46086</v>
+      </c>
+      <c r="B1298" s="14">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C1298" s="2" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D1298" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1298" s="2">
+        <v>175</v>
+      </c>
+      <c r="F1298" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G1298" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1298" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1298" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1298" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1299" s="22">
+        <v>46087</v>
+      </c>
+      <c r="B1299" s="14">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C1299" s="2" t="s">
+        <v>1822</v>
+      </c>
+      <c r="D1299" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E1299" s="2">
+        <v>155</v>
+      </c>
+      <c r="F1299" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1299" s="2">
+        <v>23</v>
+      </c>
+      <c r="H1299" s="2">
+        <v>6</v>
+      </c>
+      <c r="I1299" s="2">
+        <v>12</v>
+      </c>
+      <c r="J1299" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1300" s="22">
+        <v>46087</v>
+      </c>
+      <c r="B1300" s="14">
+        <v>0.3125</v>
+      </c>
+      <c r="C1300" s="2" t="s">
+        <v>1823</v>
+      </c>
+      <c r="D1300" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1300" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1300" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1300" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1300" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1300" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1300" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1301" s="22">
+        <v>46087</v>
+      </c>
+      <c r="B1301" s="14">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C1301" s="2" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D1301" s="2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E1301" s="2">
+        <v>263</v>
+      </c>
+      <c r="F1301" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="G1301" s="2">
+        <v>30.5</v>
+      </c>
+      <c r="H1301" s="2">
+        <v>14.7</v>
+      </c>
+      <c r="I1301" s="2">
+        <v>3</v>
+      </c>
+      <c r="J1301" s="2">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1302" s="22">
+        <v>46087</v>
+      </c>
+      <c r="B1302" s="14">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C1302" s="2" t="s">
+        <v>1825</v>
+      </c>
+      <c r="D1302" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1302" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1302" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1302" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1302" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1302" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1302" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1303" s="22">
+        <v>46087</v>
+      </c>
+      <c r="B1303" s="14">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C1303" s="2" t="s">
+        <v>1826</v>
+      </c>
+      <c r="D1303" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1303" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1303" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1303" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1303" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1303" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1303" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1304" s="22">
+        <v>46087</v>
+      </c>
+      <c r="B1304" s="14">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1304" s="2" t="s">
+        <v>1827</v>
+      </c>
+      <c r="D1304" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1304" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1304" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1304" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1304" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1304" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1304" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1305" s="22">
+        <v>46087</v>
+      </c>
+      <c r="B1305" s="14">
+        <v>0.5625</v>
+      </c>
+      <c r="C1305" s="2" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D1305" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1305" s="2">
+        <v>175</v>
+      </c>
+      <c r="F1305" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G1305" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1305" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1305" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1305" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1306" s="22">
+        <v>46087</v>
+      </c>
+      <c r="B1306" s="14">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C1306" s="2" t="s">
+        <v>1829</v>
+      </c>
+      <c r="D1306" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E1306" s="2">
+        <v>145</v>
+      </c>
+      <c r="F1306" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="G1306" s="2">
+        <v>9</v>
+      </c>
+      <c r="H1306" s="2">
+        <v>9</v>
+      </c>
+      <c r="I1306" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1306" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1307" s="22">
+        <v>46087</v>
+      </c>
+      <c r="B1307" s="14">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C1307" s="2" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D1307" s="2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E1307" s="2">
+        <v>465</v>
+      </c>
+      <c r="F1307" s="2">
+        <v>30</v>
+      </c>
+      <c r="G1307" s="2">
+        <v>55</v>
+      </c>
+      <c r="H1307" s="2">
+        <v>15</v>
+      </c>
+      <c r="I1307" s="2">
+        <v>3</v>
+      </c>
+      <c r="J1307" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1308" s="22">
+        <v>46087</v>
+      </c>
+      <c r="B1308" s="14">
+        <v>0.75</v>
+      </c>
+      <c r="C1308" s="2" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D1308" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1308" s="2">
+        <v>175</v>
+      </c>
+      <c r="F1308" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G1308" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1308" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1308" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1308" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1309" s="22">
+        <v>46087</v>
+      </c>
+      <c r="B1309" s="14">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C1309" s="2" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D1309" s="2" t="s">
+        <v>1834</v>
+      </c>
+      <c r="E1309" s="2">
+        <v>102</v>
+      </c>
+      <c r="F1309" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G1309" s="2">
+        <v>23.8</v>
+      </c>
+      <c r="H1309" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="I1309" s="2">
+        <v>16</v>
+      </c>
+      <c r="J1309" s="2">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1310" s="22">
+        <v>46088</v>
+      </c>
+      <c r="B1310" s="14">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C1310" s="2" t="s">
+        <v>1835</v>
+      </c>
+      <c r="D1310" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="E1310" s="2">
+        <v>270</v>
+      </c>
+      <c r="F1310" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1310" s="2">
+        <v>35</v>
+      </c>
+      <c r="H1310" s="2">
+        <v>12</v>
+      </c>
+      <c r="I1310" s="2">
+        <v>1</v>
+      </c>
+      <c r="J1310" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1311" s="22">
+        <v>46088</v>
+      </c>
+      <c r="B1311" s="14">
+        <v>0.3125</v>
+      </c>
+      <c r="C1311" s="2" t="s">
+        <v>1836</v>
+      </c>
+      <c r="D1311" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1311" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1311" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1311" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1311" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1311" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1311" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1312" s="22">
+        <v>46088</v>
+      </c>
+      <c r="B1312" s="14">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C1312" s="2" t="s">
+        <v>1837</v>
+      </c>
+      <c r="D1312" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="E1312" s="2">
+        <v>158</v>
+      </c>
+      <c r="F1312" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="G1312" s="2">
+        <v>18.3</v>
+      </c>
+      <c r="H1312" s="2">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="I1312" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="J1312" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1313" s="22">
+        <v>46088</v>
+      </c>
+      <c r="B1313" s="14">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C1313" s="2" t="s">
+        <v>1838</v>
+      </c>
+      <c r="D1313" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1313" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1313" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1313" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1313" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1313" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1313" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1314" s="22">
+        <v>46088</v>
+      </c>
+      <c r="B1314" s="14">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C1314" s="2" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D1314" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1314" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1314" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1314" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1314" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1314" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1314" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1315" s="22">
+        <v>46088</v>
+      </c>
+      <c r="B1315" s="14">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1315" s="2" t="s">
+        <v>1840</v>
+      </c>
+      <c r="D1315" s="2" t="s">
+        <v>1605</v>
+      </c>
+      <c r="E1315" s="2">
+        <v>245</v>
+      </c>
+      <c r="F1315" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1315" s="2">
+        <v>28</v>
+      </c>
+      <c r="H1315" s="2">
+        <v>9</v>
+      </c>
+      <c r="I1315" s="2">
+        <v>1</v>
+      </c>
+      <c r="J1315" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1316" s="22">
+        <v>46088</v>
+      </c>
+      <c r="B1316" s="14">
+        <v>0.5625</v>
+      </c>
+      <c r="C1316" s="2" t="s">
+        <v>1841</v>
+      </c>
+      <c r="D1316" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1316" s="2">
+        <v>155</v>
+      </c>
+      <c r="F1316" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G1316" s="2">
+        <v>15</v>
+      </c>
+      <c r="H1316" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1316" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1316" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1317" s="22">
+        <v>46088</v>
+      </c>
+      <c r="B1317" s="14">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C1317" s="2" t="s">
+        <v>1842</v>
+      </c>
+      <c r="D1317" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E1317" s="2">
+        <v>145</v>
+      </c>
+      <c r="F1317" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="G1317" s="2">
+        <v>9</v>
+      </c>
+      <c r="H1317" s="2">
+        <v>9</v>
+      </c>
+      <c r="I1317" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1317" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1318" s="22">
+        <v>46088</v>
+      </c>
+      <c r="B1318" s="14">
+        <v>0.75</v>
+      </c>
+      <c r="C1318" s="2" t="s">
+        <v>1843</v>
+      </c>
+      <c r="D1318" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1318" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1318" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1318" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1318" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1318" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1318" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1319" s="22">
+        <v>46088</v>
+      </c>
+      <c r="B1319" s="14">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C1319" s="2" t="s">
+        <v>1844</v>
+      </c>
+      <c r="D1319" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E1319" s="2">
+        <v>256</v>
+      </c>
+      <c r="F1319" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="G1319" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="H1319" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="I1319" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="J1319" s="2">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1320" s="22">
+        <v>46088</v>
+      </c>
+      <c r="B1320" s="14">
+        <v>0.875</v>
+      </c>
+      <c r="C1320" s="2" t="s">
+        <v>1845</v>
+      </c>
+      <c r="D1320" s="2" t="s">
+        <v>1846</v>
+      </c>
+      <c r="E1320" s="2">
+        <v>450</v>
+      </c>
+      <c r="F1320" s="2">
+        <v>20</v>
+      </c>
+      <c r="G1320" s="2">
+        <v>48</v>
+      </c>
+      <c r="H1320" s="2">
+        <v>20</v>
+      </c>
+      <c r="I1320" s="2">
+        <v>3</v>
+      </c>
+      <c r="J1320" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1321" s="22">
+        <v>46089</v>
+      </c>
+      <c r="B1321" s="14">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C1321" s="2" t="s">
+        <v>1847</v>
+      </c>
+      <c r="D1321" s="2" t="s">
+        <v>1848</v>
+      </c>
+      <c r="E1321" s="2">
+        <v>71</v>
+      </c>
+      <c r="F1321" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="G1321" s="2">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="H1321" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="I1321" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="J1321" s="2">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1322" s="22">
+        <v>46089</v>
+      </c>
+      <c r="B1322" s="14">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C1322" s="2" t="s">
+        <v>1849</v>
+      </c>
+      <c r="D1322" s="2" t="s">
+        <v>1850</v>
+      </c>
+      <c r="E1322" s="2">
+        <v>163</v>
+      </c>
+      <c r="F1322" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="G1322" s="2">
+        <v>12.2</v>
+      </c>
+      <c r="H1322" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="I1322" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="J1322" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1323" s="22">
+        <v>46089</v>
+      </c>
+      <c r="B1323" s="14">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C1323" s="2" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D1323" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1323" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1323" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1323" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1323" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1323" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1323" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1324" s="22">
+        <v>46089</v>
+      </c>
+      <c r="B1324" s="14">
+        <v>0.4375</v>
+      </c>
+      <c r="C1324" s="2" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D1324" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1324" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1324" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1324" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1324" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1324" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1324" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1325" s="22">
+        <v>46089</v>
+      </c>
+      <c r="B1325" s="14">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1325" s="2" t="s">
+        <v>1853</v>
+      </c>
+      <c r="D1325" s="2" t="s">
+        <v>1854</v>
+      </c>
+      <c r="E1325" s="2">
+        <v>245</v>
+      </c>
+      <c r="F1325" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1325" s="2">
+        <v>28</v>
+      </c>
+      <c r="H1325" s="2">
+        <v>9</v>
+      </c>
+      <c r="I1325" s="2">
+        <v>1</v>
+      </c>
+      <c r="J1325" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1326" s="22">
+        <v>46089</v>
+      </c>
+      <c r="B1326" s="14">
+        <v>0.5625</v>
+      </c>
+      <c r="C1326" s="2" t="s">
+        <v>1855</v>
+      </c>
+      <c r="D1326" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1326" s="2">
+        <v>175</v>
+      </c>
+      <c r="F1326" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G1326" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1326" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1326" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1326" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1327" s="22">
+        <v>46089</v>
+      </c>
+      <c r="B1327" s="14">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C1327" s="2" t="s">
+        <v>1856</v>
+      </c>
+      <c r="D1327" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1327" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1327" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1327" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1327" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1327" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1327" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1328" s="22">
+        <v>46089</v>
+      </c>
+      <c r="B1328" s="14">
+        <v>0.75</v>
+      </c>
+      <c r="C1328" s="2" t="s">
+        <v>1857</v>
+      </c>
+      <c r="D1328" s="2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E1328" s="2">
+        <v>465</v>
+      </c>
+      <c r="F1328" s="2">
+        <v>30</v>
+      </c>
+      <c r="G1328" s="2">
+        <v>55</v>
+      </c>
+      <c r="H1328" s="2">
+        <v>15</v>
+      </c>
+      <c r="I1328" s="2">
+        <v>3</v>
+      </c>
+      <c r="J1328" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1329" s="22">
+        <v>46089</v>
+      </c>
+      <c r="B1329" s="14">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C1329" s="2" t="s">
+        <v>1858</v>
+      </c>
+      <c r="D1329" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1329" s="2">
+        <v>155</v>
+      </c>
+      <c r="F1329" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G1329" s="2">
+        <v>15</v>
+      </c>
+      <c r="H1329" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1329" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1329" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1330" s="22">
+        <v>46089</v>
+      </c>
+      <c r="B1330" s="14">
+        <v>0.8125</v>
+      </c>
+      <c r="C1330" s="2" t="s">
+        <v>1859</v>
+      </c>
+      <c r="D1330" s="2" t="s">
+        <v>1766</v>
+      </c>
+      <c r="E1330" s="2">
+        <v>207</v>
+      </c>
+      <c r="F1330" s="2">
+        <v>13</v>
+      </c>
+      <c r="G1330" s="2">
+        <v>4</v>
+      </c>
+      <c r="H1330" s="2">
+        <v>7</v>
+      </c>
+      <c r="I1330" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J1330" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1331" s="22">
+        <v>46089</v>
+      </c>
+      <c r="B1331" s="14">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C1331" s="2" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D1331" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1331" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1331" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1331" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1331" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1331" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1331" s="2">
+        <v>2.7</v>
       </c>
     </row>
   </sheetData>
@@ -44504,7 +48740,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F24E0C0-BC77-4AA4-801C-82B038A8B8E4}">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -45461,6 +49697,60 @@
       </c>
       <c r="F48" s="2"/>
     </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="22">
+        <v>46081</v>
+      </c>
+      <c r="B49" s="28">
+        <v>97.1</v>
+      </c>
+      <c r="C49" s="28">
+        <v>37.1</v>
+      </c>
+      <c r="D49" s="2">
+        <v>28.3</v>
+      </c>
+      <c r="E49" s="28">
+        <v>50.4</v>
+      </c>
+      <c r="F49" s="2"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="22">
+        <v>46086</v>
+      </c>
+      <c r="B50" s="28">
+        <v>97.1</v>
+      </c>
+      <c r="C50" s="28">
+        <v>37.4</v>
+      </c>
+      <c r="D50" s="2">
+        <v>27.8</v>
+      </c>
+      <c r="E50" s="28">
+        <v>50.8</v>
+      </c>
+      <c r="F50" s="2"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="22">
+        <v>46088</v>
+      </c>
+      <c r="B51" s="28">
+        <v>97</v>
+      </c>
+      <c r="C51" s="28">
+        <v>37.9</v>
+      </c>
+      <c r="D51" s="2">
+        <v>27</v>
+      </c>
+      <c r="E51" s="28">
+        <v>51.4</v>
+      </c>
+      <c r="F51" s="2"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -45470,7 +49760,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D2F321-D2D4-48D2-B6F9-E306604CF730}">
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -47218,6 +51508,258 @@
       <c r="G74" s="2"/>
       <c r="H74" s="2" t="s">
         <v>1707</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" s="22">
+        <v>46079</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D75" s="2">
+        <v>34</v>
+      </c>
+      <c r="E75" s="2">
+        <v>240</v>
+      </c>
+      <c r="F75" s="2">
+        <v>3170</v>
+      </c>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76" s="22">
+        <v>46080</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D76" s="2">
+        <v>52</v>
+      </c>
+      <c r="E76" s="2">
+        <v>416</v>
+      </c>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="H76" s="2"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77" s="22">
+        <v>46080</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D77" s="2">
+        <v>72</v>
+      </c>
+      <c r="E77" s="2">
+        <v>416</v>
+      </c>
+      <c r="F77" s="2">
+        <v>5600</v>
+      </c>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78" s="22">
+        <v>46081</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D78" s="2">
+        <v>22</v>
+      </c>
+      <c r="E78" s="2">
+        <v>152</v>
+      </c>
+      <c r="F78" s="2">
+        <v>1600</v>
+      </c>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" s="22">
+        <v>46081</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D79" s="2">
+        <v>62</v>
+      </c>
+      <c r="E79" s="2">
+        <v>517</v>
+      </c>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2" t="s">
+        <v>1712</v>
+      </c>
+      <c r="H79" s="2"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" s="22">
+        <v>46082</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D80" s="2">
+        <v>69</v>
+      </c>
+      <c r="E80" s="2">
+        <v>485</v>
+      </c>
+      <c r="F80" s="2">
+        <v>15850</v>
+      </c>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81" s="22">
+        <v>46084</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D81" s="2">
+        <v>55</v>
+      </c>
+      <c r="E81" s="2">
+        <v>450</v>
+      </c>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" s="22">
+        <v>46085</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D82" s="2">
+        <v>86</v>
+      </c>
+      <c r="E82" s="2">
+        <v>747</v>
+      </c>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83" s="22">
+        <v>46087</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D83" s="2">
+        <v>70</v>
+      </c>
+      <c r="E83" s="2">
+        <v>540</v>
+      </c>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" s="22">
+        <v>46088</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D84" s="2">
+        <v>71</v>
+      </c>
+      <c r="E84" s="2">
+        <v>599</v>
+      </c>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" s="22">
+        <v>46089</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D85" s="2">
+        <v>59</v>
+      </c>
+      <c r="E85" s="2">
+        <v>443</v>
+      </c>
+      <c r="F85" s="2">
+        <v>15550</v>
+      </c>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2" t="s">
+        <v>1718</v>
       </c>
     </row>
   </sheetData>

--- a/Food Log Main.xlsx
+++ b/Food Log Main.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91998\VS\Food Log Project Jan 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{878E8079-048E-45B7-A96E-F12C39D2252B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7997BE54-2514-436A-9BD8-DFD7EB40200B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main Format 12 oct" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3516" uniqueCount="1861">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3746" uniqueCount="1980">
   <si>
     <t>date</t>
   </si>
@@ -5643,6 +5643,363 @@
   </si>
   <si>
     <t>FD20260308-2000-1j5e</t>
+  </si>
+  <si>
+    <t>FD20260309-0700-2k6f</t>
+  </si>
+  <si>
+    <t>FD20260309-0730-3l7g</t>
+  </si>
+  <si>
+    <t>FD20260309-0830-4m8h</t>
+  </si>
+  <si>
+    <t>FD20260309-1230-5n9i</t>
+  </si>
+  <si>
+    <t>FD20260309-1300-6o0j</t>
+  </si>
+  <si>
+    <t>FD20260309-1330-7p1k</t>
+  </si>
+  <si>
+    <t>FD20260309-1400-8q2l</t>
+  </si>
+  <si>
+    <t>Orange (100g)</t>
+  </si>
+  <si>
+    <t>FD20260309-1430-9r3m</t>
+  </si>
+  <si>
+    <t>FD20260309-1700-0s4n</t>
+  </si>
+  <si>
+    <t>FD20260309-1800-1t5o</t>
+  </si>
+  <si>
+    <t>FD20260309-2100-2u6p</t>
+  </si>
+  <si>
+    <t>FD20260309-2130-3v7q</t>
+  </si>
+  <si>
+    <t>FD20260309-2200-7z1u</t>
+  </si>
+  <si>
+    <t>FD20260310-0730-4w8r</t>
+  </si>
+  <si>
+    <t>FD20260310-0800-5x9s</t>
+  </si>
+  <si>
+    <t>FD20260310-0830-6y0t</t>
+  </si>
+  <si>
+    <t>FD20260310-1500-8a2v</t>
+  </si>
+  <si>
+    <t>FD20260310-1530-9b3w</t>
+  </si>
+  <si>
+    <t>FD20260310-1600-0c4x</t>
+  </si>
+  <si>
+    <t>FD20260310-1700-1d5y</t>
+  </si>
+  <si>
+    <t>FD20260310-1800-2e6z</t>
+  </si>
+  <si>
+    <t>FD20260310-2000-3f7a</t>
+  </si>
+  <si>
+    <t>FD20260310-2200-4g8b</t>
+  </si>
+  <si>
+    <t>FD20260310-2230-5h9c</t>
+  </si>
+  <si>
+    <t>FD20260311-0730-6i0d</t>
+  </si>
+  <si>
+    <t>Coconut chutney (214g)</t>
+  </si>
+  <si>
+    <t>FD20260311-0800-7j1e</t>
+  </si>
+  <si>
+    <t>Mangalore bun (245g / 2 pieces)</t>
+  </si>
+  <si>
+    <t>FD20260311-0830-8k2f</t>
+  </si>
+  <si>
+    <t>FD20260311-1200-9l3g</t>
+  </si>
+  <si>
+    <t>FD20260311-1300-0m4h</t>
+  </si>
+  <si>
+    <t>FD20260311-1500-1n5i</t>
+  </si>
+  <si>
+    <t>FD20260311-1800-2o6j</t>
+  </si>
+  <si>
+    <t>FD20260311-1830-3p7k</t>
+  </si>
+  <si>
+    <t>2 rotis + 50g chicken</t>
+  </si>
+  <si>
+    <t>FD20260311-1900-4q8l</t>
+  </si>
+  <si>
+    <t>FD20260312-0700-5r9m</t>
+  </si>
+  <si>
+    <t>FD20260312-1000-6s0n</t>
+  </si>
+  <si>
+    <t>FD20260312-1030-7t1o</t>
+  </si>
+  <si>
+    <t>FD20260312-1130-8u2p</t>
+  </si>
+  <si>
+    <t>FD20260312-1230-9v3q</t>
+  </si>
+  <si>
+    <t>FD20260312-1330-0w4r</t>
+  </si>
+  <si>
+    <t>FD20260312-1700-1x5s</t>
+  </si>
+  <si>
+    <t>FD20260312-1930-2y6t</t>
+  </si>
+  <si>
+    <t>FD20260312-2000-3z7u</t>
+  </si>
+  <si>
+    <t>FD20260313-0700-4a8v</t>
+  </si>
+  <si>
+    <t>FD20260313-0830-5b9w</t>
+  </si>
+  <si>
+    <t>FD20260313-1000-6c0x</t>
+  </si>
+  <si>
+    <t>FD20260313-1130-7d1y</t>
+  </si>
+  <si>
+    <t>FD20260313-1300-8e2z</t>
+  </si>
+  <si>
+    <t>FD20260313-1330-9f3a</t>
+  </si>
+  <si>
+    <t>FD20260313-1830-0g4b</t>
+  </si>
+  <si>
+    <t>FD20260313-1900-1h5c</t>
+  </si>
+  <si>
+    <t>FD20260313-1930-2i6d</t>
+  </si>
+  <si>
+    <t>FD20260314-0700-3j7e</t>
+  </si>
+  <si>
+    <t>FD20260314-0900-4k8f</t>
+  </si>
+  <si>
+    <t>FD20260314-0930-5l9g</t>
+  </si>
+  <si>
+    <t>FD20260314-1000-6m0h</t>
+  </si>
+  <si>
+    <t>FD20260314-1330-7n1i</t>
+  </si>
+  <si>
+    <t>FD20260314-1400-8o2j</t>
+  </si>
+  <si>
+    <t>FD20260314-1700-9p3k</t>
+  </si>
+  <si>
+    <t>FD20260314-1900-0q4l</t>
+  </si>
+  <si>
+    <t>FD20260314-1930-1r5m</t>
+  </si>
+  <si>
+    <t>150g chicken curry + 2 rotis</t>
+  </si>
+  <si>
+    <t>FD20260315-0900-2s6n</t>
+  </si>
+  <si>
+    <t>FD20260315-0930-3t7o</t>
+  </si>
+  <si>
+    <t>1 roti + 1 poached egg</t>
+  </si>
+  <si>
+    <t>FD20260315-1130-4u8p</t>
+  </si>
+  <si>
+    <t>FD20260315-1330-5v9q</t>
+  </si>
+  <si>
+    <t>FD20260315-1400-6w0r</t>
+  </si>
+  <si>
+    <t>FD20260315-1430-7x1s</t>
+  </si>
+  <si>
+    <t>FD20260315-1530-8y2t</t>
+  </si>
+  <si>
+    <t>FD20260315-1830-9z3u</t>
+  </si>
+  <si>
+    <t>FD20260315-1930-0a4v</t>
+  </si>
+  <si>
+    <t>FD20260315-2000-1b5w</t>
+  </si>
+  <si>
+    <t>½ Chocolate pudding</t>
+  </si>
+  <si>
+    <t>FD20260315-2030-2c6x</t>
+  </si>
+  <si>
+    <t>FD20260316-0700-3d7y</t>
+  </si>
+  <si>
+    <t>FD20260316-0730-4e8z</t>
+  </si>
+  <si>
+    <t>FD20260316-0800-5f9a</t>
+  </si>
+  <si>
+    <t>FD20260316-0830-6g0b</t>
+  </si>
+  <si>
+    <t>FD20260316-0900-7h1c</t>
+  </si>
+  <si>
+    <t>FD20260316-1230-8i2d</t>
+  </si>
+  <si>
+    <t>FD20260316-1300-9j3e</t>
+  </si>
+  <si>
+    <t>FD20260316-1330-0k4f</t>
+  </si>
+  <si>
+    <t>FD20260316-2000-1l5g</t>
+  </si>
+  <si>
+    <t>Chilli Chicken (200g)</t>
+  </si>
+  <si>
+    <t>FD20260316-2030-2m6h</t>
+  </si>
+  <si>
+    <t>Gin (3×30ml)</t>
+  </si>
+  <si>
+    <t>FD20260317-0730-3n7i</t>
+  </si>
+  <si>
+    <t>FD20260317-0800-4o8j</t>
+  </si>
+  <si>
+    <t>FD20260317-1300-5p9k</t>
+  </si>
+  <si>
+    <t>FD20260317-1330-6q0l</t>
+  </si>
+  <si>
+    <t>FD20260317-1830-7r1m</t>
+  </si>
+  <si>
+    <t>½ Pulled pork burger</t>
+  </si>
+  <si>
+    <t>FD20260317-1900-8s2n</t>
+  </si>
+  <si>
+    <t>FD20260317-2030-9t3o</t>
+  </si>
+  <si>
+    <t>FD20260317-2100-0u4p</t>
+  </si>
+  <si>
+    <t>FD20260317-2130-1v5q</t>
+  </si>
+  <si>
+    <t>FD20260318-0730-2w6r</t>
+  </si>
+  <si>
+    <t>FD20260318-1300-3x7s</t>
+  </si>
+  <si>
+    <t>FD20260318-1330-4y8t</t>
+  </si>
+  <si>
+    <t>FD20260318-1400-5z9u</t>
+  </si>
+  <si>
+    <t>FD20260318-1430-6a0v</t>
+  </si>
+  <si>
+    <t>FD20260318-1500-7b1w</t>
+  </si>
+  <si>
+    <t>FD20260318-1900-8c2x</t>
+  </si>
+  <si>
+    <t>FD20260318-1930-9d3y</t>
+  </si>
+  <si>
+    <t>FD20260318-2000-0e4z</t>
+  </si>
+  <si>
+    <t>FD20260318-2030-1f5a</t>
+  </si>
+  <si>
+    <t>FD20260318-2100-2g6b</t>
+  </si>
+  <si>
+    <t>FD20260318-2130-3h7c</t>
+  </si>
+  <si>
+    <t>WK20260310-wm</t>
+  </si>
+  <si>
+    <t>WK20260312-w</t>
+  </si>
+  <si>
+    <t>WK20260312-wm</t>
+  </si>
+  <si>
+    <t>WK20260313-w</t>
+  </si>
+  <si>
+    <t>WK20260313-wm</t>
+  </si>
+  <si>
+    <t>WK20260314-w</t>
+  </si>
+  <si>
+    <t>WK20260314-wm</t>
   </si>
 </sst>
 </file>
@@ -6124,7 +6481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J1331"/>
+  <dimension ref="A1:J1433"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -48714,6 +49071,3270 @@
       </c>
       <c r="J1331" s="2">
         <v>2.7</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1332" s="22">
+        <v>46090</v>
+      </c>
+      <c r="B1332" s="14">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C1332" s="2" t="s">
+        <v>1861</v>
+      </c>
+      <c r="D1332" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="E1332" s="2">
+        <v>135</v>
+      </c>
+      <c r="F1332" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1332" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1332" s="2">
+        <v>6</v>
+      </c>
+      <c r="I1332" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1332" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1333" s="22">
+        <v>46090</v>
+      </c>
+      <c r="B1333" s="14">
+        <v>0.3125</v>
+      </c>
+      <c r="C1333" s="2" t="s">
+        <v>1862</v>
+      </c>
+      <c r="D1333" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1333" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1333" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1333" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1333" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1333" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1333" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1334" s="22">
+        <v>46090</v>
+      </c>
+      <c r="B1334" s="14">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C1334" s="2" t="s">
+        <v>1863</v>
+      </c>
+      <c r="D1334" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1334" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1334" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1334" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1334" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1334" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1334" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1335" s="22">
+        <v>46090</v>
+      </c>
+      <c r="B1335" s="14">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C1335" s="2" t="s">
+        <v>1864</v>
+      </c>
+      <c r="D1335" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1335" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1335" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1335" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1335" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1335" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1335" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1336" s="22">
+        <v>46090</v>
+      </c>
+      <c r="B1336" s="14">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1336" s="2" t="s">
+        <v>1865</v>
+      </c>
+      <c r="D1336" s="2" t="s">
+        <v>1605</v>
+      </c>
+      <c r="E1336" s="2">
+        <v>245</v>
+      </c>
+      <c r="F1336" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1336" s="2">
+        <v>28</v>
+      </c>
+      <c r="H1336" s="2">
+        <v>9</v>
+      </c>
+      <c r="I1336" s="2">
+        <v>1</v>
+      </c>
+      <c r="J1336" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1337" s="22">
+        <v>46090</v>
+      </c>
+      <c r="B1337" s="14">
+        <v>0.5625</v>
+      </c>
+      <c r="C1337" s="2" t="s">
+        <v>1866</v>
+      </c>
+      <c r="D1337" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1337" s="2">
+        <v>155</v>
+      </c>
+      <c r="F1337" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G1337" s="2">
+        <v>15</v>
+      </c>
+      <c r="H1337" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1337" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1337" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1338" s="22">
+        <v>46090</v>
+      </c>
+      <c r="B1338" s="14">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C1338" s="2" t="s">
+        <v>1867</v>
+      </c>
+      <c r="D1338" s="2" t="s">
+        <v>1868</v>
+      </c>
+      <c r="E1338" s="2">
+        <v>47</v>
+      </c>
+      <c r="F1338" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="G1338" s="2">
+        <v>12</v>
+      </c>
+      <c r="H1338" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I1338" s="2">
+        <v>9</v>
+      </c>
+      <c r="J1338" s="2">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1339" s="22">
+        <v>46090</v>
+      </c>
+      <c r="B1339" s="14">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C1339" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="D1339" s="2" t="s">
+        <v>1590</v>
+      </c>
+      <c r="E1339" s="2">
+        <v>69</v>
+      </c>
+      <c r="F1339" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="G1339" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1339" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="I1339" s="2">
+        <v>15</v>
+      </c>
+      <c r="J1339" s="2">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1340" s="22">
+        <v>46090</v>
+      </c>
+      <c r="B1340" s="14">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C1340" s="2" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D1340" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E1340" s="2">
+        <v>155</v>
+      </c>
+      <c r="F1340" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1340" s="2">
+        <v>23</v>
+      </c>
+      <c r="H1340" s="2">
+        <v>6</v>
+      </c>
+      <c r="I1340" s="2">
+        <v>12</v>
+      </c>
+      <c r="J1340" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1341" s="22">
+        <v>46090</v>
+      </c>
+      <c r="B1341" s="14">
+        <v>0.75</v>
+      </c>
+      <c r="C1341" s="2" t="s">
+        <v>1871</v>
+      </c>
+      <c r="D1341" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1341" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1341" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1341" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1341" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1341" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1341" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1342" s="22">
+        <v>46090</v>
+      </c>
+      <c r="B1342" s="14">
+        <v>0.875</v>
+      </c>
+      <c r="C1342" s="2" t="s">
+        <v>1872</v>
+      </c>
+      <c r="D1342" s="2" t="s">
+        <v>1854</v>
+      </c>
+      <c r="E1342" s="2">
+        <v>245</v>
+      </c>
+      <c r="F1342" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1342" s="2">
+        <v>28</v>
+      </c>
+      <c r="H1342" s="2">
+        <v>9</v>
+      </c>
+      <c r="I1342" s="2">
+        <v>1</v>
+      </c>
+      <c r="J1342" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1343" s="22">
+        <v>46090</v>
+      </c>
+      <c r="B1343" s="14">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C1343" s="2" t="s">
+        <v>1873</v>
+      </c>
+      <c r="D1343" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E1343" s="2">
+        <v>90</v>
+      </c>
+      <c r="F1343" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1343" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1343" s="2">
+        <v>1</v>
+      </c>
+      <c r="I1343" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1343" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1344" s="22">
+        <v>46090</v>
+      </c>
+      <c r="B1344" s="14">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="C1344" s="2" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D1344" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1344" s="2">
+        <v>175</v>
+      </c>
+      <c r="F1344" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G1344" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1344" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1344" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1344" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1345" s="22">
+        <v>46091</v>
+      </c>
+      <c r="B1345" s="14">
+        <v>0.3125</v>
+      </c>
+      <c r="C1345" s="2" t="s">
+        <v>1875</v>
+      </c>
+      <c r="D1345" s="2" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E1345" s="2">
+        <v>80</v>
+      </c>
+      <c r="F1345" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1345" s="2">
+        <v>20.7</v>
+      </c>
+      <c r="H1345" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="I1345" s="2">
+        <v>10.8</v>
+      </c>
+      <c r="J1345" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1346" s="22">
+        <v>46091</v>
+      </c>
+      <c r="B1346" s="14">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C1346" s="2" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D1346" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1346" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1346" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1346" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1346" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1346" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1346" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1347" s="22">
+        <v>46091</v>
+      </c>
+      <c r="B1347" s="14">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C1347" s="2" t="s">
+        <v>1877</v>
+      </c>
+      <c r="D1347" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1347" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1347" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1347" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1347" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1347" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1347" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1348" s="22">
+        <v>46091</v>
+      </c>
+      <c r="B1348" s="14">
+        <v>0.625</v>
+      </c>
+      <c r="C1348" s="2" t="s">
+        <v>1878</v>
+      </c>
+      <c r="D1348" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1348" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1348" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1348" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1348" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1348" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1348" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1349" s="22">
+        <v>46091</v>
+      </c>
+      <c r="B1349" s="14">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C1349" s="2" t="s">
+        <v>1879</v>
+      </c>
+      <c r="D1349" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1349" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1349" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1349" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1349" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1349" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1349" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1350" s="22">
+        <v>46091</v>
+      </c>
+      <c r="B1350" s="14">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C1350" s="2" t="s">
+        <v>1880</v>
+      </c>
+      <c r="D1350" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1350" s="2">
+        <v>175</v>
+      </c>
+      <c r="F1350" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G1350" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1350" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1350" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1350" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1351" s="22">
+        <v>46091</v>
+      </c>
+      <c r="B1351" s="14">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C1351" s="2" t="s">
+        <v>1881</v>
+      </c>
+      <c r="D1351" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1351" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1351" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1351" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1351" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1351" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1351" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1352" s="22">
+        <v>46091</v>
+      </c>
+      <c r="B1352" s="14">
+        <v>0.75</v>
+      </c>
+      <c r="C1352" s="2" t="s">
+        <v>1882</v>
+      </c>
+      <c r="D1352" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E1352" s="2">
+        <v>145</v>
+      </c>
+      <c r="F1352" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="G1352" s="2">
+        <v>9</v>
+      </c>
+      <c r="H1352" s="2">
+        <v>9</v>
+      </c>
+      <c r="I1352" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1352" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1353" s="22">
+        <v>46091</v>
+      </c>
+      <c r="B1353" s="14">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C1353" s="2" t="s">
+        <v>1883</v>
+      </c>
+      <c r="D1353" s="2" t="s">
+        <v>1616</v>
+      </c>
+      <c r="E1353" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1353" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1353" s="2">
+        <v>40</v>
+      </c>
+      <c r="H1353" s="2">
+        <v>12</v>
+      </c>
+      <c r="I1353" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1353" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1354" s="22">
+        <v>46091</v>
+      </c>
+      <c r="B1354" s="14">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="C1354" s="2" t="s">
+        <v>1884</v>
+      </c>
+      <c r="D1354" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1354" s="2">
+        <v>175</v>
+      </c>
+      <c r="F1354" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G1354" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1354" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1354" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1354" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1355" s="22">
+        <v>46091</v>
+      </c>
+      <c r="B1355" s="14">
+        <v>0.9375</v>
+      </c>
+      <c r="C1355" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="D1355" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1355" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1355" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1355" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1355" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1355" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1355" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1356" s="22">
+        <v>46092</v>
+      </c>
+      <c r="B1356" s="14">
+        <v>0.3125</v>
+      </c>
+      <c r="C1356" s="2" t="s">
+        <v>1886</v>
+      </c>
+      <c r="D1356" s="2" t="s">
+        <v>1887</v>
+      </c>
+      <c r="E1356" s="2">
+        <v>464</v>
+      </c>
+      <c r="F1356" s="2">
+        <v>7.7</v>
+      </c>
+      <c r="G1356" s="2">
+        <v>13.7</v>
+      </c>
+      <c r="H1356" s="2">
+        <v>42.5</v>
+      </c>
+      <c r="I1356" s="2">
+        <v>2</v>
+      </c>
+      <c r="J1356" s="2">
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1357" s="22">
+        <v>46092</v>
+      </c>
+      <c r="B1357" s="14">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C1357" s="2" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D1357" s="2" t="s">
+        <v>1889</v>
+      </c>
+      <c r="E1357" s="2">
+        <v>320</v>
+      </c>
+      <c r="F1357" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1357" s="2">
+        <v>53.6</v>
+      </c>
+      <c r="H1357" s="2">
+        <v>11.7</v>
+      </c>
+      <c r="I1357" s="2">
+        <v>25.6</v>
+      </c>
+      <c r="J1357" s="2">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1358" s="22">
+        <v>46092</v>
+      </c>
+      <c r="B1358" s="14">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C1358" s="2" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D1358" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1358" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1358" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1358" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1358" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1358" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1358" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1359" s="22">
+        <v>46092</v>
+      </c>
+      <c r="B1359" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="C1359" s="2" t="s">
+        <v>1891</v>
+      </c>
+      <c r="D1359" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1359" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1359" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1359" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1359" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1359" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1359" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1360" s="22">
+        <v>46092</v>
+      </c>
+      <c r="B1360" s="14">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1360" s="2" t="s">
+        <v>1892</v>
+      </c>
+      <c r="D1360" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1360" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1360" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1360" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1360" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1360" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1360" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1361" s="22">
+        <v>46092</v>
+      </c>
+      <c r="B1361" s="14">
+        <v>0.625</v>
+      </c>
+      <c r="C1361" s="2" t="s">
+        <v>1893</v>
+      </c>
+      <c r="D1361" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="E1361" s="2">
+        <v>235</v>
+      </c>
+      <c r="F1361" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="G1361" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1361" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1361" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1361" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1362" s="22">
+        <v>46092</v>
+      </c>
+      <c r="B1362" s="14">
+        <v>0.75</v>
+      </c>
+      <c r="C1362" s="2" t="s">
+        <v>1894</v>
+      </c>
+      <c r="D1362" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="E1362" s="2">
+        <v>150</v>
+      </c>
+      <c r="F1362" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="G1362" s="2">
+        <v>35</v>
+      </c>
+      <c r="H1362" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="I1362" s="2">
+        <v>23.3</v>
+      </c>
+      <c r="J1362" s="2">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1363" s="22">
+        <v>46092</v>
+      </c>
+      <c r="B1363" s="14">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C1363" s="2" t="s">
+        <v>1895</v>
+      </c>
+      <c r="D1363" s="2" t="s">
+        <v>1896</v>
+      </c>
+      <c r="E1363" s="2">
+        <v>270</v>
+      </c>
+      <c r="F1363" s="2">
+        <v>12</v>
+      </c>
+      <c r="G1363" s="2">
+        <v>36</v>
+      </c>
+      <c r="H1363" s="2">
+        <v>8</v>
+      </c>
+      <c r="I1363" s="2">
+        <v>1</v>
+      </c>
+      <c r="J1363" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1364" s="22">
+        <v>46092</v>
+      </c>
+      <c r="B1364" s="14">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C1364" s="2" t="s">
+        <v>1897</v>
+      </c>
+      <c r="D1364" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E1364" s="2">
+        <v>256</v>
+      </c>
+      <c r="F1364" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="G1364" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="H1364" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="I1364" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="J1364" s="2">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1365" s="22">
+        <v>46093</v>
+      </c>
+      <c r="B1365" s="14">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C1365" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="D1365" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E1365" s="2">
+        <v>89</v>
+      </c>
+      <c r="F1365" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G1365" s="2">
+        <v>23</v>
+      </c>
+      <c r="H1365" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="I1365" s="2">
+        <v>12</v>
+      </c>
+      <c r="J1365" s="2">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1366" s="22">
+        <v>46093</v>
+      </c>
+      <c r="B1366" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C1366" s="2" t="s">
+        <v>1899</v>
+      </c>
+      <c r="D1366" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="E1366" s="2">
+        <v>235</v>
+      </c>
+      <c r="F1366" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="G1366" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1366" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1366" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1366" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1367" s="22">
+        <v>46093</v>
+      </c>
+      <c r="B1367" s="14">
+        <v>0.4375</v>
+      </c>
+      <c r="C1367" s="2" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D1367" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E1367" s="2">
+        <v>89</v>
+      </c>
+      <c r="F1367" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G1367" s="2">
+        <v>23</v>
+      </c>
+      <c r="H1367" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="I1367" s="2">
+        <v>12</v>
+      </c>
+      <c r="J1367" s="2">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1368" s="22">
+        <v>46093</v>
+      </c>
+      <c r="B1368" s="14">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C1368" s="2" t="s">
+        <v>1901</v>
+      </c>
+      <c r="D1368" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1368" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1368" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1368" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1368" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1368" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1368" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1369" s="22">
+        <v>46093</v>
+      </c>
+      <c r="B1369" s="14">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C1369" s="2" t="s">
+        <v>1902</v>
+      </c>
+      <c r="D1369" s="2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E1369" s="2">
+        <v>465</v>
+      </c>
+      <c r="F1369" s="2">
+        <v>30</v>
+      </c>
+      <c r="G1369" s="2">
+        <v>55</v>
+      </c>
+      <c r="H1369" s="2">
+        <v>15</v>
+      </c>
+      <c r="I1369" s="2">
+        <v>3</v>
+      </c>
+      <c r="J1369" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1370" s="22">
+        <v>46093</v>
+      </c>
+      <c r="B1370" s="14">
+        <v>0.5625</v>
+      </c>
+      <c r="C1370" s="2" t="s">
+        <v>1903</v>
+      </c>
+      <c r="D1370" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1370" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1370" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1370" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1370" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1370" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1370" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1371" s="22">
+        <v>46093</v>
+      </c>
+      <c r="B1371" s="14">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C1371" s="2" t="s">
+        <v>1904</v>
+      </c>
+      <c r="D1371" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1371" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1371" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1371" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1371" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1371" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1371" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1372" s="22">
+        <v>46093</v>
+      </c>
+      <c r="B1372" s="14">
+        <v>0.8125</v>
+      </c>
+      <c r="C1372" s="2" t="s">
+        <v>1905</v>
+      </c>
+      <c r="D1372" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1372" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1372" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1372" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1372" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1372" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1372" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1373" s="22">
+        <v>46093</v>
+      </c>
+      <c r="B1373" s="14">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C1373" s="2" t="s">
+        <v>1906</v>
+      </c>
+      <c r="D1373" s="2" t="s">
+        <v>1602</v>
+      </c>
+      <c r="E1373" s="2">
+        <v>35</v>
+      </c>
+      <c r="F1373" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="G1373" s="2">
+        <v>9</v>
+      </c>
+      <c r="H1373" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I1373" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="J1373" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1374" s="22">
+        <v>46094</v>
+      </c>
+      <c r="B1374" s="14">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C1374" s="2" t="s">
+        <v>1907</v>
+      </c>
+      <c r="D1374" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E1374" s="2">
+        <v>89</v>
+      </c>
+      <c r="F1374" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G1374" s="2">
+        <v>23</v>
+      </c>
+      <c r="H1374" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="I1374" s="2">
+        <v>12</v>
+      </c>
+      <c r="J1374" s="2">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1375" s="22">
+        <v>46094</v>
+      </c>
+      <c r="B1375" s="14">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C1375" s="2" t="s">
+        <v>1908</v>
+      </c>
+      <c r="D1375" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1375" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1375" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1375" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1375" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1375" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1375" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1376" s="22">
+        <v>46094</v>
+      </c>
+      <c r="B1376" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C1376" s="2" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D1376" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="E1376" s="2">
+        <v>235</v>
+      </c>
+      <c r="F1376" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="G1376" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1376" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1376" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1376" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1377" s="22">
+        <v>46094</v>
+      </c>
+      <c r="B1377" s="14">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C1377" s="2" t="s">
+        <v>1910</v>
+      </c>
+      <c r="D1377" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1377" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1377" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1377" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1377" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1377" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1377" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1378" s="22">
+        <v>46094</v>
+      </c>
+      <c r="B1378" s="14">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1378" s="2" t="s">
+        <v>1911</v>
+      </c>
+      <c r="D1378" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1378" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1378" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1378" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1378" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1378" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1378" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1379" s="22">
+        <v>46094</v>
+      </c>
+      <c r="B1379" s="14">
+        <v>0.5625</v>
+      </c>
+      <c r="C1379" s="2" t="s">
+        <v>1912</v>
+      </c>
+      <c r="D1379" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1379" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1379" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1379" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1379" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1379" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1379" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1380" s="22">
+        <v>46094</v>
+      </c>
+      <c r="B1380" s="14">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C1380" s="2" t="s">
+        <v>1913</v>
+      </c>
+      <c r="D1380" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E1380" s="2">
+        <v>145</v>
+      </c>
+      <c r="F1380" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="G1380" s="2">
+        <v>9</v>
+      </c>
+      <c r="H1380" s="2">
+        <v>9</v>
+      </c>
+      <c r="I1380" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1380" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1381" s="22">
+        <v>46094</v>
+      </c>
+      <c r="B1381" s="14">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C1381" s="2" t="s">
+        <v>1914</v>
+      </c>
+      <c r="D1381" s="2" t="s">
+        <v>1820</v>
+      </c>
+      <c r="E1381" s="2">
+        <v>336</v>
+      </c>
+      <c r="F1381" s="2">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="G1381" s="2">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="H1381" s="2">
+        <v>22.6</v>
+      </c>
+      <c r="I1381" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="J1381" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1382" s="22">
+        <v>46094</v>
+      </c>
+      <c r="B1382" s="14">
+        <v>0.8125</v>
+      </c>
+      <c r="C1382" s="2" t="s">
+        <v>1915</v>
+      </c>
+      <c r="D1382" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1382" s="2">
+        <v>175</v>
+      </c>
+      <c r="F1382" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G1382" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1382" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1382" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1382" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1383" s="22">
+        <v>46095</v>
+      </c>
+      <c r="B1383" s="14">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C1383" s="2" t="s">
+        <v>1916</v>
+      </c>
+      <c r="D1383" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E1383" s="2">
+        <v>89</v>
+      </c>
+      <c r="F1383" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G1383" s="2">
+        <v>23</v>
+      </c>
+      <c r="H1383" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="I1383" s="2">
+        <v>12</v>
+      </c>
+      <c r="J1383" s="2">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1384" s="22">
+        <v>46095</v>
+      </c>
+      <c r="B1384" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="C1384" s="2" t="s">
+        <v>1917</v>
+      </c>
+      <c r="D1384" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="E1384" s="2">
+        <v>235</v>
+      </c>
+      <c r="F1384" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="G1384" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1384" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1384" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1384" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1385" s="22">
+        <v>46095</v>
+      </c>
+      <c r="B1385" s="14">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C1385" s="2" t="s">
+        <v>1918</v>
+      </c>
+      <c r="D1385" s="2" t="s">
+        <v>1896</v>
+      </c>
+      <c r="E1385" s="2">
+        <v>270</v>
+      </c>
+      <c r="F1385" s="2">
+        <v>12</v>
+      </c>
+      <c r="G1385" s="2">
+        <v>36</v>
+      </c>
+      <c r="H1385" s="2">
+        <v>8</v>
+      </c>
+      <c r="I1385" s="2">
+        <v>1</v>
+      </c>
+      <c r="J1385" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1386" s="22">
+        <v>46095</v>
+      </c>
+      <c r="B1386" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C1386" s="2" t="s">
+        <v>1919</v>
+      </c>
+      <c r="D1386" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1386" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1386" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1386" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1386" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1386" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1386" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1387" s="22">
+        <v>46095</v>
+      </c>
+      <c r="B1387" s="14">
+        <v>0.5625</v>
+      </c>
+      <c r="C1387" s="2" t="s">
+        <v>1920</v>
+      </c>
+      <c r="D1387" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1387" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1387" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1387" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1387" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1387" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1387" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1388" s="22">
+        <v>46095</v>
+      </c>
+      <c r="B1388" s="14">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C1388" s="2" t="s">
+        <v>1921</v>
+      </c>
+      <c r="D1388" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1388" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1388" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1388" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1388" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1388" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1388" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1389" s="22">
+        <v>46095</v>
+      </c>
+      <c r="B1389" s="14">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C1389" s="2" t="s">
+        <v>1922</v>
+      </c>
+      <c r="D1389" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1389" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1389" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1389" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1389" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1389" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1389" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1390" s="22">
+        <v>46095</v>
+      </c>
+      <c r="B1390" s="14">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C1390" s="2" t="s">
+        <v>1923</v>
+      </c>
+      <c r="D1390" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E1390" s="2">
+        <v>145</v>
+      </c>
+      <c r="F1390" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="G1390" s="2">
+        <v>9</v>
+      </c>
+      <c r="H1390" s="2">
+        <v>9</v>
+      </c>
+      <c r="I1390" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1390" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1391" s="22">
+        <v>46095</v>
+      </c>
+      <c r="B1391" s="14">
+        <v>0.8125</v>
+      </c>
+      <c r="C1391" s="2" t="s">
+        <v>1924</v>
+      </c>
+      <c r="D1391" s="2" t="s">
+        <v>1925</v>
+      </c>
+      <c r="E1391" s="2">
+        <v>570</v>
+      </c>
+      <c r="F1391" s="2">
+        <v>42</v>
+      </c>
+      <c r="G1391" s="2">
+        <v>55</v>
+      </c>
+      <c r="H1391" s="2">
+        <v>20</v>
+      </c>
+      <c r="I1391" s="2">
+        <v>3</v>
+      </c>
+      <c r="J1391" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1392" s="22">
+        <v>46096</v>
+      </c>
+      <c r="B1392" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="C1392" s="2" t="s">
+        <v>1926</v>
+      </c>
+      <c r="D1392" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1392" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1392" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1392" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1392" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1392" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1392" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1393" s="22">
+        <v>46096</v>
+      </c>
+      <c r="B1393" s="14">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C1393" s="2" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D1393" s="2" t="s">
+        <v>1928</v>
+      </c>
+      <c r="E1393" s="2">
+        <v>140</v>
+      </c>
+      <c r="F1393" s="2">
+        <v>7</v>
+      </c>
+      <c r="G1393" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1393" s="2">
+        <v>4</v>
+      </c>
+      <c r="I1393" s="2">
+        <v>1</v>
+      </c>
+      <c r="J1393" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1394" s="22">
+        <v>46096</v>
+      </c>
+      <c r="B1394" s="14">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C1394" s="2" t="s">
+        <v>1929</v>
+      </c>
+      <c r="D1394" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E1394" s="2">
+        <v>155</v>
+      </c>
+      <c r="F1394" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1394" s="2">
+        <v>23</v>
+      </c>
+      <c r="H1394" s="2">
+        <v>6</v>
+      </c>
+      <c r="I1394" s="2">
+        <v>12</v>
+      </c>
+      <c r="J1394" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1395" s="22">
+        <v>46096</v>
+      </c>
+      <c r="B1395" s="14">
+        <v>0.5625</v>
+      </c>
+      <c r="C1395" s="2" t="s">
+        <v>1930</v>
+      </c>
+      <c r="D1395" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1395" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1395" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1395" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1395" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1395" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1395" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1396" s="22">
+        <v>46096</v>
+      </c>
+      <c r="B1396" s="14">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C1396" s="2" t="s">
+        <v>1931</v>
+      </c>
+      <c r="D1396" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1396" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1396" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1396" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1396" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1396" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1396" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1397" s="22">
+        <v>46096</v>
+      </c>
+      <c r="B1397" s="14">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C1397" s="2" t="s">
+        <v>1932</v>
+      </c>
+      <c r="D1397" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1397" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1397" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1397" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1397" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1397" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1397" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1398" s="22">
+        <v>46096</v>
+      </c>
+      <c r="B1398" s="14">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C1398" s="2" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D1398" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1398" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1398" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1398" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1398" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1398" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1398" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1399" s="22">
+        <v>46096</v>
+      </c>
+      <c r="B1399" s="14">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C1399" s="2" t="s">
+        <v>1934</v>
+      </c>
+      <c r="D1399" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E1399" s="2">
+        <v>145</v>
+      </c>
+      <c r="F1399" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="G1399" s="2">
+        <v>9</v>
+      </c>
+      <c r="H1399" s="2">
+        <v>9</v>
+      </c>
+      <c r="I1399" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1399" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1400" s="22">
+        <v>46096</v>
+      </c>
+      <c r="B1400" s="14">
+        <v>0.8125</v>
+      </c>
+      <c r="C1400" s="2" t="s">
+        <v>1935</v>
+      </c>
+      <c r="D1400" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1400" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1400" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1400" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1400" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1400" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1400" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1401" s="22">
+        <v>46096</v>
+      </c>
+      <c r="B1401" s="14">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C1401" s="2" t="s">
+        <v>1936</v>
+      </c>
+      <c r="D1401" s="2" t="s">
+        <v>1937</v>
+      </c>
+      <c r="E1401" s="2">
+        <v>265</v>
+      </c>
+      <c r="F1401" s="2">
+        <v>26</v>
+      </c>
+      <c r="G1401" s="2">
+        <v>12</v>
+      </c>
+      <c r="H1401" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1401" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1401" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1402" s="22">
+        <v>46096</v>
+      </c>
+      <c r="B1402" s="14">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C1402" s="2" t="s">
+        <v>1938</v>
+      </c>
+      <c r="D1402" s="2" t="s">
+        <v>1721</v>
+      </c>
+      <c r="E1402" s="2">
+        <v>63</v>
+      </c>
+      <c r="F1402" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G1402" s="2">
+        <v>16.8</v>
+      </c>
+      <c r="H1402" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="I1402" s="2">
+        <v>13</v>
+      </c>
+      <c r="J1402" s="2">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1403" s="22">
+        <v>46097</v>
+      </c>
+      <c r="B1403" s="14">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C1403" s="2" t="s">
+        <v>1939</v>
+      </c>
+      <c r="D1403" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1403" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1403" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1403" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1403" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1403" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1403" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1404" s="22">
+        <v>46097</v>
+      </c>
+      <c r="B1404" s="14">
+        <v>0.3125</v>
+      </c>
+      <c r="C1404" s="2" t="s">
+        <v>1940</v>
+      </c>
+      <c r="D1404" s="2" t="s">
+        <v>1937</v>
+      </c>
+      <c r="E1404" s="2">
+        <v>265</v>
+      </c>
+      <c r="F1404" s="2">
+        <v>26</v>
+      </c>
+      <c r="G1404" s="2">
+        <v>12</v>
+      </c>
+      <c r="H1404" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1404" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1404" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1405" s="22">
+        <v>46097</v>
+      </c>
+      <c r="B1405" s="14">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C1405" s="2" t="s">
+        <v>1941</v>
+      </c>
+      <c r="D1405" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1405" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1405" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1405" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1405" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1405" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1405" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1406" s="22">
+        <v>46097</v>
+      </c>
+      <c r="B1406" s="14">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C1406" s="2" t="s">
+        <v>1942</v>
+      </c>
+      <c r="D1406" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E1406" s="2">
+        <v>89</v>
+      </c>
+      <c r="F1406" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G1406" s="2">
+        <v>23</v>
+      </c>
+      <c r="H1406" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="I1406" s="2">
+        <v>12</v>
+      </c>
+      <c r="J1406" s="2">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1407" s="22">
+        <v>46097</v>
+      </c>
+      <c r="B1407" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="C1407" s="2" t="s">
+        <v>1943</v>
+      </c>
+      <c r="D1407" s="2" t="s">
+        <v>1721</v>
+      </c>
+      <c r="E1407" s="2">
+        <v>63</v>
+      </c>
+      <c r="F1407" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G1407" s="2">
+        <v>16.8</v>
+      </c>
+      <c r="H1407" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="I1407" s="2">
+        <v>13</v>
+      </c>
+      <c r="J1407" s="2">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1408" s="22">
+        <v>46097</v>
+      </c>
+      <c r="B1408" s="14">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C1408" s="2" t="s">
+        <v>1944</v>
+      </c>
+      <c r="D1408" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1408" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1408" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1408" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1408" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1408" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1408" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1409" s="22">
+        <v>46097</v>
+      </c>
+      <c r="B1409" s="14">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1409" s="2" t="s">
+        <v>1945</v>
+      </c>
+      <c r="D1409" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1409" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1409" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1409" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1409" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1409" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1409" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1410" s="22">
+        <v>46097</v>
+      </c>
+      <c r="B1410" s="14">
+        <v>0.5625</v>
+      </c>
+      <c r="C1410" s="2" t="s">
+        <v>1946</v>
+      </c>
+      <c r="D1410" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1410" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1410" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1410" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1410" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1410" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1410" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1411" s="22">
+        <v>46097</v>
+      </c>
+      <c r="B1411" s="14">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C1411" s="2" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D1411" s="2" t="s">
+        <v>1948</v>
+      </c>
+      <c r="E1411" s="2">
+        <v>270</v>
+      </c>
+      <c r="F1411" s="2">
+        <v>38</v>
+      </c>
+      <c r="G1411" s="2">
+        <v>13</v>
+      </c>
+      <c r="H1411" s="2">
+        <v>7</v>
+      </c>
+      <c r="I1411" s="2">
+        <v>1</v>
+      </c>
+      <c r="J1411" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1412" s="22">
+        <v>46097</v>
+      </c>
+      <c r="B1412" s="14">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C1412" s="2" t="s">
+        <v>1949</v>
+      </c>
+      <c r="D1412" s="2" t="s">
+        <v>1950</v>
+      </c>
+      <c r="E1412" s="2">
+        <v>219</v>
+      </c>
+      <c r="F1412" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1412" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1412" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1412" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1412" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1413" s="22">
+        <v>46098</v>
+      </c>
+      <c r="B1413" s="14">
+        <v>0.3125</v>
+      </c>
+      <c r="C1413" s="2" t="s">
+        <v>1951</v>
+      </c>
+      <c r="D1413" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1413" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1413" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1413" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1413" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1413" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1413" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1414" s="22">
+        <v>46098</v>
+      </c>
+      <c r="B1414" s="14">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C1414" s="2" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D1414" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="E1414" s="2">
+        <v>270</v>
+      </c>
+      <c r="F1414" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1414" s="2">
+        <v>35</v>
+      </c>
+      <c r="H1414" s="2">
+        <v>12</v>
+      </c>
+      <c r="I1414" s="2">
+        <v>1</v>
+      </c>
+      <c r="J1414" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1415" s="22">
+        <v>46098</v>
+      </c>
+      <c r="B1415" s="14">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1415" s="2" t="s">
+        <v>1953</v>
+      </c>
+      <c r="D1415" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1415" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1415" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1415" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1415" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1415" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1415" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1416" s="22">
+        <v>46098</v>
+      </c>
+      <c r="B1416" s="14">
+        <v>0.5625</v>
+      </c>
+      <c r="C1416" s="2" t="s">
+        <v>1954</v>
+      </c>
+      <c r="D1416" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="E1416" s="2">
+        <v>235</v>
+      </c>
+      <c r="F1416" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="G1416" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1416" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1416" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1416" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1417" s="22">
+        <v>46098</v>
+      </c>
+      <c r="B1417" s="14">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C1417" s="2" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D1417" s="2" t="s">
+        <v>1956</v>
+      </c>
+      <c r="E1417" s="2">
+        <v>334</v>
+      </c>
+      <c r="F1417" s="2">
+        <v>15</v>
+      </c>
+      <c r="G1417" s="2">
+        <v>23</v>
+      </c>
+      <c r="H1417" s="2">
+        <v>12</v>
+      </c>
+      <c r="I1417" s="2">
+        <v>4</v>
+      </c>
+      <c r="J1417" s="2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1418" s="22">
+        <v>46098</v>
+      </c>
+      <c r="B1418" s="14">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C1418" s="2" t="s">
+        <v>1957</v>
+      </c>
+      <c r="D1418" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E1418" s="2">
+        <v>145</v>
+      </c>
+      <c r="F1418" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="G1418" s="2">
+        <v>9</v>
+      </c>
+      <c r="H1418" s="2">
+        <v>9</v>
+      </c>
+      <c r="I1418" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1418" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1419" s="22">
+        <v>46098</v>
+      </c>
+      <c r="B1419" s="14">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C1419" s="2" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D1419" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1419" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1419" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1419" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1419" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1419" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1419" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1420" s="22">
+        <v>46098</v>
+      </c>
+      <c r="B1420" s="14">
+        <v>0.875</v>
+      </c>
+      <c r="C1420" s="2" t="s">
+        <v>1959</v>
+      </c>
+      <c r="D1420" s="2" t="s">
+        <v>1623</v>
+      </c>
+      <c r="E1420" s="2">
+        <v>45</v>
+      </c>
+      <c r="F1420" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="G1420" s="2">
+        <v>12</v>
+      </c>
+      <c r="H1420" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="I1420" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1420" s="2">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1421" s="22">
+        <v>46098</v>
+      </c>
+      <c r="B1421" s="14">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C1421" s="2" t="s">
+        <v>1960</v>
+      </c>
+      <c r="D1421" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E1421" s="2">
+        <v>155</v>
+      </c>
+      <c r="F1421" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1421" s="2">
+        <v>23</v>
+      </c>
+      <c r="H1421" s="2">
+        <v>6</v>
+      </c>
+      <c r="I1421" s="2">
+        <v>12</v>
+      </c>
+      <c r="J1421" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1422" s="22">
+        <v>46099</v>
+      </c>
+      <c r="B1422" s="14">
+        <v>0.3125</v>
+      </c>
+      <c r="C1422" s="2" t="s">
+        <v>1961</v>
+      </c>
+      <c r="D1422" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1422" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1422" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1422" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1422" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1422" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1422" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1423" s="22">
+        <v>46099</v>
+      </c>
+      <c r="B1423" s="14">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1423" s="2" t="s">
+        <v>1962</v>
+      </c>
+      <c r="D1423" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1423" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1423" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1423" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1423" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1423" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1423" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1424" s="22">
+        <v>46099</v>
+      </c>
+      <c r="B1424" s="14">
+        <v>0.5625</v>
+      </c>
+      <c r="C1424" s="2" t="s">
+        <v>1963</v>
+      </c>
+      <c r="D1424" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="E1424" s="2">
+        <v>235</v>
+      </c>
+      <c r="F1424" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="G1424" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1424" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1424" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1424" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1425" s="22">
+        <v>46099</v>
+      </c>
+      <c r="B1425" s="14">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C1425" s="2" t="s">
+        <v>1964</v>
+      </c>
+      <c r="D1425" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1425" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1425" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1425" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1425" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1425" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1425" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1426" s="22">
+        <v>46099</v>
+      </c>
+      <c r="B1426" s="14">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C1426" s="2" t="s">
+        <v>1965</v>
+      </c>
+      <c r="D1426" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1426" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1426" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1426" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1426" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1426" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1426" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1427" s="22">
+        <v>46099</v>
+      </c>
+      <c r="B1427" s="14">
+        <v>0.625</v>
+      </c>
+      <c r="C1427" s="2" t="s">
+        <v>1966</v>
+      </c>
+      <c r="D1427" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1427" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1427" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1427" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1427" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1427" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1427" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1428" s="22">
+        <v>46099</v>
+      </c>
+      <c r="B1428" s="14">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C1428" s="2" t="s">
+        <v>1967</v>
+      </c>
+      <c r="D1428" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1428" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1428" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1428" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1428" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1428" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1428" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1429" s="22">
+        <v>46099</v>
+      </c>
+      <c r="B1429" s="14">
+        <v>0.8125</v>
+      </c>
+      <c r="C1429" s="2" t="s">
+        <v>1968</v>
+      </c>
+      <c r="D1429" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1429" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1429" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1429" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1429" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1429" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1429" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1430" s="22">
+        <v>46099</v>
+      </c>
+      <c r="B1430" s="14">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C1430" s="2" t="s">
+        <v>1969</v>
+      </c>
+      <c r="D1430" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1430" s="2">
+        <v>175</v>
+      </c>
+      <c r="F1430" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G1430" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1430" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1430" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1430" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1431" s="22">
+        <v>46099</v>
+      </c>
+      <c r="B1431" s="14">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C1431" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="D1431" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E1431" s="2">
+        <v>155</v>
+      </c>
+      <c r="F1431" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1431" s="2">
+        <v>23</v>
+      </c>
+      <c r="H1431" s="2">
+        <v>6</v>
+      </c>
+      <c r="I1431" s="2">
+        <v>12</v>
+      </c>
+      <c r="J1431" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1432" s="22">
+        <v>46099</v>
+      </c>
+      <c r="B1432" s="14">
+        <v>0.875</v>
+      </c>
+      <c r="C1432" s="2" t="s">
+        <v>1971</v>
+      </c>
+      <c r="D1432" s="2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E1432" s="2">
+        <v>263</v>
+      </c>
+      <c r="F1432" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="G1432" s="2">
+        <v>30.5</v>
+      </c>
+      <c r="H1432" s="2">
+        <v>14.7</v>
+      </c>
+      <c r="I1432" s="2">
+        <v>3</v>
+      </c>
+      <c r="J1432" s="2">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1433" s="22">
+        <v>46099</v>
+      </c>
+      <c r="B1433" s="14">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C1433" s="2" t="s">
+        <v>1972</v>
+      </c>
+      <c r="D1433" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E1433" s="2">
+        <v>155</v>
+      </c>
+      <c r="F1433" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1433" s="2">
+        <v>23</v>
+      </c>
+      <c r="H1433" s="2">
+        <v>6</v>
+      </c>
+      <c r="I1433" s="2">
+        <v>12</v>
+      </c>
+      <c r="J1433" s="2">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -48740,7 +52361,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F24E0C0-BC77-4AA4-801C-82B038A8B8E4}">
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -49701,16 +53322,16 @@
       <c r="A49" s="22">
         <v>46081</v>
       </c>
-      <c r="B49" s="28">
+      <c r="B49" s="2">
         <v>97.1</v>
       </c>
-      <c r="C49" s="28">
+      <c r="C49" s="2">
         <v>37.1</v>
       </c>
       <c r="D49" s="2">
         <v>28.3</v>
       </c>
-      <c r="E49" s="28">
+      <c r="E49" s="2">
         <v>50.4</v>
       </c>
       <c r="F49" s="2"/>
@@ -49719,16 +53340,16 @@
       <c r="A50" s="22">
         <v>46086</v>
       </c>
-      <c r="B50" s="28">
+      <c r="B50" s="2">
         <v>97.1</v>
       </c>
-      <c r="C50" s="28">
+      <c r="C50" s="2">
         <v>37.4</v>
       </c>
       <c r="D50" s="2">
         <v>27.8</v>
       </c>
-      <c r="E50" s="28">
+      <c r="E50" s="2">
         <v>50.8</v>
       </c>
       <c r="F50" s="2"/>
@@ -49737,19 +53358,73 @@
       <c r="A51" s="22">
         <v>46088</v>
       </c>
-      <c r="B51" s="28">
+      <c r="B51" s="2">
         <v>97</v>
       </c>
-      <c r="C51" s="28">
+      <c r="C51" s="2">
         <v>37.9</v>
       </c>
       <c r="D51" s="2">
         <v>27</v>
       </c>
-      <c r="E51" s="28">
+      <c r="E51" s="2">
         <v>51.4</v>
       </c>
       <c r="F51" s="2"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="22">
+        <v>46094</v>
+      </c>
+      <c r="B52" s="28">
+        <v>97.9</v>
+      </c>
+      <c r="C52" s="28">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="D52" s="28">
+        <v>27.9</v>
+      </c>
+      <c r="E52" s="28">
+        <v>51.3</v>
+      </c>
+      <c r="F52" s="2"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="22">
+        <v>46095</v>
+      </c>
+      <c r="B53" s="28">
+        <v>97.6</v>
+      </c>
+      <c r="C53" s="28">
+        <v>37.1</v>
+      </c>
+      <c r="D53" s="28">
+        <v>28.6</v>
+      </c>
+      <c r="E53" s="28">
+        <v>50.3</v>
+      </c>
+      <c r="F53" s="2"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="22">
+        <v>46100</v>
+      </c>
+      <c r="B54" s="28">
+        <v>97.6</v>
+      </c>
+      <c r="C54" s="28">
+        <v>37.4</v>
+      </c>
+      <c r="D54" s="28">
+        <v>28.2</v>
+      </c>
+      <c r="E54" s="28">
+        <v>50.9</v>
+      </c>
+      <c r="F54" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -49760,7 +53435,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D2F321-D2D4-48D2-B6F9-E306604CF730}">
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -51551,10 +55226,10 @@
         <v>416</v>
       </c>
       <c r="F76" s="2"/>
-      <c r="G76" s="2" t="s">
+      <c r="G76" s="2"/>
+      <c r="H76" s="2" t="s">
         <v>1709</v>
       </c>
-      <c r="H76" s="2"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="22">
@@ -51621,10 +55296,10 @@
         <v>517</v>
       </c>
       <c r="F79" s="2"/>
-      <c r="G79" s="2" t="s">
+      <c r="G79" s="2"/>
+      <c r="H79" s="2" t="s">
         <v>1712</v>
       </c>
-      <c r="H79" s="2"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="22">
@@ -51760,6 +55435,209 @@
       <c r="G85" s="2"/>
       <c r="H85" s="2" t="s">
         <v>1718</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" s="22">
+        <v>46091</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D86" s="2">
+        <v>76</v>
+      </c>
+      <c r="E86" s="2">
+        <v>592</v>
+      </c>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="22">
+        <v>46093</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D87" s="2">
+        <v>63</v>
+      </c>
+      <c r="E87" s="2">
+        <v>533</v>
+      </c>
+      <c r="F87" s="2">
+        <v>4710</v>
+      </c>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A88" s="22">
+        <v>46093</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D88" s="2">
+        <v>71</v>
+      </c>
+      <c r="E88" s="2">
+        <v>452</v>
+      </c>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A89" s="22">
+        <v>46094</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D89" s="2">
+        <v>70</v>
+      </c>
+      <c r="E89" s="2">
+        <v>495</v>
+      </c>
+      <c r="F89" s="2">
+        <v>5140</v>
+      </c>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A90" s="22">
+        <v>46094</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D90" s="2">
+        <v>54</v>
+      </c>
+      <c r="E90" s="2">
+        <v>457</v>
+      </c>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A91" s="22">
+        <v>46095</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D91" s="2">
+        <v>91</v>
+      </c>
+      <c r="E91" s="2">
+        <v>674</v>
+      </c>
+      <c r="F91" s="2">
+        <v>6790</v>
+      </c>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92" s="22">
+        <v>46095</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D92" s="2">
+        <v>49</v>
+      </c>
+      <c r="E92" s="2">
+        <v>425</v>
+      </c>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93" s="22">
+        <v>46096</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D93" s="2">
+        <v>90</v>
+      </c>
+      <c r="E93" s="2">
+        <v>635</v>
+      </c>
+      <c r="F93" s="2">
+        <v>6780</v>
+      </c>
+      <c r="G93" s="2"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A94" s="22">
+        <v>46099</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D94" s="2">
+        <v>83</v>
+      </c>
+      <c r="E94" s="2">
+        <v>628</v>
+      </c>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2" t="s">
+        <v>1715</v>
       </c>
     </row>
   </sheetData>

--- a/Food Log Main.xlsx
+++ b/Food Log Main.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91998\VS\Food Log Project Jan 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7997BE54-2514-436A-9BD8-DFD7EB40200B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C874E65-F7A5-4B1A-96D4-73FD92362948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main Format 12 oct" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,12 @@
     <sheet name="Workouts 19oct" sheetId="6" r:id="rId3"/>
     <sheet name="Std Meals with Mac" sheetId="4" r:id="rId4"/>
     <sheet name="Body Measurements" sheetId="5" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="8" r:id="rId6"/>
-    <sheet name="Daily 23 to 11oct" sheetId="7" r:id="rId7"/>
+    <sheet name="Daily 23 to 11oct" sheetId="7" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Main Format 12 oct'!$A$1:$J$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Sheet1!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Sheet1!$A$1:$K$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Weight Tracker 23sep'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Workouts 19oct'!$A$1:$H$1</definedName>
   </definedNames>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3746" uniqueCount="1980">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3805" uniqueCount="2117">
   <si>
     <t>date</t>
   </si>
@@ -6000,6 +6000,417 @@
   </si>
   <si>
     <t>WK20260314-wm</t>
+  </si>
+  <si>
+    <t>FD20260319-0700-4i8d</t>
+  </si>
+  <si>
+    <t>FD20260319-0730-5j9e</t>
+  </si>
+  <si>
+    <t>FD20260319-0900-6k0f</t>
+  </si>
+  <si>
+    <t>FD20260319-1100-7l1g</t>
+  </si>
+  <si>
+    <t>Bagel (200g) + fried egg</t>
+  </si>
+  <si>
+    <t>FD20260319-1130-8m2h</t>
+  </si>
+  <si>
+    <t>FD20260319-1200-9n3i</t>
+  </si>
+  <si>
+    <t>Guava (200g)</t>
+  </si>
+  <si>
+    <t>FD20260319-1230-0o4j</t>
+  </si>
+  <si>
+    <t>FD20260319-1330-1p5k</t>
+  </si>
+  <si>
+    <t>FD20260319-1600-2q6l</t>
+  </si>
+  <si>
+    <t>FD20260319-1630-3r7m</t>
+  </si>
+  <si>
+    <t>FD20260319-2000-4s8n</t>
+  </si>
+  <si>
+    <t>100g chicken curry + 2 rotis</t>
+  </si>
+  <si>
+    <t>FD20260319-2030-5t9o</t>
+  </si>
+  <si>
+    <t>Chocolate pudding (½ portion)</t>
+  </si>
+  <si>
+    <t>FD20260320-0830-6u0p</t>
+  </si>
+  <si>
+    <t>FD20260320-1330-7v1q</t>
+  </si>
+  <si>
+    <t>2 pints of beer</t>
+  </si>
+  <si>
+    <t>FD20260320-1400-8w2r</t>
+  </si>
+  <si>
+    <t>Pulled chicken (150g)</t>
+  </si>
+  <si>
+    <t>FD20260320-1430-9x3s</t>
+  </si>
+  <si>
+    <t>White wine sangria</t>
+  </si>
+  <si>
+    <t>FD20260320-2030-0y4t</t>
+  </si>
+  <si>
+    <t>4 pints of beer</t>
+  </si>
+  <si>
+    <t>FD20260320-2100-1z5u</t>
+  </si>
+  <si>
+    <t>1 pint of beer</t>
+  </si>
+  <si>
+    <t>FD20260320-2130-2a6v</t>
+  </si>
+  <si>
+    <t>Chocolate ice cream (1 scoop)</t>
+  </si>
+  <si>
+    <t>FD20260320-2300-3b7w</t>
+  </si>
+  <si>
+    <t>FD20260320-2330-4c8x</t>
+  </si>
+  <si>
+    <t>FD20260320-2330-5d9y</t>
+  </si>
+  <si>
+    <t>FD20260321-0900-6e0z</t>
+  </si>
+  <si>
+    <t>FD20260321-1200-7f1a</t>
+  </si>
+  <si>
+    <t>FD20260321-1300-8g2b</t>
+  </si>
+  <si>
+    <t>FD20260321-1500-9h3c</t>
+  </si>
+  <si>
+    <t>FD20260321-1600-0i4d</t>
+  </si>
+  <si>
+    <t>FD20260321-1900-1j5e</t>
+  </si>
+  <si>
+    <t>FD20260321-1930-2k6f</t>
+  </si>
+  <si>
+    <t>FD20260322-0900-3l7g</t>
+  </si>
+  <si>
+    <t>FD20260322-1200-4m8h</t>
+  </si>
+  <si>
+    <t>FD20260322-1300-5n9i</t>
+  </si>
+  <si>
+    <t>FD20260322-1600-6o0j</t>
+  </si>
+  <si>
+    <t>FD20260322-1630-7p1k</t>
+  </si>
+  <si>
+    <t>FD20260322-1700-8q2l</t>
+  </si>
+  <si>
+    <t>FD20260322-1830-9r3m</t>
+  </si>
+  <si>
+    <t>FD20260322-1930-0s4n</t>
+  </si>
+  <si>
+    <t>FD20260323-0900-1t5o</t>
+  </si>
+  <si>
+    <t>FD20260323-0930-2u6p</t>
+  </si>
+  <si>
+    <t>FD20260323-1200-3v7q</t>
+  </si>
+  <si>
+    <t>FD20260323-1300-4w8r</t>
+  </si>
+  <si>
+    <t>FD20260323-1530-5x9s</t>
+  </si>
+  <si>
+    <t>FD20260323-1600-6y0t</t>
+  </si>
+  <si>
+    <t>FD20260323-1730-7z1u</t>
+  </si>
+  <si>
+    <t>FD20260323-1830-8a2v</t>
+  </si>
+  <si>
+    <t>FD20260323-1900-9b3w</t>
+  </si>
+  <si>
+    <t>FD20260323-1930-0c4x</t>
+  </si>
+  <si>
+    <t>Pita bread (125g) + chicken curry (100g)</t>
+  </si>
+  <si>
+    <t>FD20260324-0900-1d5y</t>
+  </si>
+  <si>
+    <t>FD20260324-1200-2e6z</t>
+  </si>
+  <si>
+    <t>FD20260324-1600-3f7a</t>
+  </si>
+  <si>
+    <t>FD20260324-1730-4g8b</t>
+  </si>
+  <si>
+    <t>FD20260324-1930-5h9c</t>
+  </si>
+  <si>
+    <t>50g pita bread + 100g chicken curry + 2 rotis</t>
+  </si>
+  <si>
+    <t>FD20260324-2100-6i0d</t>
+  </si>
+  <si>
+    <t>FD20260325-0900-7j1e</t>
+  </si>
+  <si>
+    <t>FD20260325-1200-8k2f</t>
+  </si>
+  <si>
+    <t>FD20260325-1230-9l3g</t>
+  </si>
+  <si>
+    <t>Pita bread (100g) + chicken curry (100g)</t>
+  </si>
+  <si>
+    <t>FD20260325-1330-0m4h</t>
+  </si>
+  <si>
+    <t>FD20260325-1400-1n5i</t>
+  </si>
+  <si>
+    <t>FD20260325-1530-2o6j</t>
+  </si>
+  <si>
+    <t>FD20260325-1600-3p7k</t>
+  </si>
+  <si>
+    <t>FD20260325-1930-4q8l</t>
+  </si>
+  <si>
+    <t>FD20260325-2030-5r9m</t>
+  </si>
+  <si>
+    <t>FD20260326-0900-6s0n</t>
+  </si>
+  <si>
+    <t>FD20260326-1030-7t1o</t>
+  </si>
+  <si>
+    <t>FD20260326-1200-8u2p</t>
+  </si>
+  <si>
+    <t>FD20260326-1300-9v3q</t>
+  </si>
+  <si>
+    <t>FD20260326-1530-2y6t</t>
+  </si>
+  <si>
+    <t>FD20260326-1600-0w4r</t>
+  </si>
+  <si>
+    <t>Cream bun (75g)</t>
+  </si>
+  <si>
+    <t>FD20260326-1600-3z7u</t>
+  </si>
+  <si>
+    <t>FD20260326-1630-1x5s</t>
+  </si>
+  <si>
+    <t>FD20260326-1930-4a8v</t>
+  </si>
+  <si>
+    <t>FD20260327-0900-5b9w</t>
+  </si>
+  <si>
+    <t>FD20260327-1000-6c0x</t>
+  </si>
+  <si>
+    <t>1 roti + 50g chicken curry</t>
+  </si>
+  <si>
+    <t>FD20260327-1200-7d1y</t>
+  </si>
+  <si>
+    <t>FD20260327-1230-8e2z</t>
+  </si>
+  <si>
+    <t>FD20260327-1430-9f3a</t>
+  </si>
+  <si>
+    <t>FD20260327-1700-0g4b</t>
+  </si>
+  <si>
+    <t>FD20260327-1930-1h5c</t>
+  </si>
+  <si>
+    <t>FD20260327-2000-2i6d</t>
+  </si>
+  <si>
+    <t>FD20260327-2030-3j7e</t>
+  </si>
+  <si>
+    <t>FD20260328-0200-4k8f</t>
+  </si>
+  <si>
+    <t>FD20260328-0230-5l9g</t>
+  </si>
+  <si>
+    <t>FD20260328-0900-6m0h</t>
+  </si>
+  <si>
+    <t>FD20260328-1030-7n1i</t>
+  </si>
+  <si>
+    <t>FD20260328-1400-8o2j</t>
+  </si>
+  <si>
+    <t>Chocolate Mysore Pak (120g)</t>
+  </si>
+  <si>
+    <t>FD20260328-1600-9p3k</t>
+  </si>
+  <si>
+    <t>FD20260328-1630-0q4l</t>
+  </si>
+  <si>
+    <t>FD20260328-1930-1r5m</t>
+  </si>
+  <si>
+    <t>FD20260328-2000-2s6n</t>
+  </si>
+  <si>
+    <t>100ml milk + 10g chocolate powder</t>
+  </si>
+  <si>
+    <t>FD20260328-2030-3t7o</t>
+  </si>
+  <si>
+    <t>FD20260328-2100-4u8p</t>
+  </si>
+  <si>
+    <t>FD20260329-0900-5v9q</t>
+  </si>
+  <si>
+    <t>FD20260329-0930-6w0r</t>
+  </si>
+  <si>
+    <t>Mysore Pak (50g)</t>
+  </si>
+  <si>
+    <t>FD20260329-1200-7x1s</t>
+  </si>
+  <si>
+    <t>FD20260329-1330-8y2t</t>
+  </si>
+  <si>
+    <t>FD20260329-1430-9z3u</t>
+  </si>
+  <si>
+    <t>FD20260329-1500-0a4v</t>
+  </si>
+  <si>
+    <t>Chocolate Mysore Pak (75g)</t>
+  </si>
+  <si>
+    <t>FD20260329-2000-1b5w</t>
+  </si>
+  <si>
+    <t>½ slice carrot cake</t>
+  </si>
+  <si>
+    <t>FD20260329-2100-2c6x</t>
+  </si>
+  <si>
+    <t>FD20260329-2130-3d7y</t>
+  </si>
+  <si>
+    <t>FD20260330-0900-4e8z</t>
+  </si>
+  <si>
+    <t>FD20260330-1200-5f9a</t>
+  </si>
+  <si>
+    <t>FD20260330-1430-6g0b</t>
+  </si>
+  <si>
+    <t>FD20260330-1600-7h1c</t>
+  </si>
+  <si>
+    <t>FD20260330-1630-8i2d</t>
+  </si>
+  <si>
+    <t>FD20260330-1800-9j3e</t>
+  </si>
+  <si>
+    <t>FD20260330-1900-0k4f</t>
+  </si>
+  <si>
+    <t>American corn cheese toast</t>
+  </si>
+  <si>
+    <t>FD20260330-1930-1l5g</t>
+  </si>
+  <si>
+    <t>Bread masala</t>
+  </si>
+  <si>
+    <t>WK20260320-wm</t>
+  </si>
+  <si>
+    <t>WK20260323-wm</t>
+  </si>
+  <si>
+    <t>WK20260324-w</t>
+  </si>
+  <si>
+    <t>WK20260325-wm</t>
+  </si>
+  <si>
+    <t>WK20260326-wm</t>
+  </si>
+  <si>
+    <t>WK20260327-w</t>
+  </si>
+  <si>
+    <t>WK20260327-wm</t>
   </si>
 </sst>
 </file>
@@ -6481,7 +6892,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J1433"/>
+  <dimension ref="A1:J1541"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -52335,6 +52746,3462 @@
       </c>
       <c r="J1433" s="2">
         <v>2</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1434" s="22">
+        <v>46100</v>
+      </c>
+      <c r="B1434" s="14">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C1434" s="2" t="s">
+        <v>1980</v>
+      </c>
+      <c r="D1434" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="E1434" s="2">
+        <v>135</v>
+      </c>
+      <c r="F1434" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1434" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1434" s="2">
+        <v>6</v>
+      </c>
+      <c r="I1434" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1434" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1435" s="22">
+        <v>46100</v>
+      </c>
+      <c r="B1435" s="14">
+        <v>0.3125</v>
+      </c>
+      <c r="C1435" s="2" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D1435" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1435" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1435" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1435" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1435" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1435" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1435" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1436" s="22">
+        <v>46100</v>
+      </c>
+      <c r="B1436" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="C1436" s="2" t="s">
+        <v>1982</v>
+      </c>
+      <c r="D1436" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="E1436" s="2">
+        <v>135</v>
+      </c>
+      <c r="F1436" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1436" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1436" s="2">
+        <v>6</v>
+      </c>
+      <c r="I1436" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1436" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1437" s="22">
+        <v>46100</v>
+      </c>
+      <c r="B1437" s="14">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C1437" s="2" t="s">
+        <v>1983</v>
+      </c>
+      <c r="D1437" s="2" t="s">
+        <v>1984</v>
+      </c>
+      <c r="E1437" s="2">
+        <v>590</v>
+      </c>
+      <c r="F1437" s="2">
+        <v>24</v>
+      </c>
+      <c r="G1437" s="2">
+        <v>82</v>
+      </c>
+      <c r="H1437" s="2">
+        <v>16</v>
+      </c>
+      <c r="I1437" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1437" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1438" s="22">
+        <v>46100</v>
+      </c>
+      <c r="B1438" s="14">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C1438" s="2" t="s">
+        <v>1985</v>
+      </c>
+      <c r="D1438" s="2" t="s">
+        <v>1663</v>
+      </c>
+      <c r="E1438" s="2">
+        <v>90</v>
+      </c>
+      <c r="F1438" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="G1438" s="2">
+        <v>10</v>
+      </c>
+      <c r="H1438" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="I1438" s="2">
+        <v>9</v>
+      </c>
+      <c r="J1438" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1439" s="22">
+        <v>46100</v>
+      </c>
+      <c r="B1439" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="C1439" s="2" t="s">
+        <v>1986</v>
+      </c>
+      <c r="D1439" s="2" t="s">
+        <v>1987</v>
+      </c>
+      <c r="E1439" s="2">
+        <v>120</v>
+      </c>
+      <c r="F1439" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="G1439" s="2">
+        <v>28</v>
+      </c>
+      <c r="H1439" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="I1439" s="2">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="J1439" s="2">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1440" s="22">
+        <v>46100</v>
+      </c>
+      <c r="B1440" s="14">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C1440" s="2" t="s">
+        <v>1988</v>
+      </c>
+      <c r="D1440" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1440" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1440" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1440" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1440" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1440" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1440" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1441" s="22">
+        <v>46100</v>
+      </c>
+      <c r="B1441" s="14">
+        <v>0.5625</v>
+      </c>
+      <c r="C1441" s="2" t="s">
+        <v>1989</v>
+      </c>
+      <c r="D1441" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="E1441" s="2">
+        <v>235</v>
+      </c>
+      <c r="F1441" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="G1441" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1441" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1441" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1441" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1442" s="22">
+        <v>46100</v>
+      </c>
+      <c r="B1442" s="14">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C1442" s="2" t="s">
+        <v>1990</v>
+      </c>
+      <c r="D1442" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1442" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1442" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1442" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1442" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1442" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1442" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1443" s="22">
+        <v>46100</v>
+      </c>
+      <c r="B1443" s="14">
+        <v>0.6875</v>
+      </c>
+      <c r="C1443" s="2" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D1443" s="2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E1443" s="2">
+        <v>263</v>
+      </c>
+      <c r="F1443" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="G1443" s="2">
+        <v>30.5</v>
+      </c>
+      <c r="H1443" s="2">
+        <v>14.7</v>
+      </c>
+      <c r="I1443" s="2">
+        <v>3</v>
+      </c>
+      <c r="J1443" s="2">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1444" s="22">
+        <v>46100</v>
+      </c>
+      <c r="B1444" s="14">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C1444" s="2" t="s">
+        <v>1992</v>
+      </c>
+      <c r="D1444" s="2" t="s">
+        <v>1993</v>
+      </c>
+      <c r="E1444" s="2">
+        <v>465</v>
+      </c>
+      <c r="F1444" s="2">
+        <v>30</v>
+      </c>
+      <c r="G1444" s="2">
+        <v>55</v>
+      </c>
+      <c r="H1444" s="2">
+        <v>15</v>
+      </c>
+      <c r="I1444" s="2">
+        <v>3</v>
+      </c>
+      <c r="J1444" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1445" s="22">
+        <v>46100</v>
+      </c>
+      <c r="B1445" s="14">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C1445" s="2" t="s">
+        <v>1994</v>
+      </c>
+      <c r="D1445" s="2" t="s">
+        <v>1995</v>
+      </c>
+      <c r="E1445" s="2">
+        <v>203</v>
+      </c>
+      <c r="F1445" s="2">
+        <v>22</v>
+      </c>
+      <c r="G1445" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="H1445" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="I1445" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="J1445" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1446" s="22">
+        <v>46101</v>
+      </c>
+      <c r="B1446" s="14">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C1446" s="2" t="s">
+        <v>1996</v>
+      </c>
+      <c r="D1446" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1446" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1446" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1446" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1446" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1446" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1446" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1447" s="22">
+        <v>46101</v>
+      </c>
+      <c r="B1447" s="14">
+        <v>0.5625</v>
+      </c>
+      <c r="C1447" s="2" t="s">
+        <v>1997</v>
+      </c>
+      <c r="D1447" s="2" t="s">
+        <v>1998</v>
+      </c>
+      <c r="E1447" s="2">
+        <v>380</v>
+      </c>
+      <c r="F1447" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="G1447" s="2">
+        <v>22</v>
+      </c>
+      <c r="H1447" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1447" s="2">
+        <v>1</v>
+      </c>
+      <c r="J1447" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1448" s="22">
+        <v>46101</v>
+      </c>
+      <c r="B1448" s="14">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C1448" s="2" t="s">
+        <v>1999</v>
+      </c>
+      <c r="D1448" s="2" t="s">
+        <v>2000</v>
+      </c>
+      <c r="E1448" s="2">
+        <v>250</v>
+      </c>
+      <c r="F1448" s="2">
+        <v>35</v>
+      </c>
+      <c r="G1448" s="2">
+        <v>5</v>
+      </c>
+      <c r="H1448" s="2">
+        <v>8</v>
+      </c>
+      <c r="I1448" s="2">
+        <v>2</v>
+      </c>
+      <c r="J1448" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1449" s="22">
+        <v>46101</v>
+      </c>
+      <c r="B1449" s="14">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C1449" s="2" t="s">
+        <v>2001</v>
+      </c>
+      <c r="D1449" s="2" t="s">
+        <v>2002</v>
+      </c>
+      <c r="E1449" s="2">
+        <v>150</v>
+      </c>
+      <c r="F1449" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G1449" s="2">
+        <v>15</v>
+      </c>
+      <c r="H1449" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1449" s="2">
+        <v>12</v>
+      </c>
+      <c r="J1449" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1450" s="22">
+        <v>46101</v>
+      </c>
+      <c r="B1450" s="14">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C1450" s="2" t="s">
+        <v>2003</v>
+      </c>
+      <c r="D1450" s="2" t="s">
+        <v>2004</v>
+      </c>
+      <c r="E1450" s="2">
+        <v>760</v>
+      </c>
+      <c r="F1450" s="2">
+        <v>7.4</v>
+      </c>
+      <c r="G1450" s="2">
+        <v>44</v>
+      </c>
+      <c r="H1450" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1450" s="2">
+        <v>2</v>
+      </c>
+      <c r="J1450" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1451" s="22">
+        <v>46101</v>
+      </c>
+      <c r="B1451" s="14">
+        <v>0.875</v>
+      </c>
+      <c r="C1451" s="2" t="s">
+        <v>2005</v>
+      </c>
+      <c r="D1451" s="2" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E1451" s="2">
+        <v>190</v>
+      </c>
+      <c r="F1451" s="2">
+        <v>1.85</v>
+      </c>
+      <c r="G1451" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1451" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1451" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J1451" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1452" s="22">
+        <v>46101</v>
+      </c>
+      <c r="B1452" s="14">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C1452" s="2" t="s">
+        <v>2007</v>
+      </c>
+      <c r="D1452" s="2" t="s">
+        <v>2008</v>
+      </c>
+      <c r="E1452" s="2">
+        <v>140</v>
+      </c>
+      <c r="F1452" s="2">
+        <v>3</v>
+      </c>
+      <c r="G1452" s="2">
+        <v>16</v>
+      </c>
+      <c r="H1452" s="2">
+        <v>7</v>
+      </c>
+      <c r="I1452" s="2">
+        <v>14</v>
+      </c>
+      <c r="J1452" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1453" s="22">
+        <v>46101</v>
+      </c>
+      <c r="B1453" s="14">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="C1453" s="2" t="s">
+        <v>2009</v>
+      </c>
+      <c r="D1453" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1453" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1453" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1453" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1453" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1453" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1453" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1454" s="22">
+        <v>46101</v>
+      </c>
+      <c r="B1454" s="14">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="C1454" s="2" t="s">
+        <v>2010</v>
+      </c>
+      <c r="D1454" s="2" t="s">
+        <v>1995</v>
+      </c>
+      <c r="E1454" s="2">
+        <v>203</v>
+      </c>
+      <c r="F1454" s="2">
+        <v>22</v>
+      </c>
+      <c r="G1454" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="H1454" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="I1454" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="J1454" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1455" s="22">
+        <v>46101</v>
+      </c>
+      <c r="B1455" s="14">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="C1455" s="2" t="s">
+        <v>2011</v>
+      </c>
+      <c r="D1455" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1455" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1455" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1455" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1455" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1455" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1455" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1456" s="22">
+        <v>46102</v>
+      </c>
+      <c r="B1456" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="C1456" s="2" t="s">
+        <v>2012</v>
+      </c>
+      <c r="D1456" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1456" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1456" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1456" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1456" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1456" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1456" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1457" s="22">
+        <v>46102</v>
+      </c>
+      <c r="B1457" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="C1457" s="2" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D1457" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1457" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1457" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1457" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1457" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1457" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1457" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1458" s="22">
+        <v>46102</v>
+      </c>
+      <c r="B1458" s="14">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1458" s="2" t="s">
+        <v>2014</v>
+      </c>
+      <c r="D1458" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="E1458" s="2">
+        <v>235</v>
+      </c>
+      <c r="F1458" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="G1458" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1458" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1458" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1458" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1459" s="22">
+        <v>46102</v>
+      </c>
+      <c r="B1459" s="14">
+        <v>0.625</v>
+      </c>
+      <c r="C1459" s="2" t="s">
+        <v>2015</v>
+      </c>
+      <c r="D1459" s="2" t="s">
+        <v>1993</v>
+      </c>
+      <c r="E1459" s="2">
+        <v>465</v>
+      </c>
+      <c r="F1459" s="2">
+        <v>30</v>
+      </c>
+      <c r="G1459" s="2">
+        <v>55</v>
+      </c>
+      <c r="H1459" s="2">
+        <v>15</v>
+      </c>
+      <c r="I1459" s="2">
+        <v>3</v>
+      </c>
+      <c r="J1459" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1460" s="22">
+        <v>46102</v>
+      </c>
+      <c r="B1460" s="14">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C1460" s="2" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D1460" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1460" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1460" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1460" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1460" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1460" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1460" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1461" s="22">
+        <v>46102</v>
+      </c>
+      <c r="B1461" s="14">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C1461" s="2" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D1461" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1461" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1461" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1461" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1461" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1461" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1461" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1462" s="22">
+        <v>46102</v>
+      </c>
+      <c r="B1462" s="14">
+        <v>0.8125</v>
+      </c>
+      <c r="C1462" s="2" t="s">
+        <v>2018</v>
+      </c>
+      <c r="D1462" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1462" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1462" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1462" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1462" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1462" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1462" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1463" s="22">
+        <v>46103</v>
+      </c>
+      <c r="B1463" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="C1463" s="2" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D1463" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1463" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1463" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1463" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1463" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1463" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1463" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1464" s="22">
+        <v>46103</v>
+      </c>
+      <c r="B1464" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="C1464" s="2" t="s">
+        <v>2020</v>
+      </c>
+      <c r="D1464" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1464" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1464" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1464" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1464" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1464" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1464" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1465" s="22">
+        <v>46103</v>
+      </c>
+      <c r="B1465" s="14">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1465" s="2" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D1465" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1465" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1465" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1465" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1465" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1465" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1465" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1466" s="22">
+        <v>46103</v>
+      </c>
+      <c r="B1466" s="14">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C1466" s="2" t="s">
+        <v>2022</v>
+      </c>
+      <c r="D1466" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1466" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1466" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1466" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1466" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1466" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1466" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1467" s="22">
+        <v>46103</v>
+      </c>
+      <c r="B1467" s="14">
+        <v>0.6875</v>
+      </c>
+      <c r="C1467" s="2" t="s">
+        <v>2023</v>
+      </c>
+      <c r="D1467" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1467" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1467" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1467" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1467" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1467" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1467" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1468" s="22">
+        <v>46103</v>
+      </c>
+      <c r="B1468" s="14">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C1468" s="2" t="s">
+        <v>2024</v>
+      </c>
+      <c r="D1468" s="2" t="s">
+        <v>1766</v>
+      </c>
+      <c r="E1468" s="2">
+        <v>207</v>
+      </c>
+      <c r="F1468" s="2">
+        <v>13</v>
+      </c>
+      <c r="G1468" s="2">
+        <v>4</v>
+      </c>
+      <c r="H1468" s="2">
+        <v>7</v>
+      </c>
+      <c r="I1468" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J1468" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1469" s="22">
+        <v>46103</v>
+      </c>
+      <c r="B1469" s="14">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C1469" s="2" t="s">
+        <v>2025</v>
+      </c>
+      <c r="D1469" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1469" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1469" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1469" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1469" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1469" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1469" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1470" s="22">
+        <v>46103</v>
+      </c>
+      <c r="B1470" s="14">
+        <v>0.8125</v>
+      </c>
+      <c r="C1470" s="2" t="s">
+        <v>2026</v>
+      </c>
+      <c r="D1470" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1470" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1470" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1470" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1470" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1470" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1470" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1471" s="22">
+        <v>46104</v>
+      </c>
+      <c r="B1471" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="C1471" s="2" t="s">
+        <v>2027</v>
+      </c>
+      <c r="D1471" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1471" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1471" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1471" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1471" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1471" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1471" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1472" s="22">
+        <v>46104</v>
+      </c>
+      <c r="B1472" s="14">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C1472" s="2" t="s">
+        <v>2028</v>
+      </c>
+      <c r="D1472" s="2" t="s">
+        <v>1721</v>
+      </c>
+      <c r="E1472" s="2">
+        <v>63</v>
+      </c>
+      <c r="F1472" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="G1472" s="2">
+        <v>16.8</v>
+      </c>
+      <c r="H1472" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="I1472" s="2">
+        <v>13</v>
+      </c>
+      <c r="J1472" s="2">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1473" s="22">
+        <v>46104</v>
+      </c>
+      <c r="B1473" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="C1473" s="2" t="s">
+        <v>2029</v>
+      </c>
+      <c r="D1473" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1473" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1473" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1473" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1473" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1473" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1473" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1474" s="22">
+        <v>46104</v>
+      </c>
+      <c r="B1474" s="14">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1474" s="2" t="s">
+        <v>2030</v>
+      </c>
+      <c r="D1474" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1474" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1474" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1474" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1474" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1474" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1474" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1475" s="22">
+        <v>46104</v>
+      </c>
+      <c r="B1475" s="14">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C1475" s="2" t="s">
+        <v>2031</v>
+      </c>
+      <c r="D1475" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1475" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1475" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1475" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1475" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1475" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1475" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1476" s="22">
+        <v>46104</v>
+      </c>
+      <c r="B1476" s="14">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C1476" s="2" t="s">
+        <v>2032</v>
+      </c>
+      <c r="D1476" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1476" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1476" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1476" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1476" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1476" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1476" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1477" s="22">
+        <v>46104</v>
+      </c>
+      <c r="B1477" s="14">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C1477" s="2" t="s">
+        <v>2033</v>
+      </c>
+      <c r="D1477" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="E1477" s="2">
+        <v>235</v>
+      </c>
+      <c r="F1477" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="G1477" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1477" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1477" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1477" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1478" s="22">
+        <v>46104</v>
+      </c>
+      <c r="B1478" s="14">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C1478" s="2" t="s">
+        <v>2034</v>
+      </c>
+      <c r="D1478" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E1478" s="2">
+        <v>156</v>
+      </c>
+      <c r="F1478" s="2">
+        <v>12.6</v>
+      </c>
+      <c r="G1478" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="H1478" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="I1478" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="J1478" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1479" s="22">
+        <v>46104</v>
+      </c>
+      <c r="B1479" s="14">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C1479" s="2" t="s">
+        <v>2035</v>
+      </c>
+      <c r="D1479" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E1479" s="2">
+        <v>145</v>
+      </c>
+      <c r="F1479" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="G1479" s="2">
+        <v>9</v>
+      </c>
+      <c r="H1479" s="2">
+        <v>9</v>
+      </c>
+      <c r="I1479" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1479" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1480" s="22">
+        <v>46104</v>
+      </c>
+      <c r="B1480" s="14">
+        <v>0.8125</v>
+      </c>
+      <c r="C1480" s="2" t="s">
+        <v>2036</v>
+      </c>
+      <c r="D1480" s="2" t="s">
+        <v>2037</v>
+      </c>
+      <c r="E1480" s="2">
+        <v>420</v>
+      </c>
+      <c r="F1480" s="2">
+        <v>26</v>
+      </c>
+      <c r="G1480" s="2">
+        <v>58</v>
+      </c>
+      <c r="H1480" s="2">
+        <v>8</v>
+      </c>
+      <c r="I1480" s="2">
+        <v>3</v>
+      </c>
+      <c r="J1480" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1481" s="22">
+        <v>46105</v>
+      </c>
+      <c r="B1481" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="C1481" s="2" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D1481" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1481" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1481" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1481" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1481" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1481" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1481" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1482" s="22">
+        <v>46105</v>
+      </c>
+      <c r="B1482" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="C1482" s="2" t="s">
+        <v>2039</v>
+      </c>
+      <c r="D1482" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1482" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1482" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1482" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1482" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1482" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1482" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1483" s="22">
+        <v>46105</v>
+      </c>
+      <c r="B1483" s="14">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C1483" s="2" t="s">
+        <v>2040</v>
+      </c>
+      <c r="D1483" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1483" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1483" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1483" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1483" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1483" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1483" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1484" s="22">
+        <v>46105</v>
+      </c>
+      <c r="B1484" s="14">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C1484" s="2" t="s">
+        <v>2041</v>
+      </c>
+      <c r="D1484" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="E1484" s="2">
+        <v>235</v>
+      </c>
+      <c r="F1484" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="G1484" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1484" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1484" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1484" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1485" s="22">
+        <v>46105</v>
+      </c>
+      <c r="B1485" s="14">
+        <v>0.8125</v>
+      </c>
+      <c r="C1485" s="2" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D1485" s="2" t="s">
+        <v>2043</v>
+      </c>
+      <c r="E1485" s="2">
+        <v>675</v>
+      </c>
+      <c r="F1485" s="2">
+        <v>42</v>
+      </c>
+      <c r="G1485" s="2">
+        <v>81</v>
+      </c>
+      <c r="H1485" s="2">
+        <v>20</v>
+      </c>
+      <c r="I1485" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1485" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1486" s="22">
+        <v>46105</v>
+      </c>
+      <c r="B1486" s="14">
+        <v>0.875</v>
+      </c>
+      <c r="C1486" s="2" t="s">
+        <v>2044</v>
+      </c>
+      <c r="D1486" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1486" s="2">
+        <v>175</v>
+      </c>
+      <c r="F1486" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G1486" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1486" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1486" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1486" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1487" s="22">
+        <v>46106</v>
+      </c>
+      <c r="B1487" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="C1487" s="2" t="s">
+        <v>2045</v>
+      </c>
+      <c r="D1487" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1487" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1487" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1487" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1487" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1487" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1487" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1488" s="22">
+        <v>46106</v>
+      </c>
+      <c r="B1488" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="C1488" s="2" t="s">
+        <v>2046</v>
+      </c>
+      <c r="D1488" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1488" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1488" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1488" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1488" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1488" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1488" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1489" s="22">
+        <v>46106</v>
+      </c>
+      <c r="B1489" s="14">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C1489" s="2" t="s">
+        <v>2047</v>
+      </c>
+      <c r="D1489" s="2" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1489" s="2">
+        <v>420</v>
+      </c>
+      <c r="F1489" s="2">
+        <v>24</v>
+      </c>
+      <c r="G1489" s="2">
+        <v>53</v>
+      </c>
+      <c r="H1489" s="2">
+        <v>12</v>
+      </c>
+      <c r="I1489" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1489" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1490" s="22">
+        <v>46106</v>
+      </c>
+      <c r="B1490" s="14">
+        <v>0.5625</v>
+      </c>
+      <c r="C1490" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D1490" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1490" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1490" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1490" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1490" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1490" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1490" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1491" s="22">
+        <v>46106</v>
+      </c>
+      <c r="B1491" s="14">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C1491" s="2" t="s">
+        <v>2050</v>
+      </c>
+      <c r="D1491" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="E1491" s="2">
+        <v>235</v>
+      </c>
+      <c r="F1491" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="G1491" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1491" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1491" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1491" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1492" s="22">
+        <v>46106</v>
+      </c>
+      <c r="B1492" s="14">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C1492" s="2" t="s">
+        <v>2051</v>
+      </c>
+      <c r="D1492" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1492" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1492" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1492" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1492" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1492" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1492" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1493" s="22">
+        <v>46106</v>
+      </c>
+      <c r="B1493" s="14">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C1493" s="2" t="s">
+        <v>2052</v>
+      </c>
+      <c r="D1493" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E1493" s="2">
+        <v>89</v>
+      </c>
+      <c r="F1493" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G1493" s="2">
+        <v>23</v>
+      </c>
+      <c r="H1493" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="I1493" s="2">
+        <v>12</v>
+      </c>
+      <c r="J1493" s="2">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1494" s="22">
+        <v>46106</v>
+      </c>
+      <c r="B1494" s="14">
+        <v>0.8125</v>
+      </c>
+      <c r="C1494" s="2" t="s">
+        <v>2053</v>
+      </c>
+      <c r="D1494" s="2" t="s">
+        <v>1993</v>
+      </c>
+      <c r="E1494" s="2">
+        <v>465</v>
+      </c>
+      <c r="F1494" s="2">
+        <v>30</v>
+      </c>
+      <c r="G1494" s="2">
+        <v>55</v>
+      </c>
+      <c r="H1494" s="2">
+        <v>15</v>
+      </c>
+      <c r="I1494" s="2">
+        <v>3</v>
+      </c>
+      <c r="J1494" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1495" s="22">
+        <v>46106</v>
+      </c>
+      <c r="B1495" s="14">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C1495" s="2" t="s">
+        <v>2054</v>
+      </c>
+      <c r="D1495" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1495" s="2">
+        <v>175</v>
+      </c>
+      <c r="F1495" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G1495" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1495" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1495" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1495" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1496" s="22">
+        <v>46107</v>
+      </c>
+      <c r="B1496" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="C1496" s="2" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D1496" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1496" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1496" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1496" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1496" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1496" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1496" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1497" s="22">
+        <v>46107</v>
+      </c>
+      <c r="B1497" s="14">
+        <v>0.4375</v>
+      </c>
+      <c r="C1497" s="2" t="s">
+        <v>2056</v>
+      </c>
+      <c r="D1497" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E1497" s="2">
+        <v>256</v>
+      </c>
+      <c r="F1497" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="G1497" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="H1497" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="I1497" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="J1497" s="2">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1498" s="22">
+        <v>46107</v>
+      </c>
+      <c r="B1498" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="C1498" s="2" t="s">
+        <v>2057</v>
+      </c>
+      <c r="D1498" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1498" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1498" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1498" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1498" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1498" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1498" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1499" s="22">
+        <v>46107</v>
+      </c>
+      <c r="B1499" s="14">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1499" s="2" t="s">
+        <v>2058</v>
+      </c>
+      <c r="D1499" s="2" t="s">
+        <v>1346</v>
+      </c>
+      <c r="E1499" s="2">
+        <v>204</v>
+      </c>
+      <c r="F1499" s="2">
+        <v>7.65</v>
+      </c>
+      <c r="G1499" s="2">
+        <v>42.96</v>
+      </c>
+      <c r="H1499" s="2">
+        <v>2.85</v>
+      </c>
+      <c r="I1499" s="2">
+        <v>26.76</v>
+      </c>
+      <c r="J1499" s="2">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1500" s="22">
+        <v>46107</v>
+      </c>
+      <c r="B1500" s="14">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C1500" s="2" t="s">
+        <v>2059</v>
+      </c>
+      <c r="D1500" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1500" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1500" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1500" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1500" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1500" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1500" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1501" s="22">
+        <v>46107</v>
+      </c>
+      <c r="B1501" s="14">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C1501" s="2" t="s">
+        <v>2060</v>
+      </c>
+      <c r="D1501" s="2" t="s">
+        <v>2061</v>
+      </c>
+      <c r="E1501" s="2">
+        <v>265</v>
+      </c>
+      <c r="F1501" s="2">
+        <v>6.7</v>
+      </c>
+      <c r="G1501" s="2">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="H1501" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="I1501" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="J1501" s="2">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1502" s="22">
+        <v>46107</v>
+      </c>
+      <c r="B1502" s="14">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C1502" s="2" t="s">
+        <v>2062</v>
+      </c>
+      <c r="D1502" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E1502" s="2">
+        <v>89</v>
+      </c>
+      <c r="F1502" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G1502" s="2">
+        <v>23</v>
+      </c>
+      <c r="H1502" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="I1502" s="2">
+        <v>12</v>
+      </c>
+      <c r="J1502" s="2">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1503" s="22">
+        <v>46107</v>
+      </c>
+      <c r="B1503" s="14">
+        <v>0.6875</v>
+      </c>
+      <c r="C1503" s="2" t="s">
+        <v>2063</v>
+      </c>
+      <c r="D1503" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="E1503" s="2">
+        <v>235</v>
+      </c>
+      <c r="F1503" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="G1503" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1503" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1503" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1503" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1504" s="22">
+        <v>46107</v>
+      </c>
+      <c r="B1504" s="14">
+        <v>0.8125</v>
+      </c>
+      <c r="C1504" s="2" t="s">
+        <v>2064</v>
+      </c>
+      <c r="D1504" s="2" t="s">
+        <v>1993</v>
+      </c>
+      <c r="E1504" s="2">
+        <v>465</v>
+      </c>
+      <c r="F1504" s="2">
+        <v>30</v>
+      </c>
+      <c r="G1504" s="2">
+        <v>55</v>
+      </c>
+      <c r="H1504" s="2">
+        <v>15</v>
+      </c>
+      <c r="I1504" s="2">
+        <v>3</v>
+      </c>
+      <c r="J1504" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1505" s="22">
+        <v>46108</v>
+      </c>
+      <c r="B1505" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="C1505" s="2" t="s">
+        <v>2065</v>
+      </c>
+      <c r="D1505" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1505" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1505" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1505" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1505" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1505" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1505" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1506" s="22">
+        <v>46108</v>
+      </c>
+      <c r="B1506" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C1506" s="2" t="s">
+        <v>2066</v>
+      </c>
+      <c r="D1506" s="2" t="s">
+        <v>2067</v>
+      </c>
+      <c r="E1506" s="2">
+        <v>225</v>
+      </c>
+      <c r="F1506" s="2">
+        <v>13</v>
+      </c>
+      <c r="G1506" s="2">
+        <v>21</v>
+      </c>
+      <c r="H1506" s="2">
+        <v>7</v>
+      </c>
+      <c r="I1506" s="2">
+        <v>1</v>
+      </c>
+      <c r="J1506" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1507" s="22">
+        <v>46108</v>
+      </c>
+      <c r="B1507" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="C1507" s="2" t="s">
+        <v>2068</v>
+      </c>
+      <c r="D1507" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1507" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1507" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1507" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1507" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1507" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1507" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1508" s="22">
+        <v>46108</v>
+      </c>
+      <c r="B1508" s="14">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C1508" s="2" t="s">
+        <v>2069</v>
+      </c>
+      <c r="D1508" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E1508" s="2">
+        <v>89</v>
+      </c>
+      <c r="F1508" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G1508" s="2">
+        <v>23</v>
+      </c>
+      <c r="H1508" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="I1508" s="2">
+        <v>12</v>
+      </c>
+      <c r="J1508" s="2">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1509" s="22">
+        <v>46108</v>
+      </c>
+      <c r="B1509" s="14">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C1509" s="2" t="s">
+        <v>2070</v>
+      </c>
+      <c r="D1509" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="E1509" s="2">
+        <v>235</v>
+      </c>
+      <c r="F1509" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="G1509" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1509" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1509" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1509" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1510" s="22">
+        <v>46108</v>
+      </c>
+      <c r="B1510" s="14">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C1510" s="2" t="s">
+        <v>2071</v>
+      </c>
+      <c r="D1510" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1510" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1510" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1510" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1510" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1510" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1510" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1511" s="22">
+        <v>46108</v>
+      </c>
+      <c r="B1511" s="14">
+        <v>0.8125</v>
+      </c>
+      <c r="C1511" s="2" t="s">
+        <v>2072</v>
+      </c>
+      <c r="D1511" s="2" t="s">
+        <v>1993</v>
+      </c>
+      <c r="E1511" s="2">
+        <v>465</v>
+      </c>
+      <c r="F1511" s="2">
+        <v>30</v>
+      </c>
+      <c r="G1511" s="2">
+        <v>55</v>
+      </c>
+      <c r="H1511" s="2">
+        <v>15</v>
+      </c>
+      <c r="I1511" s="2">
+        <v>3</v>
+      </c>
+      <c r="J1511" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1512" s="22">
+        <v>46108</v>
+      </c>
+      <c r="B1512" s="14">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C1512" s="2" t="s">
+        <v>2073</v>
+      </c>
+      <c r="D1512" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1512" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1512" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1512" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1512" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1512" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1512" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1513" s="22">
+        <v>46108</v>
+      </c>
+      <c r="B1513" s="14">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C1513" s="2" t="s">
+        <v>2074</v>
+      </c>
+      <c r="D1513" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E1513" s="2">
+        <v>145</v>
+      </c>
+      <c r="F1513" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="G1513" s="2">
+        <v>9</v>
+      </c>
+      <c r="H1513" s="2">
+        <v>9</v>
+      </c>
+      <c r="I1513" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1513" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1514" s="22">
+        <v>46109</v>
+      </c>
+      <c r="B1514" s="14">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="C1514" s="2" t="s">
+        <v>2075</v>
+      </c>
+      <c r="D1514" s="2" t="s">
+        <v>1755</v>
+      </c>
+      <c r="E1514" s="2">
+        <v>320</v>
+      </c>
+      <c r="F1514" s="2">
+        <v>6</v>
+      </c>
+      <c r="G1514" s="2">
+        <v>45</v>
+      </c>
+      <c r="H1514" s="2">
+        <v>12</v>
+      </c>
+      <c r="I1514" s="2">
+        <v>11</v>
+      </c>
+      <c r="J1514" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1515" s="22">
+        <v>46109</v>
+      </c>
+      <c r="B1515" s="14">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="C1515" s="2" t="s">
+        <v>2076</v>
+      </c>
+      <c r="D1515" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E1515" s="2">
+        <v>256</v>
+      </c>
+      <c r="F1515" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="G1515" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="H1515" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="I1515" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="J1515" s="2">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1516" s="22">
+        <v>46109</v>
+      </c>
+      <c r="B1516" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="C1516" s="2" t="s">
+        <v>2077</v>
+      </c>
+      <c r="D1516" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1516" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1516" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1516" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1516" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1516" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1516" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1517" s="22">
+        <v>46109</v>
+      </c>
+      <c r="B1517" s="14">
+        <v>0.4375</v>
+      </c>
+      <c r="C1517" s="2" t="s">
+        <v>2078</v>
+      </c>
+      <c r="D1517" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E1517" s="2">
+        <v>350</v>
+      </c>
+      <c r="F1517" s="2">
+        <v>12</v>
+      </c>
+      <c r="G1517" s="2">
+        <v>45</v>
+      </c>
+      <c r="H1517" s="2">
+        <v>14</v>
+      </c>
+      <c r="I1517" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1517" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1518" s="22">
+        <v>46109</v>
+      </c>
+      <c r="B1518" s="14">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C1518" s="2" t="s">
+        <v>2079</v>
+      </c>
+      <c r="D1518" s="2" t="s">
+        <v>2080</v>
+      </c>
+      <c r="E1518" s="2">
+        <v>684</v>
+      </c>
+      <c r="F1518" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="G1518" s="2">
+        <v>63</v>
+      </c>
+      <c r="H1518" s="2">
+        <v>42</v>
+      </c>
+      <c r="I1518" s="2">
+        <v>48</v>
+      </c>
+      <c r="J1518" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1519" s="22">
+        <v>46109</v>
+      </c>
+      <c r="B1519" s="14">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C1519" s="2" t="s">
+        <v>2081</v>
+      </c>
+      <c r="D1519" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1519" s="2">
+        <v>290</v>
+      </c>
+      <c r="F1519" s="2">
+        <v>11</v>
+      </c>
+      <c r="G1519" s="2">
+        <v>18</v>
+      </c>
+      <c r="H1519" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1519" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1519" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1520" s="22">
+        <v>46109</v>
+      </c>
+      <c r="B1520" s="14">
+        <v>0.6875</v>
+      </c>
+      <c r="C1520" s="2" t="s">
+        <v>2082</v>
+      </c>
+      <c r="D1520" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1520" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1520" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1520" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1520" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1520" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1520" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1521" s="22">
+        <v>46109</v>
+      </c>
+      <c r="B1521" s="14">
+        <v>0.8125</v>
+      </c>
+      <c r="C1521" s="2" t="s">
+        <v>2083</v>
+      </c>
+      <c r="D1521" s="2" t="s">
+        <v>1654</v>
+      </c>
+      <c r="E1521" s="2">
+        <v>430</v>
+      </c>
+      <c r="F1521" s="2">
+        <v>58</v>
+      </c>
+      <c r="G1521" s="2">
+        <v>4</v>
+      </c>
+      <c r="H1521" s="2">
+        <v>20</v>
+      </c>
+      <c r="I1521" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1521" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1522" s="22">
+        <v>46109</v>
+      </c>
+      <c r="B1522" s="14">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C1522" s="2" t="s">
+        <v>2084</v>
+      </c>
+      <c r="D1522" s="2" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E1522" s="2">
+        <v>120</v>
+      </c>
+      <c r="F1522" s="2">
+        <v>7</v>
+      </c>
+      <c r="G1522" s="2">
+        <v>13</v>
+      </c>
+      <c r="H1522" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="I1522" s="2">
+        <v>11</v>
+      </c>
+      <c r="J1522" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1523" s="22">
+        <v>46109</v>
+      </c>
+      <c r="B1523" s="14">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C1523" s="2" t="s">
+        <v>2086</v>
+      </c>
+      <c r="D1523" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E1523" s="2">
+        <v>63</v>
+      </c>
+      <c r="F1523" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G1523" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="H1523" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="I1523" s="2">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="J1523" s="2">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1524" s="22">
+        <v>46109</v>
+      </c>
+      <c r="B1524" s="14">
+        <v>0.875</v>
+      </c>
+      <c r="C1524" s="2" t="s">
+        <v>2087</v>
+      </c>
+      <c r="D1524" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1524" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1524" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1524" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1524" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1524" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1524" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1525" s="22">
+        <v>46110</v>
+      </c>
+      <c r="B1525" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="C1525" s="2" t="s">
+        <v>2088</v>
+      </c>
+      <c r="D1525" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1525" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1525" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1525" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1525" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1525" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1525" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1526" s="22">
+        <v>46110</v>
+      </c>
+      <c r="B1526" s="14">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C1526" s="2" t="s">
+        <v>2089</v>
+      </c>
+      <c r="D1526" s="2" t="s">
+        <v>2090</v>
+      </c>
+      <c r="E1526" s="2">
+        <v>285</v>
+      </c>
+      <c r="F1526" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="G1526" s="2">
+        <v>26</v>
+      </c>
+      <c r="H1526" s="2">
+        <v>17.5</v>
+      </c>
+      <c r="I1526" s="2">
+        <v>20</v>
+      </c>
+      <c r="J1526" s="2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1527" s="22">
+        <v>46110</v>
+      </c>
+      <c r="B1527" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="C1527" s="2" t="s">
+        <v>2091</v>
+      </c>
+      <c r="D1527" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E1527" s="2">
+        <v>145</v>
+      </c>
+      <c r="F1527" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="G1527" s="2">
+        <v>9</v>
+      </c>
+      <c r="H1527" s="2">
+        <v>9</v>
+      </c>
+      <c r="I1527" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1527" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1528" s="22">
+        <v>46110</v>
+      </c>
+      <c r="B1528" s="14">
+        <v>0.5625</v>
+      </c>
+      <c r="C1528" s="2" t="s">
+        <v>2092</v>
+      </c>
+      <c r="D1528" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1528" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1528" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1528" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1528" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1528" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1528" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1529" s="22">
+        <v>46110</v>
+      </c>
+      <c r="B1529" s="14">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C1529" s="2" t="s">
+        <v>2093</v>
+      </c>
+      <c r="D1529" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="E1529" s="2">
+        <v>235</v>
+      </c>
+      <c r="F1529" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="G1529" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1529" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1529" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1529" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1530" s="22">
+        <v>46110</v>
+      </c>
+      <c r="B1530" s="14">
+        <v>0.625</v>
+      </c>
+      <c r="C1530" s="2" t="s">
+        <v>2094</v>
+      </c>
+      <c r="D1530" s="2" t="s">
+        <v>2095</v>
+      </c>
+      <c r="E1530" s="2">
+        <v>428</v>
+      </c>
+      <c r="F1530" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="G1530" s="2">
+        <v>39</v>
+      </c>
+      <c r="H1530" s="2">
+        <v>26.3</v>
+      </c>
+      <c r="I1530" s="2">
+        <v>30</v>
+      </c>
+      <c r="J1530" s="2">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1531" s="22">
+        <v>46110</v>
+      </c>
+      <c r="B1531" s="14">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C1531" s="2" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D1531" s="2" t="s">
+        <v>2097</v>
+      </c>
+      <c r="E1531" s="2">
+        <v>175</v>
+      </c>
+      <c r="F1531" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1531" s="2">
+        <v>24</v>
+      </c>
+      <c r="H1531" s="2">
+        <v>8</v>
+      </c>
+      <c r="I1531" s="2">
+        <v>14</v>
+      </c>
+      <c r="J1531" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1532" s="22">
+        <v>46110</v>
+      </c>
+      <c r="B1532" s="14">
+        <v>0.875</v>
+      </c>
+      <c r="C1532" s="2" t="s">
+        <v>2098</v>
+      </c>
+      <c r="D1532" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1532" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1532" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1532" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1532" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1532" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1532" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1533" s="22">
+        <v>46110</v>
+      </c>
+      <c r="B1533" s="14">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C1533" s="2" t="s">
+        <v>2099</v>
+      </c>
+      <c r="D1533" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1533" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1533" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G1533" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H1533" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I1533" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J1533" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1534" s="22">
+        <v>46111</v>
+      </c>
+      <c r="B1534" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="C1534" s="2" t="s">
+        <v>2100</v>
+      </c>
+      <c r="D1534" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1534" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1534" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1534" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1534" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1534" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1534" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1535" s="22">
+        <v>46111</v>
+      </c>
+      <c r="B1535" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="C1535" s="2" t="s">
+        <v>2101</v>
+      </c>
+      <c r="D1535" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1535" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1535" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1535" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1535" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1535" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1535" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1536" s="22">
+        <v>46111</v>
+      </c>
+      <c r="B1536" s="14">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C1536" s="2" t="s">
+        <v>2102</v>
+      </c>
+      <c r="D1536" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="E1536" s="2">
+        <v>235</v>
+      </c>
+      <c r="F1536" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="G1536" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1536" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1536" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="J1536" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1537" s="22">
+        <v>46111</v>
+      </c>
+      <c r="B1537" s="14">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C1537" s="2" t="s">
+        <v>2103</v>
+      </c>
+      <c r="D1537" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1537" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1537" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1537" s="2">
+        <v>11</v>
+      </c>
+      <c r="H1537" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1537" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1537" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1538" s="22">
+        <v>46111</v>
+      </c>
+      <c r="B1538" s="14">
+        <v>0.6875</v>
+      </c>
+      <c r="C1538" s="2" t="s">
+        <v>2104</v>
+      </c>
+      <c r="D1538" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E1538" s="2">
+        <v>256</v>
+      </c>
+      <c r="F1538" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="G1538" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="H1538" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="I1538" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="J1538" s="2">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1539" s="22">
+        <v>46111</v>
+      </c>
+      <c r="B1539" s="14">
+        <v>0.75</v>
+      </c>
+      <c r="C1539" s="2" t="s">
+        <v>2105</v>
+      </c>
+      <c r="D1539" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E1539" s="2">
+        <v>335</v>
+      </c>
+      <c r="F1539" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1539" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1539" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1539" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J1539" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1540" s="22">
+        <v>46111</v>
+      </c>
+      <c r="B1540" s="14">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C1540" s="2" t="s">
+        <v>2106</v>
+      </c>
+      <c r="D1540" s="2" t="s">
+        <v>2107</v>
+      </c>
+      <c r="E1540" s="2">
+        <v>350</v>
+      </c>
+      <c r="F1540" s="2">
+        <v>12</v>
+      </c>
+      <c r="G1540" s="2">
+        <v>32</v>
+      </c>
+      <c r="H1540" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1540" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1540" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1541" s="22">
+        <v>46111</v>
+      </c>
+      <c r="B1541" s="14">
+        <v>0.8125</v>
+      </c>
+      <c r="C1541" s="2" t="s">
+        <v>2108</v>
+      </c>
+      <c r="D1541" s="2" t="s">
+        <v>2109</v>
+      </c>
+      <c r="E1541" s="2">
+        <v>400</v>
+      </c>
+      <c r="F1541" s="2">
+        <v>10</v>
+      </c>
+      <c r="G1541" s="2">
+        <v>45</v>
+      </c>
+      <c r="H1541" s="2">
+        <v>20</v>
+      </c>
+      <c r="I1541" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1541" s="2">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -52361,7 +56228,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F24E0C0-BC77-4AA4-801C-82B038A8B8E4}">
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -53376,16 +57243,16 @@
       <c r="A52" s="22">
         <v>46094</v>
       </c>
-      <c r="B52" s="28">
+      <c r="B52" s="2">
         <v>97.9</v>
       </c>
-      <c r="C52" s="28">
+      <c r="C52" s="2">
         <v>37.799999999999997</v>
       </c>
-      <c r="D52" s="28">
+      <c r="D52" s="2">
         <v>27.9</v>
       </c>
-      <c r="E52" s="28">
+      <c r="E52" s="2">
         <v>51.3</v>
       </c>
       <c r="F52" s="2"/>
@@ -53394,16 +57261,16 @@
       <c r="A53" s="22">
         <v>46095</v>
       </c>
-      <c r="B53" s="28">
+      <c r="B53" s="2">
         <v>97.6</v>
       </c>
-      <c r="C53" s="28">
+      <c r="C53" s="2">
         <v>37.1</v>
       </c>
-      <c r="D53" s="28">
+      <c r="D53" s="2">
         <v>28.6</v>
       </c>
-      <c r="E53" s="28">
+      <c r="E53" s="2">
         <v>50.3</v>
       </c>
       <c r="F53" s="2"/>
@@ -53412,19 +57279,55 @@
       <c r="A54" s="22">
         <v>46100</v>
       </c>
-      <c r="B54" s="28">
+      <c r="B54" s="2">
         <v>97.6</v>
       </c>
-      <c r="C54" s="28">
+      <c r="C54" s="2">
         <v>37.4</v>
       </c>
-      <c r="D54" s="28">
+      <c r="D54" s="2">
         <v>28.2</v>
       </c>
-      <c r="E54" s="28">
+      <c r="E54" s="2">
         <v>50.9</v>
       </c>
       <c r="F54" s="2"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="22">
+        <v>46107</v>
+      </c>
+      <c r="B55" s="2">
+        <v>97.9</v>
+      </c>
+      <c r="C55" s="28">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="D55" s="28">
+        <v>27.9</v>
+      </c>
+      <c r="E55" s="28">
+        <v>51.3</v>
+      </c>
+      <c r="F55" s="2"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="22">
+        <v>46108</v>
+      </c>
+      <c r="B56" s="28">
+        <v>97.7</v>
+      </c>
+      <c r="C56" s="28">
+        <v>37.9</v>
+      </c>
+      <c r="D56" s="28">
+        <v>27.6</v>
+      </c>
+      <c r="E56" s="28">
+        <v>51.4</v>
+      </c>
+      <c r="F56" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -53435,7 +57338,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D2F321-D2D4-48D2-B6F9-E306604CF730}">
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -55617,6 +59520,7 @@
         <v>6780</v>
       </c>
       <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="22">
@@ -55639,6 +59543,164 @@
       <c r="H94" s="2" t="s">
         <v>1715</v>
       </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95" s="22">
+        <v>46101</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D95" s="2">
+        <v>70</v>
+      </c>
+      <c r="E95" s="2">
+        <v>617</v>
+      </c>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A96" s="22">
+        <v>46104</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D96" s="2">
+        <v>60</v>
+      </c>
+      <c r="E96" s="2">
+        <v>479</v>
+      </c>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" s="22">
+        <v>46105</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D97" s="2">
+        <v>73</v>
+      </c>
+      <c r="E97" s="2">
+        <v>552</v>
+      </c>
+      <c r="F97" s="2">
+        <v>5540</v>
+      </c>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A98" s="22">
+        <v>46106</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D98" s="2">
+        <v>70</v>
+      </c>
+      <c r="E98" s="2">
+        <v>668</v>
+      </c>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2" t="s">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99" s="22">
+        <v>46107</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D99" s="2">
+        <v>90</v>
+      </c>
+      <c r="E99" s="2">
+        <v>743</v>
+      </c>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A100" s="22">
+        <v>46108</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D100" s="2">
+        <v>75</v>
+      </c>
+      <c r="E100" s="2">
+        <v>589</v>
+      </c>
+      <c r="F100" s="2">
+        <v>5580</v>
+      </c>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A101" s="22">
+        <v>46108</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D101" s="2">
+        <v>68</v>
+      </c>
+      <c r="E101" s="2">
+        <v>545</v>
+      </c>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2" t="s">
+        <v>2116</v>
+      </c>
+      <c r="H101" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -55948,10 +60010,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC2BD037-7A04-4BEA-B100-A47D0614F32C}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.5546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -56031,14 +60093,649 @@
       </c>
       <c r="H3" s="2"/>
     </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="22">
+        <v>46045</v>
+      </c>
+      <c r="B4" s="2">
+        <v>42.5</v>
+      </c>
+      <c r="C4" s="2">
+        <v>39</v>
+      </c>
+      <c r="D4" s="2">
+        <v>42</v>
+      </c>
+      <c r="E4" s="2">
+        <v>27</v>
+      </c>
+      <c r="F4" s="2">
+        <v>16</v>
+      </c>
+      <c r="G4" s="2">
+        <v>14</v>
+      </c>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="22">
+        <v>46065</v>
+      </c>
+      <c r="B5" s="2">
+        <v>42.5</v>
+      </c>
+      <c r="C5" s="2">
+        <v>39.5</v>
+      </c>
+      <c r="D5" s="2">
+        <v>42</v>
+      </c>
+      <c r="E5" s="2">
+        <v>27</v>
+      </c>
+      <c r="F5" s="2">
+        <v>16</v>
+      </c>
+      <c r="G5" s="2">
+        <v>14</v>
+      </c>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="22">
+        <v>46108</v>
+      </c>
+      <c r="B6" s="2">
+        <v>43.5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>39</v>
+      </c>
+      <c r="D6" s="2">
+        <v>42.5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>27.5</v>
+      </c>
+      <c r="F6" s="2">
+        <v>16</v>
+      </c>
+      <c r="G6" s="2">
+        <v>14</v>
+      </c>
+      <c r="H6" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F3DAC15-C829-4324-82D7-B0DBA610DC6A}">
+  <dimension ref="A1:J20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>858</v>
+      </c>
+      <c r="C2" t="s">
+        <v>859</v>
+      </c>
+      <c r="D2" t="s">
+        <v>860</v>
+      </c>
+      <c r="E2">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>861</v>
+      </c>
+      <c r="C3" t="s">
+        <v>862</v>
+      </c>
+      <c r="D3" t="s">
+        <v>860</v>
+      </c>
+      <c r="E3">
+        <v>2269</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>863</v>
+      </c>
+      <c r="C4" t="s">
+        <v>864</v>
+      </c>
+      <c r="D4" t="s">
+        <v>860</v>
+      </c>
+      <c r="E4">
+        <v>1728</v>
+      </c>
+      <c r="F4">
+        <v>50</v>
+      </c>
+      <c r="G4">
+        <v>236</v>
+      </c>
+      <c r="H4">
+        <v>67</v>
+      </c>
+      <c r="I4">
+        <v>61</v>
+      </c>
+      <c r="J4">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>865</v>
+      </c>
+      <c r="C5" t="s">
+        <v>866</v>
+      </c>
+      <c r="D5" t="s">
+        <v>860</v>
+      </c>
+      <c r="E5">
+        <v>2009</v>
+      </c>
+      <c r="F5">
+        <v>99</v>
+      </c>
+      <c r="G5">
+        <v>234</v>
+      </c>
+      <c r="H5">
+        <v>77</v>
+      </c>
+      <c r="I5">
+        <v>74</v>
+      </c>
+      <c r="J5">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>867</v>
+      </c>
+      <c r="C6" t="s">
+        <v>868</v>
+      </c>
+      <c r="D6" t="s">
+        <v>860</v>
+      </c>
+      <c r="E6">
+        <v>1682</v>
+      </c>
+      <c r="F6">
+        <v>64</v>
+      </c>
+      <c r="G6">
+        <v>229</v>
+      </c>
+      <c r="H6">
+        <v>56</v>
+      </c>
+      <c r="I6">
+        <v>64</v>
+      </c>
+      <c r="J6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>869</v>
+      </c>
+      <c r="C7" t="s">
+        <v>870</v>
+      </c>
+      <c r="D7" t="s">
+        <v>860</v>
+      </c>
+      <c r="E7">
+        <v>2221</v>
+      </c>
+      <c r="F7">
+        <v>75</v>
+      </c>
+      <c r="G7">
+        <v>260</v>
+      </c>
+      <c r="H7">
+        <v>97</v>
+      </c>
+      <c r="I7">
+        <v>52</v>
+      </c>
+      <c r="J7">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>871</v>
+      </c>
+      <c r="C8" t="s">
+        <v>872</v>
+      </c>
+      <c r="D8" t="s">
+        <v>860</v>
+      </c>
+      <c r="E8">
+        <v>1938</v>
+      </c>
+      <c r="F8">
+        <v>99.7</v>
+      </c>
+      <c r="G8">
+        <v>226</v>
+      </c>
+      <c r="H8">
+        <v>73</v>
+      </c>
+      <c r="I8">
+        <v>56</v>
+      </c>
+      <c r="J8">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>873</v>
+      </c>
+      <c r="C9" t="s">
+        <v>874</v>
+      </c>
+      <c r="D9" t="s">
+        <v>860</v>
+      </c>
+      <c r="E9">
+        <v>2092</v>
+      </c>
+      <c r="F9">
+        <v>106</v>
+      </c>
+      <c r="G9">
+        <v>237</v>
+      </c>
+      <c r="H9">
+        <v>78</v>
+      </c>
+      <c r="I9">
+        <v>78</v>
+      </c>
+      <c r="J9">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>875</v>
+      </c>
+      <c r="C10" t="s">
+        <v>876</v>
+      </c>
+      <c r="D10" t="s">
+        <v>860</v>
+      </c>
+      <c r="E10">
+        <v>2783</v>
+      </c>
+      <c r="F10">
+        <v>156</v>
+      </c>
+      <c r="G10">
+        <v>313</v>
+      </c>
+      <c r="H10">
+        <v>96</v>
+      </c>
+      <c r="I10">
+        <v>90</v>
+      </c>
+      <c r="J10">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>877</v>
+      </c>
+      <c r="C11" t="s">
+        <v>878</v>
+      </c>
+      <c r="D11" t="s">
+        <v>860</v>
+      </c>
+      <c r="E11">
+        <v>1796</v>
+      </c>
+      <c r="F11">
+        <v>78</v>
+      </c>
+      <c r="G11">
+        <v>217</v>
+      </c>
+      <c r="H11">
+        <v>70</v>
+      </c>
+      <c r="I11">
+        <v>81</v>
+      </c>
+      <c r="J11">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>879</v>
+      </c>
+      <c r="C12" t="s">
+        <v>880</v>
+      </c>
+      <c r="D12" t="s">
+        <v>860</v>
+      </c>
+      <c r="E12">
+        <v>1698</v>
+      </c>
+      <c r="F12">
+        <v>73.7</v>
+      </c>
+      <c r="G12">
+        <v>180</v>
+      </c>
+      <c r="H12">
+        <v>69</v>
+      </c>
+      <c r="I12">
+        <v>43.3</v>
+      </c>
+      <c r="J12">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>881</v>
+      </c>
+      <c r="C13" t="s">
+        <v>882</v>
+      </c>
+      <c r="D13" t="s">
+        <v>860</v>
+      </c>
+      <c r="E13">
+        <v>2099</v>
+      </c>
+      <c r="F13">
+        <v>82.8</v>
+      </c>
+      <c r="G13">
+        <v>224.5</v>
+      </c>
+      <c r="H13">
+        <v>92.2</v>
+      </c>
+      <c r="I13">
+        <v>44.5</v>
+      </c>
+      <c r="J13">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>883</v>
+      </c>
+      <c r="C14" t="s">
+        <v>884</v>
+      </c>
+      <c r="D14" t="s">
+        <v>860</v>
+      </c>
+      <c r="E14">
+        <v>2774</v>
+      </c>
+      <c r="F14">
+        <v>157</v>
+      </c>
+      <c r="G14">
+        <v>254</v>
+      </c>
+      <c r="H14">
+        <v>123</v>
+      </c>
+      <c r="I14">
+        <v>68</v>
+      </c>
+      <c r="J14">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>885</v>
+      </c>
+      <c r="C15" t="s">
+        <v>886</v>
+      </c>
+      <c r="D15" t="s">
+        <v>860</v>
+      </c>
+      <c r="E15">
+        <v>1880</v>
+      </c>
+      <c r="F15">
+        <v>98.3</v>
+      </c>
+      <c r="G15">
+        <v>237</v>
+      </c>
+      <c r="H15">
+        <v>59.9</v>
+      </c>
+      <c r="I15">
+        <v>79.599999999999994</v>
+      </c>
+      <c r="J15">
+        <v>38.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>887</v>
+      </c>
+      <c r="C16" t="s">
+        <v>888</v>
+      </c>
+      <c r="D16" t="s">
+        <v>860</v>
+      </c>
+      <c r="E16">
+        <v>1634</v>
+      </c>
+      <c r="F16">
+        <v>86.9</v>
+      </c>
+      <c r="G16">
+        <v>155.6</v>
+      </c>
+      <c r="H16">
+        <v>69.5</v>
+      </c>
+      <c r="I16">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="J16">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>889</v>
+      </c>
+      <c r="C17" t="s">
+        <v>890</v>
+      </c>
+      <c r="D17" t="s">
+        <v>860</v>
+      </c>
+      <c r="E17">
+        <v>2001</v>
+      </c>
+      <c r="F17">
+        <v>82.3</v>
+      </c>
+      <c r="G17">
+        <v>277.10000000000002</v>
+      </c>
+      <c r="H17">
+        <v>70.400000000000006</v>
+      </c>
+      <c r="I17">
+        <v>96.6</v>
+      </c>
+      <c r="J17">
+        <v>56.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>891</v>
+      </c>
+      <c r="C18" t="s">
+        <v>892</v>
+      </c>
+      <c r="D18" t="s">
+        <v>860</v>
+      </c>
+      <c r="E18">
+        <v>1878</v>
+      </c>
+      <c r="F18">
+        <v>116</v>
+      </c>
+      <c r="G18">
+        <v>128</v>
+      </c>
+      <c r="H18">
+        <v>78</v>
+      </c>
+      <c r="I18">
+        <v>28</v>
+      </c>
+      <c r="J18">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>893</v>
+      </c>
+      <c r="C19" t="s">
+        <v>894</v>
+      </c>
+      <c r="D19" t="s">
+        <v>860</v>
+      </c>
+      <c r="E19">
+        <v>2257</v>
+      </c>
+      <c r="F19">
+        <v>138</v>
+      </c>
+      <c r="G19">
+        <v>190</v>
+      </c>
+      <c r="H19">
+        <v>95</v>
+      </c>
+      <c r="I19">
+        <v>41</v>
+      </c>
+      <c r="J19">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>895</v>
+      </c>
+      <c r="C20" t="s">
+        <v>896</v>
+      </c>
+      <c r="D20" t="s">
+        <v>860</v>
+      </c>
+      <c r="E20">
+        <v>2909</v>
+      </c>
+      <c r="F20">
+        <v>170</v>
+      </c>
+      <c r="G20">
+        <v>273</v>
+      </c>
+      <c r="H20">
+        <v>126</v>
+      </c>
+      <c r="I20">
+        <v>72.599999999999994</v>
+      </c>
+      <c r="J20">
+        <v>43.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB0140AB-465A-4E35-8F6E-65CE935EFC2A}">
-  <dimension ref="A1:J111"/>
+  <dimension ref="A33:B111"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -56046,3160 +60743,321 @@
     <col min="4" max="4" width="40.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>0</v>
-      </c>
-      <c r="B32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C32" t="s">
-        <v>2</v>
-      </c>
-      <c r="D32" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" t="s">
-        <v>4</v>
-      </c>
-      <c r="F32" t="s">
-        <v>5</v>
-      </c>
-      <c r="G32" t="s">
-        <v>6</v>
-      </c>
-      <c r="H32" t="s">
-        <v>7</v>
-      </c>
-      <c r="I32" t="s">
-        <v>8</v>
-      </c>
-      <c r="J32" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="23">
-        <v>46021</v>
-      </c>
-      <c r="B33" s="24">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="C33" t="s">
-        <v>1002</v>
-      </c>
-      <c r="D33" t="s">
-        <v>102</v>
-      </c>
-      <c r="E33">
-        <v>77</v>
-      </c>
-      <c r="F33">
-        <v>2</v>
-      </c>
-      <c r="G33">
-        <v>11</v>
-      </c>
-      <c r="H33">
-        <v>2</v>
-      </c>
-      <c r="I33">
-        <v>7</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="23">
-        <v>46021</v>
-      </c>
-      <c r="B34" s="24">
-        <v>0.5</v>
-      </c>
-      <c r="C34" t="s">
-        <v>1003</v>
-      </c>
-      <c r="D34" t="s">
-        <v>116</v>
-      </c>
-      <c r="E34">
-        <v>155</v>
-      </c>
-      <c r="F34">
-        <v>15.5</v>
-      </c>
-      <c r="G34">
-        <v>15</v>
-      </c>
-      <c r="H34">
-        <v>2</v>
-      </c>
-      <c r="I34">
-        <v>7</v>
-      </c>
-      <c r="J34">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="23">
-        <v>46021</v>
-      </c>
-      <c r="B35" s="24">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1004</v>
-      </c>
-      <c r="D35" t="s">
-        <v>32</v>
-      </c>
-      <c r="E35">
-        <v>290</v>
-      </c>
-      <c r="F35">
-        <v>11</v>
-      </c>
-      <c r="G35">
-        <v>18</v>
-      </c>
-      <c r="H35">
-        <v>18</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="23">
-        <v>46021</v>
-      </c>
-      <c r="B36" s="24">
-        <v>0.8125</v>
-      </c>
-      <c r="C36" t="s">
-        <v>1005</v>
-      </c>
-      <c r="D36" t="s">
-        <v>1006</v>
-      </c>
-      <c r="E36">
-        <v>800</v>
-      </c>
-      <c r="F36">
-        <v>40</v>
-      </c>
-      <c r="G36">
-        <v>100</v>
-      </c>
-      <c r="H36">
-        <v>25</v>
-      </c>
-      <c r="I36">
-        <v>5</v>
-      </c>
-      <c r="J36">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="23">
-        <v>46021</v>
-      </c>
-      <c r="B37" s="24">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="C37" t="s">
-        <v>1007</v>
-      </c>
-      <c r="D37" t="s">
-        <v>365</v>
-      </c>
-      <c r="E37">
-        <v>256</v>
-      </c>
-      <c r="F37">
-        <v>13.2</v>
-      </c>
-      <c r="G37">
-        <v>19.2</v>
-      </c>
-      <c r="H37">
-        <v>10.6</v>
-      </c>
-      <c r="I37">
-        <v>10.6</v>
-      </c>
-      <c r="J37">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="23">
-        <v>46021</v>
-      </c>
-      <c r="B38" s="24">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="C38" t="s">
-        <v>1008</v>
-      </c>
-      <c r="D38" t="s">
-        <v>1009</v>
-      </c>
-      <c r="E38">
-        <v>175</v>
-      </c>
-      <c r="F38">
-        <v>15.5</v>
-      </c>
-      <c r="G38">
-        <v>20</v>
-      </c>
-      <c r="H38">
-        <v>2</v>
-      </c>
-      <c r="I38">
-        <v>11.5</v>
-      </c>
-      <c r="J38">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="23">
-        <v>46021</v>
-      </c>
-      <c r="B39" s="24">
-        <v>0.875</v>
-      </c>
-      <c r="C39" t="s">
-        <v>1010</v>
-      </c>
-      <c r="D39" t="s">
-        <v>1011</v>
-      </c>
-      <c r="E39">
-        <v>310</v>
-      </c>
-      <c r="F39">
-        <v>6</v>
-      </c>
-      <c r="G39">
-        <v>45</v>
-      </c>
-      <c r="H39">
-        <v>12</v>
-      </c>
-      <c r="I39">
-        <v>11</v>
-      </c>
-      <c r="J39">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="23">
-        <v>46022</v>
-      </c>
-      <c r="B40" s="24">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="C40" t="s">
-        <v>1012</v>
-      </c>
-      <c r="D40" t="s">
-        <v>102</v>
-      </c>
-      <c r="E40">
-        <v>77</v>
-      </c>
-      <c r="F40">
-        <v>2</v>
-      </c>
-      <c r="G40">
-        <v>11</v>
-      </c>
-      <c r="H40">
-        <v>2</v>
-      </c>
-      <c r="I40">
-        <v>7</v>
-      </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="23">
-        <v>46022</v>
-      </c>
-      <c r="B41" s="24">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="C41" t="s">
-        <v>1013</v>
-      </c>
-      <c r="D41" t="s">
-        <v>258</v>
-      </c>
-      <c r="E41">
-        <v>128</v>
-      </c>
-      <c r="F41">
-        <v>6.6</v>
-      </c>
-      <c r="G41">
-        <v>9.6</v>
-      </c>
-      <c r="H41">
-        <v>5.3</v>
-      </c>
-      <c r="I41">
-        <v>5.3</v>
-      </c>
-      <c r="J41">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="23">
-        <v>46022</v>
-      </c>
-      <c r="B42" s="24">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="C42" t="s">
-        <v>1014</v>
-      </c>
-      <c r="D42" t="s">
-        <v>1006</v>
-      </c>
-      <c r="E42">
-        <v>800</v>
-      </c>
-      <c r="F42">
-        <v>40</v>
-      </c>
-      <c r="G42">
-        <v>100</v>
-      </c>
-      <c r="H42">
-        <v>25</v>
-      </c>
-      <c r="I42">
-        <v>5</v>
-      </c>
-      <c r="J42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" s="23">
-        <v>46022</v>
-      </c>
-      <c r="B43" s="24">
-        <v>0.5</v>
-      </c>
-      <c r="C43" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D43" t="s">
-        <v>116</v>
-      </c>
-      <c r="E43">
-        <v>155</v>
-      </c>
-      <c r="F43">
-        <v>15.5</v>
-      </c>
-      <c r="G43">
-        <v>15</v>
-      </c>
-      <c r="H43">
-        <v>2</v>
-      </c>
-      <c r="I43">
-        <v>7</v>
-      </c>
-      <c r="J43">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="23">
-        <v>46022</v>
-      </c>
-      <c r="B44" s="24">
-        <v>0.6875</v>
-      </c>
-      <c r="C44" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D44" t="s">
-        <v>102</v>
-      </c>
-      <c r="E44">
-        <v>77</v>
-      </c>
-      <c r="F44">
-        <v>2</v>
-      </c>
-      <c r="G44">
-        <v>11</v>
-      </c>
-      <c r="H44">
-        <v>2</v>
-      </c>
-      <c r="I44">
-        <v>7</v>
-      </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="23">
-        <v>46022</v>
-      </c>
-      <c r="B45" s="24">
-        <v>0.75</v>
-      </c>
-      <c r="C45" t="s">
-        <v>1017</v>
-      </c>
-      <c r="D45" t="s">
-        <v>32</v>
-      </c>
-      <c r="E45">
-        <v>290</v>
-      </c>
-      <c r="F45">
-        <v>11</v>
-      </c>
-      <c r="G45">
-        <v>18</v>
-      </c>
-      <c r="H45">
-        <v>18</v>
-      </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
-      <c r="J45">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" s="23">
-        <v>46022</v>
-      </c>
-      <c r="B46" s="24">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="C46" t="s">
-        <v>1018</v>
-      </c>
-      <c r="D46" t="s">
-        <v>98</v>
-      </c>
-      <c r="E46">
-        <v>380</v>
-      </c>
-      <c r="F46">
-        <v>25</v>
-      </c>
-      <c r="G46">
-        <v>46</v>
-      </c>
-      <c r="H46">
-        <v>10</v>
-      </c>
-      <c r="I46">
-        <v>2</v>
-      </c>
-      <c r="J46">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="23">
-        <v>46022</v>
-      </c>
-      <c r="B47" s="24">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C47" t="s">
-        <v>1019</v>
-      </c>
-      <c r="D47" t="s">
-        <v>139</v>
-      </c>
-      <c r="E47">
-        <v>175</v>
-      </c>
-      <c r="F47">
-        <v>15.5</v>
-      </c>
-      <c r="G47">
-        <v>20</v>
-      </c>
-      <c r="H47">
-        <v>2</v>
-      </c>
-      <c r="I47">
-        <v>11.5</v>
-      </c>
-      <c r="J47">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" s="23">
-        <v>46022</v>
-      </c>
-      <c r="B48" s="24">
-        <v>0.8125</v>
-      </c>
-      <c r="C48" t="s">
-        <v>1020</v>
-      </c>
-      <c r="D48" t="s">
-        <v>1021</v>
-      </c>
-      <c r="E48">
-        <v>165</v>
-      </c>
-      <c r="F48">
-        <v>5</v>
-      </c>
-      <c r="G48">
-        <v>9</v>
-      </c>
-      <c r="H48">
-        <v>13.5</v>
-      </c>
-      <c r="I48">
-        <v>1.5</v>
-      </c>
-      <c r="J48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" s="23">
-        <v>46023</v>
-      </c>
-      <c r="B49" s="24">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="C49" t="s">
-        <v>1022</v>
-      </c>
-      <c r="D49" t="s">
-        <v>102</v>
-      </c>
-      <c r="E49">
-        <v>77</v>
-      </c>
-      <c r="F49">
-        <v>2</v>
-      </c>
-      <c r="G49">
-        <v>11</v>
-      </c>
-      <c r="H49">
-        <v>2</v>
-      </c>
-      <c r="I49">
-        <v>7</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="23">
-        <v>46023</v>
-      </c>
-      <c r="B50" s="24">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="C50" t="s">
-        <v>1023</v>
-      </c>
-      <c r="D50" t="s">
-        <v>1021</v>
-      </c>
-      <c r="E50">
-        <v>165</v>
-      </c>
-      <c r="F50">
-        <v>5</v>
-      </c>
-      <c r="G50">
-        <v>9</v>
-      </c>
-      <c r="H50">
-        <v>13.5</v>
-      </c>
-      <c r="I50">
-        <v>1.5</v>
-      </c>
-      <c r="J50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="23">
-        <v>46023</v>
-      </c>
-      <c r="B51" s="24">
-        <v>0.375</v>
-      </c>
-      <c r="C51" t="s">
-        <v>1024</v>
-      </c>
-      <c r="D51" t="s">
-        <v>258</v>
-      </c>
-      <c r="E51">
-        <v>128</v>
-      </c>
-      <c r="F51">
-        <v>6.6</v>
-      </c>
-      <c r="G51">
-        <v>9.6</v>
-      </c>
-      <c r="H51">
-        <v>5.3</v>
-      </c>
-      <c r="I51">
-        <v>5.3</v>
-      </c>
-      <c r="J51">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="23">
-        <v>46023</v>
-      </c>
-      <c r="B52" s="24">
-        <v>0.4375</v>
-      </c>
-      <c r="C52" t="s">
-        <v>1025</v>
-      </c>
-      <c r="D52" t="s">
-        <v>102</v>
-      </c>
-      <c r="E52">
-        <v>77</v>
-      </c>
-      <c r="F52">
-        <v>2</v>
-      </c>
-      <c r="G52">
-        <v>11</v>
-      </c>
-      <c r="H52">
-        <v>2</v>
-      </c>
-      <c r="I52">
-        <v>7</v>
-      </c>
-      <c r="J52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" s="23">
-        <v>46023</v>
-      </c>
-      <c r="B53" s="24">
-        <v>0.5</v>
-      </c>
-      <c r="C53" t="s">
-        <v>1026</v>
-      </c>
-      <c r="D53" t="s">
-        <v>32</v>
-      </c>
-      <c r="E53">
-        <v>290</v>
-      </c>
-      <c r="F53">
-        <v>11</v>
-      </c>
-      <c r="G53">
-        <v>18</v>
-      </c>
-      <c r="H53">
-        <v>18</v>
-      </c>
-      <c r="I53">
-        <v>0</v>
-      </c>
-      <c r="J53">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" s="23">
-        <v>46023</v>
-      </c>
-      <c r="B54" s="24">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="C54" t="s">
-        <v>1027</v>
-      </c>
-      <c r="D54" t="s">
-        <v>258</v>
-      </c>
-      <c r="E54">
-        <v>128</v>
-      </c>
-      <c r="F54">
-        <v>6.6</v>
-      </c>
-      <c r="G54">
-        <v>9.6</v>
-      </c>
-      <c r="H54">
-        <v>5.3</v>
-      </c>
-      <c r="I54">
-        <v>5.3</v>
-      </c>
-      <c r="J54">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="23">
-        <v>46023</v>
-      </c>
-      <c r="B55" s="24">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="C55" t="s">
-        <v>1028</v>
-      </c>
-      <c r="D55" t="s">
-        <v>116</v>
-      </c>
-      <c r="E55">
-        <v>155</v>
-      </c>
-      <c r="F55">
-        <v>15.5</v>
-      </c>
-      <c r="G55">
-        <v>15</v>
-      </c>
-      <c r="H55">
-        <v>2</v>
-      </c>
-      <c r="I55">
-        <v>7</v>
-      </c>
-      <c r="J55">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56" s="23">
-        <v>46023</v>
-      </c>
-      <c r="B56" s="24">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="C56" t="s">
-        <v>1029</v>
-      </c>
-      <c r="D56" t="s">
-        <v>808</v>
-      </c>
-      <c r="E56">
-        <v>145</v>
-      </c>
-      <c r="F56">
-        <v>5.5</v>
-      </c>
-      <c r="G56">
-        <v>9</v>
-      </c>
-      <c r="H56">
-        <v>9</v>
-      </c>
-      <c r="I56">
-        <v>0</v>
-      </c>
-      <c r="J56">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" s="23">
-        <v>46023</v>
-      </c>
-      <c r="B57" s="24">
-        <v>0.75</v>
-      </c>
-      <c r="C57" t="s">
-        <v>1030</v>
-      </c>
-      <c r="D57" t="s">
-        <v>932</v>
-      </c>
-      <c r="E57">
-        <v>335</v>
-      </c>
-      <c r="F57">
-        <v>21</v>
-      </c>
-      <c r="G57">
-        <v>33</v>
-      </c>
-      <c r="H57">
-        <v>13</v>
-      </c>
-      <c r="I57">
-        <v>2.5</v>
-      </c>
-      <c r="J57">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" s="23">
-        <v>46023</v>
-      </c>
-      <c r="B58" s="24">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="C58" t="s">
-        <v>1031</v>
-      </c>
-      <c r="D58" t="s">
-        <v>1032</v>
-      </c>
-      <c r="E58">
-        <v>155</v>
-      </c>
-      <c r="F58">
-        <v>3</v>
-      </c>
-      <c r="G58">
-        <v>22.5</v>
-      </c>
-      <c r="H58">
-        <v>6</v>
-      </c>
-      <c r="I58">
-        <v>5.5</v>
-      </c>
-      <c r="J58">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59" s="23">
-        <v>46023</v>
-      </c>
-      <c r="B59" s="24">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C59" t="s">
-        <v>1033</v>
-      </c>
-      <c r="D59" t="s">
-        <v>1034</v>
-      </c>
-      <c r="E59">
-        <v>136.5</v>
-      </c>
-      <c r="F59">
-        <v>3.4</v>
-      </c>
-      <c r="G59">
-        <v>27.3</v>
-      </c>
-      <c r="H59">
-        <v>0.9</v>
-      </c>
-      <c r="I59">
-        <v>18.2</v>
-      </c>
-      <c r="J59">
-        <v>10.4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A60" s="23">
-        <v>46023</v>
-      </c>
-      <c r="B60" s="24">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="C60" t="s">
-        <v>1035</v>
-      </c>
-      <c r="D60" t="s">
-        <v>1032</v>
-      </c>
-      <c r="E60">
-        <v>155</v>
-      </c>
-      <c r="F60">
-        <v>3</v>
-      </c>
-      <c r="G60">
-        <v>22.5</v>
-      </c>
-      <c r="H60">
-        <v>6</v>
-      </c>
-      <c r="I60">
-        <v>5.5</v>
-      </c>
-      <c r="J60">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A61" s="23">
-        <v>46024</v>
-      </c>
-      <c r="B61" s="24">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="C61" t="s">
-        <v>1036</v>
-      </c>
-      <c r="D61" t="s">
-        <v>102</v>
-      </c>
-      <c r="E61">
-        <v>77</v>
-      </c>
-      <c r="F61">
-        <v>2</v>
-      </c>
-      <c r="G61">
-        <v>11</v>
-      </c>
-      <c r="H61">
-        <v>2</v>
-      </c>
-      <c r="I61">
-        <v>7</v>
-      </c>
-      <c r="J61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A62" s="23">
-        <v>46024</v>
-      </c>
-      <c r="B62" s="24">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="C62" t="s">
-        <v>1037</v>
-      </c>
-      <c r="D62" t="s">
-        <v>1021</v>
-      </c>
-      <c r="E62">
-        <v>165</v>
-      </c>
-      <c r="F62">
-        <v>5</v>
-      </c>
-      <c r="G62">
-        <v>9</v>
-      </c>
-      <c r="H62">
-        <v>13.5</v>
-      </c>
-      <c r="I62">
-        <v>1.5</v>
-      </c>
-      <c r="J62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A63" s="23">
-        <v>46024</v>
-      </c>
-      <c r="B63" s="24">
-        <v>0.375</v>
-      </c>
-      <c r="C63" t="s">
-        <v>1038</v>
-      </c>
-      <c r="D63" t="s">
-        <v>258</v>
-      </c>
-      <c r="E63">
-        <v>128</v>
-      </c>
-      <c r="F63">
-        <v>6.6</v>
-      </c>
-      <c r="G63">
-        <v>9.6</v>
-      </c>
-      <c r="H63">
-        <v>5.3</v>
-      </c>
-      <c r="I63">
-        <v>5.3</v>
-      </c>
-      <c r="J63">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A64" s="23">
-        <v>46024</v>
-      </c>
-      <c r="B64" s="24">
-        <v>0.5625</v>
-      </c>
-      <c r="C64" t="s">
-        <v>1039</v>
-      </c>
-      <c r="D64" t="s">
-        <v>32</v>
-      </c>
-      <c r="E64">
-        <v>290</v>
-      </c>
-      <c r="F64">
-        <v>11</v>
-      </c>
-      <c r="G64">
-        <v>18</v>
-      </c>
-      <c r="H64">
-        <v>18</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="J64">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A65" s="23">
-        <v>46024</v>
-      </c>
-      <c r="B65" s="24">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="C65" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D65" t="s">
-        <v>808</v>
-      </c>
-      <c r="E65">
-        <v>145</v>
-      </c>
-      <c r="F65">
-        <v>5.5</v>
-      </c>
-      <c r="G65">
-        <v>9</v>
-      </c>
-      <c r="H65">
-        <v>9</v>
-      </c>
-      <c r="I65">
-        <v>0</v>
-      </c>
-      <c r="J65">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A66" s="23">
-        <v>46024</v>
-      </c>
-      <c r="B66" s="24">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C66" t="s">
-        <v>1041</v>
-      </c>
-      <c r="D66" t="s">
-        <v>1042</v>
-      </c>
-      <c r="E66">
-        <v>800</v>
-      </c>
-      <c r="F66">
-        <v>40</v>
-      </c>
-      <c r="G66">
-        <v>100</v>
-      </c>
-      <c r="H66">
-        <v>25</v>
-      </c>
-      <c r="I66">
-        <v>5</v>
-      </c>
-      <c r="J66">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A67" s="23">
-        <v>46024</v>
-      </c>
-      <c r="B67" s="24">
-        <v>0.8125</v>
-      </c>
-      <c r="C67" t="s">
-        <v>1043</v>
-      </c>
-      <c r="D67" t="s">
-        <v>365</v>
-      </c>
-      <c r="E67">
-        <v>256</v>
-      </c>
-      <c r="F67">
-        <v>13.2</v>
-      </c>
-      <c r="G67">
-        <v>19.2</v>
-      </c>
-      <c r="H67">
-        <v>10.6</v>
-      </c>
-      <c r="I67">
-        <v>10.6</v>
-      </c>
-      <c r="J67">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A68" s="23">
-        <v>46025</v>
-      </c>
-      <c r="B68" s="24">
-        <v>0.375</v>
-      </c>
-      <c r="C68" t="s">
-        <v>1044</v>
-      </c>
-      <c r="D68" t="s">
-        <v>102</v>
-      </c>
-      <c r="E68">
-        <v>77</v>
-      </c>
-      <c r="F68">
-        <v>2</v>
-      </c>
-      <c r="G68">
-        <v>11</v>
-      </c>
-      <c r="H68">
-        <v>2</v>
-      </c>
-      <c r="I68">
-        <v>7</v>
-      </c>
-      <c r="J68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A69" s="23">
-        <v>46025</v>
-      </c>
-      <c r="B69" s="24">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="C69" t="s">
-        <v>1045</v>
-      </c>
-      <c r="D69" t="s">
-        <v>258</v>
-      </c>
-      <c r="E69">
-        <v>128</v>
-      </c>
-      <c r="F69">
-        <v>6.6</v>
-      </c>
-      <c r="G69">
-        <v>9.6</v>
-      </c>
-      <c r="H69">
-        <v>5.3</v>
-      </c>
-      <c r="I69">
-        <v>5.3</v>
-      </c>
-      <c r="J69">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A70" s="23">
-        <v>46025</v>
-      </c>
-      <c r="B70" s="24">
-        <v>0.5</v>
-      </c>
-      <c r="C70" t="s">
-        <v>1046</v>
-      </c>
-      <c r="D70" t="s">
-        <v>32</v>
-      </c>
-      <c r="E70">
-        <v>290</v>
-      </c>
-      <c r="F70">
-        <v>11</v>
-      </c>
-      <c r="G70">
-        <v>18</v>
-      </c>
-      <c r="H70">
-        <v>18</v>
-      </c>
-      <c r="I70">
-        <v>0</v>
-      </c>
-      <c r="J70">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A71" s="23">
-        <v>46025</v>
-      </c>
-      <c r="B71" s="24">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="C71" t="s">
-        <v>1047</v>
-      </c>
-      <c r="D71" t="s">
-        <v>98</v>
-      </c>
-      <c r="E71">
-        <v>380</v>
-      </c>
-      <c r="F71">
-        <v>25</v>
-      </c>
-      <c r="G71">
-        <v>46</v>
-      </c>
-      <c r="H71">
-        <v>10</v>
-      </c>
-      <c r="I71">
-        <v>2</v>
-      </c>
-      <c r="J71">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A72" s="23">
-        <v>46025</v>
-      </c>
-      <c r="B72" s="24">
-        <v>0.5625</v>
-      </c>
-      <c r="C72" t="s">
-        <v>1048</v>
-      </c>
-      <c r="D72" t="s">
-        <v>116</v>
-      </c>
-      <c r="E72">
-        <v>155</v>
-      </c>
-      <c r="F72">
-        <v>15.5</v>
-      </c>
-      <c r="G72">
-        <v>15</v>
-      </c>
-      <c r="H72">
-        <v>2</v>
-      </c>
-      <c r="I72">
-        <v>7</v>
-      </c>
-      <c r="J72">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A73" s="23">
-        <v>46025</v>
-      </c>
-      <c r="B73" s="24">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="C73" t="s">
-        <v>1049</v>
-      </c>
-      <c r="D73" t="s">
-        <v>102</v>
-      </c>
-      <c r="E73">
-        <v>77</v>
-      </c>
-      <c r="F73">
-        <v>2</v>
-      </c>
-      <c r="G73">
-        <v>11</v>
-      </c>
-      <c r="H73">
-        <v>2</v>
-      </c>
-      <c r="I73">
-        <v>7</v>
-      </c>
-      <c r="J73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A74" s="23">
-        <v>46025</v>
-      </c>
-      <c r="B74" s="24">
-        <v>0.6875</v>
-      </c>
-      <c r="C74" t="s">
-        <v>1050</v>
-      </c>
-      <c r="D74" t="s">
-        <v>808</v>
-      </c>
-      <c r="E74">
-        <v>145</v>
-      </c>
-      <c r="F74">
-        <v>5.5</v>
-      </c>
-      <c r="G74">
-        <v>9</v>
-      </c>
-      <c r="H74">
-        <v>9</v>
-      </c>
-      <c r="I74">
-        <v>0</v>
-      </c>
-      <c r="J74">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A75" s="23">
-        <v>46025</v>
-      </c>
-      <c r="B75" s="24">
-        <v>0.75</v>
-      </c>
-      <c r="C75" t="s">
-        <v>1051</v>
-      </c>
-      <c r="D75" t="s">
-        <v>932</v>
-      </c>
-      <c r="E75">
-        <v>335</v>
-      </c>
-      <c r="F75">
-        <v>21</v>
-      </c>
-      <c r="G75">
-        <v>33</v>
-      </c>
-      <c r="H75">
-        <v>13</v>
-      </c>
-      <c r="I75">
-        <v>2.5</v>
-      </c>
-      <c r="J75">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A76" s="23">
-        <v>46025</v>
-      </c>
-      <c r="B76" s="24">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="C76" t="s">
-        <v>1052</v>
-      </c>
-      <c r="D76" t="s">
-        <v>116</v>
-      </c>
-      <c r="E76">
-        <v>155</v>
-      </c>
-      <c r="F76">
-        <v>15.5</v>
-      </c>
-      <c r="G76">
-        <v>15</v>
-      </c>
-      <c r="H76">
-        <v>2</v>
-      </c>
-      <c r="I76">
-        <v>7</v>
-      </c>
-      <c r="J76">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A77" s="23">
-        <v>46025</v>
-      </c>
-      <c r="B77" s="24">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C77" t="s">
-        <v>1053</v>
-      </c>
-      <c r="D77" t="s">
-        <v>205</v>
-      </c>
-      <c r="E77">
-        <v>78.75</v>
-      </c>
-      <c r="F77">
-        <v>1.95</v>
-      </c>
-      <c r="G77">
-        <v>16.8</v>
-      </c>
-      <c r="H77">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="I77">
-        <v>11.25</v>
-      </c>
-      <c r="J77">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A78" s="23">
-        <v>46025</v>
-      </c>
-      <c r="B78" s="24">
-        <v>0.875</v>
-      </c>
-      <c r="C78" t="s">
-        <v>1054</v>
-      </c>
-      <c r="D78" t="s">
-        <v>205</v>
-      </c>
-      <c r="E78">
-        <v>78.75</v>
-      </c>
-      <c r="F78">
-        <v>1.95</v>
-      </c>
-      <c r="G78">
-        <v>16.8</v>
-      </c>
-      <c r="H78">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="I78">
-        <v>11.25</v>
-      </c>
-      <c r="J78">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A79" s="23">
-        <v>46025</v>
-      </c>
-      <c r="B79" s="24">
-        <v>0.89583333333333337</v>
-      </c>
-      <c r="C79" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D79" t="s">
-        <v>1056</v>
-      </c>
-      <c r="E79">
-        <v>165</v>
-      </c>
-      <c r="F79">
-        <v>5</v>
-      </c>
-      <c r="G79">
-        <v>9</v>
-      </c>
-      <c r="H79">
-        <v>13.5</v>
-      </c>
-      <c r="I79">
-        <v>1.5</v>
-      </c>
-      <c r="J79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A80" s="23">
-        <v>46026</v>
-      </c>
-      <c r="B80" s="24">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="C80" t="s">
-        <v>1057</v>
-      </c>
-      <c r="D80" t="s">
-        <v>102</v>
-      </c>
-      <c r="E80">
-        <v>77</v>
-      </c>
-      <c r="F80">
-        <v>2</v>
-      </c>
-      <c r="G80">
-        <v>11</v>
-      </c>
-      <c r="H80">
-        <v>2</v>
-      </c>
-      <c r="I80">
-        <v>7</v>
-      </c>
-      <c r="J80">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A81" s="23">
-        <v>46026</v>
-      </c>
-      <c r="B81" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="C81" t="s">
-        <v>1058</v>
-      </c>
-      <c r="D81" t="s">
-        <v>1059</v>
-      </c>
-      <c r="E81">
-        <v>300</v>
-      </c>
-      <c r="F81">
-        <v>5</v>
-      </c>
-      <c r="G81">
-        <v>30</v>
-      </c>
-      <c r="H81">
-        <v>15</v>
-      </c>
-      <c r="I81">
-        <v>5</v>
-      </c>
-      <c r="J81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A82" s="23">
-        <v>46026</v>
-      </c>
-      <c r="B82" s="24">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="C82" t="s">
-        <v>1060</v>
-      </c>
-      <c r="D82" t="s">
-        <v>32</v>
-      </c>
-      <c r="E82">
-        <v>290</v>
-      </c>
-      <c r="F82">
-        <v>11</v>
-      </c>
-      <c r="G82">
-        <v>18</v>
-      </c>
-      <c r="H82">
-        <v>18</v>
-      </c>
-      <c r="I82">
-        <v>0</v>
-      </c>
-      <c r="J82">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A83" s="23">
-        <v>46026</v>
-      </c>
-      <c r="B83" s="24">
-        <v>0.5625</v>
-      </c>
-      <c r="C83" t="s">
-        <v>1061</v>
-      </c>
-      <c r="D83" t="s">
-        <v>1062</v>
-      </c>
-      <c r="E83">
-        <v>335</v>
-      </c>
-      <c r="F83">
-        <v>20</v>
-      </c>
-      <c r="G83">
-        <v>40</v>
-      </c>
-      <c r="H83">
-        <v>10</v>
-      </c>
-      <c r="I83">
-        <v>2</v>
-      </c>
-      <c r="J83">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A84" s="23">
-        <v>46026</v>
-      </c>
-      <c r="B84" s="24">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="C84" t="s">
-        <v>1063</v>
-      </c>
-      <c r="D84" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E84">
-        <v>310</v>
-      </c>
-      <c r="F84">
-        <v>6</v>
-      </c>
-      <c r="G84">
-        <v>45</v>
-      </c>
-      <c r="H84">
-        <v>12</v>
-      </c>
-      <c r="I84">
-        <v>11</v>
-      </c>
-      <c r="J84">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A85" s="23">
-        <v>46026</v>
-      </c>
-      <c r="B85" s="24">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="C85" t="s">
-        <v>1065</v>
-      </c>
-      <c r="D85" t="s">
-        <v>116</v>
-      </c>
-      <c r="E85">
-        <v>155</v>
-      </c>
-      <c r="F85">
-        <v>15.5</v>
-      </c>
-      <c r="G85">
-        <v>15</v>
-      </c>
-      <c r="H85">
-        <v>2</v>
-      </c>
-      <c r="I85">
-        <v>7</v>
-      </c>
-      <c r="J85">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A86" s="23">
-        <v>46026</v>
-      </c>
-      <c r="B86" s="24">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="C86" t="s">
-        <v>1066</v>
-      </c>
-      <c r="D86" t="s">
-        <v>102</v>
-      </c>
-      <c r="E86">
-        <v>77</v>
-      </c>
-      <c r="F86">
-        <v>2</v>
-      </c>
-      <c r="G86">
-        <v>11</v>
-      </c>
-      <c r="H86">
-        <v>2</v>
-      </c>
-      <c r="I86">
-        <v>7</v>
-      </c>
-      <c r="J86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A87" s="23">
-        <v>46026</v>
-      </c>
-      <c r="B87" s="24">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="C87" t="s">
-        <v>1067</v>
-      </c>
-      <c r="D87" t="s">
-        <v>1068</v>
-      </c>
-      <c r="E87">
-        <v>567</v>
-      </c>
-      <c r="F87">
-        <v>43.3</v>
-      </c>
-      <c r="G87">
-        <v>40</v>
-      </c>
-      <c r="H87">
-        <v>23.3</v>
-      </c>
-      <c r="I87">
-        <v>3.3</v>
-      </c>
-      <c r="J87">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A88" s="23">
-        <v>46026</v>
-      </c>
-      <c r="B88" s="24">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C88" t="s">
-        <v>1069</v>
-      </c>
-      <c r="D88" t="s">
-        <v>116</v>
-      </c>
-      <c r="E88">
-        <v>155</v>
-      </c>
-      <c r="F88">
-        <v>15.5</v>
-      </c>
-      <c r="G88">
-        <v>15</v>
-      </c>
-      <c r="H88">
-        <v>2</v>
-      </c>
-      <c r="I88">
-        <v>7</v>
-      </c>
-      <c r="J88">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A89" s="23">
-        <v>46027</v>
-      </c>
-      <c r="B89" s="24">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="C89" t="s">
-        <v>1070</v>
-      </c>
-      <c r="D89" t="s">
-        <v>116</v>
-      </c>
-      <c r="E89">
-        <v>155</v>
-      </c>
-      <c r="F89">
-        <v>15.5</v>
-      </c>
-      <c r="G89">
-        <v>15</v>
-      </c>
-      <c r="H89">
-        <v>2</v>
-      </c>
-      <c r="I89">
-        <v>7</v>
-      </c>
-      <c r="J89">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A90" s="23">
-        <v>46027</v>
-      </c>
-      <c r="B90" s="24">
-        <v>0.375</v>
-      </c>
-      <c r="C90" t="s">
-        <v>1071</v>
-      </c>
-      <c r="D90" t="s">
-        <v>102</v>
-      </c>
-      <c r="E90">
-        <v>77</v>
-      </c>
-      <c r="F90">
-        <v>2</v>
-      </c>
-      <c r="G90">
-        <v>11</v>
-      </c>
-      <c r="H90">
-        <v>2</v>
-      </c>
-      <c r="I90">
-        <v>7</v>
-      </c>
-      <c r="J90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A91" s="23">
-        <v>46027</v>
-      </c>
-      <c r="B91" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="C91" t="s">
-        <v>1072</v>
-      </c>
-      <c r="D91" t="s">
-        <v>808</v>
-      </c>
-      <c r="E91">
-        <v>145</v>
-      </c>
-      <c r="F91">
-        <v>5.5</v>
-      </c>
-      <c r="G91">
-        <v>9</v>
-      </c>
-      <c r="H91">
-        <v>9</v>
-      </c>
-      <c r="I91">
-        <v>0</v>
-      </c>
-      <c r="J91">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A92" s="23">
-        <v>46027</v>
-      </c>
-      <c r="B92" s="24">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="C92" t="s">
-        <v>1073</v>
-      </c>
-      <c r="D92" t="s">
-        <v>372</v>
-      </c>
-      <c r="E92">
-        <v>89</v>
-      </c>
-      <c r="F92">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="G92">
-        <v>23</v>
-      </c>
-      <c r="H92">
-        <v>0.3</v>
-      </c>
-      <c r="I92">
-        <v>12</v>
-      </c>
-      <c r="J92">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A93" s="23">
-        <v>46027</v>
-      </c>
-      <c r="B93" s="24">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="C93" t="s">
-        <v>1074</v>
-      </c>
-      <c r="D93" t="s">
-        <v>932</v>
-      </c>
-      <c r="E93">
-        <v>335</v>
-      </c>
-      <c r="F93">
-        <v>21</v>
-      </c>
-      <c r="G93">
-        <v>33</v>
-      </c>
-      <c r="H93">
-        <v>13</v>
-      </c>
-      <c r="I93">
-        <v>2.5</v>
-      </c>
-      <c r="J93">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A94" s="23">
-        <v>46027</v>
-      </c>
-      <c r="B94" s="24">
-        <v>0.5625</v>
-      </c>
-      <c r="C94" t="s">
-        <v>1075</v>
-      </c>
-      <c r="D94" t="s">
-        <v>205</v>
-      </c>
-      <c r="E94">
-        <v>78.75</v>
-      </c>
-      <c r="F94">
-        <v>1.95</v>
-      </c>
-      <c r="G94">
-        <v>16.8</v>
-      </c>
-      <c r="H94">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="I94">
-        <v>11.25</v>
-      </c>
-      <c r="J94">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A95" s="23">
-        <v>46027</v>
-      </c>
-      <c r="B95" s="24">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="C95" t="s">
-        <v>1076</v>
-      </c>
-      <c r="D95" t="s">
-        <v>1021</v>
-      </c>
-      <c r="E95">
-        <v>165</v>
-      </c>
-      <c r="F95">
-        <v>5</v>
-      </c>
-      <c r="G95">
-        <v>9</v>
-      </c>
-      <c r="H95">
-        <v>13.5</v>
-      </c>
-      <c r="I95">
-        <v>1.5</v>
-      </c>
-      <c r="J95">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A96" s="23">
-        <v>46027</v>
-      </c>
-      <c r="B96" s="24">
-        <v>0.625</v>
-      </c>
-      <c r="C96" t="s">
-        <v>1077</v>
-      </c>
-      <c r="D96" t="s">
-        <v>808</v>
-      </c>
-      <c r="E96">
-        <v>145</v>
-      </c>
-      <c r="F96">
-        <v>5.5</v>
-      </c>
-      <c r="G96">
-        <v>9</v>
-      </c>
-      <c r="H96">
-        <v>9</v>
-      </c>
-      <c r="I96">
-        <v>0</v>
-      </c>
-      <c r="J96">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A97" s="23">
-        <v>46027</v>
-      </c>
-      <c r="B97" s="24">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="C97" t="s">
-        <v>1078</v>
-      </c>
-      <c r="D97" t="s">
-        <v>116</v>
-      </c>
-      <c r="E97">
-        <v>155</v>
-      </c>
-      <c r="F97">
-        <v>15.5</v>
-      </c>
-      <c r="G97">
-        <v>15</v>
-      </c>
-      <c r="H97">
-        <v>2</v>
-      </c>
-      <c r="I97">
-        <v>7</v>
-      </c>
-      <c r="J97">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A98" s="23">
-        <v>46027</v>
-      </c>
-      <c r="B98" s="24">
-        <v>0.6875</v>
-      </c>
-      <c r="C98" t="s">
-        <v>1079</v>
-      </c>
-      <c r="D98" t="s">
-        <v>258</v>
-      </c>
-      <c r="E98">
-        <v>128</v>
-      </c>
-      <c r="F98">
-        <v>6.6</v>
-      </c>
-      <c r="G98">
-        <v>9.6</v>
-      </c>
-      <c r="H98">
-        <v>5.3</v>
-      </c>
-      <c r="I98">
-        <v>5.3</v>
-      </c>
-      <c r="J98">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A99" s="23">
-        <v>46027</v>
-      </c>
-      <c r="B99" s="24">
-        <v>0.75</v>
-      </c>
-      <c r="C99" t="s">
-        <v>1080</v>
-      </c>
-      <c r="D99" t="s">
-        <v>1081</v>
-      </c>
-      <c r="E99">
-        <v>440</v>
-      </c>
-      <c r="F99">
-        <v>22</v>
-      </c>
-      <c r="G99">
-        <v>50</v>
-      </c>
-      <c r="H99">
-        <v>16</v>
-      </c>
-      <c r="I99">
-        <v>3</v>
-      </c>
-      <c r="J99">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A100" s="23">
-        <v>46027</v>
-      </c>
-      <c r="B100" s="24">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="C100" t="s">
-        <v>1082</v>
-      </c>
-      <c r="D100" t="s">
-        <v>1083</v>
-      </c>
-      <c r="E100">
-        <v>240</v>
-      </c>
-      <c r="F100">
-        <v>16</v>
-      </c>
-      <c r="G100">
-        <v>20</v>
-      </c>
-      <c r="H100">
-        <v>12</v>
-      </c>
-      <c r="I100">
-        <v>20</v>
-      </c>
-      <c r="J100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A101" s="23">
-        <v>46028</v>
-      </c>
-      <c r="B101" s="24">
-        <v>0.375</v>
-      </c>
-      <c r="C101" t="s">
-        <v>1084</v>
-      </c>
-      <c r="D101" t="s">
-        <v>1085</v>
-      </c>
-      <c r="E101">
-        <v>450</v>
-      </c>
-      <c r="F101">
-        <v>12</v>
-      </c>
-      <c r="G101">
-        <v>48.5</v>
-      </c>
-      <c r="H101">
-        <v>27.8</v>
-      </c>
-      <c r="I101">
-        <v>3.9</v>
-      </c>
-      <c r="J101">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A102" s="23">
-        <v>46028</v>
-      </c>
-      <c r="B102" s="24">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="C102" t="s">
-        <v>1086</v>
-      </c>
-      <c r="D102" t="s">
-        <v>27</v>
-      </c>
-      <c r="E102">
-        <v>210</v>
-      </c>
-      <c r="F102">
-        <v>5.2</v>
-      </c>
-      <c r="G102">
-        <v>42</v>
-      </c>
-      <c r="H102">
-        <v>1.4</v>
-      </c>
-      <c r="I102">
-        <v>28</v>
-      </c>
-      <c r="J102">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A103" s="23">
-        <v>46028</v>
-      </c>
-      <c r="B103" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="C103" t="s">
-        <v>1087</v>
-      </c>
-      <c r="D103" t="s">
-        <v>365</v>
-      </c>
-      <c r="E103">
-        <v>256</v>
-      </c>
-      <c r="F103">
-        <v>13.2</v>
-      </c>
-      <c r="G103">
-        <v>19.2</v>
-      </c>
-      <c r="H103">
-        <v>10.6</v>
-      </c>
-      <c r="I103">
-        <v>10.6</v>
-      </c>
-      <c r="J103">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A104" s="23">
-        <v>46028</v>
-      </c>
-      <c r="B104" s="24">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="C104" t="s">
-        <v>1088</v>
-      </c>
-      <c r="D104" t="s">
-        <v>932</v>
-      </c>
-      <c r="E104">
-        <v>335</v>
-      </c>
-      <c r="F104">
-        <v>21</v>
-      </c>
-      <c r="G104">
-        <v>33</v>
-      </c>
-      <c r="H104">
-        <v>13</v>
-      </c>
-      <c r="I104">
-        <v>2.5</v>
-      </c>
-      <c r="J104">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A105" s="23">
-        <v>46028</v>
-      </c>
-      <c r="B105" s="24">
-        <v>0.5625</v>
-      </c>
-      <c r="C105" t="s">
-        <v>1089</v>
-      </c>
-      <c r="D105" t="s">
-        <v>1021</v>
-      </c>
-      <c r="E105">
-        <v>165</v>
-      </c>
-      <c r="F105">
-        <v>5</v>
-      </c>
-      <c r="G105">
-        <v>9</v>
-      </c>
-      <c r="H105">
-        <v>13.5</v>
-      </c>
-      <c r="I105">
-        <v>1.5</v>
-      </c>
-      <c r="J105">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A106" s="23">
-        <v>46028</v>
-      </c>
-      <c r="B106" s="24">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="C106" t="s">
-        <v>1090</v>
-      </c>
-      <c r="D106" t="s">
-        <v>1091</v>
-      </c>
-      <c r="E106">
-        <v>263.3</v>
-      </c>
-      <c r="F106">
-        <v>2.8</v>
-      </c>
-      <c r="G106">
-        <v>30.5</v>
-      </c>
-      <c r="H106">
-        <v>14.7</v>
-      </c>
-      <c r="I106">
-        <v>3</v>
-      </c>
-      <c r="J106">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A107" s="23">
-        <v>46028</v>
-      </c>
-      <c r="B107" s="24">
-        <v>0.75</v>
-      </c>
-      <c r="C107" t="s">
-        <v>1092</v>
-      </c>
-      <c r="D107" t="s">
-        <v>372</v>
-      </c>
-      <c r="E107">
-        <v>89</v>
-      </c>
-      <c r="F107">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="G107">
-        <v>23</v>
-      </c>
-      <c r="H107">
-        <v>0.3</v>
-      </c>
-      <c r="I107">
-        <v>12</v>
-      </c>
-      <c r="J107">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A108" s="23">
-        <v>46028</v>
-      </c>
-      <c r="B108" s="24">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="C108" t="s">
-        <v>1093</v>
-      </c>
-      <c r="D108" t="s">
-        <v>102</v>
-      </c>
-      <c r="E108">
-        <v>77</v>
-      </c>
-      <c r="F108">
-        <v>2</v>
-      </c>
-      <c r="G108">
-        <v>11</v>
-      </c>
-      <c r="H108">
-        <v>2</v>
-      </c>
-      <c r="I108">
-        <v>7</v>
-      </c>
-      <c r="J108">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A109" s="23">
-        <v>46028</v>
-      </c>
-      <c r="B109" s="24">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C109" t="s">
-        <v>1094</v>
-      </c>
-      <c r="D109" t="s">
-        <v>1095</v>
-      </c>
-      <c r="E109">
-        <v>300</v>
-      </c>
-      <c r="F109">
-        <v>25</v>
-      </c>
-      <c r="G109">
-        <v>20</v>
-      </c>
-      <c r="H109">
-        <v>15</v>
-      </c>
-      <c r="I109">
-        <v>3</v>
-      </c>
-      <c r="J109">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A110" s="23">
-        <v>46028</v>
-      </c>
-      <c r="B110" s="24">
-        <v>0.8125</v>
-      </c>
-      <c r="C110" t="s">
-        <v>1096</v>
-      </c>
-      <c r="D110" t="s">
-        <v>1021</v>
-      </c>
-      <c r="E110">
-        <v>165</v>
-      </c>
-      <c r="F110">
-        <v>5</v>
-      </c>
-      <c r="G110">
-        <v>9</v>
-      </c>
-      <c r="H110">
-        <v>13.5</v>
-      </c>
-      <c r="I110">
-        <v>1.5</v>
-      </c>
-      <c r="J110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A111" s="23">
-        <v>46028</v>
-      </c>
-      <c r="B111" s="24">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="C111" t="s">
-        <v>1097</v>
-      </c>
-      <c r="D111" t="s">
-        <v>1091</v>
-      </c>
-      <c r="E111">
-        <v>263.3</v>
-      </c>
-      <c r="F111">
-        <v>2.8</v>
-      </c>
-      <c r="G111">
-        <v>30.5</v>
-      </c>
-      <c r="H111">
-        <v>14.7</v>
-      </c>
-      <c r="I111">
-        <v>3</v>
-      </c>
-      <c r="J111">
-        <v>1.3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F3DAC15-C829-4324-82D7-B0DBA610DC6A}">
-  <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>858</v>
-      </c>
-      <c r="C2" t="s">
-        <v>859</v>
-      </c>
-      <c r="D2" t="s">
-        <v>860</v>
-      </c>
-      <c r="E2">
-        <v>1962</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>861</v>
-      </c>
-      <c r="C3" t="s">
-        <v>862</v>
-      </c>
-      <c r="D3" t="s">
-        <v>860</v>
-      </c>
-      <c r="E3">
-        <v>2269</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>863</v>
-      </c>
-      <c r="C4" t="s">
-        <v>864</v>
-      </c>
-      <c r="D4" t="s">
-        <v>860</v>
-      </c>
-      <c r="E4">
-        <v>1728</v>
-      </c>
-      <c r="F4">
-        <v>50</v>
-      </c>
-      <c r="G4">
-        <v>236</v>
-      </c>
-      <c r="H4">
-        <v>67</v>
-      </c>
-      <c r="I4">
-        <v>61</v>
-      </c>
-      <c r="J4">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>865</v>
-      </c>
-      <c r="C5" t="s">
-        <v>866</v>
-      </c>
-      <c r="D5" t="s">
-        <v>860</v>
-      </c>
-      <c r="E5">
-        <v>2009</v>
-      </c>
-      <c r="F5">
-        <v>99</v>
-      </c>
-      <c r="G5">
-        <v>234</v>
-      </c>
-      <c r="H5">
-        <v>77</v>
-      </c>
-      <c r="I5">
-        <v>74</v>
-      </c>
-      <c r="J5">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>867</v>
-      </c>
-      <c r="C6" t="s">
-        <v>868</v>
-      </c>
-      <c r="D6" t="s">
-        <v>860</v>
-      </c>
-      <c r="E6">
-        <v>1682</v>
-      </c>
-      <c r="F6">
-        <v>64</v>
-      </c>
-      <c r="G6">
-        <v>229</v>
-      </c>
-      <c r="H6">
-        <v>56</v>
-      </c>
-      <c r="I6">
-        <v>64</v>
-      </c>
-      <c r="J6">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>869</v>
-      </c>
-      <c r="C7" t="s">
-        <v>870</v>
-      </c>
-      <c r="D7" t="s">
-        <v>860</v>
-      </c>
-      <c r="E7">
-        <v>2221</v>
-      </c>
-      <c r="F7">
-        <v>75</v>
-      </c>
-      <c r="G7">
-        <v>260</v>
-      </c>
-      <c r="H7">
-        <v>97</v>
-      </c>
-      <c r="I7">
-        <v>52</v>
-      </c>
-      <c r="J7">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>871</v>
-      </c>
-      <c r="C8" t="s">
-        <v>872</v>
-      </c>
-      <c r="D8" t="s">
-        <v>860</v>
-      </c>
-      <c r="E8">
-        <v>1938</v>
-      </c>
-      <c r="F8">
-        <v>99.7</v>
-      </c>
-      <c r="G8">
-        <v>226</v>
-      </c>
-      <c r="H8">
-        <v>73</v>
-      </c>
-      <c r="I8">
-        <v>56</v>
-      </c>
-      <c r="J8">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>873</v>
-      </c>
-      <c r="C9" t="s">
-        <v>874</v>
-      </c>
-      <c r="D9" t="s">
-        <v>860</v>
-      </c>
-      <c r="E9">
-        <v>2092</v>
-      </c>
-      <c r="F9">
-        <v>106</v>
-      </c>
-      <c r="G9">
-        <v>237</v>
-      </c>
-      <c r="H9">
-        <v>78</v>
-      </c>
-      <c r="I9">
-        <v>78</v>
-      </c>
-      <c r="J9">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>875</v>
-      </c>
-      <c r="C10" t="s">
-        <v>876</v>
-      </c>
-      <c r="D10" t="s">
-        <v>860</v>
-      </c>
-      <c r="E10">
-        <v>2783</v>
-      </c>
-      <c r="F10">
-        <v>156</v>
-      </c>
-      <c r="G10">
-        <v>313</v>
-      </c>
-      <c r="H10">
-        <v>96</v>
-      </c>
-      <c r="I10">
-        <v>90</v>
-      </c>
-      <c r="J10">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>877</v>
-      </c>
-      <c r="C11" t="s">
-        <v>878</v>
-      </c>
-      <c r="D11" t="s">
-        <v>860</v>
-      </c>
-      <c r="E11">
-        <v>1796</v>
-      </c>
-      <c r="F11">
-        <v>78</v>
-      </c>
-      <c r="G11">
-        <v>217</v>
-      </c>
-      <c r="H11">
-        <v>70</v>
-      </c>
-      <c r="I11">
-        <v>81</v>
-      </c>
-      <c r="J11">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>879</v>
-      </c>
-      <c r="C12" t="s">
-        <v>880</v>
-      </c>
-      <c r="D12" t="s">
-        <v>860</v>
-      </c>
-      <c r="E12">
-        <v>1698</v>
-      </c>
-      <c r="F12">
-        <v>73.7</v>
-      </c>
-      <c r="G12">
-        <v>180</v>
-      </c>
-      <c r="H12">
-        <v>69</v>
-      </c>
-      <c r="I12">
-        <v>43.3</v>
-      </c>
-      <c r="J12">
-        <v>19.7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>881</v>
-      </c>
-      <c r="C13" t="s">
-        <v>882</v>
-      </c>
-      <c r="D13" t="s">
-        <v>860</v>
-      </c>
-      <c r="E13">
-        <v>2099</v>
-      </c>
-      <c r="F13">
-        <v>82.8</v>
-      </c>
-      <c r="G13">
-        <v>224.5</v>
-      </c>
-      <c r="H13">
-        <v>92.2</v>
-      </c>
-      <c r="I13">
-        <v>44.5</v>
-      </c>
-      <c r="J13">
-        <v>19.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>883</v>
-      </c>
-      <c r="C14" t="s">
-        <v>884</v>
-      </c>
-      <c r="D14" t="s">
-        <v>860</v>
-      </c>
-      <c r="E14">
-        <v>2774</v>
-      </c>
-      <c r="F14">
-        <v>157</v>
-      </c>
-      <c r="G14">
-        <v>254</v>
-      </c>
-      <c r="H14">
-        <v>123</v>
-      </c>
-      <c r="I14">
-        <v>68</v>
-      </c>
-      <c r="J14">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>885</v>
-      </c>
-      <c r="C15" t="s">
-        <v>886</v>
-      </c>
-      <c r="D15" t="s">
-        <v>860</v>
-      </c>
-      <c r="E15">
-        <v>1880</v>
-      </c>
-      <c r="F15">
-        <v>98.3</v>
-      </c>
-      <c r="G15">
-        <v>237</v>
-      </c>
-      <c r="H15">
-        <v>59.9</v>
-      </c>
-      <c r="I15">
-        <v>79.599999999999994</v>
-      </c>
-      <c r="J15">
-        <v>38.4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>887</v>
-      </c>
-      <c r="C16" t="s">
-        <v>888</v>
-      </c>
-      <c r="D16" t="s">
-        <v>860</v>
-      </c>
-      <c r="E16">
-        <v>1634</v>
-      </c>
-      <c r="F16">
-        <v>86.9</v>
-      </c>
-      <c r="G16">
-        <v>155.6</v>
-      </c>
-      <c r="H16">
-        <v>69.5</v>
-      </c>
-      <c r="I16">
-        <v>39.299999999999997</v>
-      </c>
-      <c r="J16">
-        <v>24.7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>889</v>
-      </c>
-      <c r="C17" t="s">
-        <v>890</v>
-      </c>
-      <c r="D17" t="s">
-        <v>860</v>
-      </c>
-      <c r="E17">
-        <v>2001</v>
-      </c>
-      <c r="F17">
-        <v>82.3</v>
-      </c>
-      <c r="G17">
-        <v>277.10000000000002</v>
-      </c>
-      <c r="H17">
-        <v>70.400000000000006</v>
-      </c>
-      <c r="I17">
-        <v>96.6</v>
-      </c>
-      <c r="J17">
-        <v>56.4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>891</v>
-      </c>
-      <c r="C18" t="s">
-        <v>892</v>
-      </c>
-      <c r="D18" t="s">
-        <v>860</v>
-      </c>
-      <c r="E18">
-        <v>1878</v>
-      </c>
-      <c r="F18">
-        <v>116</v>
-      </c>
-      <c r="G18">
-        <v>128</v>
-      </c>
-      <c r="H18">
-        <v>78</v>
-      </c>
-      <c r="I18">
-        <v>28</v>
-      </c>
-      <c r="J18">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>893</v>
-      </c>
-      <c r="C19" t="s">
-        <v>894</v>
-      </c>
-      <c r="D19" t="s">
-        <v>860</v>
-      </c>
-      <c r="E19">
-        <v>2257</v>
-      </c>
-      <c r="F19">
-        <v>138</v>
-      </c>
-      <c r="G19">
-        <v>190</v>
-      </c>
-      <c r="H19">
-        <v>95</v>
-      </c>
-      <c r="I19">
-        <v>41</v>
-      </c>
-      <c r="J19">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>895</v>
-      </c>
-      <c r="C20" t="s">
-        <v>896</v>
-      </c>
-      <c r="D20" t="s">
-        <v>860</v>
-      </c>
-      <c r="E20">
-        <v>2909</v>
-      </c>
-      <c r="F20">
-        <v>170</v>
-      </c>
-      <c r="G20">
-        <v>273</v>
-      </c>
-      <c r="H20">
-        <v>126</v>
-      </c>
-      <c r="I20">
-        <v>72.599999999999994</v>
-      </c>
-      <c r="J20">
-        <v>43.4</v>
-      </c>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="23"/>
+      <c r="B33" s="24"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="23"/>
+      <c r="B34" s="24"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="23"/>
+      <c r="B35" s="24"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="23"/>
+      <c r="B36" s="24"/>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="23"/>
+      <c r="B37" s="24"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="23"/>
+      <c r="B38" s="24"/>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="23"/>
+      <c r="B39" s="24"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="23"/>
+      <c r="B40" s="24"/>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="23"/>
+      <c r="B41" s="24"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="23"/>
+      <c r="B42" s="24"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="23"/>
+      <c r="B43" s="24"/>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="23"/>
+      <c r="B44" s="24"/>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="23"/>
+      <c r="B45" s="24"/>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="23"/>
+      <c r="B46" s="24"/>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="23"/>
+      <c r="B47" s="24"/>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="23"/>
+      <c r="B48" s="24"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="23"/>
+      <c r="B49" s="24"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="23"/>
+      <c r="B50" s="24"/>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="23"/>
+      <c r="B51" s="24"/>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="23"/>
+      <c r="B52" s="24"/>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="23"/>
+      <c r="B53" s="24"/>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="23"/>
+      <c r="B54" s="24"/>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="23"/>
+      <c r="B55" s="24"/>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="23"/>
+      <c r="B56" s="24"/>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="23"/>
+      <c r="B57" s="24"/>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="23"/>
+      <c r="B58" s="24"/>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="23"/>
+      <c r="B59" s="24"/>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="23"/>
+      <c r="B60" s="24"/>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="23"/>
+      <c r="B61" s="24"/>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="23"/>
+      <c r="B62" s="24"/>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="23"/>
+      <c r="B63" s="24"/>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" s="23"/>
+      <c r="B64" s="24"/>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="23"/>
+      <c r="B65" s="24"/>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="23"/>
+      <c r="B66" s="24"/>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" s="23"/>
+      <c r="B67" s="24"/>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" s="23"/>
+      <c r="B68" s="24"/>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" s="23"/>
+      <c r="B69" s="24"/>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" s="23"/>
+      <c r="B70" s="24"/>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" s="23"/>
+      <c r="B71" s="24"/>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="23"/>
+      <c r="B72" s="24"/>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="23"/>
+      <c r="B73" s="24"/>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="23"/>
+      <c r="B74" s="24"/>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="23"/>
+      <c r="B75" s="24"/>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="23"/>
+      <c r="B76" s="24"/>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="23"/>
+      <c r="B77" s="24"/>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="23"/>
+      <c r="B78" s="24"/>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="23"/>
+      <c r="B79" s="24"/>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="23"/>
+      <c r="B80" s="24"/>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="23"/>
+      <c r="B81" s="24"/>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="23"/>
+      <c r="B82" s="24"/>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" s="23"/>
+      <c r="B83" s="24"/>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" s="23"/>
+      <c r="B84" s="24"/>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" s="23"/>
+      <c r="B85" s="24"/>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" s="23"/>
+      <c r="B86" s="24"/>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" s="23"/>
+      <c r="B87" s="24"/>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" s="23"/>
+      <c r="B88" s="24"/>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" s="23"/>
+      <c r="B89" s="24"/>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" s="23"/>
+      <c r="B90" s="24"/>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" s="23"/>
+      <c r="B91" s="24"/>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" s="23"/>
+      <c r="B92" s="24"/>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" s="23"/>
+      <c r="B93" s="24"/>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" s="23"/>
+      <c r="B94" s="24"/>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" s="23"/>
+      <c r="B95" s="24"/>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" s="23"/>
+      <c r="B96" s="24"/>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" s="23"/>
+      <c r="B97" s="24"/>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" s="23"/>
+      <c r="B98" s="24"/>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" s="23"/>
+      <c r="B99" s="24"/>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" s="23"/>
+      <c r="B100" s="24"/>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" s="23"/>
+      <c r="B101" s="24"/>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" s="23"/>
+      <c r="B102" s="24"/>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103" s="23"/>
+      <c r="B103" s="24"/>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" s="23"/>
+      <c r="B104" s="24"/>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" s="23"/>
+      <c r="B105" s="24"/>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" s="23"/>
+      <c r="B106" s="24"/>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" s="23"/>
+      <c r="B107" s="24"/>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" s="23"/>
+      <c r="B108" s="24"/>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" s="23"/>
+      <c r="B109" s="24"/>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" s="23"/>
+      <c r="B110" s="24"/>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" s="23"/>
+      <c r="B111" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
